--- a/public/loop-library.xlsx
+++ b/public/loop-library.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr"/>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr"/>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr"/>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr"/>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr"/>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr"/>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr"/>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr"/>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr"/>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr"/>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr"/>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr"/>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr"/>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr"/>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr"/>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr"/>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr"/>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr"/>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr"/>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr"/>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L93" s="6" t="inlineStr"/>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr"/>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L95" s="6" t="inlineStr"/>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr"/>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L97" s="6" t="inlineStr"/>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr"/>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr"/>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr"/>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr"/>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L102" s="3" t="inlineStr"/>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L103" s="6" t="inlineStr"/>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L104" s="3" t="inlineStr"/>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L105" s="6" t="inlineStr"/>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L106" s="3" t="inlineStr"/>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L107" s="6" t="inlineStr"/>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L108" s="3" t="inlineStr"/>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L109" s="6" t="inlineStr"/>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L110" s="3" t="inlineStr"/>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L111" s="6" t="inlineStr"/>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L112" s="3" t="inlineStr"/>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L113" s="6" t="inlineStr"/>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L114" s="3" t="inlineStr"/>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L115" s="6" t="inlineStr"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="K116" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L116" s="3" t="inlineStr"/>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L117" s="6" t="inlineStr"/>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="K118" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L118" s="3" t="inlineStr"/>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L119" s="6" t="inlineStr"/>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="K120" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L120" s="3" t="inlineStr"/>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L121" s="6" t="inlineStr"/>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="K122" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L122" s="3" t="inlineStr"/>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L123" s="6" t="inlineStr"/>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="K124" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L124" s="3" t="inlineStr"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="K125" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L125" s="6" t="inlineStr"/>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="K126" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L126" s="3" t="inlineStr"/>
@@ -6854,7 +6854,7 @@
       </c>
       <c r="K127" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L127" s="6" t="inlineStr"/>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L128" s="3" t="inlineStr"/>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="K129" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L129" s="6" t="inlineStr"/>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="K130" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L130" s="3" t="inlineStr"/>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="K131" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L131" s="6" t="inlineStr"/>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L132" s="3" t="inlineStr"/>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="K133" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L133" s="6" t="inlineStr"/>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="K134" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L134" s="3" t="inlineStr"/>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="K135" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L135" s="6" t="inlineStr"/>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="K136" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L136" s="3" t="inlineStr"/>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="K137" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L137" s="6" t="inlineStr"/>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="K138" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L138" s="3" t="inlineStr"/>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="K139" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L139" s="6" t="inlineStr"/>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="K140" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L140" s="3" t="inlineStr"/>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="K141" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L141" s="6" t="inlineStr"/>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L142" s="3" t="inlineStr"/>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="K143" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L143" s="6" t="inlineStr"/>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="K144" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L144" s="3" t="inlineStr"/>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="K145" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L145" s="6" t="inlineStr"/>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="K146" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L146" s="3" t="inlineStr"/>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="K147" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L147" s="6" t="inlineStr"/>
@@ -7862,7 +7862,7 @@
       </c>
       <c r="K148" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L148" s="3" t="inlineStr"/>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="K149" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L149" s="6" t="inlineStr"/>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="K150" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L150" s="3" t="inlineStr"/>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="K151" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L151" s="6" t="inlineStr"/>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="K152" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L152" s="3" t="inlineStr"/>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="K153" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L153" s="6" t="inlineStr"/>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="K154" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L154" s="3" t="inlineStr"/>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="K155" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L155" s="6" t="inlineStr"/>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="K156" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L156" s="3" t="inlineStr"/>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K157" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L157" s="6" t="inlineStr"/>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="K158" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L158" s="3" t="inlineStr"/>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="K159" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L159" s="6" t="inlineStr"/>
@@ -8438,7 +8438,7 @@
       </c>
       <c r="K160" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L160" s="3" t="inlineStr"/>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="K161" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L161" s="6" t="inlineStr"/>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="K162" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L162" s="3" t="inlineStr"/>
@@ -8582,7 +8582,7 @@
       </c>
       <c r="K163" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L163" s="6" t="inlineStr"/>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="K164" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L164" s="3" t="inlineStr"/>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="K165" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L165" s="6" t="inlineStr"/>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="K166" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L166" s="3" t="inlineStr"/>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="K167" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L167" s="6" t="inlineStr"/>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="K168" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L168" s="3" t="inlineStr"/>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="K169" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L169" s="6" t="inlineStr"/>
@@ -8918,7 +8918,7 @@
       </c>
       <c r="K170" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L170" s="3" t="inlineStr"/>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="K171" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L171" s="6" t="inlineStr"/>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="K172" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L172" s="3" t="inlineStr"/>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="K173" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L173" s="6" t="inlineStr"/>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="K174" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L174" s="3" t="inlineStr"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="K175" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L175" s="6" t="inlineStr"/>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="K176" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L176" s="3" t="inlineStr"/>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="K177" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L177" s="6" t="inlineStr"/>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="K178" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L178" s="3" t="inlineStr"/>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="K179" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L179" s="6" t="inlineStr"/>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="K180" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L180" s="3" t="inlineStr"/>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="K181" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L181" s="6" t="inlineStr"/>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="K182" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L182" s="3" t="inlineStr"/>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="K183" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L183" s="6" t="inlineStr"/>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="K184" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L184" s="3" t="inlineStr"/>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="K185" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L185" s="6" t="inlineStr"/>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="K186" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L186" s="3" t="inlineStr"/>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="K187" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L187" s="6" t="inlineStr"/>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="K188" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L188" s="3" t="inlineStr"/>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="K189" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L189" s="6" t="inlineStr"/>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="K190" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L190" s="3" t="inlineStr"/>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="K191" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L191" s="6" t="inlineStr"/>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="K192" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L192" s="3" t="inlineStr"/>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="K193" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L193" s="6" t="inlineStr"/>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="K194" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L194" s="3" t="inlineStr"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="K195" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L195" s="6" t="inlineStr"/>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="K196" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L196" s="3" t="inlineStr"/>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="K197" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L197" s="6" t="inlineStr"/>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="K198" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L198" s="3" t="inlineStr"/>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="K199" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L199" s="6" t="inlineStr"/>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="K200" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L200" s="3" t="inlineStr"/>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="K201" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L201" s="6" t="inlineStr"/>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="K202" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L202" s="3" t="inlineStr"/>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="K203" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L203" s="6" t="inlineStr"/>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="K204" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L204" s="3" t="inlineStr"/>
@@ -10598,7 +10598,7 @@
       </c>
       <c r="K205" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L205" s="6" t="inlineStr"/>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K206" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L206" s="3" t="inlineStr"/>
@@ -10694,7 +10694,7 @@
       </c>
       <c r="K207" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L207" s="6" t="inlineStr"/>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="K208" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L208" s="3" t="inlineStr"/>
@@ -10790,7 +10790,7 @@
       </c>
       <c r="K209" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L209" s="6" t="inlineStr"/>
@@ -10838,7 +10838,7 @@
       </c>
       <c r="K210" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L210" s="3" t="inlineStr"/>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="K211" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L211" s="6" t="inlineStr"/>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="K212" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L212" s="3" t="inlineStr"/>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="K213" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L213" s="6" t="inlineStr"/>
@@ -11030,7 +11030,7 @@
       </c>
       <c r="K214" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L214" s="3" t="inlineStr"/>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="K215" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L215" s="6" t="inlineStr"/>
@@ -11126,7 +11126,7 @@
       </c>
       <c r="K216" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L216" s="3" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="K217" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L217" s="6" t="inlineStr"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="K218" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L218" s="3" t="inlineStr"/>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="K219" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L219" s="6" t="inlineStr"/>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="K220" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L220" s="3" t="inlineStr"/>
@@ -11366,7 +11366,7 @@
       </c>
       <c r="K221" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L221" s="6" t="inlineStr"/>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="K222" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L222" s="3" t="inlineStr"/>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="K223" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L223" s="6" t="inlineStr"/>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="K224" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L224" s="3" t="inlineStr"/>
@@ -11558,7 +11558,7 @@
       </c>
       <c r="K225" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L225" s="6" t="inlineStr"/>
@@ -11606,7 +11606,7 @@
       </c>
       <c r="K226" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L226" s="3" t="inlineStr"/>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="K227" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L227" s="6" t="inlineStr"/>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="K228" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L228" s="3" t="inlineStr"/>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="K229" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L229" s="6" t="inlineStr"/>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="K230" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L230" s="3" t="inlineStr"/>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="K231" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L231" s="6" t="inlineStr"/>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="K232" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L232" s="3" t="inlineStr"/>
@@ -11942,7 +11942,7 @@
       </c>
       <c r="K233" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L233" s="6" t="inlineStr"/>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="K234" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L234" s="3" t="inlineStr"/>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="K235" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L235" s="6" t="inlineStr"/>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="K236" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L236" s="3" t="inlineStr"/>
@@ -12134,7 +12134,7 @@
       </c>
       <c r="K237" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L237" s="6" t="inlineStr"/>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="K238" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L238" s="3" t="inlineStr"/>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="K239" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L239" s="6" t="inlineStr"/>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="K240" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L240" s="3" t="inlineStr"/>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="K241" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L241" s="6" t="inlineStr"/>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="K242" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L242" s="3" t="inlineStr"/>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="K243" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L243" s="6" t="inlineStr"/>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="K244" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L244" s="3" t="inlineStr"/>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="K245" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L245" s="6" t="inlineStr"/>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="K246" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L246" s="3" t="inlineStr"/>
@@ -12614,7 +12614,7 @@
       </c>
       <c r="K247" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L247" s="6" t="inlineStr"/>
@@ -12662,7 +12662,7 @@
       </c>
       <c r="K248" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L248" s="3" t="inlineStr"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="K249" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L249" s="6" t="inlineStr"/>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="K250" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L250" s="3" t="inlineStr"/>
@@ -12806,7 +12806,7 @@
       </c>
       <c r="K251" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L251" s="6" t="inlineStr"/>
@@ -12854,7 +12854,7 @@
       </c>
       <c r="K252" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L252" s="3" t="inlineStr"/>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="K253" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L253" s="6" t="inlineStr"/>
@@ -12950,7 +12950,7 @@
       </c>
       <c r="K254" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L254" s="3" t="inlineStr"/>
@@ -12998,7 +12998,7 @@
       </c>
       <c r="K255" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L255" s="6" t="inlineStr"/>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="K256" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L256" s="3" t="inlineStr"/>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="K257" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L257" s="6" t="inlineStr"/>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="K258" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L258" s="3" t="inlineStr"/>
@@ -13190,7 +13190,7 @@
       </c>
       <c r="K259" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L259" s="6" t="inlineStr"/>
@@ -13238,7 +13238,7 @@
       </c>
       <c r="K260" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L260" s="3" t="inlineStr"/>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="K261" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L261" s="6" t="inlineStr"/>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="K262" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L262" s="3" t="inlineStr"/>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="K263" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L263" s="6" t="inlineStr"/>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="K264" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L264" s="3" t="inlineStr"/>
@@ -13478,7 +13478,7 @@
       </c>
       <c r="K265" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L265" s="6" t="inlineStr"/>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="K266" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L266" s="3" t="inlineStr"/>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="K267" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L267" s="6" t="inlineStr"/>
@@ -13622,7 +13622,7 @@
       </c>
       <c r="K268" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L268" s="3" t="inlineStr"/>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="K269" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L269" s="6" t="inlineStr"/>
@@ -13718,7 +13718,7 @@
       </c>
       <c r="K270" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L270" s="3" t="inlineStr"/>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="K271" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L271" s="6" t="inlineStr"/>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="K272" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L272" s="3" t="inlineStr"/>
@@ -13862,7 +13862,7 @@
       </c>
       <c r="K273" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L273" s="6" t="inlineStr"/>
@@ -13910,7 +13910,7 @@
       </c>
       <c r="K274" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L274" s="3" t="inlineStr"/>
@@ -13958,7 +13958,7 @@
       </c>
       <c r="K275" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L275" s="6" t="inlineStr"/>
@@ -14006,7 +14006,7 @@
       </c>
       <c r="K276" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L276" s="3" t="inlineStr"/>
@@ -14054,7 +14054,7 @@
       </c>
       <c r="K277" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L277" s="6" t="inlineStr"/>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="K278" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L278" s="3" t="inlineStr"/>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="K279" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L279" s="6" t="inlineStr"/>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="K280" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L280" s="3" t="inlineStr"/>
@@ -14246,7 +14246,7 @@
       </c>
       <c r="K281" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L281" s="6" t="inlineStr"/>
@@ -14294,7 +14294,7 @@
       </c>
       <c r="K282" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L282" s="3" t="inlineStr"/>
@@ -14342,7 +14342,7 @@
       </c>
       <c r="K283" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L283" s="6" t="inlineStr"/>
@@ -14390,7 +14390,7 @@
       </c>
       <c r="K284" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L284" s="3" t="inlineStr"/>
@@ -14438,7 +14438,7 @@
       </c>
       <c r="K285" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L285" s="6" t="inlineStr"/>
@@ -14486,7 +14486,7 @@
       </c>
       <c r="K286" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L286" s="3" t="inlineStr"/>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="K287" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L287" s="6" t="inlineStr"/>
@@ -14582,7 +14582,7 @@
       </c>
       <c r="K288" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L288" s="3" t="inlineStr"/>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="K289" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L289" s="6" t="inlineStr"/>
@@ -14678,7 +14678,7 @@
       </c>
       <c r="K290" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L290" s="3" t="inlineStr"/>
@@ -14726,7 +14726,7 @@
       </c>
       <c r="K291" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L291" s="6" t="inlineStr"/>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="K292" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L292" s="3" t="inlineStr"/>
@@ -14822,7 +14822,7 @@
       </c>
       <c r="K293" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L293" s="6" t="inlineStr"/>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="K294" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L294" s="3" t="inlineStr"/>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="K295" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L295" s="6" t="inlineStr"/>
@@ -14966,7 +14966,7 @@
       </c>
       <c r="K296" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L296" s="3" t="inlineStr"/>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="K297" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L297" s="6" t="inlineStr"/>
@@ -15062,7 +15062,7 @@
       </c>
       <c r="K298" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L298" s="3" t="inlineStr"/>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="K299" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L299" s="6" t="inlineStr"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="K300" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L300" s="3" t="inlineStr"/>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="K301" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L301" s="6" t="inlineStr"/>
@@ -15254,7 +15254,7 @@
       </c>
       <c r="K302" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L302" s="3" t="inlineStr"/>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="K303" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L303" s="6" t="inlineStr"/>
@@ -15350,7 +15350,7 @@
       </c>
       <c r="K304" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L304" s="3" t="inlineStr"/>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="K305" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L305" s="6" t="inlineStr"/>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="K306" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L306" s="3" t="inlineStr"/>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="K307" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L307" s="6" t="inlineStr"/>
@@ -15542,7 +15542,7 @@
       </c>
       <c r="K308" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L308" s="3" t="inlineStr"/>
@@ -15590,7 +15590,7 @@
       </c>
       <c r="K309" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L309" s="6" t="inlineStr"/>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="K310" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L310" s="3" t="inlineStr"/>
@@ -15686,7 +15686,7 @@
       </c>
       <c r="K311" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L311" s="6" t="inlineStr"/>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="K312" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L312" s="3" t="inlineStr"/>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="K313" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L313" s="6" t="inlineStr"/>
@@ -15830,7 +15830,7 @@
       </c>
       <c r="K314" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L314" s="3" t="inlineStr"/>
@@ -15878,7 +15878,7 @@
       </c>
       <c r="K315" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L315" s="6" t="inlineStr"/>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="K316" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L316" s="3" t="inlineStr"/>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="K317" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L317" s="6" t="inlineStr"/>
@@ -16022,7 +16022,7 @@
       </c>
       <c r="K318" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L318" s="3" t="inlineStr"/>
@@ -16070,7 +16070,7 @@
       </c>
       <c r="K319" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L319" s="6" t="inlineStr"/>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="K320" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L320" s="3" t="inlineStr"/>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="K321" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L321" s="6" t="inlineStr"/>
@@ -16214,7 +16214,7 @@
       </c>
       <c r="K322" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L322" s="3" t="inlineStr"/>
@@ -16262,7 +16262,7 @@
       </c>
       <c r="K323" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L323" s="6" t="inlineStr"/>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="K324" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L324" s="3" t="inlineStr"/>
@@ -16358,7 +16358,7 @@
       </c>
       <c r="K325" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L325" s="6" t="inlineStr"/>
@@ -16406,7 +16406,7 @@
       </c>
       <c r="K326" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L326" s="3" t="inlineStr"/>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="K327" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L327" s="6" t="inlineStr"/>
@@ -16502,7 +16502,7 @@
       </c>
       <c r="K328" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L328" s="3" t="inlineStr"/>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="K329" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L329" s="6" t="inlineStr"/>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="K330" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L330" s="3" t="inlineStr"/>
@@ -16646,7 +16646,7 @@
       </c>
       <c r="K331" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L331" s="6" t="inlineStr"/>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="K332" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L332" s="3" t="inlineStr"/>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="K333" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L333" s="6" t="inlineStr"/>
@@ -16790,7 +16790,7 @@
       </c>
       <c r="K334" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L334" s="3" t="inlineStr"/>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="K335" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L335" s="6" t="inlineStr"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="K336" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L336" s="3" t="inlineStr"/>
@@ -16934,7 +16934,7 @@
       </c>
       <c r="K337" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L337" s="6" t="inlineStr"/>
@@ -16982,7 +16982,7 @@
       </c>
       <c r="K338" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L338" s="3" t="inlineStr"/>
@@ -17030,7 +17030,7 @@
       </c>
       <c r="K339" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L339" s="6" t="inlineStr"/>
@@ -17078,7 +17078,7 @@
       </c>
       <c r="K340" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L340" s="3" t="inlineStr"/>
@@ -17126,7 +17126,7 @@
       </c>
       <c r="K341" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L341" s="6" t="inlineStr"/>
@@ -17174,7 +17174,7 @@
       </c>
       <c r="K342" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L342" s="3" t="inlineStr"/>
@@ -17222,7 +17222,7 @@
       </c>
       <c r="K343" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L343" s="6" t="inlineStr"/>
@@ -17270,7 +17270,7 @@
       </c>
       <c r="K344" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L344" s="3" t="inlineStr"/>
@@ -17318,7 +17318,7 @@
       </c>
       <c r="K345" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L345" s="6" t="inlineStr"/>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="K346" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L346" s="3" t="inlineStr"/>
@@ -17414,7 +17414,7 @@
       </c>
       <c r="K347" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L347" s="6" t="inlineStr"/>
@@ -17462,7 +17462,7 @@
       </c>
       <c r="K348" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L348" s="3" t="inlineStr"/>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="K349" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L349" s="6" t="inlineStr"/>
@@ -17558,7 +17558,7 @@
       </c>
       <c r="K350" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L350" s="3" t="inlineStr"/>
@@ -17606,7 +17606,7 @@
       </c>
       <c r="K351" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L351" s="6" t="inlineStr"/>
@@ -17654,7 +17654,7 @@
       </c>
       <c r="K352" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L352" s="3" t="inlineStr"/>
@@ -17702,7 +17702,7 @@
       </c>
       <c r="K353" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L353" s="6" t="inlineStr"/>
@@ -17750,7 +17750,7 @@
       </c>
       <c r="K354" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L354" s="3" t="inlineStr"/>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="K355" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L355" s="6" t="inlineStr"/>
@@ -17846,7 +17846,7 @@
       </c>
       <c r="K356" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L356" s="3" t="inlineStr"/>
@@ -17894,7 +17894,7 @@
       </c>
       <c r="K357" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L357" s="6" t="inlineStr"/>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="K358" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L358" s="3" t="inlineStr"/>
@@ -17990,7 +17990,7 @@
       </c>
       <c r="K359" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L359" s="6" t="inlineStr"/>
@@ -18038,7 +18038,7 @@
       </c>
       <c r="K360" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L360" s="3" t="inlineStr"/>
@@ -18086,7 +18086,7 @@
       </c>
       <c r="K361" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L361" s="6" t="inlineStr"/>
@@ -18134,7 +18134,7 @@
       </c>
       <c r="K362" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L362" s="3" t="inlineStr"/>
@@ -18182,7 +18182,7 @@
       </c>
       <c r="K363" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L363" s="6" t="inlineStr"/>
@@ -18230,7 +18230,7 @@
       </c>
       <c r="K364" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L364" s="3" t="inlineStr"/>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="K365" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L365" s="6" t="inlineStr"/>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="K366" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L366" s="3" t="inlineStr"/>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="K367" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L367" s="6" t="inlineStr"/>
@@ -18422,7 +18422,7 @@
       </c>
       <c r="K368" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L368" s="3" t="inlineStr"/>
@@ -18470,7 +18470,7 @@
       </c>
       <c r="K369" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L369" s="6" t="inlineStr"/>
@@ -18518,7 +18518,7 @@
       </c>
       <c r="K370" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L370" s="3" t="inlineStr"/>
@@ -18566,7 +18566,7 @@
       </c>
       <c r="K371" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L371" s="6" t="inlineStr"/>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="K372" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L372" s="3" t="inlineStr"/>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="K373" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L373" s="6" t="inlineStr"/>
@@ -18710,7 +18710,7 @@
       </c>
       <c r="K374" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L374" s="3" t="inlineStr"/>
@@ -18758,7 +18758,7 @@
       </c>
       <c r="K375" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L375" s="6" t="inlineStr"/>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="K376" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L376" s="3" t="inlineStr"/>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="K377" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L377" s="6" t="inlineStr"/>
@@ -18902,7 +18902,7 @@
       </c>
       <c r="K378" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L378" s="3" t="inlineStr"/>
@@ -18950,7 +18950,7 @@
       </c>
       <c r="K379" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L379" s="6" t="inlineStr"/>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="K380" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L380" s="3" t="inlineStr"/>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="K381" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L381" s="6" t="inlineStr"/>
@@ -19094,7 +19094,7 @@
       </c>
       <c r="K382" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L382" s="3" t="inlineStr"/>
@@ -19142,7 +19142,7 @@
       </c>
       <c r="K383" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L383" s="6" t="inlineStr"/>
@@ -19190,7 +19190,7 @@
       </c>
       <c r="K384" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L384" s="3" t="inlineStr"/>
@@ -19238,7 +19238,7 @@
       </c>
       <c r="K385" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L385" s="6" t="inlineStr"/>
@@ -19286,7 +19286,7 @@
       </c>
       <c r="K386" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L386" s="3" t="inlineStr"/>
@@ -19334,7 +19334,7 @@
       </c>
       <c r="K387" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L387" s="6" t="inlineStr"/>
@@ -19382,7 +19382,7 @@
       </c>
       <c r="K388" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L388" s="3" t="inlineStr"/>
@@ -19430,7 +19430,7 @@
       </c>
       <c r="K389" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L389" s="6" t="inlineStr"/>
@@ -19478,7 +19478,7 @@
       </c>
       <c r="K390" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L390" s="3" t="inlineStr"/>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="K391" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L391" s="6" t="inlineStr"/>
@@ -19574,7 +19574,7 @@
       </c>
       <c r="K392" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L392" s="3" t="inlineStr"/>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="K393" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L393" s="6" t="inlineStr"/>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="K394" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L394" s="3" t="inlineStr"/>
@@ -19718,7 +19718,7 @@
       </c>
       <c r="K395" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L395" s="6" t="inlineStr"/>
@@ -19766,7 +19766,7 @@
       </c>
       <c r="K396" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L396" s="3" t="inlineStr"/>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="K397" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L397" s="6" t="inlineStr"/>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="K398" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L398" s="3" t="inlineStr"/>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="K399" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L399" s="6" t="inlineStr"/>
@@ -19958,7 +19958,7 @@
       </c>
       <c r="K400" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L400" s="3" t="inlineStr"/>
@@ -20006,7 +20006,7 @@
       </c>
       <c r="K401" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L401" s="6" t="inlineStr"/>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="K402" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L402" s="3" t="inlineStr"/>
@@ -20102,7 +20102,7 @@
       </c>
       <c r="K403" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L403" s="6" t="inlineStr"/>
@@ -20150,7 +20150,7 @@
       </c>
       <c r="K404" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L404" s="3" t="inlineStr"/>
@@ -20198,7 +20198,7 @@
       </c>
       <c r="K405" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L405" s="6" t="inlineStr"/>
@@ -20246,7 +20246,7 @@
       </c>
       <c r="K406" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L406" s="3" t="inlineStr"/>
@@ -20294,7 +20294,7 @@
       </c>
       <c r="K407" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L407" s="6" t="inlineStr"/>
@@ -20342,7 +20342,7 @@
       </c>
       <c r="K408" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L408" s="3" t="inlineStr"/>
@@ -20390,7 +20390,7 @@
       </c>
       <c r="K409" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L409" s="6" t="inlineStr"/>
@@ -20438,7 +20438,7 @@
       </c>
       <c r="K410" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L410" s="3" t="inlineStr"/>
@@ -20486,7 +20486,7 @@
       </c>
       <c r="K411" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L411" s="6" t="inlineStr"/>
@@ -20534,7 +20534,7 @@
       </c>
       <c r="K412" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L412" s="3" t="inlineStr"/>
@@ -20582,7 +20582,7 @@
       </c>
       <c r="K413" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L413" s="6" t="inlineStr"/>
@@ -20630,7 +20630,7 @@
       </c>
       <c r="K414" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L414" s="3" t="inlineStr"/>
@@ -20678,7 +20678,7 @@
       </c>
       <c r="K415" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L415" s="6" t="inlineStr"/>
@@ -20726,7 +20726,7 @@
       </c>
       <c r="K416" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L416" s="3" t="inlineStr"/>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="K417" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L417" s="6" t="inlineStr"/>
@@ -20822,7 +20822,7 @@
       </c>
       <c r="K418" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L418" s="3" t="inlineStr"/>
@@ -20870,7 +20870,7 @@
       </c>
       <c r="K419" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L419" s="6" t="inlineStr"/>
@@ -20918,7 +20918,7 @@
       </c>
       <c r="K420" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L420" s="3" t="inlineStr"/>
@@ -20966,7 +20966,7 @@
       </c>
       <c r="K421" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L421" s="6" t="inlineStr"/>
@@ -21014,7 +21014,7 @@
       </c>
       <c r="K422" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L422" s="3" t="inlineStr"/>
@@ -21062,7 +21062,7 @@
       </c>
       <c r="K423" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L423" s="6" t="inlineStr"/>
@@ -21110,7 +21110,7 @@
       </c>
       <c r="K424" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L424" s="3" t="inlineStr"/>
@@ -21158,7 +21158,7 @@
       </c>
       <c r="K425" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L425" s="6" t="inlineStr"/>
@@ -21206,7 +21206,7 @@
       </c>
       <c r="K426" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L426" s="3" t="inlineStr"/>
@@ -21254,7 +21254,7 @@
       </c>
       <c r="K427" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L427" s="6" t="inlineStr"/>
@@ -21302,7 +21302,7 @@
       </c>
       <c r="K428" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L428" s="3" t="inlineStr"/>
@@ -21350,7 +21350,7 @@
       </c>
       <c r="K429" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L429" s="6" t="inlineStr"/>
@@ -21398,7 +21398,7 @@
       </c>
       <c r="K430" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L430" s="3" t="inlineStr"/>
@@ -21446,7 +21446,7 @@
       </c>
       <c r="K431" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L431" s="6" t="inlineStr"/>
@@ -21494,7 +21494,7 @@
       </c>
       <c r="K432" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L432" s="3" t="inlineStr"/>
@@ -21542,7 +21542,7 @@
       </c>
       <c r="K433" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L433" s="6" t="inlineStr"/>
@@ -21590,7 +21590,7 @@
       </c>
       <c r="K434" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L434" s="3" t="inlineStr"/>
@@ -21638,7 +21638,7 @@
       </c>
       <c r="K435" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L435" s="6" t="inlineStr"/>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="K436" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L436" s="3" t="inlineStr"/>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="K437" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L437" s="6" t="inlineStr"/>
@@ -21782,7 +21782,7 @@
       </c>
       <c r="K438" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L438" s="3" t="inlineStr"/>
@@ -21830,7 +21830,7 @@
       </c>
       <c r="K439" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L439" s="6" t="inlineStr"/>
@@ -21878,7 +21878,7 @@
       </c>
       <c r="K440" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L440" s="3" t="inlineStr"/>
@@ -21926,7 +21926,7 @@
       </c>
       <c r="K441" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L441" s="6" t="inlineStr"/>
@@ -21974,7 +21974,7 @@
       </c>
       <c r="K442" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L442" s="3" t="inlineStr"/>
@@ -22022,7 +22022,7 @@
       </c>
       <c r="K443" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L443" s="6" t="inlineStr"/>
@@ -22070,7 +22070,7 @@
       </c>
       <c r="K444" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L444" s="3" t="inlineStr"/>
@@ -22118,7 +22118,7 @@
       </c>
       <c r="K445" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L445" s="6" t="inlineStr"/>
@@ -22166,7 +22166,7 @@
       </c>
       <c r="K446" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L446" s="3" t="inlineStr"/>
@@ -22214,7 +22214,7 @@
       </c>
       <c r="K447" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L447" s="6" t="inlineStr"/>
@@ -22262,7 +22262,7 @@
       </c>
       <c r="K448" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L448" s="3" t="inlineStr"/>
@@ -22310,7 +22310,7 @@
       </c>
       <c r="K449" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L449" s="6" t="inlineStr"/>
@@ -22358,7 +22358,7 @@
       </c>
       <c r="K450" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L450" s="3" t="inlineStr"/>
@@ -22406,7 +22406,7 @@
       </c>
       <c r="K451" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L451" s="6" t="inlineStr"/>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="K452" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L452" s="3" t="inlineStr"/>
@@ -22502,7 +22502,7 @@
       </c>
       <c r="K453" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L453" s="6" t="inlineStr"/>
@@ -22550,7 +22550,7 @@
       </c>
       <c r="K454" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L454" s="3" t="inlineStr"/>
@@ -22598,7 +22598,7 @@
       </c>
       <c r="K455" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L455" s="6" t="inlineStr"/>
@@ -22646,7 +22646,7 @@
       </c>
       <c r="K456" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L456" s="3" t="inlineStr"/>
@@ -22694,7 +22694,7 @@
       </c>
       <c r="K457" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L457" s="6" t="inlineStr"/>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="K458" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L458" s="3" t="inlineStr"/>
@@ -22790,7 +22790,7 @@
       </c>
       <c r="K459" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L459" s="6" t="inlineStr"/>
@@ -22838,7 +22838,7 @@
       </c>
       <c r="K460" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L460" s="3" t="inlineStr"/>
@@ -22886,7 +22886,7 @@
       </c>
       <c r="K461" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L461" s="6" t="inlineStr"/>
@@ -22934,7 +22934,7 @@
       </c>
       <c r="K462" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L462" s="3" t="inlineStr"/>
@@ -22982,7 +22982,7 @@
       </c>
       <c r="K463" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L463" s="6" t="inlineStr"/>
@@ -23030,7 +23030,7 @@
       </c>
       <c r="K464" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L464" s="3" t="inlineStr"/>
@@ -23078,7 +23078,7 @@
       </c>
       <c r="K465" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L465" s="6" t="inlineStr"/>
@@ -23126,7 +23126,7 @@
       </c>
       <c r="K466" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L466" s="3" t="inlineStr"/>
@@ -23174,7 +23174,7 @@
       </c>
       <c r="K467" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L467" s="6" t="inlineStr"/>
@@ -23222,7 +23222,7 @@
       </c>
       <c r="K468" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L468" s="3" t="inlineStr"/>
@@ -23270,7 +23270,7 @@
       </c>
       <c r="K469" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L469" s="6" t="inlineStr"/>
@@ -23318,7 +23318,7 @@
       </c>
       <c r="K470" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L470" s="3" t="inlineStr"/>
@@ -23366,7 +23366,7 @@
       </c>
       <c r="K471" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L471" s="6" t="inlineStr"/>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="K472" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L472" s="3" t="inlineStr"/>
@@ -23462,7 +23462,7 @@
       </c>
       <c r="K473" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L473" s="6" t="inlineStr"/>
@@ -23510,7 +23510,7 @@
       </c>
       <c r="K474" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L474" s="3" t="inlineStr"/>
@@ -23558,7 +23558,7 @@
       </c>
       <c r="K475" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L475" s="6" t="inlineStr"/>
@@ -23606,7 +23606,7 @@
       </c>
       <c r="K476" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L476" s="3" t="inlineStr"/>
@@ -23654,7 +23654,7 @@
       </c>
       <c r="K477" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L477" s="6" t="inlineStr"/>
@@ -23702,7 +23702,7 @@
       </c>
       <c r="K478" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L478" s="3" t="inlineStr"/>
@@ -23750,7 +23750,7 @@
       </c>
       <c r="K479" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L479" s="6" t="inlineStr"/>
@@ -23798,7 +23798,7 @@
       </c>
       <c r="K480" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L480" s="3" t="inlineStr"/>
@@ -23846,7 +23846,7 @@
       </c>
       <c r="K481" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L481" s="6" t="inlineStr"/>
@@ -23894,7 +23894,7 @@
       </c>
       <c r="K482" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L482" s="3" t="inlineStr"/>
@@ -23942,7 +23942,7 @@
       </c>
       <c r="K483" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L483" s="6" t="inlineStr"/>
@@ -23990,7 +23990,7 @@
       </c>
       <c r="K484" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L484" s="3" t="inlineStr"/>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="K485" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L485" s="6" t="inlineStr"/>
@@ -24086,7 +24086,7 @@
       </c>
       <c r="K486" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L486" s="3" t="inlineStr"/>
@@ -24134,7 +24134,7 @@
       </c>
       <c r="K487" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L487" s="6" t="inlineStr"/>
@@ -24182,7 +24182,7 @@
       </c>
       <c r="K488" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L488" s="3" t="inlineStr"/>
@@ -24230,7 +24230,7 @@
       </c>
       <c r="K489" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L489" s="6" t="inlineStr"/>
@@ -24278,7 +24278,7 @@
       </c>
       <c r="K490" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L490" s="3" t="inlineStr"/>
@@ -24326,7 +24326,7 @@
       </c>
       <c r="K491" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L491" s="6" t="inlineStr"/>
@@ -24374,7 +24374,7 @@
       </c>
       <c r="K492" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L492" s="3" t="inlineStr"/>
@@ -24422,7 +24422,7 @@
       </c>
       <c r="K493" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L493" s="6" t="inlineStr"/>
@@ -24470,7 +24470,7 @@
       </c>
       <c r="K494" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L494" s="3" t="inlineStr"/>
@@ -24518,7 +24518,7 @@
       </c>
       <c r="K495" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L495" s="6" t="inlineStr"/>
@@ -24566,7 +24566,7 @@
       </c>
       <c r="K496" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L496" s="3" t="inlineStr"/>
@@ -24614,7 +24614,7 @@
       </c>
       <c r="K497" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L497" s="6" t="inlineStr"/>
@@ -24662,7 +24662,7 @@
       </c>
       <c r="K498" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L498" s="3" t="inlineStr"/>
@@ -24710,7 +24710,7 @@
       </c>
       <c r="K499" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L499" s="6" t="inlineStr"/>
@@ -24758,7 +24758,7 @@
       </c>
       <c r="K500" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L500" s="3" t="inlineStr"/>
@@ -24806,7 +24806,7 @@
       </c>
       <c r="K501" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L501" s="6" t="inlineStr"/>
@@ -24854,7 +24854,7 @@
       </c>
       <c r="K502" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L502" s="3" t="inlineStr"/>
@@ -24902,7 +24902,7 @@
       </c>
       <c r="K503" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L503" s="6" t="inlineStr"/>
@@ -24950,7 +24950,7 @@
       </c>
       <c r="K504" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L504" s="3" t="inlineStr"/>
@@ -24998,7 +24998,7 @@
       </c>
       <c r="K505" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L505" s="6" t="inlineStr"/>
@@ -25046,7 +25046,7 @@
       </c>
       <c r="K506" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L506" s="3" t="inlineStr"/>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="K507" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L507" s="6" t="inlineStr"/>
@@ -25142,7 +25142,7 @@
       </c>
       <c r="K508" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L508" s="3" t="inlineStr"/>
@@ -25190,7 +25190,7 @@
       </c>
       <c r="K509" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L509" s="6" t="inlineStr"/>
@@ -25238,7 +25238,7 @@
       </c>
       <c r="K510" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L510" s="3" t="inlineStr"/>
@@ -25286,7 +25286,7 @@
       </c>
       <c r="K511" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L511" s="6" t="inlineStr"/>
@@ -25334,7 +25334,7 @@
       </c>
       <c r="K512" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L512" s="3" t="inlineStr"/>
@@ -25382,7 +25382,7 @@
       </c>
       <c r="K513" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L513" s="6" t="inlineStr"/>
@@ -25430,7 +25430,7 @@
       </c>
       <c r="K514" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L514" s="3" t="inlineStr"/>
@@ -25478,7 +25478,7 @@
       </c>
       <c r="K515" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L515" s="6" t="inlineStr"/>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="K516" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L516" s="3" t="inlineStr"/>
@@ -25574,7 +25574,7 @@
       </c>
       <c r="K517" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L517" s="6" t="inlineStr"/>
@@ -25622,7 +25622,7 @@
       </c>
       <c r="K518" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L518" s="3" t="inlineStr"/>
@@ -25670,7 +25670,7 @@
       </c>
       <c r="K519" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L519" s="6" t="inlineStr"/>
@@ -25718,7 +25718,7 @@
       </c>
       <c r="K520" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L520" s="3" t="inlineStr"/>
@@ -25766,7 +25766,7 @@
       </c>
       <c r="K521" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L521" s="6" t="inlineStr"/>
@@ -25814,7 +25814,7 @@
       </c>
       <c r="K522" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L522" s="3" t="inlineStr"/>
@@ -25862,7 +25862,7 @@
       </c>
       <c r="K523" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L523" s="6" t="inlineStr"/>
@@ -25910,7 +25910,7 @@
       </c>
       <c r="K524" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L524" s="3" t="inlineStr"/>
@@ -25958,7 +25958,7 @@
       </c>
       <c r="K525" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L525" s="6" t="inlineStr"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K526" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L526" s="3" t="inlineStr"/>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="K527" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L527" s="6" t="inlineStr"/>
@@ -26102,7 +26102,7 @@
       </c>
       <c r="K528" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L528" s="3" t="inlineStr"/>
@@ -26150,7 +26150,7 @@
       </c>
       <c r="K529" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L529" s="6" t="inlineStr"/>
@@ -26198,7 +26198,7 @@
       </c>
       <c r="K530" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L530" s="3" t="inlineStr"/>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="K531" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L531" s="6" t="inlineStr"/>
@@ -26294,7 +26294,7 @@
       </c>
       <c r="K532" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L532" s="3" t="inlineStr"/>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="K533" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L533" s="6" t="inlineStr"/>
@@ -26390,7 +26390,7 @@
       </c>
       <c r="K534" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L534" s="3" t="inlineStr"/>
@@ -26438,7 +26438,7 @@
       </c>
       <c r="K535" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L535" s="6" t="inlineStr"/>
@@ -26486,7 +26486,7 @@
       </c>
       <c r="K536" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L536" s="3" t="inlineStr"/>
@@ -26534,7 +26534,7 @@
       </c>
       <c r="K537" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L537" s="6" t="inlineStr"/>
@@ -26582,7 +26582,7 @@
       </c>
       <c r="K538" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L538" s="3" t="inlineStr"/>
@@ -26630,7 +26630,7 @@
       </c>
       <c r="K539" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L539" s="6" t="inlineStr"/>
@@ -26678,7 +26678,7 @@
       </c>
       <c r="K540" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L540" s="3" t="inlineStr"/>
@@ -26726,7 +26726,7 @@
       </c>
       <c r="K541" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L541" s="6" t="inlineStr"/>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="K542" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L542" s="3" t="inlineStr"/>
@@ -26822,7 +26822,7 @@
       </c>
       <c r="K543" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L543" s="6" t="inlineStr"/>
@@ -26870,7 +26870,7 @@
       </c>
       <c r="K544" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L544" s="3" t="inlineStr"/>
@@ -26918,7 +26918,7 @@
       </c>
       <c r="K545" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L545" s="6" t="inlineStr"/>
@@ -26966,7 +26966,7 @@
       </c>
       <c r="K546" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L546" s="3" t="inlineStr"/>
@@ -27014,7 +27014,7 @@
       </c>
       <c r="K547" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L547" s="6" t="inlineStr"/>
@@ -27062,7 +27062,7 @@
       </c>
       <c r="K548" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L548" s="3" t="inlineStr"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K549" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L549" s="6" t="inlineStr"/>
@@ -27158,7 +27158,7 @@
       </c>
       <c r="K550" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L550" s="3" t="inlineStr"/>
@@ -27206,7 +27206,7 @@
       </c>
       <c r="K551" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L551" s="6" t="inlineStr"/>
@@ -27254,7 +27254,7 @@
       </c>
       <c r="K552" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L552" s="3" t="inlineStr"/>
@@ -27302,7 +27302,7 @@
       </c>
       <c r="K553" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L553" s="6" t="inlineStr"/>
@@ -27350,7 +27350,7 @@
       </c>
       <c r="K554" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L554" s="3" t="inlineStr"/>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="K555" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L555" s="6" t="inlineStr"/>
@@ -27446,7 +27446,7 @@
       </c>
       <c r="K556" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L556" s="3" t="inlineStr"/>
@@ -27494,7 +27494,7 @@
       </c>
       <c r="K557" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L557" s="6" t="inlineStr"/>
@@ -27542,7 +27542,7 @@
       </c>
       <c r="K558" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L558" s="3" t="inlineStr"/>
@@ -27590,7 +27590,7 @@
       </c>
       <c r="K559" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L559" s="6" t="inlineStr"/>
@@ -27638,7 +27638,7 @@
       </c>
       <c r="K560" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L560" s="3" t="inlineStr"/>
@@ -27686,7 +27686,7 @@
       </c>
       <c r="K561" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L561" s="6" t="inlineStr"/>
@@ -27734,7 +27734,7 @@
       </c>
       <c r="K562" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L562" s="3" t="inlineStr"/>
@@ -27782,7 +27782,7 @@
       </c>
       <c r="K563" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L563" s="6" t="inlineStr"/>
@@ -27830,7 +27830,7 @@
       </c>
       <c r="K564" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L564" s="3" t="inlineStr"/>
@@ -27878,7 +27878,7 @@
       </c>
       <c r="K565" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L565" s="6" t="inlineStr"/>
@@ -27926,7 +27926,7 @@
       </c>
       <c r="K566" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L566" s="3" t="inlineStr"/>
@@ -27974,7 +27974,7 @@
       </c>
       <c r="K567" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L567" s="6" t="inlineStr"/>
@@ -28022,7 +28022,7 @@
       </c>
       <c r="K568" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L568" s="3" t="inlineStr"/>
@@ -28070,7 +28070,7 @@
       </c>
       <c r="K569" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L569" s="6" t="inlineStr"/>
@@ -28118,7 +28118,7 @@
       </c>
       <c r="K570" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L570" s="3" t="inlineStr"/>
@@ -28166,7 +28166,7 @@
       </c>
       <c r="K571" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L571" s="6" t="inlineStr"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K572" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L572" s="3" t="inlineStr"/>
@@ -28262,7 +28262,7 @@
       </c>
       <c r="K573" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L573" s="6" t="inlineStr"/>
@@ -28310,7 +28310,7 @@
       </c>
       <c r="K574" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L574" s="3" t="inlineStr"/>
@@ -28358,7 +28358,7 @@
       </c>
       <c r="K575" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L575" s="6" t="inlineStr"/>
@@ -28406,7 +28406,7 @@
       </c>
       <c r="K576" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L576" s="3" t="inlineStr"/>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="K577" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L577" s="6" t="inlineStr"/>
@@ -28502,7 +28502,7 @@
       </c>
       <c r="K578" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L578" s="3" t="inlineStr"/>
@@ -28550,7 +28550,7 @@
       </c>
       <c r="K579" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L579" s="6" t="inlineStr"/>
@@ -28598,7 +28598,7 @@
       </c>
       <c r="K580" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L580" s="3" t="inlineStr"/>
@@ -28646,7 +28646,7 @@
       </c>
       <c r="K581" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L581" s="6" t="inlineStr"/>
@@ -28694,7 +28694,7 @@
       </c>
       <c r="K582" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L582" s="3" t="inlineStr"/>
@@ -28742,7 +28742,7 @@
       </c>
       <c r="K583" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L583" s="6" t="inlineStr"/>
@@ -28790,7 +28790,7 @@
       </c>
       <c r="K584" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L584" s="3" t="inlineStr"/>
@@ -28838,7 +28838,7 @@
       </c>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L585" s="6" t="inlineStr"/>
@@ -28886,7 +28886,7 @@
       </c>
       <c r="K586" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L586" s="3" t="inlineStr"/>
@@ -28934,7 +28934,7 @@
       </c>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L587" s="6" t="inlineStr"/>
@@ -28982,7 +28982,7 @@
       </c>
       <c r="K588" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L588" s="3" t="inlineStr"/>
@@ -29030,7 +29030,7 @@
       </c>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L589" s="6" t="inlineStr"/>
@@ -29078,7 +29078,7 @@
       </c>
       <c r="K590" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L590" s="3" t="inlineStr"/>
@@ -29126,7 +29126,7 @@
       </c>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L591" s="6" t="inlineStr"/>
@@ -29174,7 +29174,7 @@
       </c>
       <c r="K592" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L592" s="3" t="inlineStr"/>
@@ -29222,7 +29222,7 @@
       </c>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L593" s="6" t="inlineStr"/>
@@ -29270,7 +29270,7 @@
       </c>
       <c r="K594" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L594" s="3" t="inlineStr"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L595" s="6" t="inlineStr"/>
@@ -29366,7 +29366,7 @@
       </c>
       <c r="K596" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L596" s="3" t="inlineStr"/>
@@ -29414,7 +29414,7 @@
       </c>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L597" s="6" t="inlineStr"/>
@@ -29462,7 +29462,7 @@
       </c>
       <c r="K598" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L598" s="3" t="inlineStr"/>
@@ -29510,7 +29510,7 @@
       </c>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L599" s="6" t="inlineStr"/>
@@ -29558,7 +29558,7 @@
       </c>
       <c r="K600" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L600" s="3" t="inlineStr"/>
@@ -29606,7 +29606,7 @@
       </c>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L601" s="6" t="inlineStr"/>
@@ -29654,7 +29654,7 @@
       </c>
       <c r="K602" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L602" s="3" t="inlineStr"/>
@@ -29702,7 +29702,7 @@
       </c>
       <c r="K603" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L603" s="6" t="inlineStr"/>
@@ -29750,7 +29750,7 @@
       </c>
       <c r="K604" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L604" s="3" t="inlineStr"/>
@@ -29798,7 +29798,7 @@
       </c>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr"/>
@@ -29846,7 +29846,7 @@
       </c>
       <c r="K606" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L606" s="3" t="inlineStr"/>
@@ -29894,7 +29894,7 @@
       </c>
       <c r="K607" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L607" s="6" t="inlineStr"/>
@@ -29942,7 +29942,7 @@
       </c>
       <c r="K608" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L608" s="3" t="inlineStr"/>
@@ -29990,7 +29990,7 @@
       </c>
       <c r="K609" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L609" s="6" t="inlineStr"/>
@@ -30038,7 +30038,7 @@
       </c>
       <c r="K610" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L610" s="3" t="inlineStr"/>
@@ -30086,7 +30086,7 @@
       </c>
       <c r="K611" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L611" s="6" t="inlineStr"/>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="K612" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L612" s="3" t="inlineStr"/>
@@ -30182,7 +30182,7 @@
       </c>
       <c r="K613" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L613" s="6" t="inlineStr"/>
@@ -30230,7 +30230,7 @@
       </c>
       <c r="K614" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L614" s="3" t="inlineStr"/>
@@ -30278,7 +30278,7 @@
       </c>
       <c r="K615" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L615" s="6" t="inlineStr"/>
@@ -30326,7 +30326,7 @@
       </c>
       <c r="K616" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L616" s="3" t="inlineStr"/>
@@ -30374,7 +30374,7 @@
       </c>
       <c r="K617" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L617" s="6" t="inlineStr"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K618" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L618" s="3" t="inlineStr"/>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="K619" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L619" s="6" t="inlineStr"/>
@@ -30518,7 +30518,7 @@
       </c>
       <c r="K620" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L620" s="3" t="inlineStr"/>
@@ -30566,7 +30566,7 @@
       </c>
       <c r="K621" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L621" s="6" t="inlineStr"/>
@@ -30614,7 +30614,7 @@
       </c>
       <c r="K622" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L622" s="3" t="inlineStr"/>
@@ -30662,7 +30662,7 @@
       </c>
       <c r="K623" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L623" s="6" t="inlineStr"/>
@@ -30710,7 +30710,7 @@
       </c>
       <c r="K624" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L624" s="3" t="inlineStr"/>
@@ -30758,7 +30758,7 @@
       </c>
       <c r="K625" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L625" s="6" t="inlineStr"/>
@@ -30806,7 +30806,7 @@
       </c>
       <c r="K626" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L626" s="3" t="inlineStr"/>
@@ -30854,7 +30854,7 @@
       </c>
       <c r="K627" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L627" s="6" t="inlineStr"/>
@@ -30902,7 +30902,7 @@
       </c>
       <c r="K628" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L628" s="3" t="inlineStr"/>
@@ -30950,7 +30950,7 @@
       </c>
       <c r="K629" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L629" s="6" t="inlineStr"/>
@@ -30998,7 +30998,7 @@
       </c>
       <c r="K630" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L630" s="3" t="inlineStr"/>
@@ -31046,7 +31046,7 @@
       </c>
       <c r="K631" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L631" s="6" t="inlineStr"/>
@@ -31094,7 +31094,7 @@
       </c>
       <c r="K632" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L632" s="3" t="inlineStr"/>
@@ -31142,7 +31142,7 @@
       </c>
       <c r="K633" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L633" s="6" t="inlineStr"/>
@@ -31190,7 +31190,7 @@
       </c>
       <c r="K634" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L634" s="3" t="inlineStr"/>
@@ -31238,7 +31238,7 @@
       </c>
       <c r="K635" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L635" s="6" t="inlineStr"/>
@@ -31286,7 +31286,7 @@
       </c>
       <c r="K636" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L636" s="3" t="inlineStr"/>
@@ -31334,7 +31334,7 @@
       </c>
       <c r="K637" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L637" s="6" t="inlineStr"/>
@@ -31382,7 +31382,7 @@
       </c>
       <c r="K638" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L638" s="3" t="inlineStr"/>
@@ -31430,7 +31430,7 @@
       </c>
       <c r="K639" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L639" s="6" t="inlineStr"/>
@@ -31478,7 +31478,7 @@
       </c>
       <c r="K640" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L640" s="3" t="inlineStr"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K641" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L641" s="6" t="inlineStr"/>
@@ -31574,7 +31574,7 @@
       </c>
       <c r="K642" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L642" s="3" t="inlineStr"/>
@@ -31622,7 +31622,7 @@
       </c>
       <c r="K643" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L643" s="6" t="inlineStr"/>
@@ -31670,7 +31670,7 @@
       </c>
       <c r="K644" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L644" s="3" t="inlineStr"/>
@@ -31718,7 +31718,7 @@
       </c>
       <c r="K645" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L645" s="6" t="inlineStr"/>
@@ -31766,7 +31766,7 @@
       </c>
       <c r="K646" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L646" s="3" t="inlineStr"/>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="K647" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L647" s="6" t="inlineStr"/>
@@ -31862,7 +31862,7 @@
       </c>
       <c r="K648" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L648" s="3" t="inlineStr"/>
@@ -31910,7 +31910,7 @@
       </c>
       <c r="K649" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L649" s="6" t="inlineStr"/>
@@ -31958,7 +31958,7 @@
       </c>
       <c r="K650" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L650" s="3" t="inlineStr"/>
@@ -32006,7 +32006,7 @@
       </c>
       <c r="K651" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L651" s="6" t="inlineStr"/>
@@ -32054,7 +32054,7 @@
       </c>
       <c r="K652" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L652" s="3" t="inlineStr"/>
@@ -32102,7 +32102,7 @@
       </c>
       <c r="K653" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L653" s="6" t="inlineStr"/>
@@ -32150,7 +32150,7 @@
       </c>
       <c r="K654" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L654" s="3" t="inlineStr"/>
@@ -32198,7 +32198,7 @@
       </c>
       <c r="K655" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L655" s="6" t="inlineStr"/>
@@ -32246,7 +32246,7 @@
       </c>
       <c r="K656" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L656" s="3" t="inlineStr"/>
@@ -32294,7 +32294,7 @@
       </c>
       <c r="K657" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L657" s="6" t="inlineStr"/>
@@ -32342,7 +32342,7 @@
       </c>
       <c r="K658" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L658" s="3" t="inlineStr"/>
@@ -32390,7 +32390,7 @@
       </c>
       <c r="K659" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L659" s="6" t="inlineStr"/>
@@ -32438,7 +32438,7 @@
       </c>
       <c r="K660" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L660" s="3" t="inlineStr"/>
@@ -32486,7 +32486,7 @@
       </c>
       <c r="K661" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L661" s="6" t="inlineStr"/>
@@ -32534,7 +32534,7 @@
       </c>
       <c r="K662" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L662" s="3" t="inlineStr"/>
@@ -32582,7 +32582,7 @@
       </c>
       <c r="K663" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L663" s="6" t="inlineStr"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K664" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L664" s="3" t="inlineStr"/>
@@ -32678,7 +32678,7 @@
       </c>
       <c r="K665" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L665" s="6" t="inlineStr"/>
@@ -32726,7 +32726,7 @@
       </c>
       <c r="K666" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L666" s="3" t="inlineStr"/>
@@ -32774,7 +32774,7 @@
       </c>
       <c r="K667" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L667" s="6" t="inlineStr"/>
@@ -32822,7 +32822,7 @@
       </c>
       <c r="K668" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L668" s="3" t="inlineStr"/>
@@ -32870,7 +32870,7 @@
       </c>
       <c r="K669" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L669" s="6" t="inlineStr"/>
@@ -32918,7 +32918,7 @@
       </c>
       <c r="K670" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L670" s="3" t="inlineStr"/>
@@ -32966,7 +32966,7 @@
       </c>
       <c r="K671" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L671" s="6" t="inlineStr"/>
@@ -33014,7 +33014,7 @@
       </c>
       <c r="K672" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L672" s="3" t="inlineStr"/>
@@ -33062,7 +33062,7 @@
       </c>
       <c r="K673" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L673" s="6" t="inlineStr"/>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="K674" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L674" s="3" t="inlineStr"/>
@@ -33158,7 +33158,7 @@
       </c>
       <c r="K675" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L675" s="6" t="inlineStr"/>
@@ -33206,7 +33206,7 @@
       </c>
       <c r="K676" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L676" s="3" t="inlineStr"/>
@@ -33254,7 +33254,7 @@
       </c>
       <c r="K677" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L677" s="6" t="inlineStr"/>
@@ -33302,7 +33302,7 @@
       </c>
       <c r="K678" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L678" s="3" t="inlineStr"/>
@@ -33350,7 +33350,7 @@
       </c>
       <c r="K679" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L679" s="6" t="inlineStr"/>
@@ -33398,7 +33398,7 @@
       </c>
       <c r="K680" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L680" s="3" t="inlineStr"/>
@@ -33446,7 +33446,7 @@
       </c>
       <c r="K681" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L681" s="6" t="inlineStr"/>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="K682" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L682" s="3" t="inlineStr"/>
@@ -33542,7 +33542,7 @@
       </c>
       <c r="K683" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L683" s="6" t="inlineStr"/>
@@ -33590,7 +33590,7 @@
       </c>
       <c r="K684" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L684" s="3" t="inlineStr"/>
@@ -33638,7 +33638,7 @@
       </c>
       <c r="K685" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L685" s="6" t="inlineStr"/>
@@ -33686,7 +33686,7 @@
       </c>
       <c r="K686" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L686" s="3" t="inlineStr"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K687" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L687" s="6" t="inlineStr"/>
@@ -33782,7 +33782,7 @@
       </c>
       <c r="K688" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L688" s="3" t="inlineStr"/>
@@ -33830,7 +33830,7 @@
       </c>
       <c r="K689" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L689" s="6" t="inlineStr"/>
@@ -33878,7 +33878,7 @@
       </c>
       <c r="K690" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L690" s="3" t="inlineStr"/>
@@ -33926,7 +33926,7 @@
       </c>
       <c r="K691" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L691" s="6" t="inlineStr"/>
@@ -33974,7 +33974,7 @@
       </c>
       <c r="K692" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L692" s="3" t="inlineStr"/>
@@ -34022,7 +34022,7 @@
       </c>
       <c r="K693" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L693" s="6" t="inlineStr"/>
@@ -34070,7 +34070,7 @@
       </c>
       <c r="K694" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L694" s="3" t="inlineStr"/>
@@ -34118,7 +34118,7 @@
       </c>
       <c r="K695" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L695" s="6" t="inlineStr"/>
@@ -34166,7 +34166,7 @@
       </c>
       <c r="K696" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L696" s="3" t="inlineStr"/>
@@ -34214,7 +34214,7 @@
       </c>
       <c r="K697" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L697" s="6" t="inlineStr"/>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="K698" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L698" s="3" t="inlineStr"/>
@@ -34310,7 +34310,7 @@
       </c>
       <c r="K699" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L699" s="6" t="inlineStr"/>
@@ -34358,7 +34358,7 @@
       </c>
       <c r="K700" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L700" s="3" t="inlineStr"/>
@@ -34406,7 +34406,7 @@
       </c>
       <c r="K701" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L701" s="6" t="inlineStr"/>
@@ -34454,7 +34454,7 @@
       </c>
       <c r="K702" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L702" s="3" t="inlineStr"/>
@@ -34502,7 +34502,7 @@
       </c>
       <c r="K703" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L703" s="6" t="inlineStr"/>
@@ -34550,7 +34550,7 @@
       </c>
       <c r="K704" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L704" s="3" t="inlineStr"/>
@@ -34598,7 +34598,7 @@
       </c>
       <c r="K705" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L705" s="6" t="inlineStr"/>
@@ -34646,7 +34646,7 @@
       </c>
       <c r="K706" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L706" s="3" t="inlineStr"/>
@@ -34694,7 +34694,7 @@
       </c>
       <c r="K707" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L707" s="6" t="inlineStr"/>
@@ -34742,7 +34742,7 @@
       </c>
       <c r="K708" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L708" s="3" t="inlineStr"/>
@@ -34790,7 +34790,7 @@
       </c>
       <c r="K709" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L709" s="6" t="inlineStr"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K710" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L710" s="3" t="inlineStr"/>
@@ -34886,7 +34886,7 @@
       </c>
       <c r="K711" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L711" s="6" t="inlineStr"/>
@@ -34934,7 +34934,7 @@
       </c>
       <c r="K712" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L712" s="3" t="inlineStr"/>
@@ -34982,7 +34982,7 @@
       </c>
       <c r="K713" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L713" s="6" t="inlineStr"/>
@@ -35030,7 +35030,7 @@
       </c>
       <c r="K714" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L714" s="3" t="inlineStr"/>
@@ -35078,7 +35078,7 @@
       </c>
       <c r="K715" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L715" s="6" t="inlineStr"/>
@@ -35126,7 +35126,7 @@
       </c>
       <c r="K716" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L716" s="3" t="inlineStr"/>
@@ -35174,7 +35174,7 @@
       </c>
       <c r="K717" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L717" s="6" t="inlineStr"/>
@@ -35222,7 +35222,7 @@
       </c>
       <c r="K718" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L718" s="3" t="inlineStr"/>
@@ -35270,7 +35270,7 @@
       </c>
       <c r="K719" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L719" s="6" t="inlineStr"/>
@@ -35318,7 +35318,7 @@
       </c>
       <c r="K720" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L720" s="3" t="inlineStr"/>
@@ -35366,7 +35366,7 @@
       </c>
       <c r="K721" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L721" s="6" t="inlineStr"/>
@@ -35414,7 +35414,7 @@
       </c>
       <c r="K722" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L722" s="3" t="inlineStr"/>
@@ -35462,7 +35462,7 @@
       </c>
       <c r="K723" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L723" s="6" t="inlineStr"/>
@@ -35510,7 +35510,7 @@
       </c>
       <c r="K724" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L724" s="3" t="inlineStr"/>
@@ -35558,7 +35558,7 @@
       </c>
       <c r="K725" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L725" s="6" t="inlineStr"/>
@@ -35606,7 +35606,7 @@
       </c>
       <c r="K726" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L726" s="3" t="inlineStr"/>
@@ -35654,7 +35654,7 @@
       </c>
       <c r="K727" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L727" s="6" t="inlineStr"/>
@@ -35702,7 +35702,7 @@
       </c>
       <c r="K728" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L728" s="3" t="inlineStr"/>
@@ -35750,7 +35750,7 @@
       </c>
       <c r="K729" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L729" s="4" t="inlineStr">
@@ -35802,7 +35802,7 @@
       </c>
       <c r="K730" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L730" s="4" t="inlineStr">
@@ -35854,7 +35854,7 @@
       </c>
       <c r="K731" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L731" s="4" t="inlineStr">
@@ -35906,7 +35906,7 @@
       </c>
       <c r="K732" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L732" s="4" t="inlineStr">
@@ -35958,7 +35958,7 @@
       </c>
       <c r="K733" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L733" s="4" t="inlineStr">
@@ -36010,7 +36010,7 @@
       </c>
       <c r="K734" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L734" s="4" t="inlineStr">
@@ -36062,7 +36062,7 @@
       </c>
       <c r="K735" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L735" s="4" t="inlineStr">
@@ -36114,7 +36114,7 @@
       </c>
       <c r="K736" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L736" s="4" t="inlineStr">
@@ -36166,7 +36166,7 @@
       </c>
       <c r="K737" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L737" s="4" t="inlineStr">
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K738" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L738" s="4" t="inlineStr">
@@ -36270,7 +36270,7 @@
       </c>
       <c r="K739" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L739" s="4" t="inlineStr">
@@ -36322,7 +36322,7 @@
       </c>
       <c r="K740" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L740" s="4" t="inlineStr">
@@ -36374,7 +36374,7 @@
       </c>
       <c r="K741" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L741" s="4" t="inlineStr">
@@ -36426,7 +36426,7 @@
       </c>
       <c r="K742" s="3" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L742" s="4" t="inlineStr">
@@ -36478,7 +36478,7 @@
       </c>
       <c r="K743" s="6" t="inlineStr">
         <is>
-          <t>2026-09-12</t>
+          <t>2026-09-13</t>
         </is>
       </c>
       <c r="L743" s="4" t="inlineStr">

--- a/public/loop-library.xlsx
+++ b/public/loop-library.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr"/>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr"/>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr"/>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr"/>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr"/>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr"/>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr"/>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr"/>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr"/>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr"/>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr"/>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr"/>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr"/>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr"/>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr"/>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr"/>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr"/>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr"/>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr"/>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr"/>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L93" s="6" t="inlineStr"/>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr"/>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L95" s="6" t="inlineStr"/>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr"/>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L97" s="6" t="inlineStr"/>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr"/>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr"/>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr"/>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr"/>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L102" s="3" t="inlineStr"/>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L103" s="6" t="inlineStr"/>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L104" s="3" t="inlineStr"/>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L105" s="6" t="inlineStr"/>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L106" s="3" t="inlineStr"/>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L107" s="6" t="inlineStr"/>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L108" s="3" t="inlineStr"/>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L109" s="6" t="inlineStr"/>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L110" s="3" t="inlineStr"/>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L111" s="6" t="inlineStr"/>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L112" s="3" t="inlineStr"/>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L113" s="6" t="inlineStr"/>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L114" s="3" t="inlineStr"/>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L115" s="6" t="inlineStr"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="K116" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L116" s="3" t="inlineStr"/>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L117" s="6" t="inlineStr"/>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="K118" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L118" s="3" t="inlineStr"/>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L119" s="6" t="inlineStr"/>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="K120" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L120" s="3" t="inlineStr"/>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L121" s="6" t="inlineStr"/>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="K122" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L122" s="3" t="inlineStr"/>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L123" s="6" t="inlineStr"/>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="K124" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L124" s="3" t="inlineStr"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="K125" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L125" s="6" t="inlineStr"/>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="K126" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L126" s="3" t="inlineStr"/>
@@ -6854,7 +6854,7 @@
       </c>
       <c r="K127" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L127" s="6" t="inlineStr"/>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L128" s="3" t="inlineStr"/>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="K129" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L129" s="6" t="inlineStr"/>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="K130" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L130" s="3" t="inlineStr"/>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="K131" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L131" s="6" t="inlineStr"/>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L132" s="3" t="inlineStr"/>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="K133" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L133" s="6" t="inlineStr"/>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="K134" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L134" s="3" t="inlineStr"/>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="K135" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L135" s="6" t="inlineStr"/>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="K136" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L136" s="3" t="inlineStr"/>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="K137" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L137" s="6" t="inlineStr"/>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="K138" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L138" s="3" t="inlineStr"/>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="K139" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L139" s="6" t="inlineStr"/>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="K140" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L140" s="3" t="inlineStr"/>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="K141" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L141" s="6" t="inlineStr"/>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L142" s="3" t="inlineStr"/>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="K143" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L143" s="6" t="inlineStr"/>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="K144" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L144" s="3" t="inlineStr"/>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="K145" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L145" s="6" t="inlineStr"/>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="K146" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L146" s="3" t="inlineStr"/>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="K147" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L147" s="6" t="inlineStr"/>
@@ -7862,7 +7862,7 @@
       </c>
       <c r="K148" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L148" s="3" t="inlineStr"/>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="K149" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L149" s="6" t="inlineStr"/>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="K150" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L150" s="3" t="inlineStr"/>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="K151" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L151" s="6" t="inlineStr"/>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="K152" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L152" s="3" t="inlineStr"/>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="K153" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L153" s="6" t="inlineStr"/>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="K154" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L154" s="3" t="inlineStr"/>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="K155" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L155" s="6" t="inlineStr"/>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="K156" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L156" s="3" t="inlineStr"/>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K157" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L157" s="6" t="inlineStr"/>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="K158" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L158" s="3" t="inlineStr"/>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="K159" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L159" s="6" t="inlineStr"/>
@@ -8438,7 +8438,7 @@
       </c>
       <c r="K160" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L160" s="3" t="inlineStr"/>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="K161" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L161" s="6" t="inlineStr"/>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="K162" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L162" s="3" t="inlineStr"/>
@@ -8582,7 +8582,7 @@
       </c>
       <c r="K163" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L163" s="6" t="inlineStr"/>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="K164" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L164" s="3" t="inlineStr"/>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="K165" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L165" s="6" t="inlineStr"/>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="K166" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L166" s="3" t="inlineStr"/>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="K167" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L167" s="6" t="inlineStr"/>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="K168" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L168" s="3" t="inlineStr"/>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="K169" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L169" s="6" t="inlineStr"/>
@@ -8918,7 +8918,7 @@
       </c>
       <c r="K170" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L170" s="3" t="inlineStr"/>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="K171" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L171" s="6" t="inlineStr"/>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="K172" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L172" s="3" t="inlineStr"/>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="K173" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L173" s="6" t="inlineStr"/>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="K174" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L174" s="3" t="inlineStr"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="K175" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L175" s="6" t="inlineStr"/>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="K176" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L176" s="3" t="inlineStr"/>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="K177" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L177" s="6" t="inlineStr"/>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="K178" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L178" s="3" t="inlineStr"/>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="K179" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L179" s="6" t="inlineStr"/>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="K180" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L180" s="3" t="inlineStr"/>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="K181" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L181" s="6" t="inlineStr"/>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="K182" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L182" s="3" t="inlineStr"/>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="K183" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L183" s="6" t="inlineStr"/>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="K184" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L184" s="3" t="inlineStr"/>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="K185" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L185" s="6" t="inlineStr"/>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="K186" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L186" s="3" t="inlineStr"/>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="K187" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L187" s="6" t="inlineStr"/>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="K188" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L188" s="3" t="inlineStr"/>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="K189" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L189" s="6" t="inlineStr"/>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="K190" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L190" s="3" t="inlineStr"/>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="K191" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L191" s="6" t="inlineStr"/>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="K192" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L192" s="3" t="inlineStr"/>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="K193" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L193" s="6" t="inlineStr"/>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="K194" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L194" s="3" t="inlineStr"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="K195" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L195" s="6" t="inlineStr"/>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="K196" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L196" s="3" t="inlineStr"/>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="K197" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L197" s="6" t="inlineStr"/>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="K198" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L198" s="3" t="inlineStr"/>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="K199" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L199" s="6" t="inlineStr"/>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="K200" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L200" s="3" t="inlineStr"/>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="K201" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L201" s="6" t="inlineStr"/>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="K202" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L202" s="3" t="inlineStr"/>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="K203" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L203" s="6" t="inlineStr"/>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="K204" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L204" s="3" t="inlineStr"/>
@@ -10598,7 +10598,7 @@
       </c>
       <c r="K205" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L205" s="6" t="inlineStr"/>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K206" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L206" s="3" t="inlineStr"/>
@@ -10694,7 +10694,7 @@
       </c>
       <c r="K207" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L207" s="6" t="inlineStr"/>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="K208" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L208" s="3" t="inlineStr"/>
@@ -10790,7 +10790,7 @@
       </c>
       <c r="K209" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L209" s="6" t="inlineStr"/>
@@ -10838,7 +10838,7 @@
       </c>
       <c r="K210" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L210" s="3" t="inlineStr"/>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="K211" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L211" s="6" t="inlineStr"/>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="K212" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L212" s="3" t="inlineStr"/>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="K213" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L213" s="6" t="inlineStr"/>
@@ -11030,7 +11030,7 @@
       </c>
       <c r="K214" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L214" s="3" t="inlineStr"/>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="K215" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L215" s="6" t="inlineStr"/>
@@ -11126,7 +11126,7 @@
       </c>
       <c r="K216" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L216" s="3" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="K217" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L217" s="6" t="inlineStr"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="K218" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L218" s="3" t="inlineStr"/>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="K219" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L219" s="6" t="inlineStr"/>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="K220" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L220" s="3" t="inlineStr"/>
@@ -11366,7 +11366,7 @@
       </c>
       <c r="K221" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L221" s="6" t="inlineStr"/>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="K222" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L222" s="3" t="inlineStr"/>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="K223" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L223" s="6" t="inlineStr"/>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="K224" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L224" s="3" t="inlineStr"/>
@@ -11558,7 +11558,7 @@
       </c>
       <c r="K225" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L225" s="6" t="inlineStr"/>
@@ -11606,7 +11606,7 @@
       </c>
       <c r="K226" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L226" s="3" t="inlineStr"/>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="K227" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L227" s="6" t="inlineStr"/>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="K228" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L228" s="3" t="inlineStr"/>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="K229" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L229" s="6" t="inlineStr"/>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="K230" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L230" s="3" t="inlineStr"/>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="K231" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L231" s="6" t="inlineStr"/>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="K232" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L232" s="3" t="inlineStr"/>
@@ -11942,7 +11942,7 @@
       </c>
       <c r="K233" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L233" s="6" t="inlineStr"/>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="K234" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L234" s="3" t="inlineStr"/>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="K235" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L235" s="6" t="inlineStr"/>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="K236" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L236" s="3" t="inlineStr"/>
@@ -12134,7 +12134,7 @@
       </c>
       <c r="K237" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L237" s="6" t="inlineStr"/>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="K238" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L238" s="3" t="inlineStr"/>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="K239" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L239" s="6" t="inlineStr"/>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="K240" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L240" s="3" t="inlineStr"/>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="K241" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L241" s="6" t="inlineStr"/>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="K242" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L242" s="3" t="inlineStr"/>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="K243" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L243" s="6" t="inlineStr"/>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="K244" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L244" s="3" t="inlineStr"/>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="K245" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L245" s="6" t="inlineStr"/>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="K246" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L246" s="3" t="inlineStr"/>
@@ -12614,7 +12614,7 @@
       </c>
       <c r="K247" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L247" s="6" t="inlineStr"/>
@@ -12662,7 +12662,7 @@
       </c>
       <c r="K248" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L248" s="3" t="inlineStr"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="K249" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L249" s="6" t="inlineStr"/>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="K250" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L250" s="3" t="inlineStr"/>
@@ -12806,7 +12806,7 @@
       </c>
       <c r="K251" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L251" s="6" t="inlineStr"/>
@@ -12854,7 +12854,7 @@
       </c>
       <c r="K252" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L252" s="3" t="inlineStr"/>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="K253" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L253" s="6" t="inlineStr"/>
@@ -12950,7 +12950,7 @@
       </c>
       <c r="K254" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L254" s="3" t="inlineStr"/>
@@ -12998,7 +12998,7 @@
       </c>
       <c r="K255" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L255" s="6" t="inlineStr"/>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="K256" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L256" s="3" t="inlineStr"/>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="K257" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L257" s="6" t="inlineStr"/>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="K258" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L258" s="3" t="inlineStr"/>
@@ -13190,7 +13190,7 @@
       </c>
       <c r="K259" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L259" s="6" t="inlineStr"/>
@@ -13238,7 +13238,7 @@
       </c>
       <c r="K260" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L260" s="3" t="inlineStr"/>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="K261" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L261" s="6" t="inlineStr"/>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="K262" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L262" s="3" t="inlineStr"/>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="K263" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L263" s="6" t="inlineStr"/>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="K264" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L264" s="3" t="inlineStr"/>
@@ -13478,7 +13478,7 @@
       </c>
       <c r="K265" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L265" s="6" t="inlineStr"/>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="K266" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L266" s="3" t="inlineStr"/>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="K267" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L267" s="6" t="inlineStr"/>
@@ -13622,7 +13622,7 @@
       </c>
       <c r="K268" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L268" s="3" t="inlineStr"/>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="K269" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L269" s="6" t="inlineStr"/>
@@ -13718,7 +13718,7 @@
       </c>
       <c r="K270" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L270" s="3" t="inlineStr"/>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="K271" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L271" s="6" t="inlineStr"/>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="K272" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L272" s="3" t="inlineStr"/>
@@ -13862,7 +13862,7 @@
       </c>
       <c r="K273" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L273" s="6" t="inlineStr"/>
@@ -13910,7 +13910,7 @@
       </c>
       <c r="K274" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L274" s="3" t="inlineStr"/>
@@ -13958,7 +13958,7 @@
       </c>
       <c r="K275" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L275" s="6" t="inlineStr"/>
@@ -14006,7 +14006,7 @@
       </c>
       <c r="K276" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L276" s="3" t="inlineStr"/>
@@ -14054,7 +14054,7 @@
       </c>
       <c r="K277" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L277" s="6" t="inlineStr"/>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="K278" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L278" s="3" t="inlineStr"/>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="K279" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L279" s="6" t="inlineStr"/>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="K280" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L280" s="3" t="inlineStr"/>
@@ -14246,7 +14246,7 @@
       </c>
       <c r="K281" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L281" s="6" t="inlineStr"/>
@@ -14294,7 +14294,7 @@
       </c>
       <c r="K282" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L282" s="3" t="inlineStr"/>
@@ -14342,7 +14342,7 @@
       </c>
       <c r="K283" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L283" s="6" t="inlineStr"/>
@@ -14390,7 +14390,7 @@
       </c>
       <c r="K284" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L284" s="3" t="inlineStr"/>
@@ -14438,7 +14438,7 @@
       </c>
       <c r="K285" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L285" s="6" t="inlineStr"/>
@@ -14486,7 +14486,7 @@
       </c>
       <c r="K286" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L286" s="3" t="inlineStr"/>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="K287" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L287" s="6" t="inlineStr"/>
@@ -14582,7 +14582,7 @@
       </c>
       <c r="K288" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L288" s="3" t="inlineStr"/>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="K289" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L289" s="6" t="inlineStr"/>
@@ -14678,7 +14678,7 @@
       </c>
       <c r="K290" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L290" s="3" t="inlineStr"/>
@@ -14726,7 +14726,7 @@
       </c>
       <c r="K291" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L291" s="6" t="inlineStr"/>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="K292" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L292" s="3" t="inlineStr"/>
@@ -14822,7 +14822,7 @@
       </c>
       <c r="K293" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L293" s="6" t="inlineStr"/>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="K294" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L294" s="3" t="inlineStr"/>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="K295" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L295" s="6" t="inlineStr"/>
@@ -14966,7 +14966,7 @@
       </c>
       <c r="K296" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L296" s="3" t="inlineStr"/>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="K297" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L297" s="6" t="inlineStr"/>
@@ -15062,7 +15062,7 @@
       </c>
       <c r="K298" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L298" s="3" t="inlineStr"/>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="K299" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L299" s="6" t="inlineStr"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="K300" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L300" s="3" t="inlineStr"/>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="K301" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L301" s="6" t="inlineStr"/>
@@ -15254,7 +15254,7 @@
       </c>
       <c r="K302" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L302" s="3" t="inlineStr"/>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="K303" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L303" s="6" t="inlineStr"/>
@@ -15350,7 +15350,7 @@
       </c>
       <c r="K304" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L304" s="3" t="inlineStr"/>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="K305" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L305" s="6" t="inlineStr"/>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="K306" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L306" s="3" t="inlineStr"/>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="K307" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L307" s="6" t="inlineStr"/>
@@ -15542,7 +15542,7 @@
       </c>
       <c r="K308" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L308" s="3" t="inlineStr"/>
@@ -15590,7 +15590,7 @@
       </c>
       <c r="K309" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L309" s="6" t="inlineStr"/>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="K310" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L310" s="3" t="inlineStr"/>
@@ -15686,7 +15686,7 @@
       </c>
       <c r="K311" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L311" s="6" t="inlineStr"/>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="K312" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L312" s="3" t="inlineStr"/>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="K313" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L313" s="6" t="inlineStr"/>
@@ -15830,7 +15830,7 @@
       </c>
       <c r="K314" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L314" s="3" t="inlineStr"/>
@@ -15878,7 +15878,7 @@
       </c>
       <c r="K315" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L315" s="6" t="inlineStr"/>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="K316" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L316" s="3" t="inlineStr"/>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="K317" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L317" s="6" t="inlineStr"/>
@@ -16022,7 +16022,7 @@
       </c>
       <c r="K318" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L318" s="3" t="inlineStr"/>
@@ -16070,7 +16070,7 @@
       </c>
       <c r="K319" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L319" s="6" t="inlineStr"/>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="K320" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L320" s="3" t="inlineStr"/>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="K321" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L321" s="6" t="inlineStr"/>
@@ -16214,7 +16214,7 @@
       </c>
       <c r="K322" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L322" s="3" t="inlineStr"/>
@@ -16262,7 +16262,7 @@
       </c>
       <c r="K323" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L323" s="6" t="inlineStr"/>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="K324" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L324" s="3" t="inlineStr"/>
@@ -16358,7 +16358,7 @@
       </c>
       <c r="K325" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L325" s="6" t="inlineStr"/>
@@ -16406,7 +16406,7 @@
       </c>
       <c r="K326" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L326" s="3" t="inlineStr"/>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="K327" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L327" s="6" t="inlineStr"/>
@@ -16502,7 +16502,7 @@
       </c>
       <c r="K328" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L328" s="3" t="inlineStr"/>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="K329" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L329" s="6" t="inlineStr"/>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="K330" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L330" s="3" t="inlineStr"/>
@@ -16646,7 +16646,7 @@
       </c>
       <c r="K331" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L331" s="6" t="inlineStr"/>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="K332" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L332" s="3" t="inlineStr"/>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="K333" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L333" s="6" t="inlineStr"/>
@@ -16790,7 +16790,7 @@
       </c>
       <c r="K334" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L334" s="3" t="inlineStr"/>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="K335" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L335" s="6" t="inlineStr"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="K336" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L336" s="3" t="inlineStr"/>
@@ -16934,7 +16934,7 @@
       </c>
       <c r="K337" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L337" s="6" t="inlineStr"/>
@@ -16982,7 +16982,7 @@
       </c>
       <c r="K338" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L338" s="3" t="inlineStr"/>
@@ -17030,7 +17030,7 @@
       </c>
       <c r="K339" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L339" s="6" t="inlineStr"/>
@@ -17078,7 +17078,7 @@
       </c>
       <c r="K340" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L340" s="3" t="inlineStr"/>
@@ -17126,7 +17126,7 @@
       </c>
       <c r="K341" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L341" s="6" t="inlineStr"/>
@@ -17174,7 +17174,7 @@
       </c>
       <c r="K342" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L342" s="3" t="inlineStr"/>
@@ -17222,7 +17222,7 @@
       </c>
       <c r="K343" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L343" s="6" t="inlineStr"/>
@@ -17270,7 +17270,7 @@
       </c>
       <c r="K344" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L344" s="3" t="inlineStr"/>
@@ -17318,7 +17318,7 @@
       </c>
       <c r="K345" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L345" s="6" t="inlineStr"/>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="K346" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L346" s="3" t="inlineStr"/>
@@ -17414,7 +17414,7 @@
       </c>
       <c r="K347" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L347" s="6" t="inlineStr"/>
@@ -17462,7 +17462,7 @@
       </c>
       <c r="K348" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L348" s="3" t="inlineStr"/>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="K349" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L349" s="6" t="inlineStr"/>
@@ -17558,7 +17558,7 @@
       </c>
       <c r="K350" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L350" s="3" t="inlineStr"/>
@@ -17606,7 +17606,7 @@
       </c>
       <c r="K351" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L351" s="6" t="inlineStr"/>
@@ -17654,7 +17654,7 @@
       </c>
       <c r="K352" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L352" s="3" t="inlineStr"/>
@@ -17702,7 +17702,7 @@
       </c>
       <c r="K353" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L353" s="6" t="inlineStr"/>
@@ -17750,7 +17750,7 @@
       </c>
       <c r="K354" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L354" s="3" t="inlineStr"/>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="K355" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L355" s="6" t="inlineStr"/>
@@ -17846,7 +17846,7 @@
       </c>
       <c r="K356" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L356" s="3" t="inlineStr"/>
@@ -17894,7 +17894,7 @@
       </c>
       <c r="K357" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L357" s="6" t="inlineStr"/>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="K358" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L358" s="3" t="inlineStr"/>
@@ -17990,7 +17990,7 @@
       </c>
       <c r="K359" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L359" s="6" t="inlineStr"/>
@@ -18038,7 +18038,7 @@
       </c>
       <c r="K360" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L360" s="3" t="inlineStr"/>
@@ -18086,7 +18086,7 @@
       </c>
       <c r="K361" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L361" s="6" t="inlineStr"/>
@@ -18134,7 +18134,7 @@
       </c>
       <c r="K362" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L362" s="3" t="inlineStr"/>
@@ -18182,7 +18182,7 @@
       </c>
       <c r="K363" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L363" s="6" t="inlineStr"/>
@@ -18230,7 +18230,7 @@
       </c>
       <c r="K364" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L364" s="3" t="inlineStr"/>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="K365" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L365" s="6" t="inlineStr"/>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="K366" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L366" s="3" t="inlineStr"/>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="K367" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L367" s="6" t="inlineStr"/>
@@ -18422,7 +18422,7 @@
       </c>
       <c r="K368" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L368" s="3" t="inlineStr"/>
@@ -18470,7 +18470,7 @@
       </c>
       <c r="K369" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L369" s="6" t="inlineStr"/>
@@ -18518,7 +18518,7 @@
       </c>
       <c r="K370" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L370" s="3" t="inlineStr"/>
@@ -18566,7 +18566,7 @@
       </c>
       <c r="K371" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L371" s="6" t="inlineStr"/>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="K372" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L372" s="3" t="inlineStr"/>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="K373" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L373" s="6" t="inlineStr"/>
@@ -18710,7 +18710,7 @@
       </c>
       <c r="K374" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L374" s="3" t="inlineStr"/>
@@ -18758,7 +18758,7 @@
       </c>
       <c r="K375" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L375" s="6" t="inlineStr"/>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="K376" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L376" s="3" t="inlineStr"/>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="K377" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L377" s="6" t="inlineStr"/>
@@ -18902,7 +18902,7 @@
       </c>
       <c r="K378" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L378" s="3" t="inlineStr"/>
@@ -18950,7 +18950,7 @@
       </c>
       <c r="K379" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L379" s="6" t="inlineStr"/>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="K380" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L380" s="3" t="inlineStr"/>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="K381" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L381" s="6" t="inlineStr"/>
@@ -19094,7 +19094,7 @@
       </c>
       <c r="K382" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L382" s="3" t="inlineStr"/>
@@ -19142,7 +19142,7 @@
       </c>
       <c r="K383" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L383" s="6" t="inlineStr"/>
@@ -19190,7 +19190,7 @@
       </c>
       <c r="K384" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L384" s="3" t="inlineStr"/>
@@ -19238,7 +19238,7 @@
       </c>
       <c r="K385" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L385" s="6" t="inlineStr"/>
@@ -19286,7 +19286,7 @@
       </c>
       <c r="K386" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L386" s="3" t="inlineStr"/>
@@ -19334,7 +19334,7 @@
       </c>
       <c r="K387" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L387" s="6" t="inlineStr"/>
@@ -19382,7 +19382,7 @@
       </c>
       <c r="K388" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L388" s="3" t="inlineStr"/>
@@ -19430,7 +19430,7 @@
       </c>
       <c r="K389" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L389" s="6" t="inlineStr"/>
@@ -19478,7 +19478,7 @@
       </c>
       <c r="K390" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L390" s="3" t="inlineStr"/>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="K391" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L391" s="6" t="inlineStr"/>
@@ -19574,7 +19574,7 @@
       </c>
       <c r="K392" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L392" s="3" t="inlineStr"/>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="K393" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L393" s="6" t="inlineStr"/>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="K394" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L394" s="3" t="inlineStr"/>
@@ -19718,7 +19718,7 @@
       </c>
       <c r="K395" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L395" s="6" t="inlineStr"/>
@@ -19766,7 +19766,7 @@
       </c>
       <c r="K396" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L396" s="3" t="inlineStr"/>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="K397" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L397" s="6" t="inlineStr"/>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="K398" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L398" s="3" t="inlineStr"/>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="K399" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L399" s="6" t="inlineStr"/>
@@ -19958,7 +19958,7 @@
       </c>
       <c r="K400" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L400" s="3" t="inlineStr"/>
@@ -20006,7 +20006,7 @@
       </c>
       <c r="K401" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L401" s="6" t="inlineStr"/>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="K402" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L402" s="3" t="inlineStr"/>
@@ -20102,7 +20102,7 @@
       </c>
       <c r="K403" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L403" s="6" t="inlineStr"/>
@@ -20150,7 +20150,7 @@
       </c>
       <c r="K404" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L404" s="3" t="inlineStr"/>
@@ -20198,7 +20198,7 @@
       </c>
       <c r="K405" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L405" s="6" t="inlineStr"/>
@@ -20246,7 +20246,7 @@
       </c>
       <c r="K406" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L406" s="3" t="inlineStr"/>
@@ -20294,7 +20294,7 @@
       </c>
       <c r="K407" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L407" s="6" t="inlineStr"/>
@@ -20342,7 +20342,7 @@
       </c>
       <c r="K408" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L408" s="3" t="inlineStr"/>
@@ -20390,7 +20390,7 @@
       </c>
       <c r="K409" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L409" s="6" t="inlineStr"/>
@@ -20438,7 +20438,7 @@
       </c>
       <c r="K410" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L410" s="3" t="inlineStr"/>
@@ -20486,7 +20486,7 @@
       </c>
       <c r="K411" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L411" s="6" t="inlineStr"/>
@@ -20534,7 +20534,7 @@
       </c>
       <c r="K412" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L412" s="3" t="inlineStr"/>
@@ -20582,7 +20582,7 @@
       </c>
       <c r="K413" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L413" s="6" t="inlineStr"/>
@@ -20630,7 +20630,7 @@
       </c>
       <c r="K414" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L414" s="3" t="inlineStr"/>
@@ -20678,7 +20678,7 @@
       </c>
       <c r="K415" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L415" s="6" t="inlineStr"/>
@@ -20726,7 +20726,7 @@
       </c>
       <c r="K416" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L416" s="3" t="inlineStr"/>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="K417" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L417" s="6" t="inlineStr"/>
@@ -20822,7 +20822,7 @@
       </c>
       <c r="K418" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L418" s="3" t="inlineStr"/>
@@ -20870,7 +20870,7 @@
       </c>
       <c r="K419" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L419" s="6" t="inlineStr"/>
@@ -20918,7 +20918,7 @@
       </c>
       <c r="K420" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L420" s="3" t="inlineStr"/>
@@ -20966,7 +20966,7 @@
       </c>
       <c r="K421" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L421" s="6" t="inlineStr"/>
@@ -21014,7 +21014,7 @@
       </c>
       <c r="K422" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L422" s="3" t="inlineStr"/>
@@ -21062,7 +21062,7 @@
       </c>
       <c r="K423" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L423" s="6" t="inlineStr"/>
@@ -21110,7 +21110,7 @@
       </c>
       <c r="K424" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L424" s="3" t="inlineStr"/>
@@ -21158,7 +21158,7 @@
       </c>
       <c r="K425" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L425" s="6" t="inlineStr"/>
@@ -21206,7 +21206,7 @@
       </c>
       <c r="K426" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L426" s="3" t="inlineStr"/>
@@ -21254,7 +21254,7 @@
       </c>
       <c r="K427" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L427" s="6" t="inlineStr"/>
@@ -21302,7 +21302,7 @@
       </c>
       <c r="K428" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L428" s="3" t="inlineStr"/>
@@ -21350,7 +21350,7 @@
       </c>
       <c r="K429" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L429" s="6" t="inlineStr"/>
@@ -21398,7 +21398,7 @@
       </c>
       <c r="K430" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L430" s="3" t="inlineStr"/>
@@ -21446,7 +21446,7 @@
       </c>
       <c r="K431" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L431" s="6" t="inlineStr"/>
@@ -21494,7 +21494,7 @@
       </c>
       <c r="K432" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L432" s="3" t="inlineStr"/>
@@ -21542,7 +21542,7 @@
       </c>
       <c r="K433" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L433" s="6" t="inlineStr"/>
@@ -21590,7 +21590,7 @@
       </c>
       <c r="K434" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L434" s="3" t="inlineStr"/>
@@ -21638,7 +21638,7 @@
       </c>
       <c r="K435" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L435" s="6" t="inlineStr"/>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="K436" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L436" s="3" t="inlineStr"/>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="K437" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L437" s="6" t="inlineStr"/>
@@ -21782,7 +21782,7 @@
       </c>
       <c r="K438" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L438" s="3" t="inlineStr"/>
@@ -21830,7 +21830,7 @@
       </c>
       <c r="K439" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L439" s="6" t="inlineStr"/>
@@ -21878,7 +21878,7 @@
       </c>
       <c r="K440" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L440" s="3" t="inlineStr"/>
@@ -21926,7 +21926,7 @@
       </c>
       <c r="K441" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L441" s="6" t="inlineStr"/>
@@ -21974,7 +21974,7 @@
       </c>
       <c r="K442" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L442" s="3" t="inlineStr"/>
@@ -22022,7 +22022,7 @@
       </c>
       <c r="K443" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L443" s="6" t="inlineStr"/>
@@ -22070,7 +22070,7 @@
       </c>
       <c r="K444" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L444" s="3" t="inlineStr"/>
@@ -22118,7 +22118,7 @@
       </c>
       <c r="K445" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L445" s="6" t="inlineStr"/>
@@ -22166,7 +22166,7 @@
       </c>
       <c r="K446" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L446" s="3" t="inlineStr"/>
@@ -22214,7 +22214,7 @@
       </c>
       <c r="K447" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L447" s="6" t="inlineStr"/>
@@ -22262,7 +22262,7 @@
       </c>
       <c r="K448" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L448" s="3" t="inlineStr"/>
@@ -22310,7 +22310,7 @@
       </c>
       <c r="K449" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L449" s="6" t="inlineStr"/>
@@ -22358,7 +22358,7 @@
       </c>
       <c r="K450" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L450" s="3" t="inlineStr"/>
@@ -22406,7 +22406,7 @@
       </c>
       <c r="K451" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L451" s="6" t="inlineStr"/>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="K452" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L452" s="3" t="inlineStr"/>
@@ -22502,7 +22502,7 @@
       </c>
       <c r="K453" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L453" s="6" t="inlineStr"/>
@@ -22550,7 +22550,7 @@
       </c>
       <c r="K454" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L454" s="3" t="inlineStr"/>
@@ -22598,7 +22598,7 @@
       </c>
       <c r="K455" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L455" s="6" t="inlineStr"/>
@@ -22646,7 +22646,7 @@
       </c>
       <c r="K456" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L456" s="3" t="inlineStr"/>
@@ -22694,7 +22694,7 @@
       </c>
       <c r="K457" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L457" s="6" t="inlineStr"/>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="K458" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L458" s="3" t="inlineStr"/>
@@ -22790,7 +22790,7 @@
       </c>
       <c r="K459" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L459" s="6" t="inlineStr"/>
@@ -22838,7 +22838,7 @@
       </c>
       <c r="K460" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L460" s="3" t="inlineStr"/>
@@ -22886,7 +22886,7 @@
       </c>
       <c r="K461" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L461" s="6" t="inlineStr"/>
@@ -22934,7 +22934,7 @@
       </c>
       <c r="K462" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L462" s="3" t="inlineStr"/>
@@ -22982,7 +22982,7 @@
       </c>
       <c r="K463" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L463" s="6" t="inlineStr"/>
@@ -23030,7 +23030,7 @@
       </c>
       <c r="K464" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L464" s="3" t="inlineStr"/>
@@ -23078,7 +23078,7 @@
       </c>
       <c r="K465" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L465" s="6" t="inlineStr"/>
@@ -23126,7 +23126,7 @@
       </c>
       <c r="K466" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L466" s="3" t="inlineStr"/>
@@ -23174,7 +23174,7 @@
       </c>
       <c r="K467" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L467" s="6" t="inlineStr"/>
@@ -23222,7 +23222,7 @@
       </c>
       <c r="K468" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L468" s="3" t="inlineStr"/>
@@ -23270,7 +23270,7 @@
       </c>
       <c r="K469" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L469" s="6" t="inlineStr"/>
@@ -23318,7 +23318,7 @@
       </c>
       <c r="K470" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L470" s="3" t="inlineStr"/>
@@ -23366,7 +23366,7 @@
       </c>
       <c r="K471" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L471" s="6" t="inlineStr"/>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="K472" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L472" s="3" t="inlineStr"/>
@@ -23462,7 +23462,7 @@
       </c>
       <c r="K473" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L473" s="6" t="inlineStr"/>
@@ -23510,7 +23510,7 @@
       </c>
       <c r="K474" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L474" s="3" t="inlineStr"/>
@@ -23558,7 +23558,7 @@
       </c>
       <c r="K475" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L475" s="6" t="inlineStr"/>
@@ -23606,7 +23606,7 @@
       </c>
       <c r="K476" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L476" s="3" t="inlineStr"/>
@@ -23654,7 +23654,7 @@
       </c>
       <c r="K477" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L477" s="6" t="inlineStr"/>
@@ -23702,7 +23702,7 @@
       </c>
       <c r="K478" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L478" s="3" t="inlineStr"/>
@@ -23750,7 +23750,7 @@
       </c>
       <c r="K479" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L479" s="6" t="inlineStr"/>
@@ -23798,7 +23798,7 @@
       </c>
       <c r="K480" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L480" s="3" t="inlineStr"/>
@@ -23846,7 +23846,7 @@
       </c>
       <c r="K481" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L481" s="6" t="inlineStr"/>
@@ -23894,7 +23894,7 @@
       </c>
       <c r="K482" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L482" s="3" t="inlineStr"/>
@@ -23942,7 +23942,7 @@
       </c>
       <c r="K483" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L483" s="6" t="inlineStr"/>
@@ -23990,7 +23990,7 @@
       </c>
       <c r="K484" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L484" s="3" t="inlineStr"/>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="K485" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L485" s="6" t="inlineStr"/>
@@ -24086,7 +24086,7 @@
       </c>
       <c r="K486" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L486" s="3" t="inlineStr"/>
@@ -24134,7 +24134,7 @@
       </c>
       <c r="K487" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L487" s="6" t="inlineStr"/>
@@ -24182,7 +24182,7 @@
       </c>
       <c r="K488" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L488" s="3" t="inlineStr"/>
@@ -24230,7 +24230,7 @@
       </c>
       <c r="K489" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L489" s="6" t="inlineStr"/>
@@ -24278,7 +24278,7 @@
       </c>
       <c r="K490" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L490" s="3" t="inlineStr"/>
@@ -24326,7 +24326,7 @@
       </c>
       <c r="K491" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L491" s="6" t="inlineStr"/>
@@ -24374,7 +24374,7 @@
       </c>
       <c r="K492" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L492" s="3" t="inlineStr"/>
@@ -24422,7 +24422,7 @@
       </c>
       <c r="K493" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L493" s="6" t="inlineStr"/>
@@ -24470,7 +24470,7 @@
       </c>
       <c r="K494" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L494" s="3" t="inlineStr"/>
@@ -24518,7 +24518,7 @@
       </c>
       <c r="K495" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L495" s="6" t="inlineStr"/>
@@ -24566,7 +24566,7 @@
       </c>
       <c r="K496" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L496" s="3" t="inlineStr"/>
@@ -24614,7 +24614,7 @@
       </c>
       <c r="K497" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L497" s="6" t="inlineStr"/>
@@ -24662,7 +24662,7 @@
       </c>
       <c r="K498" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L498" s="3" t="inlineStr"/>
@@ -24710,7 +24710,7 @@
       </c>
       <c r="K499" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L499" s="6" t="inlineStr"/>
@@ -24758,7 +24758,7 @@
       </c>
       <c r="K500" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L500" s="3" t="inlineStr"/>
@@ -24806,7 +24806,7 @@
       </c>
       <c r="K501" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L501" s="6" t="inlineStr"/>
@@ -24854,7 +24854,7 @@
       </c>
       <c r="K502" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L502" s="3" t="inlineStr"/>
@@ -24902,7 +24902,7 @@
       </c>
       <c r="K503" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L503" s="6" t="inlineStr"/>
@@ -24950,7 +24950,7 @@
       </c>
       <c r="K504" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L504" s="3" t="inlineStr"/>
@@ -24998,7 +24998,7 @@
       </c>
       <c r="K505" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L505" s="6" t="inlineStr"/>
@@ -25046,7 +25046,7 @@
       </c>
       <c r="K506" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L506" s="3" t="inlineStr"/>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="K507" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L507" s="6" t="inlineStr"/>
@@ -25142,7 +25142,7 @@
       </c>
       <c r="K508" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L508" s="3" t="inlineStr"/>
@@ -25190,7 +25190,7 @@
       </c>
       <c r="K509" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L509" s="6" t="inlineStr"/>
@@ -25238,7 +25238,7 @@
       </c>
       <c r="K510" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L510" s="3" t="inlineStr"/>
@@ -25286,7 +25286,7 @@
       </c>
       <c r="K511" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L511" s="6" t="inlineStr"/>
@@ -25334,7 +25334,7 @@
       </c>
       <c r="K512" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L512" s="3" t="inlineStr"/>
@@ -25382,7 +25382,7 @@
       </c>
       <c r="K513" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L513" s="6" t="inlineStr"/>
@@ -25430,7 +25430,7 @@
       </c>
       <c r="K514" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L514" s="3" t="inlineStr"/>
@@ -25478,7 +25478,7 @@
       </c>
       <c r="K515" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L515" s="6" t="inlineStr"/>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="K516" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L516" s="3" t="inlineStr"/>
@@ -25574,7 +25574,7 @@
       </c>
       <c r="K517" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L517" s="6" t="inlineStr"/>
@@ -25622,7 +25622,7 @@
       </c>
       <c r="K518" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L518" s="3" t="inlineStr"/>
@@ -25670,7 +25670,7 @@
       </c>
       <c r="K519" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L519" s="6" t="inlineStr"/>
@@ -25718,7 +25718,7 @@
       </c>
       <c r="K520" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L520" s="3" t="inlineStr"/>
@@ -25766,7 +25766,7 @@
       </c>
       <c r="K521" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L521" s="6" t="inlineStr"/>
@@ -25814,7 +25814,7 @@
       </c>
       <c r="K522" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L522" s="3" t="inlineStr"/>
@@ -25862,7 +25862,7 @@
       </c>
       <c r="K523" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L523" s="6" t="inlineStr"/>
@@ -25910,7 +25910,7 @@
       </c>
       <c r="K524" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L524" s="3" t="inlineStr"/>
@@ -25958,7 +25958,7 @@
       </c>
       <c r="K525" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L525" s="6" t="inlineStr"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K526" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L526" s="3" t="inlineStr"/>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="K527" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L527" s="6" t="inlineStr"/>
@@ -26102,7 +26102,7 @@
       </c>
       <c r="K528" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L528" s="3" t="inlineStr"/>
@@ -26150,7 +26150,7 @@
       </c>
       <c r="K529" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L529" s="6" t="inlineStr"/>
@@ -26198,7 +26198,7 @@
       </c>
       <c r="K530" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L530" s="3" t="inlineStr"/>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="K531" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L531" s="6" t="inlineStr"/>
@@ -26294,7 +26294,7 @@
       </c>
       <c r="K532" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L532" s="3" t="inlineStr"/>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="K533" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L533" s="6" t="inlineStr"/>
@@ -26390,7 +26390,7 @@
       </c>
       <c r="K534" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L534" s="3" t="inlineStr"/>
@@ -26438,7 +26438,7 @@
       </c>
       <c r="K535" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L535" s="6" t="inlineStr"/>
@@ -26486,7 +26486,7 @@
       </c>
       <c r="K536" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L536" s="3" t="inlineStr"/>
@@ -26534,7 +26534,7 @@
       </c>
       <c r="K537" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L537" s="6" t="inlineStr"/>
@@ -26582,7 +26582,7 @@
       </c>
       <c r="K538" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L538" s="3" t="inlineStr"/>
@@ -26630,7 +26630,7 @@
       </c>
       <c r="K539" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L539" s="6" t="inlineStr"/>
@@ -26678,7 +26678,7 @@
       </c>
       <c r="K540" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L540" s="3" t="inlineStr"/>
@@ -26726,7 +26726,7 @@
       </c>
       <c r="K541" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L541" s="6" t="inlineStr"/>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="K542" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L542" s="3" t="inlineStr"/>
@@ -26822,7 +26822,7 @@
       </c>
       <c r="K543" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L543" s="6" t="inlineStr"/>
@@ -26870,7 +26870,7 @@
       </c>
       <c r="K544" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L544" s="3" t="inlineStr"/>
@@ -26918,7 +26918,7 @@
       </c>
       <c r="K545" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L545" s="6" t="inlineStr"/>
@@ -26966,7 +26966,7 @@
       </c>
       <c r="K546" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L546" s="3" t="inlineStr"/>
@@ -27014,7 +27014,7 @@
       </c>
       <c r="K547" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L547" s="6" t="inlineStr"/>
@@ -27062,7 +27062,7 @@
       </c>
       <c r="K548" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L548" s="3" t="inlineStr"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K549" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L549" s="6" t="inlineStr"/>
@@ -27158,7 +27158,7 @@
       </c>
       <c r="K550" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L550" s="3" t="inlineStr"/>
@@ -27206,7 +27206,7 @@
       </c>
       <c r="K551" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L551" s="6" t="inlineStr"/>
@@ -27254,7 +27254,7 @@
       </c>
       <c r="K552" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L552" s="3" t="inlineStr"/>
@@ -27302,7 +27302,7 @@
       </c>
       <c r="K553" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L553" s="6" t="inlineStr"/>
@@ -27350,7 +27350,7 @@
       </c>
       <c r="K554" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L554" s="3" t="inlineStr"/>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="K555" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L555" s="6" t="inlineStr"/>
@@ -27446,7 +27446,7 @@
       </c>
       <c r="K556" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L556" s="3" t="inlineStr"/>
@@ -27494,7 +27494,7 @@
       </c>
       <c r="K557" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L557" s="6" t="inlineStr"/>
@@ -27542,7 +27542,7 @@
       </c>
       <c r="K558" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L558" s="3" t="inlineStr"/>
@@ -27590,7 +27590,7 @@
       </c>
       <c r="K559" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L559" s="6" t="inlineStr"/>
@@ -27638,7 +27638,7 @@
       </c>
       <c r="K560" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L560" s="3" t="inlineStr"/>
@@ -27686,7 +27686,7 @@
       </c>
       <c r="K561" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L561" s="6" t="inlineStr"/>
@@ -27734,7 +27734,7 @@
       </c>
       <c r="K562" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L562" s="3" t="inlineStr"/>
@@ -27782,7 +27782,7 @@
       </c>
       <c r="K563" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L563" s="6" t="inlineStr"/>
@@ -27830,7 +27830,7 @@
       </c>
       <c r="K564" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L564" s="3" t="inlineStr"/>
@@ -27878,7 +27878,7 @@
       </c>
       <c r="K565" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L565" s="6" t="inlineStr"/>
@@ -27926,7 +27926,7 @@
       </c>
       <c r="K566" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L566" s="3" t="inlineStr"/>
@@ -27974,7 +27974,7 @@
       </c>
       <c r="K567" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L567" s="6" t="inlineStr"/>
@@ -28022,7 +28022,7 @@
       </c>
       <c r="K568" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L568" s="3" t="inlineStr"/>
@@ -28070,7 +28070,7 @@
       </c>
       <c r="K569" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L569" s="6" t="inlineStr"/>
@@ -28118,7 +28118,7 @@
       </c>
       <c r="K570" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L570" s="3" t="inlineStr"/>
@@ -28166,7 +28166,7 @@
       </c>
       <c r="K571" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L571" s="6" t="inlineStr"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K572" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L572" s="3" t="inlineStr"/>
@@ -28262,7 +28262,7 @@
       </c>
       <c r="K573" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L573" s="6" t="inlineStr"/>
@@ -28310,7 +28310,7 @@
       </c>
       <c r="K574" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L574" s="3" t="inlineStr"/>
@@ -28358,7 +28358,7 @@
       </c>
       <c r="K575" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L575" s="6" t="inlineStr"/>
@@ -28406,7 +28406,7 @@
       </c>
       <c r="K576" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L576" s="3" t="inlineStr"/>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="K577" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L577" s="6" t="inlineStr"/>
@@ -28502,7 +28502,7 @@
       </c>
       <c r="K578" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L578" s="3" t="inlineStr"/>
@@ -28550,7 +28550,7 @@
       </c>
       <c r="K579" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L579" s="6" t="inlineStr"/>
@@ -28598,7 +28598,7 @@
       </c>
       <c r="K580" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L580" s="3" t="inlineStr"/>
@@ -28646,7 +28646,7 @@
       </c>
       <c r="K581" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L581" s="6" t="inlineStr"/>
@@ -28694,7 +28694,7 @@
       </c>
       <c r="K582" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L582" s="3" t="inlineStr"/>
@@ -28742,7 +28742,7 @@
       </c>
       <c r="K583" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L583" s="6" t="inlineStr"/>
@@ -28790,7 +28790,7 @@
       </c>
       <c r="K584" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L584" s="3" t="inlineStr"/>
@@ -28838,7 +28838,7 @@
       </c>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L585" s="6" t="inlineStr"/>
@@ -28886,7 +28886,7 @@
       </c>
       <c r="K586" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L586" s="3" t="inlineStr"/>
@@ -28934,7 +28934,7 @@
       </c>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L587" s="6" t="inlineStr"/>
@@ -28982,7 +28982,7 @@
       </c>
       <c r="K588" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L588" s="3" t="inlineStr"/>
@@ -29030,7 +29030,7 @@
       </c>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L589" s="6" t="inlineStr"/>
@@ -29078,7 +29078,7 @@
       </c>
       <c r="K590" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L590" s="3" t="inlineStr"/>
@@ -29126,7 +29126,7 @@
       </c>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L591" s="6" t="inlineStr"/>
@@ -29174,7 +29174,7 @@
       </c>
       <c r="K592" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L592" s="3" t="inlineStr"/>
@@ -29222,7 +29222,7 @@
       </c>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L593" s="6" t="inlineStr"/>
@@ -29270,7 +29270,7 @@
       </c>
       <c r="K594" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L594" s="3" t="inlineStr"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L595" s="6" t="inlineStr"/>
@@ -29366,7 +29366,7 @@
       </c>
       <c r="K596" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L596" s="3" t="inlineStr"/>
@@ -29414,7 +29414,7 @@
       </c>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L597" s="6" t="inlineStr"/>
@@ -29462,7 +29462,7 @@
       </c>
       <c r="K598" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L598" s="3" t="inlineStr"/>
@@ -29510,7 +29510,7 @@
       </c>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L599" s="6" t="inlineStr"/>
@@ -29558,7 +29558,7 @@
       </c>
       <c r="K600" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L600" s="3" t="inlineStr"/>
@@ -29606,7 +29606,7 @@
       </c>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L601" s="6" t="inlineStr"/>
@@ -29654,7 +29654,7 @@
       </c>
       <c r="K602" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L602" s="3" t="inlineStr"/>
@@ -29702,7 +29702,7 @@
       </c>
       <c r="K603" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L603" s="6" t="inlineStr"/>
@@ -29750,7 +29750,7 @@
       </c>
       <c r="K604" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L604" s="3" t="inlineStr"/>
@@ -29798,7 +29798,7 @@
       </c>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr"/>
@@ -29846,7 +29846,7 @@
       </c>
       <c r="K606" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L606" s="3" t="inlineStr"/>
@@ -29894,7 +29894,7 @@
       </c>
       <c r="K607" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L607" s="6" t="inlineStr"/>
@@ -29942,7 +29942,7 @@
       </c>
       <c r="K608" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L608" s="3" t="inlineStr"/>
@@ -29990,7 +29990,7 @@
       </c>
       <c r="K609" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L609" s="6" t="inlineStr"/>
@@ -30038,7 +30038,7 @@
       </c>
       <c r="K610" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L610" s="3" t="inlineStr"/>
@@ -30086,7 +30086,7 @@
       </c>
       <c r="K611" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L611" s="6" t="inlineStr"/>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="K612" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L612" s="3" t="inlineStr"/>
@@ -30182,7 +30182,7 @@
       </c>
       <c r="K613" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L613" s="6" t="inlineStr"/>
@@ -30230,7 +30230,7 @@
       </c>
       <c r="K614" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L614" s="3" t="inlineStr"/>
@@ -30278,7 +30278,7 @@
       </c>
       <c r="K615" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L615" s="6" t="inlineStr"/>
@@ -30326,7 +30326,7 @@
       </c>
       <c r="K616" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L616" s="3" t="inlineStr"/>
@@ -30374,7 +30374,7 @@
       </c>
       <c r="K617" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L617" s="6" t="inlineStr"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K618" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L618" s="3" t="inlineStr"/>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="K619" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L619" s="6" t="inlineStr"/>
@@ -30518,7 +30518,7 @@
       </c>
       <c r="K620" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L620" s="3" t="inlineStr"/>
@@ -30566,7 +30566,7 @@
       </c>
       <c r="K621" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L621" s="6" t="inlineStr"/>
@@ -30614,7 +30614,7 @@
       </c>
       <c r="K622" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L622" s="3" t="inlineStr"/>
@@ -30662,7 +30662,7 @@
       </c>
       <c r="K623" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L623" s="6" t="inlineStr"/>
@@ -30710,7 +30710,7 @@
       </c>
       <c r="K624" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L624" s="3" t="inlineStr"/>
@@ -30758,7 +30758,7 @@
       </c>
       <c r="K625" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L625" s="6" t="inlineStr"/>
@@ -30806,7 +30806,7 @@
       </c>
       <c r="K626" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L626" s="3" t="inlineStr"/>
@@ -30854,7 +30854,7 @@
       </c>
       <c r="K627" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L627" s="6" t="inlineStr"/>
@@ -30902,7 +30902,7 @@
       </c>
       <c r="K628" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L628" s="3" t="inlineStr"/>
@@ -30950,7 +30950,7 @@
       </c>
       <c r="K629" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L629" s="6" t="inlineStr"/>
@@ -30998,7 +30998,7 @@
       </c>
       <c r="K630" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L630" s="3" t="inlineStr"/>
@@ -31046,7 +31046,7 @@
       </c>
       <c r="K631" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L631" s="6" t="inlineStr"/>
@@ -31094,7 +31094,7 @@
       </c>
       <c r="K632" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L632" s="3" t="inlineStr"/>
@@ -31142,7 +31142,7 @@
       </c>
       <c r="K633" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L633" s="6" t="inlineStr"/>
@@ -31190,7 +31190,7 @@
       </c>
       <c r="K634" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L634" s="3" t="inlineStr"/>
@@ -31238,7 +31238,7 @@
       </c>
       <c r="K635" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L635" s="6" t="inlineStr"/>
@@ -31286,7 +31286,7 @@
       </c>
       <c r="K636" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L636" s="3" t="inlineStr"/>
@@ -31334,7 +31334,7 @@
       </c>
       <c r="K637" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L637" s="6" t="inlineStr"/>
@@ -31382,7 +31382,7 @@
       </c>
       <c r="K638" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L638" s="3" t="inlineStr"/>
@@ -31430,7 +31430,7 @@
       </c>
       <c r="K639" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L639" s="6" t="inlineStr"/>
@@ -31478,7 +31478,7 @@
       </c>
       <c r="K640" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L640" s="3" t="inlineStr"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K641" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L641" s="6" t="inlineStr"/>
@@ -31574,7 +31574,7 @@
       </c>
       <c r="K642" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L642" s="3" t="inlineStr"/>
@@ -31622,7 +31622,7 @@
       </c>
       <c r="K643" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L643" s="6" t="inlineStr"/>
@@ -31670,7 +31670,7 @@
       </c>
       <c r="K644" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L644" s="3" t="inlineStr"/>
@@ -31718,7 +31718,7 @@
       </c>
       <c r="K645" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L645" s="6" t="inlineStr"/>
@@ -31766,7 +31766,7 @@
       </c>
       <c r="K646" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L646" s="3" t="inlineStr"/>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="K647" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L647" s="6" t="inlineStr"/>
@@ -31862,7 +31862,7 @@
       </c>
       <c r="K648" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L648" s="3" t="inlineStr"/>
@@ -31910,7 +31910,7 @@
       </c>
       <c r="K649" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L649" s="6" t="inlineStr"/>
@@ -31958,7 +31958,7 @@
       </c>
       <c r="K650" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L650" s="3" t="inlineStr"/>
@@ -32006,7 +32006,7 @@
       </c>
       <c r="K651" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L651" s="6" t="inlineStr"/>
@@ -32054,7 +32054,7 @@
       </c>
       <c r="K652" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L652" s="3" t="inlineStr"/>
@@ -32102,7 +32102,7 @@
       </c>
       <c r="K653" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L653" s="6" t="inlineStr"/>
@@ -32150,7 +32150,7 @@
       </c>
       <c r="K654" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L654" s="3" t="inlineStr"/>
@@ -32198,7 +32198,7 @@
       </c>
       <c r="K655" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L655" s="6" t="inlineStr"/>
@@ -32246,7 +32246,7 @@
       </c>
       <c r="K656" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L656" s="3" t="inlineStr"/>
@@ -32294,7 +32294,7 @@
       </c>
       <c r="K657" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L657" s="6" t="inlineStr"/>
@@ -32342,7 +32342,7 @@
       </c>
       <c r="K658" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L658" s="3" t="inlineStr"/>
@@ -32390,7 +32390,7 @@
       </c>
       <c r="K659" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L659" s="6" t="inlineStr"/>
@@ -32438,7 +32438,7 @@
       </c>
       <c r="K660" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L660" s="3" t="inlineStr"/>
@@ -32486,7 +32486,7 @@
       </c>
       <c r="K661" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L661" s="6" t="inlineStr"/>
@@ -32534,7 +32534,7 @@
       </c>
       <c r="K662" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L662" s="3" t="inlineStr"/>
@@ -32582,7 +32582,7 @@
       </c>
       <c r="K663" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L663" s="6" t="inlineStr"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K664" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L664" s="3" t="inlineStr"/>
@@ -32678,7 +32678,7 @@
       </c>
       <c r="K665" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L665" s="6" t="inlineStr"/>
@@ -32726,7 +32726,7 @@
       </c>
       <c r="K666" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L666" s="3" t="inlineStr"/>
@@ -32774,7 +32774,7 @@
       </c>
       <c r="K667" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L667" s="6" t="inlineStr"/>
@@ -32822,7 +32822,7 @@
       </c>
       <c r="K668" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L668" s="3" t="inlineStr"/>
@@ -32870,7 +32870,7 @@
       </c>
       <c r="K669" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L669" s="6" t="inlineStr"/>
@@ -32918,7 +32918,7 @@
       </c>
       <c r="K670" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L670" s="3" t="inlineStr"/>
@@ -32966,7 +32966,7 @@
       </c>
       <c r="K671" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L671" s="6" t="inlineStr"/>
@@ -33014,7 +33014,7 @@
       </c>
       <c r="K672" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L672" s="3" t="inlineStr"/>
@@ -33062,7 +33062,7 @@
       </c>
       <c r="K673" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L673" s="6" t="inlineStr"/>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="K674" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L674" s="3" t="inlineStr"/>
@@ -33158,7 +33158,7 @@
       </c>
       <c r="K675" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L675" s="6" t="inlineStr"/>
@@ -33206,7 +33206,7 @@
       </c>
       <c r="K676" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L676" s="3" t="inlineStr"/>
@@ -33254,7 +33254,7 @@
       </c>
       <c r="K677" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L677" s="6" t="inlineStr"/>
@@ -33302,7 +33302,7 @@
       </c>
       <c r="K678" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L678" s="3" t="inlineStr"/>
@@ -33350,7 +33350,7 @@
       </c>
       <c r="K679" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L679" s="6" t="inlineStr"/>
@@ -33398,7 +33398,7 @@
       </c>
       <c r="K680" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L680" s="3" t="inlineStr"/>
@@ -33446,7 +33446,7 @@
       </c>
       <c r="K681" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L681" s="6" t="inlineStr"/>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="K682" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L682" s="3" t="inlineStr"/>
@@ -33542,7 +33542,7 @@
       </c>
       <c r="K683" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L683" s="6" t="inlineStr"/>
@@ -33590,7 +33590,7 @@
       </c>
       <c r="K684" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L684" s="3" t="inlineStr"/>
@@ -33638,7 +33638,7 @@
       </c>
       <c r="K685" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L685" s="6" t="inlineStr"/>
@@ -33686,7 +33686,7 @@
       </c>
       <c r="K686" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L686" s="3" t="inlineStr"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K687" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L687" s="6" t="inlineStr"/>
@@ -33782,7 +33782,7 @@
       </c>
       <c r="K688" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L688" s="3" t="inlineStr"/>
@@ -33830,7 +33830,7 @@
       </c>
       <c r="K689" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L689" s="6" t="inlineStr"/>
@@ -33878,7 +33878,7 @@
       </c>
       <c r="K690" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L690" s="3" t="inlineStr"/>
@@ -33926,7 +33926,7 @@
       </c>
       <c r="K691" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L691" s="6" t="inlineStr"/>
@@ -33974,7 +33974,7 @@
       </c>
       <c r="K692" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L692" s="3" t="inlineStr"/>
@@ -34022,7 +34022,7 @@
       </c>
       <c r="K693" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L693" s="6" t="inlineStr"/>
@@ -34070,7 +34070,7 @@
       </c>
       <c r="K694" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L694" s="3" t="inlineStr"/>
@@ -34118,7 +34118,7 @@
       </c>
       <c r="K695" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L695" s="6" t="inlineStr"/>
@@ -34166,7 +34166,7 @@
       </c>
       <c r="K696" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L696" s="3" t="inlineStr"/>
@@ -34214,7 +34214,7 @@
       </c>
       <c r="K697" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L697" s="6" t="inlineStr"/>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="K698" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L698" s="3" t="inlineStr"/>
@@ -34310,7 +34310,7 @@
       </c>
       <c r="K699" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L699" s="6" t="inlineStr"/>
@@ -34358,7 +34358,7 @@
       </c>
       <c r="K700" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L700" s="3" t="inlineStr"/>
@@ -34406,7 +34406,7 @@
       </c>
       <c r="K701" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L701" s="6" t="inlineStr"/>
@@ -34454,7 +34454,7 @@
       </c>
       <c r="K702" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L702" s="3" t="inlineStr"/>
@@ -34502,7 +34502,7 @@
       </c>
       <c r="K703" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L703" s="6" t="inlineStr"/>
@@ -34550,7 +34550,7 @@
       </c>
       <c r="K704" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L704" s="3" t="inlineStr"/>
@@ -34598,7 +34598,7 @@
       </c>
       <c r="K705" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L705" s="6" t="inlineStr"/>
@@ -34646,7 +34646,7 @@
       </c>
       <c r="K706" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L706" s="3" t="inlineStr"/>
@@ -34694,7 +34694,7 @@
       </c>
       <c r="K707" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L707" s="6" t="inlineStr"/>
@@ -34742,7 +34742,7 @@
       </c>
       <c r="K708" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L708" s="3" t="inlineStr"/>
@@ -34790,7 +34790,7 @@
       </c>
       <c r="K709" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L709" s="6" t="inlineStr"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K710" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L710" s="3" t="inlineStr"/>
@@ -34886,7 +34886,7 @@
       </c>
       <c r="K711" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L711" s="6" t="inlineStr"/>
@@ -34934,7 +34934,7 @@
       </c>
       <c r="K712" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L712" s="3" t="inlineStr"/>
@@ -34982,7 +34982,7 @@
       </c>
       <c r="K713" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L713" s="6" t="inlineStr"/>
@@ -35030,7 +35030,7 @@
       </c>
       <c r="K714" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L714" s="3" t="inlineStr"/>
@@ -35078,7 +35078,7 @@
       </c>
       <c r="K715" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L715" s="6" t="inlineStr"/>
@@ -35126,7 +35126,7 @@
       </c>
       <c r="K716" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L716" s="3" t="inlineStr"/>
@@ -35174,7 +35174,7 @@
       </c>
       <c r="K717" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L717" s="6" t="inlineStr"/>
@@ -35222,7 +35222,7 @@
       </c>
       <c r="K718" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L718" s="3" t="inlineStr"/>
@@ -35270,7 +35270,7 @@
       </c>
       <c r="K719" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L719" s="6" t="inlineStr"/>
@@ -35318,7 +35318,7 @@
       </c>
       <c r="K720" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L720" s="3" t="inlineStr"/>
@@ -35366,7 +35366,7 @@
       </c>
       <c r="K721" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L721" s="6" t="inlineStr"/>
@@ -35414,7 +35414,7 @@
       </c>
       <c r="K722" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L722" s="3" t="inlineStr"/>
@@ -35462,7 +35462,7 @@
       </c>
       <c r="K723" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L723" s="6" t="inlineStr"/>
@@ -35510,7 +35510,7 @@
       </c>
       <c r="K724" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L724" s="3" t="inlineStr"/>
@@ -35558,7 +35558,7 @@
       </c>
       <c r="K725" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L725" s="6" t="inlineStr"/>
@@ -35606,7 +35606,7 @@
       </c>
       <c r="K726" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L726" s="3" t="inlineStr"/>
@@ -35654,7 +35654,7 @@
       </c>
       <c r="K727" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L727" s="6" t="inlineStr"/>
@@ -35702,7 +35702,7 @@
       </c>
       <c r="K728" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L728" s="3" t="inlineStr"/>
@@ -35750,7 +35750,7 @@
       </c>
       <c r="K729" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L729" s="4" t="inlineStr">
@@ -35802,7 +35802,7 @@
       </c>
       <c r="K730" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L730" s="4" t="inlineStr">
@@ -35854,7 +35854,7 @@
       </c>
       <c r="K731" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L731" s="4" t="inlineStr">
@@ -35906,7 +35906,7 @@
       </c>
       <c r="K732" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L732" s="4" t="inlineStr">
@@ -35958,7 +35958,7 @@
       </c>
       <c r="K733" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L733" s="4" t="inlineStr">
@@ -36010,7 +36010,7 @@
       </c>
       <c r="K734" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L734" s="4" t="inlineStr">
@@ -36062,7 +36062,7 @@
       </c>
       <c r="K735" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L735" s="4" t="inlineStr">
@@ -36114,7 +36114,7 @@
       </c>
       <c r="K736" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L736" s="4" t="inlineStr">
@@ -36166,7 +36166,7 @@
       </c>
       <c r="K737" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L737" s="4" t="inlineStr">
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K738" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L738" s="4" t="inlineStr">
@@ -36270,7 +36270,7 @@
       </c>
       <c r="K739" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L739" s="4" t="inlineStr">
@@ -36322,7 +36322,7 @@
       </c>
       <c r="K740" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L740" s="4" t="inlineStr">
@@ -36374,7 +36374,7 @@
       </c>
       <c r="K741" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L741" s="4" t="inlineStr">
@@ -36426,7 +36426,7 @@
       </c>
       <c r="K742" s="3" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L742" s="4" t="inlineStr">
@@ -36478,7 +36478,7 @@
       </c>
       <c r="K743" s="6" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="L743" s="4" t="inlineStr">

--- a/public/loop-library.xlsx
+++ b/public/loop-library.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr"/>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr"/>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr"/>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr"/>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr"/>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr"/>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr"/>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr"/>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr"/>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr"/>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr"/>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr"/>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr"/>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr"/>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr"/>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr"/>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr"/>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr"/>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr"/>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr"/>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L93" s="6" t="inlineStr"/>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr"/>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L95" s="6" t="inlineStr"/>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr"/>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L97" s="6" t="inlineStr"/>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr"/>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr"/>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr"/>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr"/>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L102" s="3" t="inlineStr"/>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L103" s="6" t="inlineStr"/>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L104" s="3" t="inlineStr"/>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L105" s="6" t="inlineStr"/>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L106" s="3" t="inlineStr"/>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L107" s="6" t="inlineStr"/>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L108" s="3" t="inlineStr"/>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L109" s="6" t="inlineStr"/>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L110" s="3" t="inlineStr"/>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L111" s="6" t="inlineStr"/>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L112" s="3" t="inlineStr"/>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L113" s="6" t="inlineStr"/>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L114" s="3" t="inlineStr"/>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L115" s="6" t="inlineStr"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="K116" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L116" s="3" t="inlineStr"/>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L117" s="6" t="inlineStr"/>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="K118" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L118" s="3" t="inlineStr"/>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L119" s="6" t="inlineStr"/>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="K120" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L120" s="3" t="inlineStr"/>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L121" s="6" t="inlineStr"/>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="K122" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L122" s="3" t="inlineStr"/>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L123" s="6" t="inlineStr"/>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="K124" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L124" s="3" t="inlineStr"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="K125" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L125" s="6" t="inlineStr"/>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="K126" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L126" s="3" t="inlineStr"/>
@@ -6854,7 +6854,7 @@
       </c>
       <c r="K127" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L127" s="6" t="inlineStr"/>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L128" s="3" t="inlineStr"/>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="K129" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L129" s="6" t="inlineStr"/>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="K130" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L130" s="3" t="inlineStr"/>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="K131" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L131" s="6" t="inlineStr"/>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L132" s="3" t="inlineStr"/>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="K133" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L133" s="6" t="inlineStr"/>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="K134" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L134" s="3" t="inlineStr"/>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="K135" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L135" s="6" t="inlineStr"/>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="K136" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L136" s="3" t="inlineStr"/>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="K137" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L137" s="6" t="inlineStr"/>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="K138" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L138" s="3" t="inlineStr"/>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="K139" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L139" s="6" t="inlineStr"/>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="K140" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L140" s="3" t="inlineStr"/>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="K141" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L141" s="6" t="inlineStr"/>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L142" s="3" t="inlineStr"/>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="K143" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L143" s="6" t="inlineStr"/>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="K144" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L144" s="3" t="inlineStr"/>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="K145" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L145" s="6" t="inlineStr"/>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="K146" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L146" s="3" t="inlineStr"/>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="K147" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L147" s="6" t="inlineStr"/>
@@ -7862,7 +7862,7 @@
       </c>
       <c r="K148" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L148" s="3" t="inlineStr"/>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="K149" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L149" s="6" t="inlineStr"/>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="K150" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L150" s="3" t="inlineStr"/>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="K151" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L151" s="6" t="inlineStr"/>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="K152" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L152" s="3" t="inlineStr"/>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="K153" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L153" s="6" t="inlineStr"/>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="K154" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L154" s="3" t="inlineStr"/>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="K155" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L155" s="6" t="inlineStr"/>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="K156" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L156" s="3" t="inlineStr"/>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K157" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L157" s="6" t="inlineStr"/>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="K158" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L158" s="3" t="inlineStr"/>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="K159" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L159" s="6" t="inlineStr"/>
@@ -8438,7 +8438,7 @@
       </c>
       <c r="K160" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L160" s="3" t="inlineStr"/>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="K161" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L161" s="6" t="inlineStr"/>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="K162" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L162" s="3" t="inlineStr"/>
@@ -8582,7 +8582,7 @@
       </c>
       <c r="K163" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L163" s="6" t="inlineStr"/>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="K164" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L164" s="3" t="inlineStr"/>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="K165" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L165" s="6" t="inlineStr"/>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="K166" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L166" s="3" t="inlineStr"/>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="K167" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L167" s="6" t="inlineStr"/>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="K168" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L168" s="3" t="inlineStr"/>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="K169" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L169" s="6" t="inlineStr"/>
@@ -8918,7 +8918,7 @@
       </c>
       <c r="K170" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L170" s="3" t="inlineStr"/>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="K171" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L171" s="6" t="inlineStr"/>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="K172" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L172" s="3" t="inlineStr"/>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="K173" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L173" s="6" t="inlineStr"/>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="K174" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L174" s="3" t="inlineStr"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="K175" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L175" s="6" t="inlineStr"/>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="K176" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L176" s="3" t="inlineStr"/>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="K177" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L177" s="6" t="inlineStr"/>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="K178" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L178" s="3" t="inlineStr"/>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="K179" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L179" s="6" t="inlineStr"/>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="K180" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L180" s="3" t="inlineStr"/>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="K181" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L181" s="6" t="inlineStr"/>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="K182" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L182" s="3" t="inlineStr"/>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="K183" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L183" s="6" t="inlineStr"/>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="K184" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L184" s="3" t="inlineStr"/>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="K185" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L185" s="6" t="inlineStr"/>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="K186" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L186" s="3" t="inlineStr"/>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="K187" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L187" s="6" t="inlineStr"/>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="K188" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L188" s="3" t="inlineStr"/>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="K189" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L189" s="6" t="inlineStr"/>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="K190" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L190" s="3" t="inlineStr"/>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="K191" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L191" s="6" t="inlineStr"/>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="K192" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L192" s="3" t="inlineStr"/>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="K193" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L193" s="6" t="inlineStr"/>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="K194" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L194" s="3" t="inlineStr"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="K195" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L195" s="6" t="inlineStr"/>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="K196" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L196" s="3" t="inlineStr"/>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="K197" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L197" s="6" t="inlineStr"/>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="K198" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L198" s="3" t="inlineStr"/>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="K199" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L199" s="6" t="inlineStr"/>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="K200" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L200" s="3" t="inlineStr"/>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="K201" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L201" s="6" t="inlineStr"/>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="K202" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L202" s="3" t="inlineStr"/>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="K203" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L203" s="6" t="inlineStr"/>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="K204" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L204" s="3" t="inlineStr"/>
@@ -10598,7 +10598,7 @@
       </c>
       <c r="K205" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L205" s="6" t="inlineStr"/>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K206" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L206" s="3" t="inlineStr"/>
@@ -10694,7 +10694,7 @@
       </c>
       <c r="K207" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L207" s="6" t="inlineStr"/>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="K208" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L208" s="3" t="inlineStr"/>
@@ -10790,7 +10790,7 @@
       </c>
       <c r="K209" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L209" s="6" t="inlineStr"/>
@@ -10838,7 +10838,7 @@
       </c>
       <c r="K210" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L210" s="3" t="inlineStr"/>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="K211" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L211" s="6" t="inlineStr"/>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="K212" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L212" s="3" t="inlineStr"/>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="K213" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L213" s="6" t="inlineStr"/>
@@ -11030,7 +11030,7 @@
       </c>
       <c r="K214" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L214" s="3" t="inlineStr"/>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="K215" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L215" s="6" t="inlineStr"/>
@@ -11126,7 +11126,7 @@
       </c>
       <c r="K216" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L216" s="3" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="K217" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L217" s="6" t="inlineStr"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="K218" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L218" s="3" t="inlineStr"/>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="K219" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L219" s="6" t="inlineStr"/>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="K220" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L220" s="3" t="inlineStr"/>
@@ -11366,7 +11366,7 @@
       </c>
       <c r="K221" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L221" s="6" t="inlineStr"/>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="K222" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L222" s="3" t="inlineStr"/>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="K223" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L223" s="6" t="inlineStr"/>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="K224" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L224" s="3" t="inlineStr"/>
@@ -11558,7 +11558,7 @@
       </c>
       <c r="K225" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L225" s="6" t="inlineStr"/>
@@ -11606,7 +11606,7 @@
       </c>
       <c r="K226" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L226" s="3" t="inlineStr"/>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="K227" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L227" s="6" t="inlineStr"/>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="K228" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L228" s="3" t="inlineStr"/>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="K229" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L229" s="6" t="inlineStr"/>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="K230" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L230" s="3" t="inlineStr"/>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="K231" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L231" s="6" t="inlineStr"/>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="K232" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L232" s="3" t="inlineStr"/>
@@ -11942,7 +11942,7 @@
       </c>
       <c r="K233" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L233" s="6" t="inlineStr"/>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="K234" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L234" s="3" t="inlineStr"/>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="K235" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L235" s="6" t="inlineStr"/>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="K236" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L236" s="3" t="inlineStr"/>
@@ -12134,7 +12134,7 @@
       </c>
       <c r="K237" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L237" s="6" t="inlineStr"/>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="K238" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L238" s="3" t="inlineStr"/>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="K239" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L239" s="6" t="inlineStr"/>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="K240" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L240" s="3" t="inlineStr"/>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="K241" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L241" s="6" t="inlineStr"/>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="K242" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L242" s="3" t="inlineStr"/>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="K243" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L243" s="6" t="inlineStr"/>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="K244" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L244" s="3" t="inlineStr"/>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="K245" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L245" s="6" t="inlineStr"/>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="K246" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L246" s="3" t="inlineStr"/>
@@ -12614,7 +12614,7 @@
       </c>
       <c r="K247" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L247" s="6" t="inlineStr"/>
@@ -12662,7 +12662,7 @@
       </c>
       <c r="K248" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L248" s="3" t="inlineStr"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="K249" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L249" s="6" t="inlineStr"/>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="K250" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L250" s="3" t="inlineStr"/>
@@ -12806,7 +12806,7 @@
       </c>
       <c r="K251" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L251" s="6" t="inlineStr"/>
@@ -12854,7 +12854,7 @@
       </c>
       <c r="K252" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L252" s="3" t="inlineStr"/>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="K253" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L253" s="6" t="inlineStr"/>
@@ -12950,7 +12950,7 @@
       </c>
       <c r="K254" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L254" s="3" t="inlineStr"/>
@@ -12998,7 +12998,7 @@
       </c>
       <c r="K255" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L255" s="6" t="inlineStr"/>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="K256" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L256" s="3" t="inlineStr"/>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="K257" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L257" s="6" t="inlineStr"/>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="K258" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L258" s="3" t="inlineStr"/>
@@ -13190,7 +13190,7 @@
       </c>
       <c r="K259" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L259" s="6" t="inlineStr"/>
@@ -13238,7 +13238,7 @@
       </c>
       <c r="K260" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L260" s="3" t="inlineStr"/>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="K261" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L261" s="6" t="inlineStr"/>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="K262" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L262" s="3" t="inlineStr"/>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="K263" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L263" s="6" t="inlineStr"/>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="K264" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L264" s="3" t="inlineStr"/>
@@ -13478,7 +13478,7 @@
       </c>
       <c r="K265" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L265" s="6" t="inlineStr"/>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="K266" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L266" s="3" t="inlineStr"/>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="K267" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L267" s="6" t="inlineStr"/>
@@ -13622,7 +13622,7 @@
       </c>
       <c r="K268" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L268" s="3" t="inlineStr"/>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="K269" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L269" s="6" t="inlineStr"/>
@@ -13718,7 +13718,7 @@
       </c>
       <c r="K270" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L270" s="3" t="inlineStr"/>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="K271" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L271" s="6" t="inlineStr"/>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="K272" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L272" s="3" t="inlineStr"/>
@@ -13862,7 +13862,7 @@
       </c>
       <c r="K273" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L273" s="6" t="inlineStr"/>
@@ -13910,7 +13910,7 @@
       </c>
       <c r="K274" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L274" s="3" t="inlineStr"/>
@@ -13958,7 +13958,7 @@
       </c>
       <c r="K275" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L275" s="6" t="inlineStr"/>
@@ -14006,7 +14006,7 @@
       </c>
       <c r="K276" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L276" s="3" t="inlineStr"/>
@@ -14054,7 +14054,7 @@
       </c>
       <c r="K277" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L277" s="6" t="inlineStr"/>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="K278" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L278" s="3" t="inlineStr"/>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="K279" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L279" s="6" t="inlineStr"/>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="K280" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L280" s="3" t="inlineStr"/>
@@ -14246,7 +14246,7 @@
       </c>
       <c r="K281" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L281" s="6" t="inlineStr"/>
@@ -14294,7 +14294,7 @@
       </c>
       <c r="K282" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L282" s="3" t="inlineStr"/>
@@ -14342,7 +14342,7 @@
       </c>
       <c r="K283" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L283" s="6" t="inlineStr"/>
@@ -14390,7 +14390,7 @@
       </c>
       <c r="K284" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L284" s="3" t="inlineStr"/>
@@ -14438,7 +14438,7 @@
       </c>
       <c r="K285" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L285" s="6" t="inlineStr"/>
@@ -14486,7 +14486,7 @@
       </c>
       <c r="K286" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L286" s="3" t="inlineStr"/>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="K287" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L287" s="6" t="inlineStr"/>
@@ -14582,7 +14582,7 @@
       </c>
       <c r="K288" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L288" s="3" t="inlineStr"/>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="K289" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L289" s="6" t="inlineStr"/>
@@ -14678,7 +14678,7 @@
       </c>
       <c r="K290" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L290" s="3" t="inlineStr"/>
@@ -14726,7 +14726,7 @@
       </c>
       <c r="K291" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L291" s="6" t="inlineStr"/>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="K292" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L292" s="3" t="inlineStr"/>
@@ -14822,7 +14822,7 @@
       </c>
       <c r="K293" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L293" s="6" t="inlineStr"/>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="K294" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L294" s="3" t="inlineStr"/>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="K295" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L295" s="6" t="inlineStr"/>
@@ -14966,7 +14966,7 @@
       </c>
       <c r="K296" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L296" s="3" t="inlineStr"/>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="K297" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L297" s="6" t="inlineStr"/>
@@ -15062,7 +15062,7 @@
       </c>
       <c r="K298" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L298" s="3" t="inlineStr"/>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="K299" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L299" s="6" t="inlineStr"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="K300" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L300" s="3" t="inlineStr"/>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="K301" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L301" s="6" t="inlineStr"/>
@@ -15254,7 +15254,7 @@
       </c>
       <c r="K302" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L302" s="3" t="inlineStr"/>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="K303" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L303" s="6" t="inlineStr"/>
@@ -15350,7 +15350,7 @@
       </c>
       <c r="K304" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L304" s="3" t="inlineStr"/>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="K305" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L305" s="6" t="inlineStr"/>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="K306" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L306" s="3" t="inlineStr"/>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="K307" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L307" s="6" t="inlineStr"/>
@@ -15542,7 +15542,7 @@
       </c>
       <c r="K308" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L308" s="3" t="inlineStr"/>
@@ -15590,7 +15590,7 @@
       </c>
       <c r="K309" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L309" s="6" t="inlineStr"/>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="K310" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L310" s="3" t="inlineStr"/>
@@ -15686,7 +15686,7 @@
       </c>
       <c r="K311" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L311" s="6" t="inlineStr"/>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="K312" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L312" s="3" t="inlineStr"/>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="K313" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L313" s="6" t="inlineStr"/>
@@ -15830,7 +15830,7 @@
       </c>
       <c r="K314" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L314" s="3" t="inlineStr"/>
@@ -15878,7 +15878,7 @@
       </c>
       <c r="K315" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L315" s="6" t="inlineStr"/>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="K316" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L316" s="3" t="inlineStr"/>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="K317" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L317" s="6" t="inlineStr"/>
@@ -16022,7 +16022,7 @@
       </c>
       <c r="K318" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L318" s="3" t="inlineStr"/>
@@ -16070,7 +16070,7 @@
       </c>
       <c r="K319" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L319" s="6" t="inlineStr"/>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="K320" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L320" s="3" t="inlineStr"/>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="K321" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L321" s="6" t="inlineStr"/>
@@ -16214,7 +16214,7 @@
       </c>
       <c r="K322" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L322" s="3" t="inlineStr"/>
@@ -16262,7 +16262,7 @@
       </c>
       <c r="K323" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L323" s="6" t="inlineStr"/>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="K324" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L324" s="3" t="inlineStr"/>
@@ -16358,7 +16358,7 @@
       </c>
       <c r="K325" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L325" s="6" t="inlineStr"/>
@@ -16406,7 +16406,7 @@
       </c>
       <c r="K326" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L326" s="3" t="inlineStr"/>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="K327" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L327" s="6" t="inlineStr"/>
@@ -16502,7 +16502,7 @@
       </c>
       <c r="K328" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L328" s="3" t="inlineStr"/>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="K329" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L329" s="6" t="inlineStr"/>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="K330" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L330" s="3" t="inlineStr"/>
@@ -16646,7 +16646,7 @@
       </c>
       <c r="K331" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L331" s="6" t="inlineStr"/>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="K332" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L332" s="3" t="inlineStr"/>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="K333" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L333" s="6" t="inlineStr"/>
@@ -16790,7 +16790,7 @@
       </c>
       <c r="K334" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L334" s="3" t="inlineStr"/>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="K335" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L335" s="6" t="inlineStr"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="K336" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L336" s="3" t="inlineStr"/>
@@ -16934,7 +16934,7 @@
       </c>
       <c r="K337" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L337" s="6" t="inlineStr"/>
@@ -16982,7 +16982,7 @@
       </c>
       <c r="K338" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L338" s="3" t="inlineStr"/>
@@ -17030,7 +17030,7 @@
       </c>
       <c r="K339" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L339" s="6" t="inlineStr"/>
@@ -17078,7 +17078,7 @@
       </c>
       <c r="K340" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L340" s="3" t="inlineStr"/>
@@ -17126,7 +17126,7 @@
       </c>
       <c r="K341" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L341" s="6" t="inlineStr"/>
@@ -17174,7 +17174,7 @@
       </c>
       <c r="K342" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L342" s="3" t="inlineStr"/>
@@ -17222,7 +17222,7 @@
       </c>
       <c r="K343" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L343" s="6" t="inlineStr"/>
@@ -17270,7 +17270,7 @@
       </c>
       <c r="K344" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L344" s="3" t="inlineStr"/>
@@ -17318,7 +17318,7 @@
       </c>
       <c r="K345" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L345" s="6" t="inlineStr"/>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="K346" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L346" s="3" t="inlineStr"/>
@@ -17414,7 +17414,7 @@
       </c>
       <c r="K347" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L347" s="6" t="inlineStr"/>
@@ -17462,7 +17462,7 @@
       </c>
       <c r="K348" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L348" s="3" t="inlineStr"/>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="K349" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L349" s="6" t="inlineStr"/>
@@ -17558,7 +17558,7 @@
       </c>
       <c r="K350" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L350" s="3" t="inlineStr"/>
@@ -17606,7 +17606,7 @@
       </c>
       <c r="K351" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L351" s="6" t="inlineStr"/>
@@ -17654,7 +17654,7 @@
       </c>
       <c r="K352" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L352" s="3" t="inlineStr"/>
@@ -17702,7 +17702,7 @@
       </c>
       <c r="K353" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L353" s="6" t="inlineStr"/>
@@ -17750,7 +17750,7 @@
       </c>
       <c r="K354" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L354" s="3" t="inlineStr"/>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="K355" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L355" s="6" t="inlineStr"/>
@@ -17846,7 +17846,7 @@
       </c>
       <c r="K356" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L356" s="3" t="inlineStr"/>
@@ -17894,7 +17894,7 @@
       </c>
       <c r="K357" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L357" s="6" t="inlineStr"/>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="K358" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L358" s="3" t="inlineStr"/>
@@ -17990,7 +17990,7 @@
       </c>
       <c r="K359" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L359" s="6" t="inlineStr"/>
@@ -18038,7 +18038,7 @@
       </c>
       <c r="K360" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L360" s="3" t="inlineStr"/>
@@ -18086,7 +18086,7 @@
       </c>
       <c r="K361" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L361" s="6" t="inlineStr"/>
@@ -18134,7 +18134,7 @@
       </c>
       <c r="K362" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L362" s="3" t="inlineStr"/>
@@ -18182,7 +18182,7 @@
       </c>
       <c r="K363" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L363" s="6" t="inlineStr"/>
@@ -18230,7 +18230,7 @@
       </c>
       <c r="K364" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L364" s="3" t="inlineStr"/>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="K365" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L365" s="6" t="inlineStr"/>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="K366" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L366" s="3" t="inlineStr"/>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="K367" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L367" s="6" t="inlineStr"/>
@@ -18422,7 +18422,7 @@
       </c>
       <c r="K368" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L368" s="3" t="inlineStr"/>
@@ -18470,7 +18470,7 @@
       </c>
       <c r="K369" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L369" s="6" t="inlineStr"/>
@@ -18518,7 +18518,7 @@
       </c>
       <c r="K370" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L370" s="3" t="inlineStr"/>
@@ -18566,7 +18566,7 @@
       </c>
       <c r="K371" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L371" s="6" t="inlineStr"/>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="K372" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L372" s="3" t="inlineStr"/>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="K373" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L373" s="6" t="inlineStr"/>
@@ -18710,7 +18710,7 @@
       </c>
       <c r="K374" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L374" s="3" t="inlineStr"/>
@@ -18758,7 +18758,7 @@
       </c>
       <c r="K375" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L375" s="6" t="inlineStr"/>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="K376" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L376" s="3" t="inlineStr"/>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="K377" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L377" s="6" t="inlineStr"/>
@@ -18902,7 +18902,7 @@
       </c>
       <c r="K378" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L378" s="3" t="inlineStr"/>
@@ -18950,7 +18950,7 @@
       </c>
       <c r="K379" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L379" s="6" t="inlineStr"/>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="K380" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L380" s="3" t="inlineStr"/>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="K381" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L381" s="6" t="inlineStr"/>
@@ -19094,7 +19094,7 @@
       </c>
       <c r="K382" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L382" s="3" t="inlineStr"/>
@@ -19142,7 +19142,7 @@
       </c>
       <c r="K383" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L383" s="6" t="inlineStr"/>
@@ -19190,7 +19190,7 @@
       </c>
       <c r="K384" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L384" s="3" t="inlineStr"/>
@@ -19238,7 +19238,7 @@
       </c>
       <c r="K385" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L385" s="6" t="inlineStr"/>
@@ -19286,7 +19286,7 @@
       </c>
       <c r="K386" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L386" s="3" t="inlineStr"/>
@@ -19334,7 +19334,7 @@
       </c>
       <c r="K387" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L387" s="6" t="inlineStr"/>
@@ -19382,7 +19382,7 @@
       </c>
       <c r="K388" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L388" s="3" t="inlineStr"/>
@@ -19430,7 +19430,7 @@
       </c>
       <c r="K389" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L389" s="6" t="inlineStr"/>
@@ -19478,7 +19478,7 @@
       </c>
       <c r="K390" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L390" s="3" t="inlineStr"/>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="K391" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L391" s="6" t="inlineStr"/>
@@ -19574,7 +19574,7 @@
       </c>
       <c r="K392" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L392" s="3" t="inlineStr"/>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="K393" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L393" s="6" t="inlineStr"/>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="K394" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L394" s="3" t="inlineStr"/>
@@ -19718,7 +19718,7 @@
       </c>
       <c r="K395" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L395" s="6" t="inlineStr"/>
@@ -19766,7 +19766,7 @@
       </c>
       <c r="K396" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L396" s="3" t="inlineStr"/>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="K397" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L397" s="6" t="inlineStr"/>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="K398" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L398" s="3" t="inlineStr"/>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="K399" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L399" s="6" t="inlineStr"/>
@@ -19958,7 +19958,7 @@
       </c>
       <c r="K400" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L400" s="3" t="inlineStr"/>
@@ -20006,7 +20006,7 @@
       </c>
       <c r="K401" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L401" s="6" t="inlineStr"/>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="K402" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L402" s="3" t="inlineStr"/>
@@ -20102,7 +20102,7 @@
       </c>
       <c r="K403" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L403" s="6" t="inlineStr"/>
@@ -20150,7 +20150,7 @@
       </c>
       <c r="K404" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L404" s="3" t="inlineStr"/>
@@ -20198,7 +20198,7 @@
       </c>
       <c r="K405" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L405" s="6" t="inlineStr"/>
@@ -20246,7 +20246,7 @@
       </c>
       <c r="K406" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L406" s="3" t="inlineStr"/>
@@ -20294,7 +20294,7 @@
       </c>
       <c r="K407" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L407" s="6" t="inlineStr"/>
@@ -20342,7 +20342,7 @@
       </c>
       <c r="K408" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L408" s="3" t="inlineStr"/>
@@ -20390,7 +20390,7 @@
       </c>
       <c r="K409" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L409" s="6" t="inlineStr"/>
@@ -20438,7 +20438,7 @@
       </c>
       <c r="K410" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L410" s="3" t="inlineStr"/>
@@ -20486,7 +20486,7 @@
       </c>
       <c r="K411" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L411" s="6" t="inlineStr"/>
@@ -20534,7 +20534,7 @@
       </c>
       <c r="K412" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L412" s="3" t="inlineStr"/>
@@ -20582,7 +20582,7 @@
       </c>
       <c r="K413" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L413" s="6" t="inlineStr"/>
@@ -20630,7 +20630,7 @@
       </c>
       <c r="K414" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L414" s="3" t="inlineStr"/>
@@ -20678,7 +20678,7 @@
       </c>
       <c r="K415" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L415" s="6" t="inlineStr"/>
@@ -20726,7 +20726,7 @@
       </c>
       <c r="K416" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L416" s="3" t="inlineStr"/>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="K417" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L417" s="6" t="inlineStr"/>
@@ -20822,7 +20822,7 @@
       </c>
       <c r="K418" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L418" s="3" t="inlineStr"/>
@@ -20870,7 +20870,7 @@
       </c>
       <c r="K419" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L419" s="6" t="inlineStr"/>
@@ -20918,7 +20918,7 @@
       </c>
       <c r="K420" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L420" s="3" t="inlineStr"/>
@@ -20966,7 +20966,7 @@
       </c>
       <c r="K421" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L421" s="6" t="inlineStr"/>
@@ -21014,7 +21014,7 @@
       </c>
       <c r="K422" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L422" s="3" t="inlineStr"/>
@@ -21062,7 +21062,7 @@
       </c>
       <c r="K423" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L423" s="6" t="inlineStr"/>
@@ -21110,7 +21110,7 @@
       </c>
       <c r="K424" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L424" s="3" t="inlineStr"/>
@@ -21158,7 +21158,7 @@
       </c>
       <c r="K425" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L425" s="6" t="inlineStr"/>
@@ -21206,7 +21206,7 @@
       </c>
       <c r="K426" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L426" s="3" t="inlineStr"/>
@@ -21254,7 +21254,7 @@
       </c>
       <c r="K427" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L427" s="6" t="inlineStr"/>
@@ -21302,7 +21302,7 @@
       </c>
       <c r="K428" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L428" s="3" t="inlineStr"/>
@@ -21350,7 +21350,7 @@
       </c>
       <c r="K429" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L429" s="6" t="inlineStr"/>
@@ -21398,7 +21398,7 @@
       </c>
       <c r="K430" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L430" s="3" t="inlineStr"/>
@@ -21446,7 +21446,7 @@
       </c>
       <c r="K431" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L431" s="6" t="inlineStr"/>
@@ -21494,7 +21494,7 @@
       </c>
       <c r="K432" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L432" s="3" t="inlineStr"/>
@@ -21542,7 +21542,7 @@
       </c>
       <c r="K433" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L433" s="6" t="inlineStr"/>
@@ -21590,7 +21590,7 @@
       </c>
       <c r="K434" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L434" s="3" t="inlineStr"/>
@@ -21638,7 +21638,7 @@
       </c>
       <c r="K435" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L435" s="6" t="inlineStr"/>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="K436" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L436" s="3" t="inlineStr"/>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="K437" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L437" s="6" t="inlineStr"/>
@@ -21782,7 +21782,7 @@
       </c>
       <c r="K438" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L438" s="3" t="inlineStr"/>
@@ -21830,7 +21830,7 @@
       </c>
       <c r="K439" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L439" s="6" t="inlineStr"/>
@@ -21878,7 +21878,7 @@
       </c>
       <c r="K440" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L440" s="3" t="inlineStr"/>
@@ -21926,7 +21926,7 @@
       </c>
       <c r="K441" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L441" s="6" t="inlineStr"/>
@@ -21974,7 +21974,7 @@
       </c>
       <c r="K442" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L442" s="3" t="inlineStr"/>
@@ -22022,7 +22022,7 @@
       </c>
       <c r="K443" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L443" s="6" t="inlineStr"/>
@@ -22070,7 +22070,7 @@
       </c>
       <c r="K444" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L444" s="3" t="inlineStr"/>
@@ -22118,7 +22118,7 @@
       </c>
       <c r="K445" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L445" s="6" t="inlineStr"/>
@@ -22166,7 +22166,7 @@
       </c>
       <c r="K446" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L446" s="3" t="inlineStr"/>
@@ -22214,7 +22214,7 @@
       </c>
       <c r="K447" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L447" s="6" t="inlineStr"/>
@@ -22262,7 +22262,7 @@
       </c>
       <c r="K448" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L448" s="3" t="inlineStr"/>
@@ -22310,7 +22310,7 @@
       </c>
       <c r="K449" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L449" s="6" t="inlineStr"/>
@@ -22358,7 +22358,7 @@
       </c>
       <c r="K450" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L450" s="3" t="inlineStr"/>
@@ -22406,7 +22406,7 @@
       </c>
       <c r="K451" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L451" s="6" t="inlineStr"/>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="K452" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L452" s="3" t="inlineStr"/>
@@ -22502,7 +22502,7 @@
       </c>
       <c r="K453" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L453" s="6" t="inlineStr"/>
@@ -22550,7 +22550,7 @@
       </c>
       <c r="K454" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L454" s="3" t="inlineStr"/>
@@ -22598,7 +22598,7 @@
       </c>
       <c r="K455" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L455" s="6" t="inlineStr"/>
@@ -22646,7 +22646,7 @@
       </c>
       <c r="K456" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L456" s="3" t="inlineStr"/>
@@ -22694,7 +22694,7 @@
       </c>
       <c r="K457" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L457" s="6" t="inlineStr"/>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="K458" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L458" s="3" t="inlineStr"/>
@@ -22790,7 +22790,7 @@
       </c>
       <c r="K459" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L459" s="6" t="inlineStr"/>
@@ -22838,7 +22838,7 @@
       </c>
       <c r="K460" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L460" s="3" t="inlineStr"/>
@@ -22886,7 +22886,7 @@
       </c>
       <c r="K461" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L461" s="6" t="inlineStr"/>
@@ -22934,7 +22934,7 @@
       </c>
       <c r="K462" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L462" s="3" t="inlineStr"/>
@@ -22982,7 +22982,7 @@
       </c>
       <c r="K463" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L463" s="6" t="inlineStr"/>
@@ -23030,7 +23030,7 @@
       </c>
       <c r="K464" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L464" s="3" t="inlineStr"/>
@@ -23078,7 +23078,7 @@
       </c>
       <c r="K465" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L465" s="6" t="inlineStr"/>
@@ -23126,7 +23126,7 @@
       </c>
       <c r="K466" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L466" s="3" t="inlineStr"/>
@@ -23174,7 +23174,7 @@
       </c>
       <c r="K467" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L467" s="6" t="inlineStr"/>
@@ -23222,7 +23222,7 @@
       </c>
       <c r="K468" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L468" s="3" t="inlineStr"/>
@@ -23270,7 +23270,7 @@
       </c>
       <c r="K469" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L469" s="6" t="inlineStr"/>
@@ -23318,7 +23318,7 @@
       </c>
       <c r="K470" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L470" s="3" t="inlineStr"/>
@@ -23366,7 +23366,7 @@
       </c>
       <c r="K471" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L471" s="6" t="inlineStr"/>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="K472" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L472" s="3" t="inlineStr"/>
@@ -23462,7 +23462,7 @@
       </c>
       <c r="K473" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L473" s="6" t="inlineStr"/>
@@ -23510,7 +23510,7 @@
       </c>
       <c r="K474" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L474" s="3" t="inlineStr"/>
@@ -23558,7 +23558,7 @@
       </c>
       <c r="K475" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L475" s="6" t="inlineStr"/>
@@ -23606,7 +23606,7 @@
       </c>
       <c r="K476" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L476" s="3" t="inlineStr"/>
@@ -23654,7 +23654,7 @@
       </c>
       <c r="K477" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L477" s="6" t="inlineStr"/>
@@ -23702,7 +23702,7 @@
       </c>
       <c r="K478" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L478" s="3" t="inlineStr"/>
@@ -23750,7 +23750,7 @@
       </c>
       <c r="K479" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L479" s="6" t="inlineStr"/>
@@ -23798,7 +23798,7 @@
       </c>
       <c r="K480" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L480" s="3" t="inlineStr"/>
@@ -23846,7 +23846,7 @@
       </c>
       <c r="K481" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L481" s="6" t="inlineStr"/>
@@ -23894,7 +23894,7 @@
       </c>
       <c r="K482" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L482" s="3" t="inlineStr"/>
@@ -23942,7 +23942,7 @@
       </c>
       <c r="K483" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L483" s="6" t="inlineStr"/>
@@ -23990,7 +23990,7 @@
       </c>
       <c r="K484" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L484" s="3" t="inlineStr"/>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="K485" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L485" s="6" t="inlineStr"/>
@@ -24086,7 +24086,7 @@
       </c>
       <c r="K486" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L486" s="3" t="inlineStr"/>
@@ -24134,7 +24134,7 @@
       </c>
       <c r="K487" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L487" s="6" t="inlineStr"/>
@@ -24182,7 +24182,7 @@
       </c>
       <c r="K488" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L488" s="3" t="inlineStr"/>
@@ -24230,7 +24230,7 @@
       </c>
       <c r="K489" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L489" s="6" t="inlineStr"/>
@@ -24278,7 +24278,7 @@
       </c>
       <c r="K490" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L490" s="3" t="inlineStr"/>
@@ -24326,7 +24326,7 @@
       </c>
       <c r="K491" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L491" s="6" t="inlineStr"/>
@@ -24374,7 +24374,7 @@
       </c>
       <c r="K492" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L492" s="3" t="inlineStr"/>
@@ -24422,7 +24422,7 @@
       </c>
       <c r="K493" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L493" s="6" t="inlineStr"/>
@@ -24470,7 +24470,7 @@
       </c>
       <c r="K494" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L494" s="3" t="inlineStr"/>
@@ -24518,7 +24518,7 @@
       </c>
       <c r="K495" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L495" s="6" t="inlineStr"/>
@@ -24566,7 +24566,7 @@
       </c>
       <c r="K496" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L496" s="3" t="inlineStr"/>
@@ -24614,7 +24614,7 @@
       </c>
       <c r="K497" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L497" s="6" t="inlineStr"/>
@@ -24662,7 +24662,7 @@
       </c>
       <c r="K498" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L498" s="3" t="inlineStr"/>
@@ -24710,7 +24710,7 @@
       </c>
       <c r="K499" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L499" s="6" t="inlineStr"/>
@@ -24758,7 +24758,7 @@
       </c>
       <c r="K500" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L500" s="3" t="inlineStr"/>
@@ -24806,7 +24806,7 @@
       </c>
       <c r="K501" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L501" s="6" t="inlineStr"/>
@@ -24854,7 +24854,7 @@
       </c>
       <c r="K502" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L502" s="3" t="inlineStr"/>
@@ -24902,7 +24902,7 @@
       </c>
       <c r="K503" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L503" s="6" t="inlineStr"/>
@@ -24950,7 +24950,7 @@
       </c>
       <c r="K504" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L504" s="3" t="inlineStr"/>
@@ -24998,7 +24998,7 @@
       </c>
       <c r="K505" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L505" s="6" t="inlineStr"/>
@@ -25046,7 +25046,7 @@
       </c>
       <c r="K506" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L506" s="3" t="inlineStr"/>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="K507" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L507" s="6" t="inlineStr"/>
@@ -25142,7 +25142,7 @@
       </c>
       <c r="K508" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L508" s="3" t="inlineStr"/>
@@ -25190,7 +25190,7 @@
       </c>
       <c r="K509" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L509" s="6" t="inlineStr"/>
@@ -25238,7 +25238,7 @@
       </c>
       <c r="K510" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L510" s="3" t="inlineStr"/>
@@ -25286,7 +25286,7 @@
       </c>
       <c r="K511" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L511" s="6" t="inlineStr"/>
@@ -25334,7 +25334,7 @@
       </c>
       <c r="K512" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L512" s="3" t="inlineStr"/>
@@ -25382,7 +25382,7 @@
       </c>
       <c r="K513" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L513" s="6" t="inlineStr"/>
@@ -25430,7 +25430,7 @@
       </c>
       <c r="K514" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L514" s="3" t="inlineStr"/>
@@ -25478,7 +25478,7 @@
       </c>
       <c r="K515" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L515" s="6" t="inlineStr"/>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="K516" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L516" s="3" t="inlineStr"/>
@@ -25574,7 +25574,7 @@
       </c>
       <c r="K517" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L517" s="6" t="inlineStr"/>
@@ -25622,7 +25622,7 @@
       </c>
       <c r="K518" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L518" s="3" t="inlineStr"/>
@@ -25670,7 +25670,7 @@
       </c>
       <c r="K519" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L519" s="6" t="inlineStr"/>
@@ -25718,7 +25718,7 @@
       </c>
       <c r="K520" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L520" s="3" t="inlineStr"/>
@@ -25766,7 +25766,7 @@
       </c>
       <c r="K521" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L521" s="6" t="inlineStr"/>
@@ -25814,7 +25814,7 @@
       </c>
       <c r="K522" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L522" s="3" t="inlineStr"/>
@@ -25862,7 +25862,7 @@
       </c>
       <c r="K523" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L523" s="6" t="inlineStr"/>
@@ -25910,7 +25910,7 @@
       </c>
       <c r="K524" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L524" s="3" t="inlineStr"/>
@@ -25958,7 +25958,7 @@
       </c>
       <c r="K525" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L525" s="6" t="inlineStr"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K526" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L526" s="3" t="inlineStr"/>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="K527" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L527" s="6" t="inlineStr"/>
@@ -26102,7 +26102,7 @@
       </c>
       <c r="K528" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L528" s="3" t="inlineStr"/>
@@ -26150,7 +26150,7 @@
       </c>
       <c r="K529" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L529" s="6" t="inlineStr"/>
@@ -26198,7 +26198,7 @@
       </c>
       <c r="K530" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L530" s="3" t="inlineStr"/>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="K531" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L531" s="6" t="inlineStr"/>
@@ -26294,7 +26294,7 @@
       </c>
       <c r="K532" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L532" s="3" t="inlineStr"/>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="K533" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L533" s="6" t="inlineStr"/>
@@ -26390,7 +26390,7 @@
       </c>
       <c r="K534" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L534" s="3" t="inlineStr"/>
@@ -26438,7 +26438,7 @@
       </c>
       <c r="K535" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L535" s="6" t="inlineStr"/>
@@ -26486,7 +26486,7 @@
       </c>
       <c r="K536" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L536" s="3" t="inlineStr"/>
@@ -26534,7 +26534,7 @@
       </c>
       <c r="K537" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L537" s="6" t="inlineStr"/>
@@ -26582,7 +26582,7 @@
       </c>
       <c r="K538" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L538" s="3" t="inlineStr"/>
@@ -26630,7 +26630,7 @@
       </c>
       <c r="K539" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L539" s="6" t="inlineStr"/>
@@ -26678,7 +26678,7 @@
       </c>
       <c r="K540" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L540" s="3" t="inlineStr"/>
@@ -26726,7 +26726,7 @@
       </c>
       <c r="K541" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L541" s="6" t="inlineStr"/>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="K542" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L542" s="3" t="inlineStr"/>
@@ -26822,7 +26822,7 @@
       </c>
       <c r="K543" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L543" s="6" t="inlineStr"/>
@@ -26870,7 +26870,7 @@
       </c>
       <c r="K544" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L544" s="3" t="inlineStr"/>
@@ -26918,7 +26918,7 @@
       </c>
       <c r="K545" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L545" s="6" t="inlineStr"/>
@@ -26966,7 +26966,7 @@
       </c>
       <c r="K546" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L546" s="3" t="inlineStr"/>
@@ -27014,7 +27014,7 @@
       </c>
       <c r="K547" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L547" s="6" t="inlineStr"/>
@@ -27062,7 +27062,7 @@
       </c>
       <c r="K548" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L548" s="3" t="inlineStr"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K549" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L549" s="6" t="inlineStr"/>
@@ -27158,7 +27158,7 @@
       </c>
       <c r="K550" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L550" s="3" t="inlineStr"/>
@@ -27206,7 +27206,7 @@
       </c>
       <c r="K551" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L551" s="6" t="inlineStr"/>
@@ -27254,7 +27254,7 @@
       </c>
       <c r="K552" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L552" s="3" t="inlineStr"/>
@@ -27302,7 +27302,7 @@
       </c>
       <c r="K553" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L553" s="6" t="inlineStr"/>
@@ -27350,7 +27350,7 @@
       </c>
       <c r="K554" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L554" s="3" t="inlineStr"/>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="K555" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L555" s="6" t="inlineStr"/>
@@ -27446,7 +27446,7 @@
       </c>
       <c r="K556" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L556" s="3" t="inlineStr"/>
@@ -27494,7 +27494,7 @@
       </c>
       <c r="K557" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L557" s="6" t="inlineStr"/>
@@ -27542,7 +27542,7 @@
       </c>
       <c r="K558" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L558" s="3" t="inlineStr"/>
@@ -27590,7 +27590,7 @@
       </c>
       <c r="K559" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L559" s="6" t="inlineStr"/>
@@ -27638,7 +27638,7 @@
       </c>
       <c r="K560" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L560" s="3" t="inlineStr"/>
@@ -27686,7 +27686,7 @@
       </c>
       <c r="K561" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L561" s="6" t="inlineStr"/>
@@ -27734,7 +27734,7 @@
       </c>
       <c r="K562" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L562" s="3" t="inlineStr"/>
@@ -27782,7 +27782,7 @@
       </c>
       <c r="K563" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L563" s="6" t="inlineStr"/>
@@ -27830,7 +27830,7 @@
       </c>
       <c r="K564" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L564" s="3" t="inlineStr"/>
@@ -27878,7 +27878,7 @@
       </c>
       <c r="K565" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L565" s="6" t="inlineStr"/>
@@ -27926,7 +27926,7 @@
       </c>
       <c r="K566" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L566" s="3" t="inlineStr"/>
@@ -27974,7 +27974,7 @@
       </c>
       <c r="K567" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L567" s="6" t="inlineStr"/>
@@ -28022,7 +28022,7 @@
       </c>
       <c r="K568" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L568" s="3" t="inlineStr"/>
@@ -28070,7 +28070,7 @@
       </c>
       <c r="K569" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L569" s="6" t="inlineStr"/>
@@ -28118,7 +28118,7 @@
       </c>
       <c r="K570" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L570" s="3" t="inlineStr"/>
@@ -28166,7 +28166,7 @@
       </c>
       <c r="K571" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L571" s="6" t="inlineStr"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K572" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L572" s="3" t="inlineStr"/>
@@ -28262,7 +28262,7 @@
       </c>
       <c r="K573" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L573" s="6" t="inlineStr"/>
@@ -28310,7 +28310,7 @@
       </c>
       <c r="K574" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L574" s="3" t="inlineStr"/>
@@ -28358,7 +28358,7 @@
       </c>
       <c r="K575" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L575" s="6" t="inlineStr"/>
@@ -28406,7 +28406,7 @@
       </c>
       <c r="K576" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L576" s="3" t="inlineStr"/>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="K577" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L577" s="6" t="inlineStr"/>
@@ -28502,7 +28502,7 @@
       </c>
       <c r="K578" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L578" s="3" t="inlineStr"/>
@@ -28550,7 +28550,7 @@
       </c>
       <c r="K579" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L579" s="6" t="inlineStr"/>
@@ -28598,7 +28598,7 @@
       </c>
       <c r="K580" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L580" s="3" t="inlineStr"/>
@@ -28646,7 +28646,7 @@
       </c>
       <c r="K581" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L581" s="6" t="inlineStr"/>
@@ -28694,7 +28694,7 @@
       </c>
       <c r="K582" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L582" s="3" t="inlineStr"/>
@@ -28742,7 +28742,7 @@
       </c>
       <c r="K583" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L583" s="6" t="inlineStr"/>
@@ -28790,7 +28790,7 @@
       </c>
       <c r="K584" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L584" s="3" t="inlineStr"/>
@@ -28838,7 +28838,7 @@
       </c>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L585" s="6" t="inlineStr"/>
@@ -28886,7 +28886,7 @@
       </c>
       <c r="K586" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L586" s="3" t="inlineStr"/>
@@ -28934,7 +28934,7 @@
       </c>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L587" s="6" t="inlineStr"/>
@@ -28982,7 +28982,7 @@
       </c>
       <c r="K588" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L588" s="3" t="inlineStr"/>
@@ -29030,7 +29030,7 @@
       </c>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L589" s="6" t="inlineStr"/>
@@ -29078,7 +29078,7 @@
       </c>
       <c r="K590" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L590" s="3" t="inlineStr"/>
@@ -29126,7 +29126,7 @@
       </c>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L591" s="6" t="inlineStr"/>
@@ -29174,7 +29174,7 @@
       </c>
       <c r="K592" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L592" s="3" t="inlineStr"/>
@@ -29222,7 +29222,7 @@
       </c>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L593" s="6" t="inlineStr"/>
@@ -29270,7 +29270,7 @@
       </c>
       <c r="K594" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L594" s="3" t="inlineStr"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L595" s="6" t="inlineStr"/>
@@ -29366,7 +29366,7 @@
       </c>
       <c r="K596" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L596" s="3" t="inlineStr"/>
@@ -29414,7 +29414,7 @@
       </c>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L597" s="6" t="inlineStr"/>
@@ -29462,7 +29462,7 @@
       </c>
       <c r="K598" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L598" s="3" t="inlineStr"/>
@@ -29510,7 +29510,7 @@
       </c>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L599" s="6" t="inlineStr"/>
@@ -29558,7 +29558,7 @@
       </c>
       <c r="K600" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L600" s="3" t="inlineStr"/>
@@ -29606,7 +29606,7 @@
       </c>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L601" s="6" t="inlineStr"/>
@@ -29654,7 +29654,7 @@
       </c>
       <c r="K602" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L602" s="3" t="inlineStr"/>
@@ -29702,7 +29702,7 @@
       </c>
       <c r="K603" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L603" s="6" t="inlineStr"/>
@@ -29750,7 +29750,7 @@
       </c>
       <c r="K604" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L604" s="3" t="inlineStr"/>
@@ -29798,7 +29798,7 @@
       </c>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr"/>
@@ -29846,7 +29846,7 @@
       </c>
       <c r="K606" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L606" s="3" t="inlineStr"/>
@@ -29894,7 +29894,7 @@
       </c>
       <c r="K607" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L607" s="6" t="inlineStr"/>
@@ -29942,7 +29942,7 @@
       </c>
       <c r="K608" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L608" s="3" t="inlineStr"/>
@@ -29990,7 +29990,7 @@
       </c>
       <c r="K609" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L609" s="6" t="inlineStr"/>
@@ -30038,7 +30038,7 @@
       </c>
       <c r="K610" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L610" s="3" t="inlineStr"/>
@@ -30086,7 +30086,7 @@
       </c>
       <c r="K611" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L611" s="6" t="inlineStr"/>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="K612" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L612" s="3" t="inlineStr"/>
@@ -30182,7 +30182,7 @@
       </c>
       <c r="K613" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L613" s="6" t="inlineStr"/>
@@ -30230,7 +30230,7 @@
       </c>
       <c r="K614" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L614" s="3" t="inlineStr"/>
@@ -30278,7 +30278,7 @@
       </c>
       <c r="K615" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L615" s="6" t="inlineStr"/>
@@ -30326,7 +30326,7 @@
       </c>
       <c r="K616" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L616" s="3" t="inlineStr"/>
@@ -30374,7 +30374,7 @@
       </c>
       <c r="K617" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L617" s="6" t="inlineStr"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K618" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L618" s="3" t="inlineStr"/>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="K619" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L619" s="6" t="inlineStr"/>
@@ -30518,7 +30518,7 @@
       </c>
       <c r="K620" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L620" s="3" t="inlineStr"/>
@@ -30566,7 +30566,7 @@
       </c>
       <c r="K621" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L621" s="6" t="inlineStr"/>
@@ -30614,7 +30614,7 @@
       </c>
       <c r="K622" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L622" s="3" t="inlineStr"/>
@@ -30662,7 +30662,7 @@
       </c>
       <c r="K623" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L623" s="6" t="inlineStr"/>
@@ -30710,7 +30710,7 @@
       </c>
       <c r="K624" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L624" s="3" t="inlineStr"/>
@@ -30758,7 +30758,7 @@
       </c>
       <c r="K625" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L625" s="6" t="inlineStr"/>
@@ -30806,7 +30806,7 @@
       </c>
       <c r="K626" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L626" s="3" t="inlineStr"/>
@@ -30854,7 +30854,7 @@
       </c>
       <c r="K627" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L627" s="6" t="inlineStr"/>
@@ -30902,7 +30902,7 @@
       </c>
       <c r="K628" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L628" s="3" t="inlineStr"/>
@@ -30950,7 +30950,7 @@
       </c>
       <c r="K629" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L629" s="6" t="inlineStr"/>
@@ -30998,7 +30998,7 @@
       </c>
       <c r="K630" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L630" s="3" t="inlineStr"/>
@@ -31046,7 +31046,7 @@
       </c>
       <c r="K631" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L631" s="6" t="inlineStr"/>
@@ -31094,7 +31094,7 @@
       </c>
       <c r="K632" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L632" s="3" t="inlineStr"/>
@@ -31142,7 +31142,7 @@
       </c>
       <c r="K633" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L633" s="6" t="inlineStr"/>
@@ -31190,7 +31190,7 @@
       </c>
       <c r="K634" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L634" s="3" t="inlineStr"/>
@@ -31238,7 +31238,7 @@
       </c>
       <c r="K635" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L635" s="6" t="inlineStr"/>
@@ -31286,7 +31286,7 @@
       </c>
       <c r="K636" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L636" s="3" t="inlineStr"/>
@@ -31334,7 +31334,7 @@
       </c>
       <c r="K637" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L637" s="6" t="inlineStr"/>
@@ -31382,7 +31382,7 @@
       </c>
       <c r="K638" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L638" s="3" t="inlineStr"/>
@@ -31430,7 +31430,7 @@
       </c>
       <c r="K639" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L639" s="6" t="inlineStr"/>
@@ -31478,7 +31478,7 @@
       </c>
       <c r="K640" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L640" s="3" t="inlineStr"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K641" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L641" s="6" t="inlineStr"/>
@@ -31574,7 +31574,7 @@
       </c>
       <c r="K642" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L642" s="3" t="inlineStr"/>
@@ -31622,7 +31622,7 @@
       </c>
       <c r="K643" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L643" s="6" t="inlineStr"/>
@@ -31670,7 +31670,7 @@
       </c>
       <c r="K644" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L644" s="3" t="inlineStr"/>
@@ -31718,7 +31718,7 @@
       </c>
       <c r="K645" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L645" s="6" t="inlineStr"/>
@@ -31766,7 +31766,7 @@
       </c>
       <c r="K646" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L646" s="3" t="inlineStr"/>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="K647" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L647" s="6" t="inlineStr"/>
@@ -31862,7 +31862,7 @@
       </c>
       <c r="K648" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L648" s="3" t="inlineStr"/>
@@ -31910,7 +31910,7 @@
       </c>
       <c r="K649" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L649" s="6" t="inlineStr"/>
@@ -31958,7 +31958,7 @@
       </c>
       <c r="K650" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L650" s="3" t="inlineStr"/>
@@ -32006,7 +32006,7 @@
       </c>
       <c r="K651" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L651" s="6" t="inlineStr"/>
@@ -32054,7 +32054,7 @@
       </c>
       <c r="K652" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L652" s="3" t="inlineStr"/>
@@ -32102,7 +32102,7 @@
       </c>
       <c r="K653" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L653" s="6" t="inlineStr"/>
@@ -32150,7 +32150,7 @@
       </c>
       <c r="K654" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L654" s="3" t="inlineStr"/>
@@ -32198,7 +32198,7 @@
       </c>
       <c r="K655" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L655" s="6" t="inlineStr"/>
@@ -32246,7 +32246,7 @@
       </c>
       <c r="K656" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L656" s="3" t="inlineStr"/>
@@ -32294,7 +32294,7 @@
       </c>
       <c r="K657" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L657" s="6" t="inlineStr"/>
@@ -32342,7 +32342,7 @@
       </c>
       <c r="K658" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L658" s="3" t="inlineStr"/>
@@ -32390,7 +32390,7 @@
       </c>
       <c r="K659" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L659" s="6" t="inlineStr"/>
@@ -32438,7 +32438,7 @@
       </c>
       <c r="K660" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L660" s="3" t="inlineStr"/>
@@ -32486,7 +32486,7 @@
       </c>
       <c r="K661" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L661" s="6" t="inlineStr"/>
@@ -32534,7 +32534,7 @@
       </c>
       <c r="K662" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L662" s="3" t="inlineStr"/>
@@ -32582,7 +32582,7 @@
       </c>
       <c r="K663" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L663" s="6" t="inlineStr"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K664" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L664" s="3" t="inlineStr"/>
@@ -32678,7 +32678,7 @@
       </c>
       <c r="K665" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L665" s="6" t="inlineStr"/>
@@ -32726,7 +32726,7 @@
       </c>
       <c r="K666" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L666" s="3" t="inlineStr"/>
@@ -32774,7 +32774,7 @@
       </c>
       <c r="K667" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L667" s="6" t="inlineStr"/>
@@ -32822,7 +32822,7 @@
       </c>
       <c r="K668" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L668" s="3" t="inlineStr"/>
@@ -32870,7 +32870,7 @@
       </c>
       <c r="K669" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L669" s="6" t="inlineStr"/>
@@ -32918,7 +32918,7 @@
       </c>
       <c r="K670" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L670" s="3" t="inlineStr"/>
@@ -32966,7 +32966,7 @@
       </c>
       <c r="K671" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L671" s="6" t="inlineStr"/>
@@ -33014,7 +33014,7 @@
       </c>
       <c r="K672" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L672" s="3" t="inlineStr"/>
@@ -33062,7 +33062,7 @@
       </c>
       <c r="K673" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L673" s="6" t="inlineStr"/>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="K674" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L674" s="3" t="inlineStr"/>
@@ -33158,7 +33158,7 @@
       </c>
       <c r="K675" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L675" s="6" t="inlineStr"/>
@@ -33206,7 +33206,7 @@
       </c>
       <c r="K676" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L676" s="3" t="inlineStr"/>
@@ -33254,7 +33254,7 @@
       </c>
       <c r="K677" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L677" s="6" t="inlineStr"/>
@@ -33302,7 +33302,7 @@
       </c>
       <c r="K678" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L678" s="3" t="inlineStr"/>
@@ -33350,7 +33350,7 @@
       </c>
       <c r="K679" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L679" s="6" t="inlineStr"/>
@@ -33398,7 +33398,7 @@
       </c>
       <c r="K680" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L680" s="3" t="inlineStr"/>
@@ -33446,7 +33446,7 @@
       </c>
       <c r="K681" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L681" s="6" t="inlineStr"/>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="K682" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L682" s="3" t="inlineStr"/>
@@ -33542,7 +33542,7 @@
       </c>
       <c r="K683" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L683" s="6" t="inlineStr"/>
@@ -33590,7 +33590,7 @@
       </c>
       <c r="K684" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L684" s="3" t="inlineStr"/>
@@ -33638,7 +33638,7 @@
       </c>
       <c r="K685" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L685" s="6" t="inlineStr"/>
@@ -33686,7 +33686,7 @@
       </c>
       <c r="K686" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L686" s="3" t="inlineStr"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K687" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L687" s="6" t="inlineStr"/>
@@ -33782,7 +33782,7 @@
       </c>
       <c r="K688" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L688" s="3" t="inlineStr"/>
@@ -33830,7 +33830,7 @@
       </c>
       <c r="K689" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L689" s="6" t="inlineStr"/>
@@ -33878,7 +33878,7 @@
       </c>
       <c r="K690" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L690" s="3" t="inlineStr"/>
@@ -33926,7 +33926,7 @@
       </c>
       <c r="K691" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L691" s="6" t="inlineStr"/>
@@ -33974,7 +33974,7 @@
       </c>
       <c r="K692" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L692" s="3" t="inlineStr"/>
@@ -34022,7 +34022,7 @@
       </c>
       <c r="K693" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L693" s="6" t="inlineStr"/>
@@ -34070,7 +34070,7 @@
       </c>
       <c r="K694" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L694" s="3" t="inlineStr"/>
@@ -34118,7 +34118,7 @@
       </c>
       <c r="K695" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L695" s="6" t="inlineStr"/>
@@ -34166,7 +34166,7 @@
       </c>
       <c r="K696" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L696" s="3" t="inlineStr"/>
@@ -34214,7 +34214,7 @@
       </c>
       <c r="K697" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L697" s="6" t="inlineStr"/>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="K698" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L698" s="3" t="inlineStr"/>
@@ -34310,7 +34310,7 @@
       </c>
       <c r="K699" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L699" s="6" t="inlineStr"/>
@@ -34358,7 +34358,7 @@
       </c>
       <c r="K700" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L700" s="3" t="inlineStr"/>
@@ -34406,7 +34406,7 @@
       </c>
       <c r="K701" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L701" s="6" t="inlineStr"/>
@@ -34454,7 +34454,7 @@
       </c>
       <c r="K702" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L702" s="3" t="inlineStr"/>
@@ -34502,7 +34502,7 @@
       </c>
       <c r="K703" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L703" s="6" t="inlineStr"/>
@@ -34550,7 +34550,7 @@
       </c>
       <c r="K704" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L704" s="3" t="inlineStr"/>
@@ -34598,7 +34598,7 @@
       </c>
       <c r="K705" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L705" s="6" t="inlineStr"/>
@@ -34646,7 +34646,7 @@
       </c>
       <c r="K706" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L706" s="3" t="inlineStr"/>
@@ -34694,7 +34694,7 @@
       </c>
       <c r="K707" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L707" s="6" t="inlineStr"/>
@@ -34742,7 +34742,7 @@
       </c>
       <c r="K708" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L708" s="3" t="inlineStr"/>
@@ -34790,7 +34790,7 @@
       </c>
       <c r="K709" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L709" s="6" t="inlineStr"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K710" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L710" s="3" t="inlineStr"/>
@@ -34886,7 +34886,7 @@
       </c>
       <c r="K711" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L711" s="6" t="inlineStr"/>
@@ -34934,7 +34934,7 @@
       </c>
       <c r="K712" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L712" s="3" t="inlineStr"/>
@@ -34982,7 +34982,7 @@
       </c>
       <c r="K713" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L713" s="6" t="inlineStr"/>
@@ -35030,7 +35030,7 @@
       </c>
       <c r="K714" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L714" s="3" t="inlineStr"/>
@@ -35078,7 +35078,7 @@
       </c>
       <c r="K715" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L715" s="6" t="inlineStr"/>
@@ -35126,7 +35126,7 @@
       </c>
       <c r="K716" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L716" s="3" t="inlineStr"/>
@@ -35174,7 +35174,7 @@
       </c>
       <c r="K717" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L717" s="6" t="inlineStr"/>
@@ -35222,7 +35222,7 @@
       </c>
       <c r="K718" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L718" s="3" t="inlineStr"/>
@@ -35270,7 +35270,7 @@
       </c>
       <c r="K719" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L719" s="6" t="inlineStr"/>
@@ -35318,7 +35318,7 @@
       </c>
       <c r="K720" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L720" s="3" t="inlineStr"/>
@@ -35366,7 +35366,7 @@
       </c>
       <c r="K721" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L721" s="6" t="inlineStr"/>
@@ -35414,7 +35414,7 @@
       </c>
       <c r="K722" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L722" s="3" t="inlineStr"/>
@@ -35462,7 +35462,7 @@
       </c>
       <c r="K723" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L723" s="6" t="inlineStr"/>
@@ -35510,7 +35510,7 @@
       </c>
       <c r="K724" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L724" s="3" t="inlineStr"/>
@@ -35558,7 +35558,7 @@
       </c>
       <c r="K725" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L725" s="6" t="inlineStr"/>
@@ -35606,7 +35606,7 @@
       </c>
       <c r="K726" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L726" s="3" t="inlineStr"/>
@@ -35654,7 +35654,7 @@
       </c>
       <c r="K727" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L727" s="6" t="inlineStr"/>
@@ -35702,7 +35702,7 @@
       </c>
       <c r="K728" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L728" s="3" t="inlineStr"/>
@@ -35750,7 +35750,7 @@
       </c>
       <c r="K729" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L729" s="4" t="inlineStr">
@@ -35802,7 +35802,7 @@
       </c>
       <c r="K730" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L730" s="4" t="inlineStr">
@@ -35854,7 +35854,7 @@
       </c>
       <c r="K731" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L731" s="4" t="inlineStr">
@@ -35906,7 +35906,7 @@
       </c>
       <c r="K732" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L732" s="4" t="inlineStr">
@@ -35958,7 +35958,7 @@
       </c>
       <c r="K733" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L733" s="4" t="inlineStr">
@@ -36010,7 +36010,7 @@
       </c>
       <c r="K734" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L734" s="4" t="inlineStr">
@@ -36062,7 +36062,7 @@
       </c>
       <c r="K735" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L735" s="4" t="inlineStr">
@@ -36114,7 +36114,7 @@
       </c>
       <c r="K736" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L736" s="4" t="inlineStr">
@@ -36166,7 +36166,7 @@
       </c>
       <c r="K737" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L737" s="4" t="inlineStr">
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K738" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L738" s="4" t="inlineStr">
@@ -36270,7 +36270,7 @@
       </c>
       <c r="K739" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L739" s="4" t="inlineStr">
@@ -36322,7 +36322,7 @@
       </c>
       <c r="K740" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L740" s="4" t="inlineStr">
@@ -36374,7 +36374,7 @@
       </c>
       <c r="K741" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L741" s="4" t="inlineStr">
@@ -36426,7 +36426,7 @@
       </c>
       <c r="K742" s="3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L742" s="4" t="inlineStr">
@@ -36478,7 +36478,7 @@
       </c>
       <c r="K743" s="6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="L743" s="4" t="inlineStr">

--- a/public/loop-library.xlsx
+++ b/public/loop-library.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr"/>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr"/>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr"/>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr"/>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr"/>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr"/>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr"/>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr"/>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr"/>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr"/>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr"/>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr"/>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr"/>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr"/>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr"/>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr"/>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr"/>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr"/>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr"/>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr"/>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L93" s="6" t="inlineStr"/>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr"/>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L95" s="6" t="inlineStr"/>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr"/>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L97" s="6" t="inlineStr"/>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr"/>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr"/>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr"/>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr"/>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L102" s="3" t="inlineStr"/>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L103" s="6" t="inlineStr"/>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L104" s="3" t="inlineStr"/>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L105" s="6" t="inlineStr"/>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L106" s="3" t="inlineStr"/>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L107" s="6" t="inlineStr"/>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L108" s="3" t="inlineStr"/>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L109" s="6" t="inlineStr"/>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L110" s="3" t="inlineStr"/>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L111" s="6" t="inlineStr"/>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L112" s="3" t="inlineStr"/>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L113" s="6" t="inlineStr"/>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L114" s="3" t="inlineStr"/>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L115" s="6" t="inlineStr"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="K116" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L116" s="3" t="inlineStr"/>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L117" s="6" t="inlineStr"/>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="K118" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L118" s="3" t="inlineStr"/>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L119" s="6" t="inlineStr"/>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="K120" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L120" s="3" t="inlineStr"/>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L121" s="6" t="inlineStr"/>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="K122" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L122" s="3" t="inlineStr"/>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L123" s="6" t="inlineStr"/>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="K124" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L124" s="3" t="inlineStr"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="K125" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L125" s="6" t="inlineStr"/>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="K126" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L126" s="3" t="inlineStr"/>
@@ -6854,7 +6854,7 @@
       </c>
       <c r="K127" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L127" s="6" t="inlineStr"/>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L128" s="3" t="inlineStr"/>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="K129" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L129" s="6" t="inlineStr"/>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="K130" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L130" s="3" t="inlineStr"/>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="K131" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L131" s="6" t="inlineStr"/>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L132" s="3" t="inlineStr"/>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="K133" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L133" s="6" t="inlineStr"/>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="K134" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L134" s="3" t="inlineStr"/>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="K135" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L135" s="6" t="inlineStr"/>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="K136" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L136" s="3" t="inlineStr"/>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="K137" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L137" s="6" t="inlineStr"/>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="K138" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L138" s="3" t="inlineStr"/>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="K139" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L139" s="6" t="inlineStr"/>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="K140" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L140" s="3" t="inlineStr"/>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="K141" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L141" s="6" t="inlineStr"/>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L142" s="3" t="inlineStr"/>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="K143" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L143" s="6" t="inlineStr"/>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="K144" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L144" s="3" t="inlineStr"/>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="K145" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L145" s="6" t="inlineStr"/>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="K146" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L146" s="3" t="inlineStr"/>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="K147" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L147" s="6" t="inlineStr"/>
@@ -7862,7 +7862,7 @@
       </c>
       <c r="K148" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L148" s="3" t="inlineStr"/>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="K149" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L149" s="6" t="inlineStr"/>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="K150" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L150" s="3" t="inlineStr"/>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="K151" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L151" s="6" t="inlineStr"/>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="K152" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L152" s="3" t="inlineStr"/>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="K153" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L153" s="6" t="inlineStr"/>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="K154" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L154" s="3" t="inlineStr"/>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="K155" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L155" s="6" t="inlineStr"/>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="K156" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L156" s="3" t="inlineStr"/>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K157" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L157" s="6" t="inlineStr"/>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="K158" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L158" s="3" t="inlineStr"/>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="K159" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L159" s="6" t="inlineStr"/>
@@ -8438,7 +8438,7 @@
       </c>
       <c r="K160" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L160" s="3" t="inlineStr"/>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="K161" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L161" s="6" t="inlineStr"/>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="K162" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L162" s="3" t="inlineStr"/>
@@ -8582,7 +8582,7 @@
       </c>
       <c r="K163" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L163" s="6" t="inlineStr"/>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="K164" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L164" s="3" t="inlineStr"/>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="K165" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L165" s="6" t="inlineStr"/>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="K166" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L166" s="3" t="inlineStr"/>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="K167" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L167" s="6" t="inlineStr"/>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="K168" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L168" s="3" t="inlineStr"/>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="K169" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L169" s="6" t="inlineStr"/>
@@ -8918,7 +8918,7 @@
       </c>
       <c r="K170" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L170" s="3" t="inlineStr"/>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="K171" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L171" s="6" t="inlineStr"/>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="K172" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L172" s="3" t="inlineStr"/>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="K173" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L173" s="6" t="inlineStr"/>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="K174" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L174" s="3" t="inlineStr"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="K175" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L175" s="6" t="inlineStr"/>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="K176" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L176" s="3" t="inlineStr"/>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="K177" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L177" s="6" t="inlineStr"/>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="K178" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L178" s="3" t="inlineStr"/>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="K179" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L179" s="6" t="inlineStr"/>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="K180" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L180" s="3" t="inlineStr"/>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="K181" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L181" s="6" t="inlineStr"/>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="K182" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L182" s="3" t="inlineStr"/>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="K183" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L183" s="6" t="inlineStr"/>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="K184" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L184" s="3" t="inlineStr"/>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="K185" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L185" s="6" t="inlineStr"/>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="K186" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L186" s="3" t="inlineStr"/>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="K187" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L187" s="6" t="inlineStr"/>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="K188" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L188" s="3" t="inlineStr"/>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="K189" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L189" s="6" t="inlineStr"/>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="K190" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L190" s="3" t="inlineStr"/>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="K191" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L191" s="6" t="inlineStr"/>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="K192" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L192" s="3" t="inlineStr"/>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="K193" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L193" s="6" t="inlineStr"/>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="K194" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L194" s="3" t="inlineStr"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="K195" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L195" s="6" t="inlineStr"/>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="K196" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L196" s="3" t="inlineStr"/>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="K197" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L197" s="6" t="inlineStr"/>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="K198" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L198" s="3" t="inlineStr"/>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="K199" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L199" s="6" t="inlineStr"/>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="K200" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L200" s="3" t="inlineStr"/>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="K201" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L201" s="6" t="inlineStr"/>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="K202" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L202" s="3" t="inlineStr"/>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="K203" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L203" s="6" t="inlineStr"/>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="K204" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L204" s="3" t="inlineStr"/>
@@ -10598,7 +10598,7 @@
       </c>
       <c r="K205" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L205" s="6" t="inlineStr"/>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K206" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L206" s="3" t="inlineStr"/>
@@ -10694,7 +10694,7 @@
       </c>
       <c r="K207" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L207" s="6" t="inlineStr"/>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="K208" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L208" s="3" t="inlineStr"/>
@@ -10790,7 +10790,7 @@
       </c>
       <c r="K209" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L209" s="6" t="inlineStr"/>
@@ -10838,7 +10838,7 @@
       </c>
       <c r="K210" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L210" s="3" t="inlineStr"/>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="K211" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L211" s="6" t="inlineStr"/>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="K212" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L212" s="3" t="inlineStr"/>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="K213" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L213" s="6" t="inlineStr"/>
@@ -11030,7 +11030,7 @@
       </c>
       <c r="K214" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L214" s="3" t="inlineStr"/>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="K215" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L215" s="6" t="inlineStr"/>
@@ -11126,7 +11126,7 @@
       </c>
       <c r="K216" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L216" s="3" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="K217" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L217" s="6" t="inlineStr"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="K218" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L218" s="3" t="inlineStr"/>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="K219" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L219" s="6" t="inlineStr"/>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="K220" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L220" s="3" t="inlineStr"/>
@@ -11366,7 +11366,7 @@
       </c>
       <c r="K221" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L221" s="6" t="inlineStr"/>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="K222" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L222" s="3" t="inlineStr"/>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="K223" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L223" s="6" t="inlineStr"/>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="K224" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L224" s="3" t="inlineStr"/>
@@ -11558,7 +11558,7 @@
       </c>
       <c r="K225" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L225" s="6" t="inlineStr"/>
@@ -11606,7 +11606,7 @@
       </c>
       <c r="K226" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L226" s="3" t="inlineStr"/>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="K227" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L227" s="6" t="inlineStr"/>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="K228" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L228" s="3" t="inlineStr"/>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="K229" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L229" s="6" t="inlineStr"/>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="K230" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L230" s="3" t="inlineStr"/>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="K231" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L231" s="6" t="inlineStr"/>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="K232" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L232" s="3" t="inlineStr"/>
@@ -11942,7 +11942,7 @@
       </c>
       <c r="K233" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L233" s="6" t="inlineStr"/>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="K234" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L234" s="3" t="inlineStr"/>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="K235" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L235" s="6" t="inlineStr"/>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="K236" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L236" s="3" t="inlineStr"/>
@@ -12134,7 +12134,7 @@
       </c>
       <c r="K237" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L237" s="6" t="inlineStr"/>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="K238" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L238" s="3" t="inlineStr"/>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="K239" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L239" s="6" t="inlineStr"/>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="K240" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L240" s="3" t="inlineStr"/>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="K241" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L241" s="6" t="inlineStr"/>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="K242" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L242" s="3" t="inlineStr"/>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="K243" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L243" s="6" t="inlineStr"/>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="K244" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L244" s="3" t="inlineStr"/>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="K245" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L245" s="6" t="inlineStr"/>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="K246" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L246" s="3" t="inlineStr"/>
@@ -12614,7 +12614,7 @@
       </c>
       <c r="K247" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L247" s="6" t="inlineStr"/>
@@ -12662,7 +12662,7 @@
       </c>
       <c r="K248" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L248" s="3" t="inlineStr"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="K249" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L249" s="6" t="inlineStr"/>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="K250" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L250" s="3" t="inlineStr"/>
@@ -12806,7 +12806,7 @@
       </c>
       <c r="K251" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L251" s="6" t="inlineStr"/>
@@ -12854,7 +12854,7 @@
       </c>
       <c r="K252" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L252" s="3" t="inlineStr"/>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="K253" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L253" s="6" t="inlineStr"/>
@@ -12950,7 +12950,7 @@
       </c>
       <c r="K254" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L254" s="3" t="inlineStr"/>
@@ -12998,7 +12998,7 @@
       </c>
       <c r="K255" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L255" s="6" t="inlineStr"/>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="K256" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L256" s="3" t="inlineStr"/>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="K257" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L257" s="6" t="inlineStr"/>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="K258" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L258" s="3" t="inlineStr"/>
@@ -13190,7 +13190,7 @@
       </c>
       <c r="K259" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L259" s="6" t="inlineStr"/>
@@ -13238,7 +13238,7 @@
       </c>
       <c r="K260" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L260" s="3" t="inlineStr"/>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="K261" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L261" s="6" t="inlineStr"/>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="K262" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L262" s="3" t="inlineStr"/>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="K263" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L263" s="6" t="inlineStr"/>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="K264" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L264" s="3" t="inlineStr"/>
@@ -13478,7 +13478,7 @@
       </c>
       <c r="K265" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L265" s="6" t="inlineStr"/>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="K266" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L266" s="3" t="inlineStr"/>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="K267" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L267" s="6" t="inlineStr"/>
@@ -13622,7 +13622,7 @@
       </c>
       <c r="K268" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L268" s="3" t="inlineStr"/>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="K269" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L269" s="6" t="inlineStr"/>
@@ -13718,7 +13718,7 @@
       </c>
       <c r="K270" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L270" s="3" t="inlineStr"/>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="K271" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L271" s="6" t="inlineStr"/>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="K272" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L272" s="3" t="inlineStr"/>
@@ -13862,7 +13862,7 @@
       </c>
       <c r="K273" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L273" s="6" t="inlineStr"/>
@@ -13910,7 +13910,7 @@
       </c>
       <c r="K274" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L274" s="3" t="inlineStr"/>
@@ -13958,7 +13958,7 @@
       </c>
       <c r="K275" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L275" s="6" t="inlineStr"/>
@@ -14006,7 +14006,7 @@
       </c>
       <c r="K276" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L276" s="3" t="inlineStr"/>
@@ -14054,7 +14054,7 @@
       </c>
       <c r="K277" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L277" s="6" t="inlineStr"/>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="K278" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L278" s="3" t="inlineStr"/>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="K279" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L279" s="6" t="inlineStr"/>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="K280" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L280" s="3" t="inlineStr"/>
@@ -14246,7 +14246,7 @@
       </c>
       <c r="K281" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L281" s="6" t="inlineStr"/>
@@ -14294,7 +14294,7 @@
       </c>
       <c r="K282" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L282" s="3" t="inlineStr"/>
@@ -14342,7 +14342,7 @@
       </c>
       <c r="K283" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L283" s="6" t="inlineStr"/>
@@ -14390,7 +14390,7 @@
       </c>
       <c r="K284" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L284" s="3" t="inlineStr"/>
@@ -14438,7 +14438,7 @@
       </c>
       <c r="K285" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L285" s="6" t="inlineStr"/>
@@ -14486,7 +14486,7 @@
       </c>
       <c r="K286" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L286" s="3" t="inlineStr"/>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="K287" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L287" s="6" t="inlineStr"/>
@@ -14582,7 +14582,7 @@
       </c>
       <c r="K288" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L288" s="3" t="inlineStr"/>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="K289" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L289" s="6" t="inlineStr"/>
@@ -14678,7 +14678,7 @@
       </c>
       <c r="K290" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L290" s="3" t="inlineStr"/>
@@ -14726,7 +14726,7 @@
       </c>
       <c r="K291" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L291" s="6" t="inlineStr"/>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="K292" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L292" s="3" t="inlineStr"/>
@@ -14822,7 +14822,7 @@
       </c>
       <c r="K293" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L293" s="6" t="inlineStr"/>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="K294" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L294" s="3" t="inlineStr"/>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="K295" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L295" s="6" t="inlineStr"/>
@@ -14966,7 +14966,7 @@
       </c>
       <c r="K296" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L296" s="3" t="inlineStr"/>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="K297" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L297" s="6" t="inlineStr"/>
@@ -15062,7 +15062,7 @@
       </c>
       <c r="K298" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L298" s="3" t="inlineStr"/>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="K299" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L299" s="6" t="inlineStr"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="K300" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L300" s="3" t="inlineStr"/>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="K301" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L301" s="6" t="inlineStr"/>
@@ -15254,7 +15254,7 @@
       </c>
       <c r="K302" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L302" s="3" t="inlineStr"/>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="K303" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L303" s="6" t="inlineStr"/>
@@ -15350,7 +15350,7 @@
       </c>
       <c r="K304" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L304" s="3" t="inlineStr"/>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="K305" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L305" s="6" t="inlineStr"/>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="K306" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L306" s="3" t="inlineStr"/>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="K307" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L307" s="6" t="inlineStr"/>
@@ -15542,7 +15542,7 @@
       </c>
       <c r="K308" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L308" s="3" t="inlineStr"/>
@@ -15590,7 +15590,7 @@
       </c>
       <c r="K309" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L309" s="6" t="inlineStr"/>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="K310" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L310" s="3" t="inlineStr"/>
@@ -15686,7 +15686,7 @@
       </c>
       <c r="K311" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L311" s="6" t="inlineStr"/>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="K312" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L312" s="3" t="inlineStr"/>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="K313" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L313" s="6" t="inlineStr"/>
@@ -15830,7 +15830,7 @@
       </c>
       <c r="K314" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L314" s="3" t="inlineStr"/>
@@ -15878,7 +15878,7 @@
       </c>
       <c r="K315" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L315" s="6" t="inlineStr"/>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="K316" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L316" s="3" t="inlineStr"/>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="K317" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L317" s="6" t="inlineStr"/>
@@ -16022,7 +16022,7 @@
       </c>
       <c r="K318" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L318" s="3" t="inlineStr"/>
@@ -16070,7 +16070,7 @@
       </c>
       <c r="K319" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L319" s="6" t="inlineStr"/>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="K320" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L320" s="3" t="inlineStr"/>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="K321" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L321" s="6" t="inlineStr"/>
@@ -16214,7 +16214,7 @@
       </c>
       <c r="K322" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L322" s="3" t="inlineStr"/>
@@ -16262,7 +16262,7 @@
       </c>
       <c r="K323" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L323" s="6" t="inlineStr"/>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="K324" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L324" s="3" t="inlineStr"/>
@@ -16358,7 +16358,7 @@
       </c>
       <c r="K325" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L325" s="6" t="inlineStr"/>
@@ -16406,7 +16406,7 @@
       </c>
       <c r="K326" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L326" s="3" t="inlineStr"/>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="K327" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L327" s="6" t="inlineStr"/>
@@ -16502,7 +16502,7 @@
       </c>
       <c r="K328" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L328" s="3" t="inlineStr"/>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="K329" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L329" s="6" t="inlineStr"/>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="K330" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L330" s="3" t="inlineStr"/>
@@ -16646,7 +16646,7 @@
       </c>
       <c r="K331" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L331" s="6" t="inlineStr"/>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="K332" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L332" s="3" t="inlineStr"/>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="K333" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L333" s="6" t="inlineStr"/>
@@ -16790,7 +16790,7 @@
       </c>
       <c r="K334" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L334" s="3" t="inlineStr"/>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="K335" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L335" s="6" t="inlineStr"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="K336" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L336" s="3" t="inlineStr"/>
@@ -16934,7 +16934,7 @@
       </c>
       <c r="K337" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L337" s="6" t="inlineStr"/>
@@ -16982,7 +16982,7 @@
       </c>
       <c r="K338" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L338" s="3" t="inlineStr"/>
@@ -17030,7 +17030,7 @@
       </c>
       <c r="K339" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L339" s="6" t="inlineStr"/>
@@ -17078,7 +17078,7 @@
       </c>
       <c r="K340" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L340" s="3" t="inlineStr"/>
@@ -17126,7 +17126,7 @@
       </c>
       <c r="K341" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L341" s="6" t="inlineStr"/>
@@ -17174,7 +17174,7 @@
       </c>
       <c r="K342" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L342" s="3" t="inlineStr"/>
@@ -17222,7 +17222,7 @@
       </c>
       <c r="K343" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L343" s="6" t="inlineStr"/>
@@ -17270,7 +17270,7 @@
       </c>
       <c r="K344" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L344" s="3" t="inlineStr"/>
@@ -17318,7 +17318,7 @@
       </c>
       <c r="K345" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L345" s="6" t="inlineStr"/>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="K346" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L346" s="3" t="inlineStr"/>
@@ -17414,7 +17414,7 @@
       </c>
       <c r="K347" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L347" s="6" t="inlineStr"/>
@@ -17462,7 +17462,7 @@
       </c>
       <c r="K348" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L348" s="3" t="inlineStr"/>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="K349" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L349" s="6" t="inlineStr"/>
@@ -17558,7 +17558,7 @@
       </c>
       <c r="K350" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L350" s="3" t="inlineStr"/>
@@ -17606,7 +17606,7 @@
       </c>
       <c r="K351" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L351" s="6" t="inlineStr"/>
@@ -17654,7 +17654,7 @@
       </c>
       <c r="K352" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L352" s="3" t="inlineStr"/>
@@ -17702,7 +17702,7 @@
       </c>
       <c r="K353" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L353" s="6" t="inlineStr"/>
@@ -17750,7 +17750,7 @@
       </c>
       <c r="K354" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L354" s="3" t="inlineStr"/>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="K355" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L355" s="6" t="inlineStr"/>
@@ -17846,7 +17846,7 @@
       </c>
       <c r="K356" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L356" s="3" t="inlineStr"/>
@@ -17894,7 +17894,7 @@
       </c>
       <c r="K357" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L357" s="6" t="inlineStr"/>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="K358" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L358" s="3" t="inlineStr"/>
@@ -17990,7 +17990,7 @@
       </c>
       <c r="K359" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L359" s="6" t="inlineStr"/>
@@ -18038,7 +18038,7 @@
       </c>
       <c r="K360" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L360" s="3" t="inlineStr"/>
@@ -18086,7 +18086,7 @@
       </c>
       <c r="K361" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L361" s="6" t="inlineStr"/>
@@ -18134,7 +18134,7 @@
       </c>
       <c r="K362" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L362" s="3" t="inlineStr"/>
@@ -18182,7 +18182,7 @@
       </c>
       <c r="K363" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L363" s="6" t="inlineStr"/>
@@ -18230,7 +18230,7 @@
       </c>
       <c r="K364" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L364" s="3" t="inlineStr"/>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="K365" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L365" s="6" t="inlineStr"/>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="K366" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L366" s="3" t="inlineStr"/>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="K367" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L367" s="6" t="inlineStr"/>
@@ -18422,7 +18422,7 @@
       </c>
       <c r="K368" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L368" s="3" t="inlineStr"/>
@@ -18470,7 +18470,7 @@
       </c>
       <c r="K369" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L369" s="6" t="inlineStr"/>
@@ -18518,7 +18518,7 @@
       </c>
       <c r="K370" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L370" s="3" t="inlineStr"/>
@@ -18566,7 +18566,7 @@
       </c>
       <c r="K371" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L371" s="6" t="inlineStr"/>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="K372" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L372" s="3" t="inlineStr"/>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="K373" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L373" s="6" t="inlineStr"/>
@@ -18710,7 +18710,7 @@
       </c>
       <c r="K374" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L374" s="3" t="inlineStr"/>
@@ -18758,7 +18758,7 @@
       </c>
       <c r="K375" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L375" s="6" t="inlineStr"/>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="K376" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L376" s="3" t="inlineStr"/>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="K377" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L377" s="6" t="inlineStr"/>
@@ -18902,7 +18902,7 @@
       </c>
       <c r="K378" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L378" s="3" t="inlineStr"/>
@@ -18950,7 +18950,7 @@
       </c>
       <c r="K379" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L379" s="6" t="inlineStr"/>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="K380" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L380" s="3" t="inlineStr"/>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="K381" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L381" s="6" t="inlineStr"/>
@@ -19094,7 +19094,7 @@
       </c>
       <c r="K382" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L382" s="3" t="inlineStr"/>
@@ -19142,7 +19142,7 @@
       </c>
       <c r="K383" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L383" s="6" t="inlineStr"/>
@@ -19190,7 +19190,7 @@
       </c>
       <c r="K384" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L384" s="3" t="inlineStr"/>
@@ -19238,7 +19238,7 @@
       </c>
       <c r="K385" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L385" s="6" t="inlineStr"/>
@@ -19286,7 +19286,7 @@
       </c>
       <c r="K386" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L386" s="3" t="inlineStr"/>
@@ -19334,7 +19334,7 @@
       </c>
       <c r="K387" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L387" s="6" t="inlineStr"/>
@@ -19382,7 +19382,7 @@
       </c>
       <c r="K388" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L388" s="3" t="inlineStr"/>
@@ -19430,7 +19430,7 @@
       </c>
       <c r="K389" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L389" s="6" t="inlineStr"/>
@@ -19478,7 +19478,7 @@
       </c>
       <c r="K390" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L390" s="3" t="inlineStr"/>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="K391" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L391" s="6" t="inlineStr"/>
@@ -19574,7 +19574,7 @@
       </c>
       <c r="K392" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L392" s="3" t="inlineStr"/>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="K393" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L393" s="6" t="inlineStr"/>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="K394" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L394" s="3" t="inlineStr"/>
@@ -19718,7 +19718,7 @@
       </c>
       <c r="K395" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L395" s="6" t="inlineStr"/>
@@ -19766,7 +19766,7 @@
       </c>
       <c r="K396" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L396" s="3" t="inlineStr"/>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="K397" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L397" s="6" t="inlineStr"/>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="K398" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L398" s="3" t="inlineStr"/>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="K399" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L399" s="6" t="inlineStr"/>
@@ -19958,7 +19958,7 @@
       </c>
       <c r="K400" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L400" s="3" t="inlineStr"/>
@@ -20006,7 +20006,7 @@
       </c>
       <c r="K401" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L401" s="6" t="inlineStr"/>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="K402" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L402" s="3" t="inlineStr"/>
@@ -20102,7 +20102,7 @@
       </c>
       <c r="K403" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L403" s="6" t="inlineStr"/>
@@ -20150,7 +20150,7 @@
       </c>
       <c r="K404" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L404" s="3" t="inlineStr"/>
@@ -20198,7 +20198,7 @@
       </c>
       <c r="K405" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L405" s="6" t="inlineStr"/>
@@ -20246,7 +20246,7 @@
       </c>
       <c r="K406" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L406" s="3" t="inlineStr"/>
@@ -20294,7 +20294,7 @@
       </c>
       <c r="K407" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L407" s="6" t="inlineStr"/>
@@ -20342,7 +20342,7 @@
       </c>
       <c r="K408" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L408" s="3" t="inlineStr"/>
@@ -20390,7 +20390,7 @@
       </c>
       <c r="K409" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L409" s="6" t="inlineStr"/>
@@ -20438,7 +20438,7 @@
       </c>
       <c r="K410" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L410" s="3" t="inlineStr"/>
@@ -20486,7 +20486,7 @@
       </c>
       <c r="K411" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L411" s="6" t="inlineStr"/>
@@ -20534,7 +20534,7 @@
       </c>
       <c r="K412" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L412" s="3" t="inlineStr"/>
@@ -20582,7 +20582,7 @@
       </c>
       <c r="K413" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L413" s="6" t="inlineStr"/>
@@ -20630,7 +20630,7 @@
       </c>
       <c r="K414" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L414" s="3" t="inlineStr"/>
@@ -20678,7 +20678,7 @@
       </c>
       <c r="K415" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L415" s="6" t="inlineStr"/>
@@ -20726,7 +20726,7 @@
       </c>
       <c r="K416" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L416" s="3" t="inlineStr"/>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="K417" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L417" s="6" t="inlineStr"/>
@@ -20822,7 +20822,7 @@
       </c>
       <c r="K418" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L418" s="3" t="inlineStr"/>
@@ -20870,7 +20870,7 @@
       </c>
       <c r="K419" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L419" s="6" t="inlineStr"/>
@@ -20918,7 +20918,7 @@
       </c>
       <c r="K420" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L420" s="3" t="inlineStr"/>
@@ -20966,7 +20966,7 @@
       </c>
       <c r="K421" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L421" s="6" t="inlineStr"/>
@@ -21014,7 +21014,7 @@
       </c>
       <c r="K422" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L422" s="3" t="inlineStr"/>
@@ -21062,7 +21062,7 @@
       </c>
       <c r="K423" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L423" s="6" t="inlineStr"/>
@@ -21110,7 +21110,7 @@
       </c>
       <c r="K424" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L424" s="3" t="inlineStr"/>
@@ -21158,7 +21158,7 @@
       </c>
       <c r="K425" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L425" s="6" t="inlineStr"/>
@@ -21206,7 +21206,7 @@
       </c>
       <c r="K426" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L426" s="3" t="inlineStr"/>
@@ -21254,7 +21254,7 @@
       </c>
       <c r="K427" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L427" s="6" t="inlineStr"/>
@@ -21302,7 +21302,7 @@
       </c>
       <c r="K428" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L428" s="3" t="inlineStr"/>
@@ -21350,7 +21350,7 @@
       </c>
       <c r="K429" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L429" s="6" t="inlineStr"/>
@@ -21398,7 +21398,7 @@
       </c>
       <c r="K430" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L430" s="3" t="inlineStr"/>
@@ -21446,7 +21446,7 @@
       </c>
       <c r="K431" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L431" s="6" t="inlineStr"/>
@@ -21494,7 +21494,7 @@
       </c>
       <c r="K432" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L432" s="3" t="inlineStr"/>
@@ -21542,7 +21542,7 @@
       </c>
       <c r="K433" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L433" s="6" t="inlineStr"/>
@@ -21590,7 +21590,7 @@
       </c>
       <c r="K434" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L434" s="3" t="inlineStr"/>
@@ -21638,7 +21638,7 @@
       </c>
       <c r="K435" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L435" s="6" t="inlineStr"/>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="K436" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L436" s="3" t="inlineStr"/>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="K437" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L437" s="6" t="inlineStr"/>
@@ -21782,7 +21782,7 @@
       </c>
       <c r="K438" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L438" s="3" t="inlineStr"/>
@@ -21830,7 +21830,7 @@
       </c>
       <c r="K439" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L439" s="6" t="inlineStr"/>
@@ -21878,7 +21878,7 @@
       </c>
       <c r="K440" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L440" s="3" t="inlineStr"/>
@@ -21926,7 +21926,7 @@
       </c>
       <c r="K441" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L441" s="6" t="inlineStr"/>
@@ -21974,7 +21974,7 @@
       </c>
       <c r="K442" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L442" s="3" t="inlineStr"/>
@@ -22022,7 +22022,7 @@
       </c>
       <c r="K443" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L443" s="6" t="inlineStr"/>
@@ -22070,7 +22070,7 @@
       </c>
       <c r="K444" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L444" s="3" t="inlineStr"/>
@@ -22118,7 +22118,7 @@
       </c>
       <c r="K445" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L445" s="6" t="inlineStr"/>
@@ -22166,7 +22166,7 @@
       </c>
       <c r="K446" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L446" s="3" t="inlineStr"/>
@@ -22214,7 +22214,7 @@
       </c>
       <c r="K447" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L447" s="6" t="inlineStr"/>
@@ -22262,7 +22262,7 @@
       </c>
       <c r="K448" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L448" s="3" t="inlineStr"/>
@@ -22310,7 +22310,7 @@
       </c>
       <c r="K449" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L449" s="6" t="inlineStr"/>
@@ -22358,7 +22358,7 @@
       </c>
       <c r="K450" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L450" s="3" t="inlineStr"/>
@@ -22406,7 +22406,7 @@
       </c>
       <c r="K451" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L451" s="6" t="inlineStr"/>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="K452" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L452" s="3" t="inlineStr"/>
@@ -22502,7 +22502,7 @@
       </c>
       <c r="K453" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L453" s="6" t="inlineStr"/>
@@ -22550,7 +22550,7 @@
       </c>
       <c r="K454" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L454" s="3" t="inlineStr"/>
@@ -22598,7 +22598,7 @@
       </c>
       <c r="K455" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L455" s="6" t="inlineStr"/>
@@ -22646,7 +22646,7 @@
       </c>
       <c r="K456" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L456" s="3" t="inlineStr"/>
@@ -22694,7 +22694,7 @@
       </c>
       <c r="K457" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L457" s="6" t="inlineStr"/>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="K458" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L458" s="3" t="inlineStr"/>
@@ -22790,7 +22790,7 @@
       </c>
       <c r="K459" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L459" s="6" t="inlineStr"/>
@@ -22838,7 +22838,7 @@
       </c>
       <c r="K460" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L460" s="3" t="inlineStr"/>
@@ -22886,7 +22886,7 @@
       </c>
       <c r="K461" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L461" s="6" t="inlineStr"/>
@@ -22934,7 +22934,7 @@
       </c>
       <c r="K462" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L462" s="3" t="inlineStr"/>
@@ -22982,7 +22982,7 @@
       </c>
       <c r="K463" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L463" s="6" t="inlineStr"/>
@@ -23030,7 +23030,7 @@
       </c>
       <c r="K464" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L464" s="3" t="inlineStr"/>
@@ -23078,7 +23078,7 @@
       </c>
       <c r="K465" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L465" s="6" t="inlineStr"/>
@@ -23126,7 +23126,7 @@
       </c>
       <c r="K466" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L466" s="3" t="inlineStr"/>
@@ -23174,7 +23174,7 @@
       </c>
       <c r="K467" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L467" s="6" t="inlineStr"/>
@@ -23222,7 +23222,7 @@
       </c>
       <c r="K468" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L468" s="3" t="inlineStr"/>
@@ -23270,7 +23270,7 @@
       </c>
       <c r="K469" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L469" s="6" t="inlineStr"/>
@@ -23318,7 +23318,7 @@
       </c>
       <c r="K470" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L470" s="3" t="inlineStr"/>
@@ -23366,7 +23366,7 @@
       </c>
       <c r="K471" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L471" s="6" t="inlineStr"/>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="K472" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L472" s="3" t="inlineStr"/>
@@ -23462,7 +23462,7 @@
       </c>
       <c r="K473" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L473" s="6" t="inlineStr"/>
@@ -23510,7 +23510,7 @@
       </c>
       <c r="K474" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L474" s="3" t="inlineStr"/>
@@ -23558,7 +23558,7 @@
       </c>
       <c r="K475" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L475" s="6" t="inlineStr"/>
@@ -23606,7 +23606,7 @@
       </c>
       <c r="K476" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L476" s="3" t="inlineStr"/>
@@ -23654,7 +23654,7 @@
       </c>
       <c r="K477" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L477" s="6" t="inlineStr"/>
@@ -23702,7 +23702,7 @@
       </c>
       <c r="K478" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L478" s="3" t="inlineStr"/>
@@ -23750,7 +23750,7 @@
       </c>
       <c r="K479" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L479" s="6" t="inlineStr"/>
@@ -23798,7 +23798,7 @@
       </c>
       <c r="K480" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L480" s="3" t="inlineStr"/>
@@ -23846,7 +23846,7 @@
       </c>
       <c r="K481" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L481" s="6" t="inlineStr"/>
@@ -23894,7 +23894,7 @@
       </c>
       <c r="K482" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L482" s="3" t="inlineStr"/>
@@ -23942,7 +23942,7 @@
       </c>
       <c r="K483" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L483" s="6" t="inlineStr"/>
@@ -23990,7 +23990,7 @@
       </c>
       <c r="K484" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L484" s="3" t="inlineStr"/>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="K485" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L485" s="6" t="inlineStr"/>
@@ -24086,7 +24086,7 @@
       </c>
       <c r="K486" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L486" s="3" t="inlineStr"/>
@@ -24134,7 +24134,7 @@
       </c>
       <c r="K487" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L487" s="6" t="inlineStr"/>
@@ -24182,7 +24182,7 @@
       </c>
       <c r="K488" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L488" s="3" t="inlineStr"/>
@@ -24230,7 +24230,7 @@
       </c>
       <c r="K489" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L489" s="6" t="inlineStr"/>
@@ -24278,7 +24278,7 @@
       </c>
       <c r="K490" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L490" s="3" t="inlineStr"/>
@@ -24326,7 +24326,7 @@
       </c>
       <c r="K491" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L491" s="6" t="inlineStr"/>
@@ -24374,7 +24374,7 @@
       </c>
       <c r="K492" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L492" s="3" t="inlineStr"/>
@@ -24422,7 +24422,7 @@
       </c>
       <c r="K493" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L493" s="6" t="inlineStr"/>
@@ -24470,7 +24470,7 @@
       </c>
       <c r="K494" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L494" s="3" t="inlineStr"/>
@@ -24518,7 +24518,7 @@
       </c>
       <c r="K495" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L495" s="6" t="inlineStr"/>
@@ -24566,7 +24566,7 @@
       </c>
       <c r="K496" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L496" s="3" t="inlineStr"/>
@@ -24614,7 +24614,7 @@
       </c>
       <c r="K497" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L497" s="6" t="inlineStr"/>
@@ -24662,7 +24662,7 @@
       </c>
       <c r="K498" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L498" s="3" t="inlineStr"/>
@@ -24710,7 +24710,7 @@
       </c>
       <c r="K499" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L499" s="6" t="inlineStr"/>
@@ -24758,7 +24758,7 @@
       </c>
       <c r="K500" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L500" s="3" t="inlineStr"/>
@@ -24806,7 +24806,7 @@
       </c>
       <c r="K501" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L501" s="6" t="inlineStr"/>
@@ -24854,7 +24854,7 @@
       </c>
       <c r="K502" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L502" s="3" t="inlineStr"/>
@@ -24902,7 +24902,7 @@
       </c>
       <c r="K503" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L503" s="6" t="inlineStr"/>
@@ -24950,7 +24950,7 @@
       </c>
       <c r="K504" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L504" s="3" t="inlineStr"/>
@@ -24998,7 +24998,7 @@
       </c>
       <c r="K505" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L505" s="6" t="inlineStr"/>
@@ -25046,7 +25046,7 @@
       </c>
       <c r="K506" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L506" s="3" t="inlineStr"/>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="K507" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L507" s="6" t="inlineStr"/>
@@ -25142,7 +25142,7 @@
       </c>
       <c r="K508" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L508" s="3" t="inlineStr"/>
@@ -25190,7 +25190,7 @@
       </c>
       <c r="K509" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L509" s="6" t="inlineStr"/>
@@ -25238,7 +25238,7 @@
       </c>
       <c r="K510" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L510" s="3" t="inlineStr"/>
@@ -25286,7 +25286,7 @@
       </c>
       <c r="K511" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L511" s="6" t="inlineStr"/>
@@ -25334,7 +25334,7 @@
       </c>
       <c r="K512" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L512" s="3" t="inlineStr"/>
@@ -25382,7 +25382,7 @@
       </c>
       <c r="K513" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L513" s="6" t="inlineStr"/>
@@ -25430,7 +25430,7 @@
       </c>
       <c r="K514" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L514" s="3" t="inlineStr"/>
@@ -25478,7 +25478,7 @@
       </c>
       <c r="K515" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L515" s="6" t="inlineStr"/>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="K516" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L516" s="3" t="inlineStr"/>
@@ -25574,7 +25574,7 @@
       </c>
       <c r="K517" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L517" s="6" t="inlineStr"/>
@@ -25622,7 +25622,7 @@
       </c>
       <c r="K518" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L518" s="3" t="inlineStr"/>
@@ -25670,7 +25670,7 @@
       </c>
       <c r="K519" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L519" s="6" t="inlineStr"/>
@@ -25718,7 +25718,7 @@
       </c>
       <c r="K520" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L520" s="3" t="inlineStr"/>
@@ -25766,7 +25766,7 @@
       </c>
       <c r="K521" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L521" s="6" t="inlineStr"/>
@@ -25814,7 +25814,7 @@
       </c>
       <c r="K522" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L522" s="3" t="inlineStr"/>
@@ -25862,7 +25862,7 @@
       </c>
       <c r="K523" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L523" s="6" t="inlineStr"/>
@@ -25910,7 +25910,7 @@
       </c>
       <c r="K524" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L524" s="3" t="inlineStr"/>
@@ -25958,7 +25958,7 @@
       </c>
       <c r="K525" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L525" s="6" t="inlineStr"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K526" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L526" s="3" t="inlineStr"/>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="K527" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L527" s="6" t="inlineStr"/>
@@ -26102,7 +26102,7 @@
       </c>
       <c r="K528" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L528" s="3" t="inlineStr"/>
@@ -26150,7 +26150,7 @@
       </c>
       <c r="K529" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L529" s="6" t="inlineStr"/>
@@ -26198,7 +26198,7 @@
       </c>
       <c r="K530" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L530" s="3" t="inlineStr"/>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="K531" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L531" s="6" t="inlineStr"/>
@@ -26294,7 +26294,7 @@
       </c>
       <c r="K532" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L532" s="3" t="inlineStr"/>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="K533" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L533" s="6" t="inlineStr"/>
@@ -26390,7 +26390,7 @@
       </c>
       <c r="K534" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L534" s="3" t="inlineStr"/>
@@ -26438,7 +26438,7 @@
       </c>
       <c r="K535" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L535" s="6" t="inlineStr"/>
@@ -26486,7 +26486,7 @@
       </c>
       <c r="K536" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L536" s="3" t="inlineStr"/>
@@ -26534,7 +26534,7 @@
       </c>
       <c r="K537" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L537" s="6" t="inlineStr"/>
@@ -26582,7 +26582,7 @@
       </c>
       <c r="K538" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L538" s="3" t="inlineStr"/>
@@ -26630,7 +26630,7 @@
       </c>
       <c r="K539" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L539" s="6" t="inlineStr"/>
@@ -26678,7 +26678,7 @@
       </c>
       <c r="K540" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L540" s="3" t="inlineStr"/>
@@ -26726,7 +26726,7 @@
       </c>
       <c r="K541" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L541" s="6" t="inlineStr"/>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="K542" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L542" s="3" t="inlineStr"/>
@@ -26822,7 +26822,7 @@
       </c>
       <c r="K543" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L543" s="6" t="inlineStr"/>
@@ -26870,7 +26870,7 @@
       </c>
       <c r="K544" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L544" s="3" t="inlineStr"/>
@@ -26918,7 +26918,7 @@
       </c>
       <c r="K545" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L545" s="6" t="inlineStr"/>
@@ -26966,7 +26966,7 @@
       </c>
       <c r="K546" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L546" s="3" t="inlineStr"/>
@@ -27014,7 +27014,7 @@
       </c>
       <c r="K547" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L547" s="6" t="inlineStr"/>
@@ -27062,7 +27062,7 @@
       </c>
       <c r="K548" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L548" s="3" t="inlineStr"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K549" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L549" s="6" t="inlineStr"/>
@@ -27158,7 +27158,7 @@
       </c>
       <c r="K550" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L550" s="3" t="inlineStr"/>
@@ -27206,7 +27206,7 @@
       </c>
       <c r="K551" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L551" s="6" t="inlineStr"/>
@@ -27254,7 +27254,7 @@
       </c>
       <c r="K552" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L552" s="3" t="inlineStr"/>
@@ -27302,7 +27302,7 @@
       </c>
       <c r="K553" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L553" s="6" t="inlineStr"/>
@@ -27350,7 +27350,7 @@
       </c>
       <c r="K554" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L554" s="3" t="inlineStr"/>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="K555" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L555" s="6" t="inlineStr"/>
@@ -27446,7 +27446,7 @@
       </c>
       <c r="K556" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L556" s="3" t="inlineStr"/>
@@ -27494,7 +27494,7 @@
       </c>
       <c r="K557" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L557" s="6" t="inlineStr"/>
@@ -27542,7 +27542,7 @@
       </c>
       <c r="K558" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L558" s="3" t="inlineStr"/>
@@ -27590,7 +27590,7 @@
       </c>
       <c r="K559" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L559" s="6" t="inlineStr"/>
@@ -27638,7 +27638,7 @@
       </c>
       <c r="K560" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L560" s="3" t="inlineStr"/>
@@ -27686,7 +27686,7 @@
       </c>
       <c r="K561" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L561" s="6" t="inlineStr"/>
@@ -27734,7 +27734,7 @@
       </c>
       <c r="K562" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L562" s="3" t="inlineStr"/>
@@ -27782,7 +27782,7 @@
       </c>
       <c r="K563" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L563" s="6" t="inlineStr"/>
@@ -27830,7 +27830,7 @@
       </c>
       <c r="K564" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L564" s="3" t="inlineStr"/>
@@ -27878,7 +27878,7 @@
       </c>
       <c r="K565" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L565" s="6" t="inlineStr"/>
@@ -27926,7 +27926,7 @@
       </c>
       <c r="K566" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L566" s="3" t="inlineStr"/>
@@ -27974,7 +27974,7 @@
       </c>
       <c r="K567" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L567" s="6" t="inlineStr"/>
@@ -28022,7 +28022,7 @@
       </c>
       <c r="K568" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L568" s="3" t="inlineStr"/>
@@ -28070,7 +28070,7 @@
       </c>
       <c r="K569" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L569" s="6" t="inlineStr"/>
@@ -28118,7 +28118,7 @@
       </c>
       <c r="K570" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L570" s="3" t="inlineStr"/>
@@ -28166,7 +28166,7 @@
       </c>
       <c r="K571" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L571" s="6" t="inlineStr"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K572" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L572" s="3" t="inlineStr"/>
@@ -28262,7 +28262,7 @@
       </c>
       <c r="K573" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L573" s="6" t="inlineStr"/>
@@ -28310,7 +28310,7 @@
       </c>
       <c r="K574" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L574" s="3" t="inlineStr"/>
@@ -28358,7 +28358,7 @@
       </c>
       <c r="K575" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L575" s="6" t="inlineStr"/>
@@ -28406,7 +28406,7 @@
       </c>
       <c r="K576" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L576" s="3" t="inlineStr"/>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="K577" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L577" s="6" t="inlineStr"/>
@@ -28502,7 +28502,7 @@
       </c>
       <c r="K578" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L578" s="3" t="inlineStr"/>
@@ -28550,7 +28550,7 @@
       </c>
       <c r="K579" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L579" s="6" t="inlineStr"/>
@@ -28598,7 +28598,7 @@
       </c>
       <c r="K580" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L580" s="3" t="inlineStr"/>
@@ -28646,7 +28646,7 @@
       </c>
       <c r="K581" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L581" s="6" t="inlineStr"/>
@@ -28694,7 +28694,7 @@
       </c>
       <c r="K582" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L582" s="3" t="inlineStr"/>
@@ -28742,7 +28742,7 @@
       </c>
       <c r="K583" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L583" s="6" t="inlineStr"/>
@@ -28790,7 +28790,7 @@
       </c>
       <c r="K584" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L584" s="3" t="inlineStr"/>
@@ -28838,7 +28838,7 @@
       </c>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L585" s="6" t="inlineStr"/>
@@ -28886,7 +28886,7 @@
       </c>
       <c r="K586" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L586" s="3" t="inlineStr"/>
@@ -28934,7 +28934,7 @@
       </c>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L587" s="6" t="inlineStr"/>
@@ -28982,7 +28982,7 @@
       </c>
       <c r="K588" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L588" s="3" t="inlineStr"/>
@@ -29030,7 +29030,7 @@
       </c>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L589" s="6" t="inlineStr"/>
@@ -29078,7 +29078,7 @@
       </c>
       <c r="K590" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L590" s="3" t="inlineStr"/>
@@ -29126,7 +29126,7 @@
       </c>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L591" s="6" t="inlineStr"/>
@@ -29174,7 +29174,7 @@
       </c>
       <c r="K592" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L592" s="3" t="inlineStr"/>
@@ -29222,7 +29222,7 @@
       </c>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L593" s="6" t="inlineStr"/>
@@ -29270,7 +29270,7 @@
       </c>
       <c r="K594" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L594" s="3" t="inlineStr"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L595" s="6" t="inlineStr"/>
@@ -29366,7 +29366,7 @@
       </c>
       <c r="K596" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L596" s="3" t="inlineStr"/>
@@ -29414,7 +29414,7 @@
       </c>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L597" s="6" t="inlineStr"/>
@@ -29462,7 +29462,7 @@
       </c>
       <c r="K598" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L598" s="3" t="inlineStr"/>
@@ -29510,7 +29510,7 @@
       </c>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L599" s="6" t="inlineStr"/>
@@ -29558,7 +29558,7 @@
       </c>
       <c r="K600" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L600" s="3" t="inlineStr"/>
@@ -29606,7 +29606,7 @@
       </c>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L601" s="6" t="inlineStr"/>
@@ -29654,7 +29654,7 @@
       </c>
       <c r="K602" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L602" s="3" t="inlineStr"/>
@@ -29702,7 +29702,7 @@
       </c>
       <c r="K603" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L603" s="6" t="inlineStr"/>
@@ -29750,7 +29750,7 @@
       </c>
       <c r="K604" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L604" s="3" t="inlineStr"/>
@@ -29798,7 +29798,7 @@
       </c>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr"/>
@@ -29846,7 +29846,7 @@
       </c>
       <c r="K606" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L606" s="3" t="inlineStr"/>
@@ -29894,7 +29894,7 @@
       </c>
       <c r="K607" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L607" s="6" t="inlineStr"/>
@@ -29942,7 +29942,7 @@
       </c>
       <c r="K608" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L608" s="3" t="inlineStr"/>
@@ -29990,7 +29990,7 @@
       </c>
       <c r="K609" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L609" s="6" t="inlineStr"/>
@@ -30038,7 +30038,7 @@
       </c>
       <c r="K610" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L610" s="3" t="inlineStr"/>
@@ -30086,7 +30086,7 @@
       </c>
       <c r="K611" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L611" s="6" t="inlineStr"/>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="K612" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L612" s="3" t="inlineStr"/>
@@ -30182,7 +30182,7 @@
       </c>
       <c r="K613" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L613" s="6" t="inlineStr"/>
@@ -30230,7 +30230,7 @@
       </c>
       <c r="K614" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L614" s="3" t="inlineStr"/>
@@ -30278,7 +30278,7 @@
       </c>
       <c r="K615" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L615" s="6" t="inlineStr"/>
@@ -30326,7 +30326,7 @@
       </c>
       <c r="K616" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L616" s="3" t="inlineStr"/>
@@ -30374,7 +30374,7 @@
       </c>
       <c r="K617" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L617" s="6" t="inlineStr"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K618" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L618" s="3" t="inlineStr"/>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="K619" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L619" s="6" t="inlineStr"/>
@@ -30518,7 +30518,7 @@
       </c>
       <c r="K620" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L620" s="3" t="inlineStr"/>
@@ -30566,7 +30566,7 @@
       </c>
       <c r="K621" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L621" s="6" t="inlineStr"/>
@@ -30614,7 +30614,7 @@
       </c>
       <c r="K622" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L622" s="3" t="inlineStr"/>
@@ -30662,7 +30662,7 @@
       </c>
       <c r="K623" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L623" s="6" t="inlineStr"/>
@@ -30710,7 +30710,7 @@
       </c>
       <c r="K624" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L624" s="3" t="inlineStr"/>
@@ -30758,7 +30758,7 @@
       </c>
       <c r="K625" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L625" s="6" t="inlineStr"/>
@@ -30806,7 +30806,7 @@
       </c>
       <c r="K626" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L626" s="3" t="inlineStr"/>
@@ -30854,7 +30854,7 @@
       </c>
       <c r="K627" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L627" s="6" t="inlineStr"/>
@@ -30902,7 +30902,7 @@
       </c>
       <c r="K628" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L628" s="3" t="inlineStr"/>
@@ -30950,7 +30950,7 @@
       </c>
       <c r="K629" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L629" s="6" t="inlineStr"/>
@@ -30998,7 +30998,7 @@
       </c>
       <c r="K630" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L630" s="3" t="inlineStr"/>
@@ -31046,7 +31046,7 @@
       </c>
       <c r="K631" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L631" s="6" t="inlineStr"/>
@@ -31094,7 +31094,7 @@
       </c>
       <c r="K632" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L632" s="3" t="inlineStr"/>
@@ -31142,7 +31142,7 @@
       </c>
       <c r="K633" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L633" s="6" t="inlineStr"/>
@@ -31190,7 +31190,7 @@
       </c>
       <c r="K634" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L634" s="3" t="inlineStr"/>
@@ -31238,7 +31238,7 @@
       </c>
       <c r="K635" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L635" s="6" t="inlineStr"/>
@@ -31286,7 +31286,7 @@
       </c>
       <c r="K636" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L636" s="3" t="inlineStr"/>
@@ -31334,7 +31334,7 @@
       </c>
       <c r="K637" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L637" s="6" t="inlineStr"/>
@@ -31382,7 +31382,7 @@
       </c>
       <c r="K638" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L638" s="3" t="inlineStr"/>
@@ -31430,7 +31430,7 @@
       </c>
       <c r="K639" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L639" s="6" t="inlineStr"/>
@@ -31478,7 +31478,7 @@
       </c>
       <c r="K640" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L640" s="3" t="inlineStr"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K641" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L641" s="6" t="inlineStr"/>
@@ -31574,7 +31574,7 @@
       </c>
       <c r="K642" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L642" s="3" t="inlineStr"/>
@@ -31622,7 +31622,7 @@
       </c>
       <c r="K643" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L643" s="6" t="inlineStr"/>
@@ -31670,7 +31670,7 @@
       </c>
       <c r="K644" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L644" s="3" t="inlineStr"/>
@@ -31718,7 +31718,7 @@
       </c>
       <c r="K645" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L645" s="6" t="inlineStr"/>
@@ -31766,7 +31766,7 @@
       </c>
       <c r="K646" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L646" s="3" t="inlineStr"/>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="K647" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L647" s="6" t="inlineStr"/>
@@ -31862,7 +31862,7 @@
       </c>
       <c r="K648" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L648" s="3" t="inlineStr"/>
@@ -31910,7 +31910,7 @@
       </c>
       <c r="K649" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L649" s="6" t="inlineStr"/>
@@ -31958,7 +31958,7 @@
       </c>
       <c r="K650" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L650" s="3" t="inlineStr"/>
@@ -32006,7 +32006,7 @@
       </c>
       <c r="K651" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L651" s="6" t="inlineStr"/>
@@ -32054,7 +32054,7 @@
       </c>
       <c r="K652" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L652" s="3" t="inlineStr"/>
@@ -32102,7 +32102,7 @@
       </c>
       <c r="K653" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L653" s="6" t="inlineStr"/>
@@ -32150,7 +32150,7 @@
       </c>
       <c r="K654" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L654" s="3" t="inlineStr"/>
@@ -32198,7 +32198,7 @@
       </c>
       <c r="K655" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L655" s="6" t="inlineStr"/>
@@ -32246,7 +32246,7 @@
       </c>
       <c r="K656" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L656" s="3" t="inlineStr"/>
@@ -32294,7 +32294,7 @@
       </c>
       <c r="K657" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L657" s="6" t="inlineStr"/>
@@ -32342,7 +32342,7 @@
       </c>
       <c r="K658" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L658" s="3" t="inlineStr"/>
@@ -32390,7 +32390,7 @@
       </c>
       <c r="K659" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L659" s="6" t="inlineStr"/>
@@ -32438,7 +32438,7 @@
       </c>
       <c r="K660" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L660" s="3" t="inlineStr"/>
@@ -32486,7 +32486,7 @@
       </c>
       <c r="K661" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L661" s="6" t="inlineStr"/>
@@ -32534,7 +32534,7 @@
       </c>
       <c r="K662" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L662" s="3" t="inlineStr"/>
@@ -32582,7 +32582,7 @@
       </c>
       <c r="K663" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L663" s="6" t="inlineStr"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K664" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L664" s="3" t="inlineStr"/>
@@ -32678,7 +32678,7 @@
       </c>
       <c r="K665" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L665" s="6" t="inlineStr"/>
@@ -32726,7 +32726,7 @@
       </c>
       <c r="K666" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L666" s="3" t="inlineStr"/>
@@ -32774,7 +32774,7 @@
       </c>
       <c r="K667" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L667" s="6" t="inlineStr"/>
@@ -32822,7 +32822,7 @@
       </c>
       <c r="K668" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L668" s="3" t="inlineStr"/>
@@ -32870,7 +32870,7 @@
       </c>
       <c r="K669" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L669" s="6" t="inlineStr"/>
@@ -32918,7 +32918,7 @@
       </c>
       <c r="K670" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L670" s="3" t="inlineStr"/>
@@ -32966,7 +32966,7 @@
       </c>
       <c r="K671" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L671" s="6" t="inlineStr"/>
@@ -33014,7 +33014,7 @@
       </c>
       <c r="K672" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L672" s="3" t="inlineStr"/>
@@ -33062,7 +33062,7 @@
       </c>
       <c r="K673" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L673" s="6" t="inlineStr"/>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="K674" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L674" s="3" t="inlineStr"/>
@@ -33158,7 +33158,7 @@
       </c>
       <c r="K675" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L675" s="6" t="inlineStr"/>
@@ -33206,7 +33206,7 @@
       </c>
       <c r="K676" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L676" s="3" t="inlineStr"/>
@@ -33254,7 +33254,7 @@
       </c>
       <c r="K677" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L677" s="6" t="inlineStr"/>
@@ -33302,7 +33302,7 @@
       </c>
       <c r="K678" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L678" s="3" t="inlineStr"/>
@@ -33350,7 +33350,7 @@
       </c>
       <c r="K679" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L679" s="6" t="inlineStr"/>
@@ -33398,7 +33398,7 @@
       </c>
       <c r="K680" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L680" s="3" t="inlineStr"/>
@@ -33446,7 +33446,7 @@
       </c>
       <c r="K681" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L681" s="6" t="inlineStr"/>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="K682" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L682" s="3" t="inlineStr"/>
@@ -33542,7 +33542,7 @@
       </c>
       <c r="K683" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L683" s="6" t="inlineStr"/>
@@ -33590,7 +33590,7 @@
       </c>
       <c r="K684" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L684" s="3" t="inlineStr"/>
@@ -33638,7 +33638,7 @@
       </c>
       <c r="K685" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L685" s="6" t="inlineStr"/>
@@ -33686,7 +33686,7 @@
       </c>
       <c r="K686" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L686" s="3" t="inlineStr"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K687" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L687" s="6" t="inlineStr"/>
@@ -33782,7 +33782,7 @@
       </c>
       <c r="K688" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L688" s="3" t="inlineStr"/>
@@ -33830,7 +33830,7 @@
       </c>
       <c r="K689" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L689" s="6" t="inlineStr"/>
@@ -33878,7 +33878,7 @@
       </c>
       <c r="K690" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L690" s="3" t="inlineStr"/>
@@ -33926,7 +33926,7 @@
       </c>
       <c r="K691" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L691" s="6" t="inlineStr"/>
@@ -33974,7 +33974,7 @@
       </c>
       <c r="K692" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L692" s="3" t="inlineStr"/>
@@ -34022,7 +34022,7 @@
       </c>
       <c r="K693" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L693" s="6" t="inlineStr"/>
@@ -34070,7 +34070,7 @@
       </c>
       <c r="K694" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L694" s="3" t="inlineStr"/>
@@ -34118,7 +34118,7 @@
       </c>
       <c r="K695" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L695" s="6" t="inlineStr"/>
@@ -34166,7 +34166,7 @@
       </c>
       <c r="K696" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L696" s="3" t="inlineStr"/>
@@ -34214,7 +34214,7 @@
       </c>
       <c r="K697" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L697" s="6" t="inlineStr"/>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="K698" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L698" s="3" t="inlineStr"/>
@@ -34310,7 +34310,7 @@
       </c>
       <c r="K699" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L699" s="6" t="inlineStr"/>
@@ -34358,7 +34358,7 @@
       </c>
       <c r="K700" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L700" s="3" t="inlineStr"/>
@@ -34406,7 +34406,7 @@
       </c>
       <c r="K701" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L701" s="6" t="inlineStr"/>
@@ -34454,7 +34454,7 @@
       </c>
       <c r="K702" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L702" s="3" t="inlineStr"/>
@@ -34502,7 +34502,7 @@
       </c>
       <c r="K703" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L703" s="6" t="inlineStr"/>
@@ -34550,7 +34550,7 @@
       </c>
       <c r="K704" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L704" s="3" t="inlineStr"/>
@@ -34598,7 +34598,7 @@
       </c>
       <c r="K705" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L705" s="6" t="inlineStr"/>
@@ -34646,7 +34646,7 @@
       </c>
       <c r="K706" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L706" s="3" t="inlineStr"/>
@@ -34694,7 +34694,7 @@
       </c>
       <c r="K707" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L707" s="6" t="inlineStr"/>
@@ -34742,7 +34742,7 @@
       </c>
       <c r="K708" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L708" s="3" t="inlineStr"/>
@@ -34790,7 +34790,7 @@
       </c>
       <c r="K709" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L709" s="6" t="inlineStr"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K710" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L710" s="3" t="inlineStr"/>
@@ -34886,7 +34886,7 @@
       </c>
       <c r="K711" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L711" s="6" t="inlineStr"/>
@@ -34934,7 +34934,7 @@
       </c>
       <c r="K712" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L712" s="3" t="inlineStr"/>
@@ -34982,7 +34982,7 @@
       </c>
       <c r="K713" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L713" s="6" t="inlineStr"/>
@@ -35030,7 +35030,7 @@
       </c>
       <c r="K714" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L714" s="3" t="inlineStr"/>
@@ -35078,7 +35078,7 @@
       </c>
       <c r="K715" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L715" s="6" t="inlineStr"/>
@@ -35126,7 +35126,7 @@
       </c>
       <c r="K716" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L716" s="3" t="inlineStr"/>
@@ -35174,7 +35174,7 @@
       </c>
       <c r="K717" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L717" s="6" t="inlineStr"/>
@@ -35222,7 +35222,7 @@
       </c>
       <c r="K718" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L718" s="3" t="inlineStr"/>
@@ -35270,7 +35270,7 @@
       </c>
       <c r="K719" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L719" s="6" t="inlineStr"/>
@@ -35318,7 +35318,7 @@
       </c>
       <c r="K720" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L720" s="3" t="inlineStr"/>
@@ -35366,7 +35366,7 @@
       </c>
       <c r="K721" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L721" s="6" t="inlineStr"/>
@@ -35414,7 +35414,7 @@
       </c>
       <c r="K722" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L722" s="3" t="inlineStr"/>
@@ -35462,7 +35462,7 @@
       </c>
       <c r="K723" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L723" s="6" t="inlineStr"/>
@@ -35510,7 +35510,7 @@
       </c>
       <c r="K724" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L724" s="3" t="inlineStr"/>
@@ -35558,7 +35558,7 @@
       </c>
       <c r="K725" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L725" s="6" t="inlineStr"/>
@@ -35606,7 +35606,7 @@
       </c>
       <c r="K726" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L726" s="3" t="inlineStr"/>
@@ -35654,7 +35654,7 @@
       </c>
       <c r="K727" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L727" s="6" t="inlineStr"/>
@@ -35702,7 +35702,7 @@
       </c>
       <c r="K728" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L728" s="3" t="inlineStr"/>
@@ -35750,7 +35750,7 @@
       </c>
       <c r="K729" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L729" s="4" t="inlineStr">
@@ -35802,7 +35802,7 @@
       </c>
       <c r="K730" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L730" s="4" t="inlineStr">
@@ -35854,7 +35854,7 @@
       </c>
       <c r="K731" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L731" s="4" t="inlineStr">
@@ -35906,7 +35906,7 @@
       </c>
       <c r="K732" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L732" s="4" t="inlineStr">
@@ -35958,7 +35958,7 @@
       </c>
       <c r="K733" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L733" s="4" t="inlineStr">
@@ -36010,7 +36010,7 @@
       </c>
       <c r="K734" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L734" s="4" t="inlineStr">
@@ -36062,7 +36062,7 @@
       </c>
       <c r="K735" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L735" s="4" t="inlineStr">
@@ -36114,7 +36114,7 @@
       </c>
       <c r="K736" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L736" s="4" t="inlineStr">
@@ -36166,7 +36166,7 @@
       </c>
       <c r="K737" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L737" s="4" t="inlineStr">
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K738" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L738" s="4" t="inlineStr">
@@ -36270,7 +36270,7 @@
       </c>
       <c r="K739" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L739" s="4" t="inlineStr">
@@ -36322,7 +36322,7 @@
       </c>
       <c r="K740" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L740" s="4" t="inlineStr">
@@ -36374,7 +36374,7 @@
       </c>
       <c r="K741" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L741" s="4" t="inlineStr">
@@ -36426,7 +36426,7 @@
       </c>
       <c r="K742" s="3" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L742" s="4" t="inlineStr">
@@ -36478,7 +36478,7 @@
       </c>
       <c r="K743" s="6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="L743" s="4" t="inlineStr">

--- a/public/loop-library.xlsx
+++ b/public/loop-library.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr"/>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr"/>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr"/>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr"/>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr"/>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr"/>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr"/>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr"/>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr"/>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr"/>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr"/>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr"/>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr"/>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr"/>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr"/>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr"/>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr"/>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr"/>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr"/>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr"/>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L93" s="6" t="inlineStr"/>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr"/>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L95" s="6" t="inlineStr"/>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr"/>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L97" s="6" t="inlineStr"/>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr"/>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr"/>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr"/>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr"/>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L102" s="3" t="inlineStr"/>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L103" s="6" t="inlineStr"/>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L104" s="3" t="inlineStr"/>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L105" s="6" t="inlineStr"/>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L106" s="3" t="inlineStr"/>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L107" s="6" t="inlineStr"/>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L108" s="3" t="inlineStr"/>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L109" s="6" t="inlineStr"/>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L110" s="3" t="inlineStr"/>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L111" s="6" t="inlineStr"/>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L112" s="3" t="inlineStr"/>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L113" s="6" t="inlineStr"/>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L114" s="3" t="inlineStr"/>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L115" s="6" t="inlineStr"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="K116" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L116" s="3" t="inlineStr"/>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L117" s="6" t="inlineStr"/>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="K118" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L118" s="3" t="inlineStr"/>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L119" s="6" t="inlineStr"/>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="K120" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L120" s="3" t="inlineStr"/>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L121" s="6" t="inlineStr"/>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="K122" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L122" s="3" t="inlineStr"/>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L123" s="6" t="inlineStr"/>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="K124" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L124" s="3" t="inlineStr"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="K125" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L125" s="6" t="inlineStr"/>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="K126" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L126" s="3" t="inlineStr"/>
@@ -6854,7 +6854,7 @@
       </c>
       <c r="K127" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L127" s="6" t="inlineStr"/>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L128" s="3" t="inlineStr"/>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="K129" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L129" s="6" t="inlineStr"/>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="K130" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L130" s="3" t="inlineStr"/>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="K131" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L131" s="6" t="inlineStr"/>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L132" s="3" t="inlineStr"/>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="K133" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L133" s="6" t="inlineStr"/>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="K134" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L134" s="3" t="inlineStr"/>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="K135" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L135" s="6" t="inlineStr"/>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="K136" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L136" s="3" t="inlineStr"/>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="K137" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L137" s="6" t="inlineStr"/>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="K138" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L138" s="3" t="inlineStr"/>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="K139" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L139" s="6" t="inlineStr"/>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="K140" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L140" s="3" t="inlineStr"/>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="K141" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L141" s="6" t="inlineStr"/>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L142" s="3" t="inlineStr"/>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="K143" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L143" s="6" t="inlineStr"/>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="K144" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L144" s="3" t="inlineStr"/>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="K145" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L145" s="6" t="inlineStr"/>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="K146" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L146" s="3" t="inlineStr"/>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="K147" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L147" s="6" t="inlineStr"/>
@@ -7862,7 +7862,7 @@
       </c>
       <c r="K148" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L148" s="3" t="inlineStr"/>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="K149" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L149" s="6" t="inlineStr"/>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="K150" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L150" s="3" t="inlineStr"/>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="K151" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L151" s="6" t="inlineStr"/>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="K152" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L152" s="3" t="inlineStr"/>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="K153" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L153" s="6" t="inlineStr"/>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="K154" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L154" s="3" t="inlineStr"/>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="K155" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L155" s="6" t="inlineStr"/>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="K156" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L156" s="3" t="inlineStr"/>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K157" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L157" s="6" t="inlineStr"/>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="K158" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L158" s="3" t="inlineStr"/>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="K159" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L159" s="6" t="inlineStr"/>
@@ -8438,7 +8438,7 @@
       </c>
       <c r="K160" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L160" s="3" t="inlineStr"/>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="K161" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L161" s="6" t="inlineStr"/>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="K162" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L162" s="3" t="inlineStr"/>
@@ -8582,7 +8582,7 @@
       </c>
       <c r="K163" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L163" s="6" t="inlineStr"/>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="K164" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L164" s="3" t="inlineStr"/>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="K165" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L165" s="6" t="inlineStr"/>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="K166" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L166" s="3" t="inlineStr"/>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="K167" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L167" s="6" t="inlineStr"/>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="K168" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L168" s="3" t="inlineStr"/>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="K169" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L169" s="6" t="inlineStr"/>
@@ -8918,7 +8918,7 @@
       </c>
       <c r="K170" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L170" s="3" t="inlineStr"/>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="K171" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L171" s="6" t="inlineStr"/>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="K172" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L172" s="3" t="inlineStr"/>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="K173" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L173" s="6" t="inlineStr"/>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="K174" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L174" s="3" t="inlineStr"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="K175" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L175" s="6" t="inlineStr"/>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="K176" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L176" s="3" t="inlineStr"/>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="K177" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L177" s="6" t="inlineStr"/>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="K178" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L178" s="3" t="inlineStr"/>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="K179" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L179" s="6" t="inlineStr"/>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="K180" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L180" s="3" t="inlineStr"/>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="K181" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L181" s="6" t="inlineStr"/>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="K182" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L182" s="3" t="inlineStr"/>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="K183" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L183" s="6" t="inlineStr"/>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="K184" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L184" s="3" t="inlineStr"/>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="K185" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L185" s="6" t="inlineStr"/>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="K186" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L186" s="3" t="inlineStr"/>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="K187" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L187" s="6" t="inlineStr"/>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="K188" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L188" s="3" t="inlineStr"/>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="K189" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L189" s="6" t="inlineStr"/>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="K190" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L190" s="3" t="inlineStr"/>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="K191" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L191" s="6" t="inlineStr"/>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="K192" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L192" s="3" t="inlineStr"/>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="K193" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L193" s="6" t="inlineStr"/>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="K194" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L194" s="3" t="inlineStr"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="K195" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L195" s="6" t="inlineStr"/>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="K196" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L196" s="3" t="inlineStr"/>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="K197" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L197" s="6" t="inlineStr"/>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="K198" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L198" s="3" t="inlineStr"/>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="K199" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L199" s="6" t="inlineStr"/>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="K200" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L200" s="3" t="inlineStr"/>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="K201" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L201" s="6" t="inlineStr"/>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="K202" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L202" s="3" t="inlineStr"/>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="K203" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L203" s="6" t="inlineStr"/>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="K204" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L204" s="3" t="inlineStr"/>
@@ -10598,7 +10598,7 @@
       </c>
       <c r="K205" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L205" s="6" t="inlineStr"/>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K206" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L206" s="3" t="inlineStr"/>
@@ -10694,7 +10694,7 @@
       </c>
       <c r="K207" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L207" s="6" t="inlineStr"/>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="K208" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L208" s="3" t="inlineStr"/>
@@ -10790,7 +10790,7 @@
       </c>
       <c r="K209" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L209" s="6" t="inlineStr"/>
@@ -10838,7 +10838,7 @@
       </c>
       <c r="K210" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L210" s="3" t="inlineStr"/>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="K211" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L211" s="6" t="inlineStr"/>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="K212" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L212" s="3" t="inlineStr"/>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="K213" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L213" s="6" t="inlineStr"/>
@@ -11030,7 +11030,7 @@
       </c>
       <c r="K214" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L214" s="3" t="inlineStr"/>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="K215" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L215" s="6" t="inlineStr"/>
@@ -11126,7 +11126,7 @@
       </c>
       <c r="K216" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L216" s="3" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="K217" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L217" s="6" t="inlineStr"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="K218" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L218" s="3" t="inlineStr"/>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="K219" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L219" s="6" t="inlineStr"/>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="K220" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L220" s="3" t="inlineStr"/>
@@ -11366,7 +11366,7 @@
       </c>
       <c r="K221" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L221" s="6" t="inlineStr"/>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="K222" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L222" s="3" t="inlineStr"/>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="K223" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L223" s="6" t="inlineStr"/>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="K224" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L224" s="3" t="inlineStr"/>
@@ -11558,7 +11558,7 @@
       </c>
       <c r="K225" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L225" s="6" t="inlineStr"/>
@@ -11606,7 +11606,7 @@
       </c>
       <c r="K226" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L226" s="3" t="inlineStr"/>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="K227" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L227" s="6" t="inlineStr"/>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="K228" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L228" s="3" t="inlineStr"/>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="K229" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L229" s="6" t="inlineStr"/>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="K230" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L230" s="3" t="inlineStr"/>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="K231" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L231" s="6" t="inlineStr"/>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="K232" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L232" s="3" t="inlineStr"/>
@@ -11942,7 +11942,7 @@
       </c>
       <c r="K233" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L233" s="6" t="inlineStr"/>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="K234" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L234" s="3" t="inlineStr"/>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="K235" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L235" s="6" t="inlineStr"/>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="K236" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L236" s="3" t="inlineStr"/>
@@ -12134,7 +12134,7 @@
       </c>
       <c r="K237" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L237" s="6" t="inlineStr"/>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="K238" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L238" s="3" t="inlineStr"/>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="K239" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L239" s="6" t="inlineStr"/>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="K240" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L240" s="3" t="inlineStr"/>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="K241" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L241" s="6" t="inlineStr"/>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="K242" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L242" s="3" t="inlineStr"/>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="K243" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L243" s="6" t="inlineStr"/>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="K244" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L244" s="3" t="inlineStr"/>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="K245" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L245" s="6" t="inlineStr"/>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="K246" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L246" s="3" t="inlineStr"/>
@@ -12614,7 +12614,7 @@
       </c>
       <c r="K247" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L247" s="6" t="inlineStr"/>
@@ -12662,7 +12662,7 @@
       </c>
       <c r="K248" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L248" s="3" t="inlineStr"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="K249" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L249" s="6" t="inlineStr"/>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="K250" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L250" s="3" t="inlineStr"/>
@@ -12806,7 +12806,7 @@
       </c>
       <c r="K251" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L251" s="6" t="inlineStr"/>
@@ -12854,7 +12854,7 @@
       </c>
       <c r="K252" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L252" s="3" t="inlineStr"/>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="K253" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L253" s="6" t="inlineStr"/>
@@ -12950,7 +12950,7 @@
       </c>
       <c r="K254" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L254" s="3" t="inlineStr"/>
@@ -12998,7 +12998,7 @@
       </c>
       <c r="K255" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L255" s="6" t="inlineStr"/>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="K256" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L256" s="3" t="inlineStr"/>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="K257" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L257" s="6" t="inlineStr"/>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="K258" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L258" s="3" t="inlineStr"/>
@@ -13190,7 +13190,7 @@
       </c>
       <c r="K259" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L259" s="6" t="inlineStr"/>
@@ -13238,7 +13238,7 @@
       </c>
       <c r="K260" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L260" s="3" t="inlineStr"/>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="K261" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L261" s="6" t="inlineStr"/>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="K262" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L262" s="3" t="inlineStr"/>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="K263" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L263" s="6" t="inlineStr"/>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="K264" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L264" s="3" t="inlineStr"/>
@@ -13478,7 +13478,7 @@
       </c>
       <c r="K265" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L265" s="6" t="inlineStr"/>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="K266" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L266" s="3" t="inlineStr"/>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="K267" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L267" s="6" t="inlineStr"/>
@@ -13622,7 +13622,7 @@
       </c>
       <c r="K268" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L268" s="3" t="inlineStr"/>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="K269" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L269" s="6" t="inlineStr"/>
@@ -13718,7 +13718,7 @@
       </c>
       <c r="K270" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L270" s="3" t="inlineStr"/>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="K271" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L271" s="6" t="inlineStr"/>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="K272" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L272" s="3" t="inlineStr"/>
@@ -13862,7 +13862,7 @@
       </c>
       <c r="K273" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L273" s="6" t="inlineStr"/>
@@ -13910,7 +13910,7 @@
       </c>
       <c r="K274" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L274" s="3" t="inlineStr"/>
@@ -13958,7 +13958,7 @@
       </c>
       <c r="K275" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L275" s="6" t="inlineStr"/>
@@ -14006,7 +14006,7 @@
       </c>
       <c r="K276" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L276" s="3" t="inlineStr"/>
@@ -14054,7 +14054,7 @@
       </c>
       <c r="K277" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L277" s="6" t="inlineStr"/>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="K278" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L278" s="3" t="inlineStr"/>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="K279" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L279" s="6" t="inlineStr"/>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="K280" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L280" s="3" t="inlineStr"/>
@@ -14246,7 +14246,7 @@
       </c>
       <c r="K281" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L281" s="6" t="inlineStr"/>
@@ -14294,7 +14294,7 @@
       </c>
       <c r="K282" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L282" s="3" t="inlineStr"/>
@@ -14342,7 +14342,7 @@
       </c>
       <c r="K283" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L283" s="6" t="inlineStr"/>
@@ -14390,7 +14390,7 @@
       </c>
       <c r="K284" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L284" s="3" t="inlineStr"/>
@@ -14438,7 +14438,7 @@
       </c>
       <c r="K285" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L285" s="6" t="inlineStr"/>
@@ -14486,7 +14486,7 @@
       </c>
       <c r="K286" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L286" s="3" t="inlineStr"/>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="K287" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L287" s="6" t="inlineStr"/>
@@ -14582,7 +14582,7 @@
       </c>
       <c r="K288" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L288" s="3" t="inlineStr"/>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="K289" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L289" s="6" t="inlineStr"/>
@@ -14678,7 +14678,7 @@
       </c>
       <c r="K290" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L290" s="3" t="inlineStr"/>
@@ -14726,7 +14726,7 @@
       </c>
       <c r="K291" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L291" s="6" t="inlineStr"/>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="K292" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L292" s="3" t="inlineStr"/>
@@ -14822,7 +14822,7 @@
       </c>
       <c r="K293" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L293" s="6" t="inlineStr"/>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="K294" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L294" s="3" t="inlineStr"/>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="K295" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L295" s="6" t="inlineStr"/>
@@ -14966,7 +14966,7 @@
       </c>
       <c r="K296" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L296" s="3" t="inlineStr"/>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="K297" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L297" s="6" t="inlineStr"/>
@@ -15062,7 +15062,7 @@
       </c>
       <c r="K298" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L298" s="3" t="inlineStr"/>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="K299" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L299" s="6" t="inlineStr"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="K300" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L300" s="3" t="inlineStr"/>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="K301" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L301" s="6" t="inlineStr"/>
@@ -15254,7 +15254,7 @@
       </c>
       <c r="K302" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L302" s="3" t="inlineStr"/>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="K303" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L303" s="6" t="inlineStr"/>
@@ -15350,7 +15350,7 @@
       </c>
       <c r="K304" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L304" s="3" t="inlineStr"/>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="K305" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L305" s="6" t="inlineStr"/>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="K306" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L306" s="3" t="inlineStr"/>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="K307" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L307" s="6" t="inlineStr"/>
@@ -15542,7 +15542,7 @@
       </c>
       <c r="K308" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L308" s="3" t="inlineStr"/>
@@ -15590,7 +15590,7 @@
       </c>
       <c r="K309" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L309" s="6" t="inlineStr"/>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="K310" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L310" s="3" t="inlineStr"/>
@@ -15686,7 +15686,7 @@
       </c>
       <c r="K311" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L311" s="6" t="inlineStr"/>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="K312" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L312" s="3" t="inlineStr"/>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="K313" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L313" s="6" t="inlineStr"/>
@@ -15830,7 +15830,7 @@
       </c>
       <c r="K314" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L314" s="3" t="inlineStr"/>
@@ -15878,7 +15878,7 @@
       </c>
       <c r="K315" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L315" s="6" t="inlineStr"/>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="K316" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L316" s="3" t="inlineStr"/>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="K317" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L317" s="6" t="inlineStr"/>
@@ -16022,7 +16022,7 @@
       </c>
       <c r="K318" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L318" s="3" t="inlineStr"/>
@@ -16070,7 +16070,7 @@
       </c>
       <c r="K319" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L319" s="6" t="inlineStr"/>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="K320" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L320" s="3" t="inlineStr"/>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="K321" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L321" s="6" t="inlineStr"/>
@@ -16214,7 +16214,7 @@
       </c>
       <c r="K322" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L322" s="3" t="inlineStr"/>
@@ -16262,7 +16262,7 @@
       </c>
       <c r="K323" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L323" s="6" t="inlineStr"/>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="K324" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L324" s="3" t="inlineStr"/>
@@ -16358,7 +16358,7 @@
       </c>
       <c r="K325" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L325" s="6" t="inlineStr"/>
@@ -16406,7 +16406,7 @@
       </c>
       <c r="K326" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L326" s="3" t="inlineStr"/>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="K327" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L327" s="6" t="inlineStr"/>
@@ -16502,7 +16502,7 @@
       </c>
       <c r="K328" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L328" s="3" t="inlineStr"/>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="K329" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L329" s="6" t="inlineStr"/>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="K330" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L330" s="3" t="inlineStr"/>
@@ -16646,7 +16646,7 @@
       </c>
       <c r="K331" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L331" s="6" t="inlineStr"/>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="K332" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L332" s="3" t="inlineStr"/>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="K333" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L333" s="6" t="inlineStr"/>
@@ -16790,7 +16790,7 @@
       </c>
       <c r="K334" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L334" s="3" t="inlineStr"/>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="K335" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L335" s="6" t="inlineStr"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="K336" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L336" s="3" t="inlineStr"/>
@@ -16934,7 +16934,7 @@
       </c>
       <c r="K337" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L337" s="6" t="inlineStr"/>
@@ -16982,7 +16982,7 @@
       </c>
       <c r="K338" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L338" s="3" t="inlineStr"/>
@@ -17030,7 +17030,7 @@
       </c>
       <c r="K339" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L339" s="6" t="inlineStr"/>
@@ -17078,7 +17078,7 @@
       </c>
       <c r="K340" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L340" s="3" t="inlineStr"/>
@@ -17126,7 +17126,7 @@
       </c>
       <c r="K341" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L341" s="6" t="inlineStr"/>
@@ -17174,7 +17174,7 @@
       </c>
       <c r="K342" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L342" s="3" t="inlineStr"/>
@@ -17222,7 +17222,7 @@
       </c>
       <c r="K343" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L343" s="6" t="inlineStr"/>
@@ -17270,7 +17270,7 @@
       </c>
       <c r="K344" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L344" s="3" t="inlineStr"/>
@@ -17318,7 +17318,7 @@
       </c>
       <c r="K345" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L345" s="6" t="inlineStr"/>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="K346" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L346" s="3" t="inlineStr"/>
@@ -17414,7 +17414,7 @@
       </c>
       <c r="K347" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L347" s="6" t="inlineStr"/>
@@ -17462,7 +17462,7 @@
       </c>
       <c r="K348" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L348" s="3" t="inlineStr"/>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="K349" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L349" s="6" t="inlineStr"/>
@@ -17558,7 +17558,7 @@
       </c>
       <c r="K350" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L350" s="3" t="inlineStr"/>
@@ -17606,7 +17606,7 @@
       </c>
       <c r="K351" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L351" s="6" t="inlineStr"/>
@@ -17654,7 +17654,7 @@
       </c>
       <c r="K352" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L352" s="3" t="inlineStr"/>
@@ -17702,7 +17702,7 @@
       </c>
       <c r="K353" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L353" s="6" t="inlineStr"/>
@@ -17750,7 +17750,7 @@
       </c>
       <c r="K354" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L354" s="3" t="inlineStr"/>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="K355" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L355" s="6" t="inlineStr"/>
@@ -17846,7 +17846,7 @@
       </c>
       <c r="K356" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L356" s="3" t="inlineStr"/>
@@ -17894,7 +17894,7 @@
       </c>
       <c r="K357" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L357" s="6" t="inlineStr"/>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="K358" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L358" s="3" t="inlineStr"/>
@@ -17990,7 +17990,7 @@
       </c>
       <c r="K359" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L359" s="6" t="inlineStr"/>
@@ -18038,7 +18038,7 @@
       </c>
       <c r="K360" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L360" s="3" t="inlineStr"/>
@@ -18086,7 +18086,7 @@
       </c>
       <c r="K361" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L361" s="6" t="inlineStr"/>
@@ -18134,7 +18134,7 @@
       </c>
       <c r="K362" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L362" s="3" t="inlineStr"/>
@@ -18182,7 +18182,7 @@
       </c>
       <c r="K363" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L363" s="6" t="inlineStr"/>
@@ -18230,7 +18230,7 @@
       </c>
       <c r="K364" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L364" s="3" t="inlineStr"/>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="K365" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L365" s="6" t="inlineStr"/>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="K366" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L366" s="3" t="inlineStr"/>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="K367" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L367" s="6" t="inlineStr"/>
@@ -18422,7 +18422,7 @@
       </c>
       <c r="K368" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L368" s="3" t="inlineStr"/>
@@ -18470,7 +18470,7 @@
       </c>
       <c r="K369" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L369" s="6" t="inlineStr"/>
@@ -18518,7 +18518,7 @@
       </c>
       <c r="K370" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L370" s="3" t="inlineStr"/>
@@ -18566,7 +18566,7 @@
       </c>
       <c r="K371" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L371" s="6" t="inlineStr"/>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="K372" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L372" s="3" t="inlineStr"/>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="K373" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L373" s="6" t="inlineStr"/>
@@ -18710,7 +18710,7 @@
       </c>
       <c r="K374" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L374" s="3" t="inlineStr"/>
@@ -18758,7 +18758,7 @@
       </c>
       <c r="K375" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L375" s="6" t="inlineStr"/>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="K376" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L376" s="3" t="inlineStr"/>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="K377" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L377" s="6" t="inlineStr"/>
@@ -18902,7 +18902,7 @@
       </c>
       <c r="K378" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L378" s="3" t="inlineStr"/>
@@ -18950,7 +18950,7 @@
       </c>
       <c r="K379" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L379" s="6" t="inlineStr"/>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="K380" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L380" s="3" t="inlineStr"/>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="K381" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L381" s="6" t="inlineStr"/>
@@ -19094,7 +19094,7 @@
       </c>
       <c r="K382" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L382" s="3" t="inlineStr"/>
@@ -19142,7 +19142,7 @@
       </c>
       <c r="K383" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L383" s="6" t="inlineStr"/>
@@ -19190,7 +19190,7 @@
       </c>
       <c r="K384" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L384" s="3" t="inlineStr"/>
@@ -19238,7 +19238,7 @@
       </c>
       <c r="K385" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L385" s="6" t="inlineStr"/>
@@ -19286,7 +19286,7 @@
       </c>
       <c r="K386" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L386" s="3" t="inlineStr"/>
@@ -19334,7 +19334,7 @@
       </c>
       <c r="K387" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L387" s="6" t="inlineStr"/>
@@ -19382,7 +19382,7 @@
       </c>
       <c r="K388" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L388" s="3" t="inlineStr"/>
@@ -19430,7 +19430,7 @@
       </c>
       <c r="K389" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L389" s="6" t="inlineStr"/>
@@ -19478,7 +19478,7 @@
       </c>
       <c r="K390" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L390" s="3" t="inlineStr"/>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="K391" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L391" s="6" t="inlineStr"/>
@@ -19574,7 +19574,7 @@
       </c>
       <c r="K392" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L392" s="3" t="inlineStr"/>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="K393" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L393" s="6" t="inlineStr"/>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="K394" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L394" s="3" t="inlineStr"/>
@@ -19718,7 +19718,7 @@
       </c>
       <c r="K395" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L395" s="6" t="inlineStr"/>
@@ -19766,7 +19766,7 @@
       </c>
       <c r="K396" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L396" s="3" t="inlineStr"/>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="K397" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L397" s="6" t="inlineStr"/>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="K398" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L398" s="3" t="inlineStr"/>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="K399" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L399" s="6" t="inlineStr"/>
@@ -19958,7 +19958,7 @@
       </c>
       <c r="K400" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L400" s="3" t="inlineStr"/>
@@ -20006,7 +20006,7 @@
       </c>
       <c r="K401" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L401" s="6" t="inlineStr"/>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="K402" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L402" s="3" t="inlineStr"/>
@@ -20102,7 +20102,7 @@
       </c>
       <c r="K403" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L403" s="6" t="inlineStr"/>
@@ -20150,7 +20150,7 @@
       </c>
       <c r="K404" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L404" s="3" t="inlineStr"/>
@@ -20198,7 +20198,7 @@
       </c>
       <c r="K405" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L405" s="6" t="inlineStr"/>
@@ -20246,7 +20246,7 @@
       </c>
       <c r="K406" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L406" s="3" t="inlineStr"/>
@@ -20294,7 +20294,7 @@
       </c>
       <c r="K407" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L407" s="6" t="inlineStr"/>
@@ -20342,7 +20342,7 @@
       </c>
       <c r="K408" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L408" s="3" t="inlineStr"/>
@@ -20390,7 +20390,7 @@
       </c>
       <c r="K409" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L409" s="6" t="inlineStr"/>
@@ -20438,7 +20438,7 @@
       </c>
       <c r="K410" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L410" s="3" t="inlineStr"/>
@@ -20486,7 +20486,7 @@
       </c>
       <c r="K411" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L411" s="6" t="inlineStr"/>
@@ -20534,7 +20534,7 @@
       </c>
       <c r="K412" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L412" s="3" t="inlineStr"/>
@@ -20582,7 +20582,7 @@
       </c>
       <c r="K413" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L413" s="6" t="inlineStr"/>
@@ -20630,7 +20630,7 @@
       </c>
       <c r="K414" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L414" s="3" t="inlineStr"/>
@@ -20678,7 +20678,7 @@
       </c>
       <c r="K415" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L415" s="6" t="inlineStr"/>
@@ -20726,7 +20726,7 @@
       </c>
       <c r="K416" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L416" s="3" t="inlineStr"/>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="K417" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L417" s="6" t="inlineStr"/>
@@ -20822,7 +20822,7 @@
       </c>
       <c r="K418" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L418" s="3" t="inlineStr"/>
@@ -20870,7 +20870,7 @@
       </c>
       <c r="K419" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L419" s="6" t="inlineStr"/>
@@ -20918,7 +20918,7 @@
       </c>
       <c r="K420" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L420" s="3" t="inlineStr"/>
@@ -20966,7 +20966,7 @@
       </c>
       <c r="K421" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L421" s="6" t="inlineStr"/>
@@ -21014,7 +21014,7 @@
       </c>
       <c r="K422" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L422" s="3" t="inlineStr"/>
@@ -21062,7 +21062,7 @@
       </c>
       <c r="K423" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L423" s="6" t="inlineStr"/>
@@ -21110,7 +21110,7 @@
       </c>
       <c r="K424" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L424" s="3" t="inlineStr"/>
@@ -21158,7 +21158,7 @@
       </c>
       <c r="K425" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L425" s="6" t="inlineStr"/>
@@ -21206,7 +21206,7 @@
       </c>
       <c r="K426" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L426" s="3" t="inlineStr"/>
@@ -21254,7 +21254,7 @@
       </c>
       <c r="K427" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L427" s="6" t="inlineStr"/>
@@ -21302,7 +21302,7 @@
       </c>
       <c r="K428" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L428" s="3" t="inlineStr"/>
@@ -21350,7 +21350,7 @@
       </c>
       <c r="K429" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L429" s="6" t="inlineStr"/>
@@ -21398,7 +21398,7 @@
       </c>
       <c r="K430" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L430" s="3" t="inlineStr"/>
@@ -21446,7 +21446,7 @@
       </c>
       <c r="K431" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L431" s="6" t="inlineStr"/>
@@ -21494,7 +21494,7 @@
       </c>
       <c r="K432" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L432" s="3" t="inlineStr"/>
@@ -21542,7 +21542,7 @@
       </c>
       <c r="K433" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L433" s="6" t="inlineStr"/>
@@ -21590,7 +21590,7 @@
       </c>
       <c r="K434" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L434" s="3" t="inlineStr"/>
@@ -21638,7 +21638,7 @@
       </c>
       <c r="K435" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L435" s="6" t="inlineStr"/>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="K436" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L436" s="3" t="inlineStr"/>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="K437" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L437" s="6" t="inlineStr"/>
@@ -21782,7 +21782,7 @@
       </c>
       <c r="K438" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L438" s="3" t="inlineStr"/>
@@ -21830,7 +21830,7 @@
       </c>
       <c r="K439" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L439" s="6" t="inlineStr"/>
@@ -21878,7 +21878,7 @@
       </c>
       <c r="K440" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L440" s="3" t="inlineStr"/>
@@ -21926,7 +21926,7 @@
       </c>
       <c r="K441" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L441" s="6" t="inlineStr"/>
@@ -21974,7 +21974,7 @@
       </c>
       <c r="K442" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L442" s="3" t="inlineStr"/>
@@ -22022,7 +22022,7 @@
       </c>
       <c r="K443" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L443" s="6" t="inlineStr"/>
@@ -22070,7 +22070,7 @@
       </c>
       <c r="K444" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L444" s="3" t="inlineStr"/>
@@ -22118,7 +22118,7 @@
       </c>
       <c r="K445" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L445" s="6" t="inlineStr"/>
@@ -22166,7 +22166,7 @@
       </c>
       <c r="K446" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L446" s="3" t="inlineStr"/>
@@ -22214,7 +22214,7 @@
       </c>
       <c r="K447" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L447" s="6" t="inlineStr"/>
@@ -22262,7 +22262,7 @@
       </c>
       <c r="K448" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L448" s="3" t="inlineStr"/>
@@ -22310,7 +22310,7 @@
       </c>
       <c r="K449" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L449" s="6" t="inlineStr"/>
@@ -22358,7 +22358,7 @@
       </c>
       <c r="K450" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L450" s="3" t="inlineStr"/>
@@ -22406,7 +22406,7 @@
       </c>
       <c r="K451" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L451" s="6" t="inlineStr"/>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="K452" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L452" s="3" t="inlineStr"/>
@@ -22502,7 +22502,7 @@
       </c>
       <c r="K453" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L453" s="6" t="inlineStr"/>
@@ -22550,7 +22550,7 @@
       </c>
       <c r="K454" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L454" s="3" t="inlineStr"/>
@@ -22598,7 +22598,7 @@
       </c>
       <c r="K455" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L455" s="6" t="inlineStr"/>
@@ -22646,7 +22646,7 @@
       </c>
       <c r="K456" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L456" s="3" t="inlineStr"/>
@@ -22694,7 +22694,7 @@
       </c>
       <c r="K457" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L457" s="6" t="inlineStr"/>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="K458" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L458" s="3" t="inlineStr"/>
@@ -22790,7 +22790,7 @@
       </c>
       <c r="K459" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L459" s="6" t="inlineStr"/>
@@ -22838,7 +22838,7 @@
       </c>
       <c r="K460" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L460" s="3" t="inlineStr"/>
@@ -22886,7 +22886,7 @@
       </c>
       <c r="K461" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L461" s="6" t="inlineStr"/>
@@ -22934,7 +22934,7 @@
       </c>
       <c r="K462" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L462" s="3" t="inlineStr"/>
@@ -22982,7 +22982,7 @@
       </c>
       <c r="K463" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L463" s="6" t="inlineStr"/>
@@ -23030,7 +23030,7 @@
       </c>
       <c r="K464" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L464" s="3" t="inlineStr"/>
@@ -23078,7 +23078,7 @@
       </c>
       <c r="K465" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L465" s="6" t="inlineStr"/>
@@ -23126,7 +23126,7 @@
       </c>
       <c r="K466" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L466" s="3" t="inlineStr"/>
@@ -23174,7 +23174,7 @@
       </c>
       <c r="K467" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L467" s="6" t="inlineStr"/>
@@ -23222,7 +23222,7 @@
       </c>
       <c r="K468" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L468" s="3" t="inlineStr"/>
@@ -23270,7 +23270,7 @@
       </c>
       <c r="K469" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L469" s="6" t="inlineStr"/>
@@ -23318,7 +23318,7 @@
       </c>
       <c r="K470" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L470" s="3" t="inlineStr"/>
@@ -23366,7 +23366,7 @@
       </c>
       <c r="K471" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L471" s="6" t="inlineStr"/>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="K472" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L472" s="3" t="inlineStr"/>
@@ -23462,7 +23462,7 @@
       </c>
       <c r="K473" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L473" s="6" t="inlineStr"/>
@@ -23510,7 +23510,7 @@
       </c>
       <c r="K474" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L474" s="3" t="inlineStr"/>
@@ -23558,7 +23558,7 @@
       </c>
       <c r="K475" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L475" s="6" t="inlineStr"/>
@@ -23606,7 +23606,7 @@
       </c>
       <c r="K476" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L476" s="3" t="inlineStr"/>
@@ -23654,7 +23654,7 @@
       </c>
       <c r="K477" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L477" s="6" t="inlineStr"/>
@@ -23702,7 +23702,7 @@
       </c>
       <c r="K478" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L478" s="3" t="inlineStr"/>
@@ -23750,7 +23750,7 @@
       </c>
       <c r="K479" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L479" s="6" t="inlineStr"/>
@@ -23798,7 +23798,7 @@
       </c>
       <c r="K480" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L480" s="3" t="inlineStr"/>
@@ -23846,7 +23846,7 @@
       </c>
       <c r="K481" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L481" s="6" t="inlineStr"/>
@@ -23894,7 +23894,7 @@
       </c>
       <c r="K482" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L482" s="3" t="inlineStr"/>
@@ -23942,7 +23942,7 @@
       </c>
       <c r="K483" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L483" s="6" t="inlineStr"/>
@@ -23990,7 +23990,7 @@
       </c>
       <c r="K484" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L484" s="3" t="inlineStr"/>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="K485" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L485" s="6" t="inlineStr"/>
@@ -24086,7 +24086,7 @@
       </c>
       <c r="K486" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L486" s="3" t="inlineStr"/>
@@ -24134,7 +24134,7 @@
       </c>
       <c r="K487" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L487" s="6" t="inlineStr"/>
@@ -24182,7 +24182,7 @@
       </c>
       <c r="K488" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L488" s="3" t="inlineStr"/>
@@ -24230,7 +24230,7 @@
       </c>
       <c r="K489" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L489" s="6" t="inlineStr"/>
@@ -24278,7 +24278,7 @@
       </c>
       <c r="K490" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L490" s="3" t="inlineStr"/>
@@ -24326,7 +24326,7 @@
       </c>
       <c r="K491" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L491" s="6" t="inlineStr"/>
@@ -24374,7 +24374,7 @@
       </c>
       <c r="K492" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L492" s="3" t="inlineStr"/>
@@ -24422,7 +24422,7 @@
       </c>
       <c r="K493" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L493" s="6" t="inlineStr"/>
@@ -24470,7 +24470,7 @@
       </c>
       <c r="K494" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L494" s="3" t="inlineStr"/>
@@ -24518,7 +24518,7 @@
       </c>
       <c r="K495" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L495" s="6" t="inlineStr"/>
@@ -24566,7 +24566,7 @@
       </c>
       <c r="K496" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L496" s="3" t="inlineStr"/>
@@ -24614,7 +24614,7 @@
       </c>
       <c r="K497" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L497" s="6" t="inlineStr"/>
@@ -24662,7 +24662,7 @@
       </c>
       <c r="K498" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L498" s="3" t="inlineStr"/>
@@ -24710,7 +24710,7 @@
       </c>
       <c r="K499" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L499" s="6" t="inlineStr"/>
@@ -24758,7 +24758,7 @@
       </c>
       <c r="K500" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L500" s="3" t="inlineStr"/>
@@ -24806,7 +24806,7 @@
       </c>
       <c r="K501" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L501" s="6" t="inlineStr"/>
@@ -24854,7 +24854,7 @@
       </c>
       <c r="K502" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L502" s="3" t="inlineStr"/>
@@ -24902,7 +24902,7 @@
       </c>
       <c r="K503" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L503" s="6" t="inlineStr"/>
@@ -24950,7 +24950,7 @@
       </c>
       <c r="K504" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L504" s="3" t="inlineStr"/>
@@ -24998,7 +24998,7 @@
       </c>
       <c r="K505" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L505" s="6" t="inlineStr"/>
@@ -25046,7 +25046,7 @@
       </c>
       <c r="K506" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L506" s="3" t="inlineStr"/>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="K507" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L507" s="6" t="inlineStr"/>
@@ -25142,7 +25142,7 @@
       </c>
       <c r="K508" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L508" s="3" t="inlineStr"/>
@@ -25190,7 +25190,7 @@
       </c>
       <c r="K509" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L509" s="6" t="inlineStr"/>
@@ -25238,7 +25238,7 @@
       </c>
       <c r="K510" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L510" s="3" t="inlineStr"/>
@@ -25286,7 +25286,7 @@
       </c>
       <c r="K511" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L511" s="6" t="inlineStr"/>
@@ -25334,7 +25334,7 @@
       </c>
       <c r="K512" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L512" s="3" t="inlineStr"/>
@@ -25382,7 +25382,7 @@
       </c>
       <c r="K513" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L513" s="6" t="inlineStr"/>
@@ -25430,7 +25430,7 @@
       </c>
       <c r="K514" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L514" s="3" t="inlineStr"/>
@@ -25478,7 +25478,7 @@
       </c>
       <c r="K515" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L515" s="6" t="inlineStr"/>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="K516" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L516" s="3" t="inlineStr"/>
@@ -25574,7 +25574,7 @@
       </c>
       <c r="K517" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L517" s="6" t="inlineStr"/>
@@ -25622,7 +25622,7 @@
       </c>
       <c r="K518" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L518" s="3" t="inlineStr"/>
@@ -25670,7 +25670,7 @@
       </c>
       <c r="K519" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L519" s="6" t="inlineStr"/>
@@ -25718,7 +25718,7 @@
       </c>
       <c r="K520" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L520" s="3" t="inlineStr"/>
@@ -25766,7 +25766,7 @@
       </c>
       <c r="K521" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L521" s="6" t="inlineStr"/>
@@ -25814,7 +25814,7 @@
       </c>
       <c r="K522" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L522" s="3" t="inlineStr"/>
@@ -25862,7 +25862,7 @@
       </c>
       <c r="K523" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L523" s="6" t="inlineStr"/>
@@ -25910,7 +25910,7 @@
       </c>
       <c r="K524" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L524" s="3" t="inlineStr"/>
@@ -25958,7 +25958,7 @@
       </c>
       <c r="K525" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L525" s="6" t="inlineStr"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K526" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L526" s="3" t="inlineStr"/>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="K527" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L527" s="6" t="inlineStr"/>
@@ -26102,7 +26102,7 @@
       </c>
       <c r="K528" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L528" s="3" t="inlineStr"/>
@@ -26150,7 +26150,7 @@
       </c>
       <c r="K529" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L529" s="6" t="inlineStr"/>
@@ -26198,7 +26198,7 @@
       </c>
       <c r="K530" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L530" s="3" t="inlineStr"/>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="K531" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L531" s="6" t="inlineStr"/>
@@ -26294,7 +26294,7 @@
       </c>
       <c r="K532" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L532" s="3" t="inlineStr"/>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="K533" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L533" s="6" t="inlineStr"/>
@@ -26390,7 +26390,7 @@
       </c>
       <c r="K534" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L534" s="3" t="inlineStr"/>
@@ -26438,7 +26438,7 @@
       </c>
       <c r="K535" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L535" s="6" t="inlineStr"/>
@@ -26486,7 +26486,7 @@
       </c>
       <c r="K536" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L536" s="3" t="inlineStr"/>
@@ -26534,7 +26534,7 @@
       </c>
       <c r="K537" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L537" s="6" t="inlineStr"/>
@@ -26582,7 +26582,7 @@
       </c>
       <c r="K538" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L538" s="3" t="inlineStr"/>
@@ -26630,7 +26630,7 @@
       </c>
       <c r="K539" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L539" s="6" t="inlineStr"/>
@@ -26678,7 +26678,7 @@
       </c>
       <c r="K540" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L540" s="3" t="inlineStr"/>
@@ -26726,7 +26726,7 @@
       </c>
       <c r="K541" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L541" s="6" t="inlineStr"/>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="K542" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L542" s="3" t="inlineStr"/>
@@ -26822,7 +26822,7 @@
       </c>
       <c r="K543" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L543" s="6" t="inlineStr"/>
@@ -26870,7 +26870,7 @@
       </c>
       <c r="K544" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L544" s="3" t="inlineStr"/>
@@ -26918,7 +26918,7 @@
       </c>
       <c r="K545" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L545" s="6" t="inlineStr"/>
@@ -26966,7 +26966,7 @@
       </c>
       <c r="K546" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L546" s="3" t="inlineStr"/>
@@ -27014,7 +27014,7 @@
       </c>
       <c r="K547" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L547" s="6" t="inlineStr"/>
@@ -27062,7 +27062,7 @@
       </c>
       <c r="K548" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L548" s="3" t="inlineStr"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K549" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L549" s="6" t="inlineStr"/>
@@ -27158,7 +27158,7 @@
       </c>
       <c r="K550" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L550" s="3" t="inlineStr"/>
@@ -27206,7 +27206,7 @@
       </c>
       <c r="K551" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L551" s="6" t="inlineStr"/>
@@ -27254,7 +27254,7 @@
       </c>
       <c r="K552" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L552" s="3" t="inlineStr"/>
@@ -27302,7 +27302,7 @@
       </c>
       <c r="K553" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L553" s="6" t="inlineStr"/>
@@ -27350,7 +27350,7 @@
       </c>
       <c r="K554" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L554" s="3" t="inlineStr"/>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="K555" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L555" s="6" t="inlineStr"/>
@@ -27446,7 +27446,7 @@
       </c>
       <c r="K556" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L556" s="3" t="inlineStr"/>
@@ -27494,7 +27494,7 @@
       </c>
       <c r="K557" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L557" s="6" t="inlineStr"/>
@@ -27542,7 +27542,7 @@
       </c>
       <c r="K558" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L558" s="3" t="inlineStr"/>
@@ -27590,7 +27590,7 @@
       </c>
       <c r="K559" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L559" s="6" t="inlineStr"/>
@@ -27638,7 +27638,7 @@
       </c>
       <c r="K560" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L560" s="3" t="inlineStr"/>
@@ -27686,7 +27686,7 @@
       </c>
       <c r="K561" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L561" s="6" t="inlineStr"/>
@@ -27734,7 +27734,7 @@
       </c>
       <c r="K562" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L562" s="3" t="inlineStr"/>
@@ -27782,7 +27782,7 @@
       </c>
       <c r="K563" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L563" s="6" t="inlineStr"/>
@@ -27830,7 +27830,7 @@
       </c>
       <c r="K564" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L564" s="3" t="inlineStr"/>
@@ -27878,7 +27878,7 @@
       </c>
       <c r="K565" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L565" s="6" t="inlineStr"/>
@@ -27926,7 +27926,7 @@
       </c>
       <c r="K566" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L566" s="3" t="inlineStr"/>
@@ -27974,7 +27974,7 @@
       </c>
       <c r="K567" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L567" s="6" t="inlineStr"/>
@@ -28022,7 +28022,7 @@
       </c>
       <c r="K568" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L568" s="3" t="inlineStr"/>
@@ -28070,7 +28070,7 @@
       </c>
       <c r="K569" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L569" s="6" t="inlineStr"/>
@@ -28118,7 +28118,7 @@
       </c>
       <c r="K570" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L570" s="3" t="inlineStr"/>
@@ -28166,7 +28166,7 @@
       </c>
       <c r="K571" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L571" s="6" t="inlineStr"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K572" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L572" s="3" t="inlineStr"/>
@@ -28262,7 +28262,7 @@
       </c>
       <c r="K573" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L573" s="6" t="inlineStr"/>
@@ -28310,7 +28310,7 @@
       </c>
       <c r="K574" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L574" s="3" t="inlineStr"/>
@@ -28358,7 +28358,7 @@
       </c>
       <c r="K575" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L575" s="6" t="inlineStr"/>
@@ -28406,7 +28406,7 @@
       </c>
       <c r="K576" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L576" s="3" t="inlineStr"/>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="K577" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L577" s="6" t="inlineStr"/>
@@ -28502,7 +28502,7 @@
       </c>
       <c r="K578" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L578" s="3" t="inlineStr"/>
@@ -28550,7 +28550,7 @@
       </c>
       <c r="K579" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L579" s="6" t="inlineStr"/>
@@ -28598,7 +28598,7 @@
       </c>
       <c r="K580" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L580" s="3" t="inlineStr"/>
@@ -28646,7 +28646,7 @@
       </c>
       <c r="K581" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L581" s="6" t="inlineStr"/>
@@ -28694,7 +28694,7 @@
       </c>
       <c r="K582" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L582" s="3" t="inlineStr"/>
@@ -28742,7 +28742,7 @@
       </c>
       <c r="K583" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L583" s="6" t="inlineStr"/>
@@ -28790,7 +28790,7 @@
       </c>
       <c r="K584" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L584" s="3" t="inlineStr"/>
@@ -28838,7 +28838,7 @@
       </c>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L585" s="6" t="inlineStr"/>
@@ -28886,7 +28886,7 @@
       </c>
       <c r="K586" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L586" s="3" t="inlineStr"/>
@@ -28934,7 +28934,7 @@
       </c>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L587" s="6" t="inlineStr"/>
@@ -28982,7 +28982,7 @@
       </c>
       <c r="K588" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L588" s="3" t="inlineStr"/>
@@ -29030,7 +29030,7 @@
       </c>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L589" s="6" t="inlineStr"/>
@@ -29078,7 +29078,7 @@
       </c>
       <c r="K590" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L590" s="3" t="inlineStr"/>
@@ -29126,7 +29126,7 @@
       </c>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L591" s="6" t="inlineStr"/>
@@ -29174,7 +29174,7 @@
       </c>
       <c r="K592" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L592" s="3" t="inlineStr"/>
@@ -29222,7 +29222,7 @@
       </c>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L593" s="6" t="inlineStr"/>
@@ -29270,7 +29270,7 @@
       </c>
       <c r="K594" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L594" s="3" t="inlineStr"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L595" s="6" t="inlineStr"/>
@@ -29366,7 +29366,7 @@
       </c>
       <c r="K596" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L596" s="3" t="inlineStr"/>
@@ -29414,7 +29414,7 @@
       </c>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L597" s="6" t="inlineStr"/>
@@ -29462,7 +29462,7 @@
       </c>
       <c r="K598" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L598" s="3" t="inlineStr"/>
@@ -29510,7 +29510,7 @@
       </c>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L599" s="6" t="inlineStr"/>
@@ -29558,7 +29558,7 @@
       </c>
       <c r="K600" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L600" s="3" t="inlineStr"/>
@@ -29606,7 +29606,7 @@
       </c>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L601" s="6" t="inlineStr"/>
@@ -29654,7 +29654,7 @@
       </c>
       <c r="K602" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L602" s="3" t="inlineStr"/>
@@ -29702,7 +29702,7 @@
       </c>
       <c r="K603" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L603" s="6" t="inlineStr"/>
@@ -29750,7 +29750,7 @@
       </c>
       <c r="K604" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L604" s="3" t="inlineStr"/>
@@ -29798,7 +29798,7 @@
       </c>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr"/>
@@ -29846,7 +29846,7 @@
       </c>
       <c r="K606" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L606" s="3" t="inlineStr"/>
@@ -29894,7 +29894,7 @@
       </c>
       <c r="K607" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L607" s="6" t="inlineStr"/>
@@ -29942,7 +29942,7 @@
       </c>
       <c r="K608" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L608" s="3" t="inlineStr"/>
@@ -29990,7 +29990,7 @@
       </c>
       <c r="K609" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L609" s="6" t="inlineStr"/>
@@ -30038,7 +30038,7 @@
       </c>
       <c r="K610" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L610" s="3" t="inlineStr"/>
@@ -30086,7 +30086,7 @@
       </c>
       <c r="K611" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L611" s="6" t="inlineStr"/>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="K612" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L612" s="3" t="inlineStr"/>
@@ -30182,7 +30182,7 @@
       </c>
       <c r="K613" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L613" s="6" t="inlineStr"/>
@@ -30230,7 +30230,7 @@
       </c>
       <c r="K614" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L614" s="3" t="inlineStr"/>
@@ -30278,7 +30278,7 @@
       </c>
       <c r="K615" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L615" s="6" t="inlineStr"/>
@@ -30326,7 +30326,7 @@
       </c>
       <c r="K616" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L616" s="3" t="inlineStr"/>
@@ -30374,7 +30374,7 @@
       </c>
       <c r="K617" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L617" s="6" t="inlineStr"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K618" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L618" s="3" t="inlineStr"/>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="K619" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L619" s="6" t="inlineStr"/>
@@ -30518,7 +30518,7 @@
       </c>
       <c r="K620" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L620" s="3" t="inlineStr"/>
@@ -30566,7 +30566,7 @@
       </c>
       <c r="K621" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L621" s="6" t="inlineStr"/>
@@ -30614,7 +30614,7 @@
       </c>
       <c r="K622" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L622" s="3" t="inlineStr"/>
@@ -30662,7 +30662,7 @@
       </c>
       <c r="K623" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L623" s="6" t="inlineStr"/>
@@ -30710,7 +30710,7 @@
       </c>
       <c r="K624" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L624" s="3" t="inlineStr"/>
@@ -30758,7 +30758,7 @@
       </c>
       <c r="K625" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L625" s="6" t="inlineStr"/>
@@ -30806,7 +30806,7 @@
       </c>
       <c r="K626" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L626" s="3" t="inlineStr"/>
@@ -30854,7 +30854,7 @@
       </c>
       <c r="K627" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L627" s="6" t="inlineStr"/>
@@ -30902,7 +30902,7 @@
       </c>
       <c r="K628" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L628" s="3" t="inlineStr"/>
@@ -30950,7 +30950,7 @@
       </c>
       <c r="K629" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L629" s="6" t="inlineStr"/>
@@ -30998,7 +30998,7 @@
       </c>
       <c r="K630" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L630" s="3" t="inlineStr"/>
@@ -31046,7 +31046,7 @@
       </c>
       <c r="K631" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L631" s="6" t="inlineStr"/>
@@ -31094,7 +31094,7 @@
       </c>
       <c r="K632" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L632" s="3" t="inlineStr"/>
@@ -31142,7 +31142,7 @@
       </c>
       <c r="K633" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L633" s="6" t="inlineStr"/>
@@ -31190,7 +31190,7 @@
       </c>
       <c r="K634" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L634" s="3" t="inlineStr"/>
@@ -31238,7 +31238,7 @@
       </c>
       <c r="K635" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L635" s="6" t="inlineStr"/>
@@ -31286,7 +31286,7 @@
       </c>
       <c r="K636" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L636" s="3" t="inlineStr"/>
@@ -31334,7 +31334,7 @@
       </c>
       <c r="K637" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L637" s="6" t="inlineStr"/>
@@ -31382,7 +31382,7 @@
       </c>
       <c r="K638" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L638" s="3" t="inlineStr"/>
@@ -31430,7 +31430,7 @@
       </c>
       <c r="K639" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L639" s="6" t="inlineStr"/>
@@ -31478,7 +31478,7 @@
       </c>
       <c r="K640" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L640" s="3" t="inlineStr"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K641" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L641" s="6" t="inlineStr"/>
@@ -31574,7 +31574,7 @@
       </c>
       <c r="K642" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L642" s="3" t="inlineStr"/>
@@ -31622,7 +31622,7 @@
       </c>
       <c r="K643" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L643" s="6" t="inlineStr"/>
@@ -31670,7 +31670,7 @@
       </c>
       <c r="K644" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L644" s="3" t="inlineStr"/>
@@ -31718,7 +31718,7 @@
       </c>
       <c r="K645" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L645" s="6" t="inlineStr"/>
@@ -31766,7 +31766,7 @@
       </c>
       <c r="K646" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L646" s="3" t="inlineStr"/>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="K647" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L647" s="6" t="inlineStr"/>
@@ -31862,7 +31862,7 @@
       </c>
       <c r="K648" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L648" s="3" t="inlineStr"/>
@@ -31910,7 +31910,7 @@
       </c>
       <c r="K649" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L649" s="6" t="inlineStr"/>
@@ -31958,7 +31958,7 @@
       </c>
       <c r="K650" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L650" s="3" t="inlineStr"/>
@@ -32006,7 +32006,7 @@
       </c>
       <c r="K651" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L651" s="6" t="inlineStr"/>
@@ -32054,7 +32054,7 @@
       </c>
       <c r="K652" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L652" s="3" t="inlineStr"/>
@@ -32102,7 +32102,7 @@
       </c>
       <c r="K653" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L653" s="6" t="inlineStr"/>
@@ -32150,7 +32150,7 @@
       </c>
       <c r="K654" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L654" s="3" t="inlineStr"/>
@@ -32198,7 +32198,7 @@
       </c>
       <c r="K655" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L655" s="6" t="inlineStr"/>
@@ -32246,7 +32246,7 @@
       </c>
       <c r="K656" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L656" s="3" t="inlineStr"/>
@@ -32294,7 +32294,7 @@
       </c>
       <c r="K657" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L657" s="6" t="inlineStr"/>
@@ -32342,7 +32342,7 @@
       </c>
       <c r="K658" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L658" s="3" t="inlineStr"/>
@@ -32390,7 +32390,7 @@
       </c>
       <c r="K659" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L659" s="6" t="inlineStr"/>
@@ -32438,7 +32438,7 @@
       </c>
       <c r="K660" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L660" s="3" t="inlineStr"/>
@@ -32486,7 +32486,7 @@
       </c>
       <c r="K661" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L661" s="6" t="inlineStr"/>
@@ -32534,7 +32534,7 @@
       </c>
       <c r="K662" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L662" s="3" t="inlineStr"/>
@@ -32582,7 +32582,7 @@
       </c>
       <c r="K663" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L663" s="6" t="inlineStr"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K664" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L664" s="3" t="inlineStr"/>
@@ -32678,7 +32678,7 @@
       </c>
       <c r="K665" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L665" s="6" t="inlineStr"/>
@@ -32726,7 +32726,7 @@
       </c>
       <c r="K666" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L666" s="3" t="inlineStr"/>
@@ -32774,7 +32774,7 @@
       </c>
       <c r="K667" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L667" s="6" t="inlineStr"/>
@@ -32822,7 +32822,7 @@
       </c>
       <c r="K668" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L668" s="3" t="inlineStr"/>
@@ -32870,7 +32870,7 @@
       </c>
       <c r="K669" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L669" s="6" t="inlineStr"/>
@@ -32918,7 +32918,7 @@
       </c>
       <c r="K670" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L670" s="3" t="inlineStr"/>
@@ -32966,7 +32966,7 @@
       </c>
       <c r="K671" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L671" s="6" t="inlineStr"/>
@@ -33014,7 +33014,7 @@
       </c>
       <c r="K672" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L672" s="3" t="inlineStr"/>
@@ -33062,7 +33062,7 @@
       </c>
       <c r="K673" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L673" s="6" t="inlineStr"/>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="K674" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L674" s="3" t="inlineStr"/>
@@ -33158,7 +33158,7 @@
       </c>
       <c r="K675" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L675" s="6" t="inlineStr"/>
@@ -33206,7 +33206,7 @@
       </c>
       <c r="K676" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L676" s="3" t="inlineStr"/>
@@ -33254,7 +33254,7 @@
       </c>
       <c r="K677" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L677" s="6" t="inlineStr"/>
@@ -33302,7 +33302,7 @@
       </c>
       <c r="K678" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L678" s="3" t="inlineStr"/>
@@ -33350,7 +33350,7 @@
       </c>
       <c r="K679" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L679" s="6" t="inlineStr"/>
@@ -33398,7 +33398,7 @@
       </c>
       <c r="K680" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L680" s="3" t="inlineStr"/>
@@ -33446,7 +33446,7 @@
       </c>
       <c r="K681" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L681" s="6" t="inlineStr"/>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="K682" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L682" s="3" t="inlineStr"/>
@@ -33542,7 +33542,7 @@
       </c>
       <c r="K683" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L683" s="6" t="inlineStr"/>
@@ -33590,7 +33590,7 @@
       </c>
       <c r="K684" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L684" s="3" t="inlineStr"/>
@@ -33638,7 +33638,7 @@
       </c>
       <c r="K685" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L685" s="6" t="inlineStr"/>
@@ -33686,7 +33686,7 @@
       </c>
       <c r="K686" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L686" s="3" t="inlineStr"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K687" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L687" s="6" t="inlineStr"/>
@@ -33782,7 +33782,7 @@
       </c>
       <c r="K688" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L688" s="3" t="inlineStr"/>
@@ -33830,7 +33830,7 @@
       </c>
       <c r="K689" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L689" s="6" t="inlineStr"/>
@@ -33878,7 +33878,7 @@
       </c>
       <c r="K690" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L690" s="3" t="inlineStr"/>
@@ -33926,7 +33926,7 @@
       </c>
       <c r="K691" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L691" s="6" t="inlineStr"/>
@@ -33974,7 +33974,7 @@
       </c>
       <c r="K692" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L692" s="3" t="inlineStr"/>
@@ -34022,7 +34022,7 @@
       </c>
       <c r="K693" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L693" s="6" t="inlineStr"/>
@@ -34070,7 +34070,7 @@
       </c>
       <c r="K694" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L694" s="3" t="inlineStr"/>
@@ -34118,7 +34118,7 @@
       </c>
       <c r="K695" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L695" s="6" t="inlineStr"/>
@@ -34166,7 +34166,7 @@
       </c>
       <c r="K696" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L696" s="3" t="inlineStr"/>
@@ -34214,7 +34214,7 @@
       </c>
       <c r="K697" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L697" s="6" t="inlineStr"/>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="K698" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L698" s="3" t="inlineStr"/>
@@ -34310,7 +34310,7 @@
       </c>
       <c r="K699" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L699" s="6" t="inlineStr"/>
@@ -34358,7 +34358,7 @@
       </c>
       <c r="K700" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L700" s="3" t="inlineStr"/>
@@ -34406,7 +34406,7 @@
       </c>
       <c r="K701" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L701" s="6" t="inlineStr"/>
@@ -34454,7 +34454,7 @@
       </c>
       <c r="K702" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L702" s="3" t="inlineStr"/>
@@ -34502,7 +34502,7 @@
       </c>
       <c r="K703" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L703" s="6" t="inlineStr"/>
@@ -34550,7 +34550,7 @@
       </c>
       <c r="K704" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L704" s="3" t="inlineStr"/>
@@ -34598,7 +34598,7 @@
       </c>
       <c r="K705" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L705" s="6" t="inlineStr"/>
@@ -34646,7 +34646,7 @@
       </c>
       <c r="K706" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L706" s="3" t="inlineStr"/>
@@ -34694,7 +34694,7 @@
       </c>
       <c r="K707" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L707" s="6" t="inlineStr"/>
@@ -34742,7 +34742,7 @@
       </c>
       <c r="K708" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L708" s="3" t="inlineStr"/>
@@ -34790,7 +34790,7 @@
       </c>
       <c r="K709" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L709" s="6" t="inlineStr"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K710" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L710" s="3" t="inlineStr"/>
@@ -34886,7 +34886,7 @@
       </c>
       <c r="K711" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L711" s="6" t="inlineStr"/>
@@ -34934,7 +34934,7 @@
       </c>
       <c r="K712" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L712" s="3" t="inlineStr"/>
@@ -34982,7 +34982,7 @@
       </c>
       <c r="K713" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L713" s="6" t="inlineStr"/>
@@ -35030,7 +35030,7 @@
       </c>
       <c r="K714" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L714" s="3" t="inlineStr"/>
@@ -35078,7 +35078,7 @@
       </c>
       <c r="K715" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L715" s="6" t="inlineStr"/>
@@ -35126,7 +35126,7 @@
       </c>
       <c r="K716" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L716" s="3" t="inlineStr"/>
@@ -35174,7 +35174,7 @@
       </c>
       <c r="K717" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L717" s="6" t="inlineStr"/>
@@ -35222,7 +35222,7 @@
       </c>
       <c r="K718" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L718" s="3" t="inlineStr"/>
@@ -35270,7 +35270,7 @@
       </c>
       <c r="K719" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L719" s="6" t="inlineStr"/>
@@ -35318,7 +35318,7 @@
       </c>
       <c r="K720" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L720" s="3" t="inlineStr"/>
@@ -35366,7 +35366,7 @@
       </c>
       <c r="K721" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L721" s="6" t="inlineStr"/>
@@ -35414,7 +35414,7 @@
       </c>
       <c r="K722" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L722" s="3" t="inlineStr"/>
@@ -35462,7 +35462,7 @@
       </c>
       <c r="K723" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L723" s="6" t="inlineStr"/>
@@ -35510,7 +35510,7 @@
       </c>
       <c r="K724" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L724" s="3" t="inlineStr"/>
@@ -35558,7 +35558,7 @@
       </c>
       <c r="K725" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L725" s="6" t="inlineStr"/>
@@ -35606,7 +35606,7 @@
       </c>
       <c r="K726" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L726" s="3" t="inlineStr"/>
@@ -35654,7 +35654,7 @@
       </c>
       <c r="K727" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L727" s="6" t="inlineStr"/>
@@ -35702,7 +35702,7 @@
       </c>
       <c r="K728" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L728" s="3" t="inlineStr"/>
@@ -35750,7 +35750,7 @@
       </c>
       <c r="K729" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L729" s="4" t="inlineStr">
@@ -35802,7 +35802,7 @@
       </c>
       <c r="K730" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L730" s="4" t="inlineStr">
@@ -35854,7 +35854,7 @@
       </c>
       <c r="K731" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L731" s="4" t="inlineStr">
@@ -35906,7 +35906,7 @@
       </c>
       <c r="K732" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L732" s="4" t="inlineStr">
@@ -35958,7 +35958,7 @@
       </c>
       <c r="K733" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L733" s="4" t="inlineStr">
@@ -36010,7 +36010,7 @@
       </c>
       <c r="K734" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L734" s="4" t="inlineStr">
@@ -36062,7 +36062,7 @@
       </c>
       <c r="K735" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L735" s="4" t="inlineStr">
@@ -36114,7 +36114,7 @@
       </c>
       <c r="K736" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L736" s="4" t="inlineStr">
@@ -36166,7 +36166,7 @@
       </c>
       <c r="K737" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L737" s="4" t="inlineStr">
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K738" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L738" s="4" t="inlineStr">
@@ -36270,7 +36270,7 @@
       </c>
       <c r="K739" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L739" s="4" t="inlineStr">
@@ -36322,7 +36322,7 @@
       </c>
       <c r="K740" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L740" s="4" t="inlineStr">
@@ -36374,7 +36374,7 @@
       </c>
       <c r="K741" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L741" s="4" t="inlineStr">
@@ -36426,7 +36426,7 @@
       </c>
       <c r="K742" s="3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L742" s="4" t="inlineStr">
@@ -36478,7 +36478,7 @@
       </c>
       <c r="K743" s="6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="L743" s="4" t="inlineStr">

--- a/public/loop-library.xlsx
+++ b/public/loop-library.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr"/>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr"/>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr"/>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr"/>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr"/>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr"/>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr"/>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr"/>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr"/>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr"/>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr"/>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr"/>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr"/>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr"/>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr"/>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr"/>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr"/>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr"/>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr"/>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr"/>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L93" s="6" t="inlineStr"/>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr"/>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L95" s="6" t="inlineStr"/>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr"/>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L97" s="6" t="inlineStr"/>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr"/>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr"/>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr"/>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr"/>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L102" s="3" t="inlineStr"/>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L103" s="6" t="inlineStr"/>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L104" s="3" t="inlineStr"/>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L105" s="6" t="inlineStr"/>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L106" s="3" t="inlineStr"/>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L107" s="6" t="inlineStr"/>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L108" s="3" t="inlineStr"/>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L109" s="6" t="inlineStr"/>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L110" s="3" t="inlineStr"/>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L111" s="6" t="inlineStr"/>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L112" s="3" t="inlineStr"/>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L113" s="6" t="inlineStr"/>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L114" s="3" t="inlineStr"/>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L115" s="6" t="inlineStr"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="K116" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L116" s="3" t="inlineStr"/>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L117" s="6" t="inlineStr"/>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="K118" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L118" s="3" t="inlineStr"/>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L119" s="6" t="inlineStr"/>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="K120" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L120" s="3" t="inlineStr"/>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L121" s="6" t="inlineStr"/>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="K122" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L122" s="3" t="inlineStr"/>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L123" s="6" t="inlineStr"/>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="K124" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L124" s="3" t="inlineStr"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="K125" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L125" s="6" t="inlineStr"/>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="K126" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L126" s="3" t="inlineStr"/>
@@ -6854,7 +6854,7 @@
       </c>
       <c r="K127" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L127" s="6" t="inlineStr"/>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L128" s="3" t="inlineStr"/>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="K129" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L129" s="6" t="inlineStr"/>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="K130" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L130" s="3" t="inlineStr"/>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="K131" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L131" s="6" t="inlineStr"/>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L132" s="3" t="inlineStr"/>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="K133" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L133" s="6" t="inlineStr"/>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="K134" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L134" s="3" t="inlineStr"/>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="K135" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L135" s="6" t="inlineStr"/>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="K136" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L136" s="3" t="inlineStr"/>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="K137" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L137" s="6" t="inlineStr"/>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="K138" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L138" s="3" t="inlineStr"/>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="K139" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L139" s="6" t="inlineStr"/>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="K140" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L140" s="3" t="inlineStr"/>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="K141" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L141" s="6" t="inlineStr"/>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L142" s="3" t="inlineStr"/>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="K143" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L143" s="6" t="inlineStr"/>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="K144" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L144" s="3" t="inlineStr"/>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="K145" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L145" s="6" t="inlineStr"/>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="K146" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L146" s="3" t="inlineStr"/>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="K147" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L147" s="6" t="inlineStr"/>
@@ -7862,7 +7862,7 @@
       </c>
       <c r="K148" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L148" s="3" t="inlineStr"/>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="K149" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L149" s="6" t="inlineStr"/>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="K150" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L150" s="3" t="inlineStr"/>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="K151" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L151" s="6" t="inlineStr"/>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="K152" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L152" s="3" t="inlineStr"/>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="K153" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L153" s="6" t="inlineStr"/>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="K154" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L154" s="3" t="inlineStr"/>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="K155" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L155" s="6" t="inlineStr"/>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="K156" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L156" s="3" t="inlineStr"/>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K157" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L157" s="6" t="inlineStr"/>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="K158" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L158" s="3" t="inlineStr"/>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="K159" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L159" s="6" t="inlineStr"/>
@@ -8438,7 +8438,7 @@
       </c>
       <c r="K160" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L160" s="3" t="inlineStr"/>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="K161" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L161" s="6" t="inlineStr"/>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="K162" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L162" s="3" t="inlineStr"/>
@@ -8582,7 +8582,7 @@
       </c>
       <c r="K163" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L163" s="6" t="inlineStr"/>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="K164" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L164" s="3" t="inlineStr"/>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="K165" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L165" s="6" t="inlineStr"/>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="K166" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L166" s="3" t="inlineStr"/>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="K167" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L167" s="6" t="inlineStr"/>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="K168" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L168" s="3" t="inlineStr"/>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="K169" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L169" s="6" t="inlineStr"/>
@@ -8918,7 +8918,7 @@
       </c>
       <c r="K170" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L170" s="3" t="inlineStr"/>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="K171" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L171" s="6" t="inlineStr"/>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="K172" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L172" s="3" t="inlineStr"/>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="K173" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L173" s="6" t="inlineStr"/>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="K174" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L174" s="3" t="inlineStr"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="K175" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L175" s="6" t="inlineStr"/>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="K176" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L176" s="3" t="inlineStr"/>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="K177" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L177" s="6" t="inlineStr"/>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="K178" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L178" s="3" t="inlineStr"/>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="K179" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L179" s="6" t="inlineStr"/>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="K180" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L180" s="3" t="inlineStr"/>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="K181" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L181" s="6" t="inlineStr"/>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="K182" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L182" s="3" t="inlineStr"/>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="K183" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L183" s="6" t="inlineStr"/>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="K184" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L184" s="3" t="inlineStr"/>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="K185" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L185" s="6" t="inlineStr"/>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="K186" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L186" s="3" t="inlineStr"/>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="K187" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L187" s="6" t="inlineStr"/>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="K188" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L188" s="3" t="inlineStr"/>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="K189" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L189" s="6" t="inlineStr"/>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="K190" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L190" s="3" t="inlineStr"/>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="K191" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L191" s="6" t="inlineStr"/>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="K192" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L192" s="3" t="inlineStr"/>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="K193" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L193" s="6" t="inlineStr"/>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="K194" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L194" s="3" t="inlineStr"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="K195" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L195" s="6" t="inlineStr"/>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="K196" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L196" s="3" t="inlineStr"/>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="K197" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L197" s="6" t="inlineStr"/>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="K198" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L198" s="3" t="inlineStr"/>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="K199" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L199" s="6" t="inlineStr"/>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="K200" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L200" s="3" t="inlineStr"/>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="K201" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L201" s="6" t="inlineStr"/>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="K202" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L202" s="3" t="inlineStr"/>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="K203" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L203" s="6" t="inlineStr"/>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="K204" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L204" s="3" t="inlineStr"/>
@@ -10598,7 +10598,7 @@
       </c>
       <c r="K205" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L205" s="6" t="inlineStr"/>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K206" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L206" s="3" t="inlineStr"/>
@@ -10694,7 +10694,7 @@
       </c>
       <c r="K207" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L207" s="6" t="inlineStr"/>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="K208" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L208" s="3" t="inlineStr"/>
@@ -10790,7 +10790,7 @@
       </c>
       <c r="K209" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L209" s="6" t="inlineStr"/>
@@ -10838,7 +10838,7 @@
       </c>
       <c r="K210" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L210" s="3" t="inlineStr"/>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="K211" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L211" s="6" t="inlineStr"/>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="K212" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L212" s="3" t="inlineStr"/>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="K213" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L213" s="6" t="inlineStr"/>
@@ -11030,7 +11030,7 @@
       </c>
       <c r="K214" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L214" s="3" t="inlineStr"/>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="K215" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L215" s="6" t="inlineStr"/>
@@ -11126,7 +11126,7 @@
       </c>
       <c r="K216" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L216" s="3" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="K217" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L217" s="6" t="inlineStr"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="K218" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L218" s="3" t="inlineStr"/>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="K219" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L219" s="6" t="inlineStr"/>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="K220" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L220" s="3" t="inlineStr"/>
@@ -11366,7 +11366,7 @@
       </c>
       <c r="K221" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L221" s="6" t="inlineStr"/>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="K222" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L222" s="3" t="inlineStr"/>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="K223" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L223" s="6" t="inlineStr"/>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="K224" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L224" s="3" t="inlineStr"/>
@@ -11558,7 +11558,7 @@
       </c>
       <c r="K225" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L225" s="6" t="inlineStr"/>
@@ -11606,7 +11606,7 @@
       </c>
       <c r="K226" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L226" s="3" t="inlineStr"/>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="K227" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L227" s="6" t="inlineStr"/>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="K228" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L228" s="3" t="inlineStr"/>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="K229" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L229" s="6" t="inlineStr"/>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="K230" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L230" s="3" t="inlineStr"/>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="K231" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L231" s="6" t="inlineStr"/>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="K232" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L232" s="3" t="inlineStr"/>
@@ -11942,7 +11942,7 @@
       </c>
       <c r="K233" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L233" s="6" t="inlineStr"/>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="K234" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L234" s="3" t="inlineStr"/>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="K235" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L235" s="6" t="inlineStr"/>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="K236" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L236" s="3" t="inlineStr"/>
@@ -12134,7 +12134,7 @@
       </c>
       <c r="K237" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L237" s="6" t="inlineStr"/>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="K238" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L238" s="3" t="inlineStr"/>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="K239" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L239" s="6" t="inlineStr"/>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="K240" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L240" s="3" t="inlineStr"/>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="K241" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L241" s="6" t="inlineStr"/>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="K242" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L242" s="3" t="inlineStr"/>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="K243" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L243" s="6" t="inlineStr"/>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="K244" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L244" s="3" t="inlineStr"/>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="K245" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L245" s="6" t="inlineStr"/>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="K246" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L246" s="3" t="inlineStr"/>
@@ -12614,7 +12614,7 @@
       </c>
       <c r="K247" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L247" s="6" t="inlineStr"/>
@@ -12662,7 +12662,7 @@
       </c>
       <c r="K248" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L248" s="3" t="inlineStr"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="K249" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L249" s="6" t="inlineStr"/>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="K250" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L250" s="3" t="inlineStr"/>
@@ -12806,7 +12806,7 @@
       </c>
       <c r="K251" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L251" s="6" t="inlineStr"/>
@@ -12854,7 +12854,7 @@
       </c>
       <c r="K252" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L252" s="3" t="inlineStr"/>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="K253" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L253" s="6" t="inlineStr"/>
@@ -12950,7 +12950,7 @@
       </c>
       <c r="K254" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L254" s="3" t="inlineStr"/>
@@ -12998,7 +12998,7 @@
       </c>
       <c r="K255" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L255" s="6" t="inlineStr"/>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="K256" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L256" s="3" t="inlineStr"/>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="K257" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L257" s="6" t="inlineStr"/>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="K258" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L258" s="3" t="inlineStr"/>
@@ -13190,7 +13190,7 @@
       </c>
       <c r="K259" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L259" s="6" t="inlineStr"/>
@@ -13238,7 +13238,7 @@
       </c>
       <c r="K260" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L260" s="3" t="inlineStr"/>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="K261" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L261" s="6" t="inlineStr"/>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="K262" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L262" s="3" t="inlineStr"/>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="K263" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L263" s="6" t="inlineStr"/>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="K264" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L264" s="3" t="inlineStr"/>
@@ -13478,7 +13478,7 @@
       </c>
       <c r="K265" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L265" s="6" t="inlineStr"/>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="K266" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L266" s="3" t="inlineStr"/>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="K267" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L267" s="6" t="inlineStr"/>
@@ -13622,7 +13622,7 @@
       </c>
       <c r="K268" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L268" s="3" t="inlineStr"/>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="K269" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L269" s="6" t="inlineStr"/>
@@ -13718,7 +13718,7 @@
       </c>
       <c r="K270" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L270" s="3" t="inlineStr"/>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="K271" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L271" s="6" t="inlineStr"/>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="K272" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L272" s="3" t="inlineStr"/>
@@ -13862,7 +13862,7 @@
       </c>
       <c r="K273" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L273" s="6" t="inlineStr"/>
@@ -13910,7 +13910,7 @@
       </c>
       <c r="K274" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L274" s="3" t="inlineStr"/>
@@ -13958,7 +13958,7 @@
       </c>
       <c r="K275" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L275" s="6" t="inlineStr"/>
@@ -14006,7 +14006,7 @@
       </c>
       <c r="K276" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L276" s="3" t="inlineStr"/>
@@ -14054,7 +14054,7 @@
       </c>
       <c r="K277" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L277" s="6" t="inlineStr"/>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="K278" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L278" s="3" t="inlineStr"/>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="K279" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L279" s="6" t="inlineStr"/>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="K280" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L280" s="3" t="inlineStr"/>
@@ -14246,7 +14246,7 @@
       </c>
       <c r="K281" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L281" s="6" t="inlineStr"/>
@@ -14294,7 +14294,7 @@
       </c>
       <c r="K282" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L282" s="3" t="inlineStr"/>
@@ -14342,7 +14342,7 @@
       </c>
       <c r="K283" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L283" s="6" t="inlineStr"/>
@@ -14390,7 +14390,7 @@
       </c>
       <c r="K284" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L284" s="3" t="inlineStr"/>
@@ -14438,7 +14438,7 @@
       </c>
       <c r="K285" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L285" s="6" t="inlineStr"/>
@@ -14486,7 +14486,7 @@
       </c>
       <c r="K286" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L286" s="3" t="inlineStr"/>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="K287" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L287" s="6" t="inlineStr"/>
@@ -14582,7 +14582,7 @@
       </c>
       <c r="K288" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L288" s="3" t="inlineStr"/>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="K289" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L289" s="6" t="inlineStr"/>
@@ -14678,7 +14678,7 @@
       </c>
       <c r="K290" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L290" s="3" t="inlineStr"/>
@@ -14726,7 +14726,7 @@
       </c>
       <c r="K291" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L291" s="6" t="inlineStr"/>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="K292" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L292" s="3" t="inlineStr"/>
@@ -14822,7 +14822,7 @@
       </c>
       <c r="K293" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L293" s="6" t="inlineStr"/>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="K294" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L294" s="3" t="inlineStr"/>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="K295" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L295" s="6" t="inlineStr"/>
@@ -14966,7 +14966,7 @@
       </c>
       <c r="K296" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L296" s="3" t="inlineStr"/>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="K297" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L297" s="6" t="inlineStr"/>
@@ -15062,7 +15062,7 @@
       </c>
       <c r="K298" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L298" s="3" t="inlineStr"/>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="K299" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L299" s="6" t="inlineStr"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="K300" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L300" s="3" t="inlineStr"/>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="K301" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L301" s="6" t="inlineStr"/>
@@ -15254,7 +15254,7 @@
       </c>
       <c r="K302" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L302" s="3" t="inlineStr"/>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="K303" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L303" s="6" t="inlineStr"/>
@@ -15350,7 +15350,7 @@
       </c>
       <c r="K304" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L304" s="3" t="inlineStr"/>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="K305" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L305" s="6" t="inlineStr"/>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="K306" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L306" s="3" t="inlineStr"/>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="K307" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L307" s="6" t="inlineStr"/>
@@ -15542,7 +15542,7 @@
       </c>
       <c r="K308" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L308" s="3" t="inlineStr"/>
@@ -15590,7 +15590,7 @@
       </c>
       <c r="K309" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L309" s="6" t="inlineStr"/>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="K310" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L310" s="3" t="inlineStr"/>
@@ -15686,7 +15686,7 @@
       </c>
       <c r="K311" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L311" s="6" t="inlineStr"/>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="K312" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L312" s="3" t="inlineStr"/>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="K313" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L313" s="6" t="inlineStr"/>
@@ -15830,7 +15830,7 @@
       </c>
       <c r="K314" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L314" s="3" t="inlineStr"/>
@@ -15878,7 +15878,7 @@
       </c>
       <c r="K315" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L315" s="6" t="inlineStr"/>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="K316" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L316" s="3" t="inlineStr"/>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="K317" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L317" s="6" t="inlineStr"/>
@@ -16022,7 +16022,7 @@
       </c>
       <c r="K318" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L318" s="3" t="inlineStr"/>
@@ -16070,7 +16070,7 @@
       </c>
       <c r="K319" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L319" s="6" t="inlineStr"/>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="K320" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L320" s="3" t="inlineStr"/>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="K321" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L321" s="6" t="inlineStr"/>
@@ -16214,7 +16214,7 @@
       </c>
       <c r="K322" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L322" s="3" t="inlineStr"/>
@@ -16262,7 +16262,7 @@
       </c>
       <c r="K323" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L323" s="6" t="inlineStr"/>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="K324" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L324" s="3" t="inlineStr"/>
@@ -16358,7 +16358,7 @@
       </c>
       <c r="K325" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L325" s="6" t="inlineStr"/>
@@ -16406,7 +16406,7 @@
       </c>
       <c r="K326" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L326" s="3" t="inlineStr"/>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="K327" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L327" s="6" t="inlineStr"/>
@@ -16502,7 +16502,7 @@
       </c>
       <c r="K328" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L328" s="3" t="inlineStr"/>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="K329" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L329" s="6" t="inlineStr"/>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="K330" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L330" s="3" t="inlineStr"/>
@@ -16646,7 +16646,7 @@
       </c>
       <c r="K331" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L331" s="6" t="inlineStr"/>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="K332" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L332" s="3" t="inlineStr"/>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="K333" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L333" s="6" t="inlineStr"/>
@@ -16790,7 +16790,7 @@
       </c>
       <c r="K334" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L334" s="3" t="inlineStr"/>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="K335" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L335" s="6" t="inlineStr"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="K336" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L336" s="3" t="inlineStr"/>
@@ -16934,7 +16934,7 @@
       </c>
       <c r="K337" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L337" s="6" t="inlineStr"/>
@@ -16982,7 +16982,7 @@
       </c>
       <c r="K338" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L338" s="3" t="inlineStr"/>
@@ -17030,7 +17030,7 @@
       </c>
       <c r="K339" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L339" s="6" t="inlineStr"/>
@@ -17078,7 +17078,7 @@
       </c>
       <c r="K340" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L340" s="3" t="inlineStr"/>
@@ -17126,7 +17126,7 @@
       </c>
       <c r="K341" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L341" s="6" t="inlineStr"/>
@@ -17174,7 +17174,7 @@
       </c>
       <c r="K342" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L342" s="3" t="inlineStr"/>
@@ -17222,7 +17222,7 @@
       </c>
       <c r="K343" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L343" s="6" t="inlineStr"/>
@@ -17270,7 +17270,7 @@
       </c>
       <c r="K344" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L344" s="3" t="inlineStr"/>
@@ -17318,7 +17318,7 @@
       </c>
       <c r="K345" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L345" s="6" t="inlineStr"/>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="K346" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L346" s="3" t="inlineStr"/>
@@ -17414,7 +17414,7 @@
       </c>
       <c r="K347" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L347" s="6" t="inlineStr"/>
@@ -17462,7 +17462,7 @@
       </c>
       <c r="K348" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L348" s="3" t="inlineStr"/>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="K349" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L349" s="6" t="inlineStr"/>
@@ -17558,7 +17558,7 @@
       </c>
       <c r="K350" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L350" s="3" t="inlineStr"/>
@@ -17606,7 +17606,7 @@
       </c>
       <c r="K351" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L351" s="6" t="inlineStr"/>
@@ -17654,7 +17654,7 @@
       </c>
       <c r="K352" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L352" s="3" t="inlineStr"/>
@@ -17702,7 +17702,7 @@
       </c>
       <c r="K353" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L353" s="6" t="inlineStr"/>
@@ -17750,7 +17750,7 @@
       </c>
       <c r="K354" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L354" s="3" t="inlineStr"/>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="K355" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L355" s="6" t="inlineStr"/>
@@ -17846,7 +17846,7 @@
       </c>
       <c r="K356" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L356" s="3" t="inlineStr"/>
@@ -17894,7 +17894,7 @@
       </c>
       <c r="K357" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L357" s="6" t="inlineStr"/>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="K358" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L358" s="3" t="inlineStr"/>
@@ -17990,7 +17990,7 @@
       </c>
       <c r="K359" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L359" s="6" t="inlineStr"/>
@@ -18038,7 +18038,7 @@
       </c>
       <c r="K360" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L360" s="3" t="inlineStr"/>
@@ -18086,7 +18086,7 @@
       </c>
       <c r="K361" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L361" s="6" t="inlineStr"/>
@@ -18134,7 +18134,7 @@
       </c>
       <c r="K362" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L362" s="3" t="inlineStr"/>
@@ -18182,7 +18182,7 @@
       </c>
       <c r="K363" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L363" s="6" t="inlineStr"/>
@@ -18230,7 +18230,7 @@
       </c>
       <c r="K364" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L364" s="3" t="inlineStr"/>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="K365" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L365" s="6" t="inlineStr"/>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="K366" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L366" s="3" t="inlineStr"/>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="K367" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L367" s="6" t="inlineStr"/>
@@ -18422,7 +18422,7 @@
       </c>
       <c r="K368" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L368" s="3" t="inlineStr"/>
@@ -18470,7 +18470,7 @@
       </c>
       <c r="K369" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L369" s="6" t="inlineStr"/>
@@ -18518,7 +18518,7 @@
       </c>
       <c r="K370" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L370" s="3" t="inlineStr"/>
@@ -18566,7 +18566,7 @@
       </c>
       <c r="K371" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L371" s="6" t="inlineStr"/>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="K372" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L372" s="3" t="inlineStr"/>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="K373" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L373" s="6" t="inlineStr"/>
@@ -18710,7 +18710,7 @@
       </c>
       <c r="K374" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L374" s="3" t="inlineStr"/>
@@ -18758,7 +18758,7 @@
       </c>
       <c r="K375" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L375" s="6" t="inlineStr"/>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="K376" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L376" s="3" t="inlineStr"/>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="K377" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L377" s="6" t="inlineStr"/>
@@ -18902,7 +18902,7 @@
       </c>
       <c r="K378" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L378" s="3" t="inlineStr"/>
@@ -18950,7 +18950,7 @@
       </c>
       <c r="K379" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L379" s="6" t="inlineStr"/>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="K380" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L380" s="3" t="inlineStr"/>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="K381" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L381" s="6" t="inlineStr"/>
@@ -19094,7 +19094,7 @@
       </c>
       <c r="K382" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L382" s="3" t="inlineStr"/>
@@ -19142,7 +19142,7 @@
       </c>
       <c r="K383" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L383" s="6" t="inlineStr"/>
@@ -19190,7 +19190,7 @@
       </c>
       <c r="K384" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L384" s="3" t="inlineStr"/>
@@ -19238,7 +19238,7 @@
       </c>
       <c r="K385" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L385" s="6" t="inlineStr"/>
@@ -19286,7 +19286,7 @@
       </c>
       <c r="K386" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L386" s="3" t="inlineStr"/>
@@ -19334,7 +19334,7 @@
       </c>
       <c r="K387" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L387" s="6" t="inlineStr"/>
@@ -19382,7 +19382,7 @@
       </c>
       <c r="K388" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L388" s="3" t="inlineStr"/>
@@ -19430,7 +19430,7 @@
       </c>
       <c r="K389" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L389" s="6" t="inlineStr"/>
@@ -19478,7 +19478,7 @@
       </c>
       <c r="K390" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L390" s="3" t="inlineStr"/>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="K391" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L391" s="6" t="inlineStr"/>
@@ -19574,7 +19574,7 @@
       </c>
       <c r="K392" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L392" s="3" t="inlineStr"/>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="K393" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L393" s="6" t="inlineStr"/>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="K394" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L394" s="3" t="inlineStr"/>
@@ -19718,7 +19718,7 @@
       </c>
       <c r="K395" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L395" s="6" t="inlineStr"/>
@@ -19766,7 +19766,7 @@
       </c>
       <c r="K396" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L396" s="3" t="inlineStr"/>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="K397" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L397" s="6" t="inlineStr"/>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="K398" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L398" s="3" t="inlineStr"/>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="K399" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L399" s="6" t="inlineStr"/>
@@ -19958,7 +19958,7 @@
       </c>
       <c r="K400" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L400" s="3" t="inlineStr"/>
@@ -20006,7 +20006,7 @@
       </c>
       <c r="K401" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L401" s="6" t="inlineStr"/>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="K402" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L402" s="3" t="inlineStr"/>
@@ -20102,7 +20102,7 @@
       </c>
       <c r="K403" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L403" s="6" t="inlineStr"/>
@@ -20150,7 +20150,7 @@
       </c>
       <c r="K404" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L404" s="3" t="inlineStr"/>
@@ -20198,7 +20198,7 @@
       </c>
       <c r="K405" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L405" s="6" t="inlineStr"/>
@@ -20246,7 +20246,7 @@
       </c>
       <c r="K406" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L406" s="3" t="inlineStr"/>
@@ -20294,7 +20294,7 @@
       </c>
       <c r="K407" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L407" s="6" t="inlineStr"/>
@@ -20342,7 +20342,7 @@
       </c>
       <c r="K408" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L408" s="3" t="inlineStr"/>
@@ -20390,7 +20390,7 @@
       </c>
       <c r="K409" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L409" s="6" t="inlineStr"/>
@@ -20438,7 +20438,7 @@
       </c>
       <c r="K410" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L410" s="3" t="inlineStr"/>
@@ -20486,7 +20486,7 @@
       </c>
       <c r="K411" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L411" s="6" t="inlineStr"/>
@@ -20534,7 +20534,7 @@
       </c>
       <c r="K412" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L412" s="3" t="inlineStr"/>
@@ -20582,7 +20582,7 @@
       </c>
       <c r="K413" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L413" s="6" t="inlineStr"/>
@@ -20630,7 +20630,7 @@
       </c>
       <c r="K414" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L414" s="3" t="inlineStr"/>
@@ -20678,7 +20678,7 @@
       </c>
       <c r="K415" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L415" s="6" t="inlineStr"/>
@@ -20726,7 +20726,7 @@
       </c>
       <c r="K416" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L416" s="3" t="inlineStr"/>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="K417" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L417" s="6" t="inlineStr"/>
@@ -20822,7 +20822,7 @@
       </c>
       <c r="K418" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L418" s="3" t="inlineStr"/>
@@ -20870,7 +20870,7 @@
       </c>
       <c r="K419" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L419" s="6" t="inlineStr"/>
@@ -20918,7 +20918,7 @@
       </c>
       <c r="K420" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L420" s="3" t="inlineStr"/>
@@ -20966,7 +20966,7 @@
       </c>
       <c r="K421" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L421" s="6" t="inlineStr"/>
@@ -21014,7 +21014,7 @@
       </c>
       <c r="K422" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L422" s="3" t="inlineStr"/>
@@ -21062,7 +21062,7 @@
       </c>
       <c r="K423" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L423" s="6" t="inlineStr"/>
@@ -21110,7 +21110,7 @@
       </c>
       <c r="K424" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L424" s="3" t="inlineStr"/>
@@ -21158,7 +21158,7 @@
       </c>
       <c r="K425" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L425" s="6" t="inlineStr"/>
@@ -21206,7 +21206,7 @@
       </c>
       <c r="K426" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L426" s="3" t="inlineStr"/>
@@ -21254,7 +21254,7 @@
       </c>
       <c r="K427" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L427" s="6" t="inlineStr"/>
@@ -21302,7 +21302,7 @@
       </c>
       <c r="K428" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L428" s="3" t="inlineStr"/>
@@ -21350,7 +21350,7 @@
       </c>
       <c r="K429" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L429" s="6" t="inlineStr"/>
@@ -21398,7 +21398,7 @@
       </c>
       <c r="K430" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L430" s="3" t="inlineStr"/>
@@ -21446,7 +21446,7 @@
       </c>
       <c r="K431" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L431" s="6" t="inlineStr"/>
@@ -21494,7 +21494,7 @@
       </c>
       <c r="K432" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L432" s="3" t="inlineStr"/>
@@ -21542,7 +21542,7 @@
       </c>
       <c r="K433" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L433" s="6" t="inlineStr"/>
@@ -21590,7 +21590,7 @@
       </c>
       <c r="K434" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L434" s="3" t="inlineStr"/>
@@ -21638,7 +21638,7 @@
       </c>
       <c r="K435" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L435" s="6" t="inlineStr"/>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="K436" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L436" s="3" t="inlineStr"/>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="K437" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L437" s="6" t="inlineStr"/>
@@ -21782,7 +21782,7 @@
       </c>
       <c r="K438" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L438" s="3" t="inlineStr"/>
@@ -21830,7 +21830,7 @@
       </c>
       <c r="K439" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L439" s="6" t="inlineStr"/>
@@ -21878,7 +21878,7 @@
       </c>
       <c r="K440" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L440" s="3" t="inlineStr"/>
@@ -21926,7 +21926,7 @@
       </c>
       <c r="K441" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L441" s="6" t="inlineStr"/>
@@ -21974,7 +21974,7 @@
       </c>
       <c r="K442" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L442" s="3" t="inlineStr"/>
@@ -22022,7 +22022,7 @@
       </c>
       <c r="K443" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L443" s="6" t="inlineStr"/>
@@ -22070,7 +22070,7 @@
       </c>
       <c r="K444" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L444" s="3" t="inlineStr"/>
@@ -22118,7 +22118,7 @@
       </c>
       <c r="K445" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L445" s="6" t="inlineStr"/>
@@ -22166,7 +22166,7 @@
       </c>
       <c r="K446" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L446" s="3" t="inlineStr"/>
@@ -22214,7 +22214,7 @@
       </c>
       <c r="K447" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L447" s="6" t="inlineStr"/>
@@ -22262,7 +22262,7 @@
       </c>
       <c r="K448" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L448" s="3" t="inlineStr"/>
@@ -22310,7 +22310,7 @@
       </c>
       <c r="K449" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L449" s="6" t="inlineStr"/>
@@ -22358,7 +22358,7 @@
       </c>
       <c r="K450" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L450" s="3" t="inlineStr"/>
@@ -22406,7 +22406,7 @@
       </c>
       <c r="K451" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L451" s="6" t="inlineStr"/>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="K452" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L452" s="3" t="inlineStr"/>
@@ -22502,7 +22502,7 @@
       </c>
       <c r="K453" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L453" s="6" t="inlineStr"/>
@@ -22550,7 +22550,7 @@
       </c>
       <c r="K454" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L454" s="3" t="inlineStr"/>
@@ -22598,7 +22598,7 @@
       </c>
       <c r="K455" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L455" s="6" t="inlineStr"/>
@@ -22646,7 +22646,7 @@
       </c>
       <c r="K456" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L456" s="3" t="inlineStr"/>
@@ -22694,7 +22694,7 @@
       </c>
       <c r="K457" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L457" s="6" t="inlineStr"/>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="K458" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L458" s="3" t="inlineStr"/>
@@ -22790,7 +22790,7 @@
       </c>
       <c r="K459" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L459" s="6" t="inlineStr"/>
@@ -22838,7 +22838,7 @@
       </c>
       <c r="K460" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L460" s="3" t="inlineStr"/>
@@ -22886,7 +22886,7 @@
       </c>
       <c r="K461" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L461" s="6" t="inlineStr"/>
@@ -22934,7 +22934,7 @@
       </c>
       <c r="K462" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L462" s="3" t="inlineStr"/>
@@ -22982,7 +22982,7 @@
       </c>
       <c r="K463" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L463" s="6" t="inlineStr"/>
@@ -23030,7 +23030,7 @@
       </c>
       <c r="K464" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L464" s="3" t="inlineStr"/>
@@ -23078,7 +23078,7 @@
       </c>
       <c r="K465" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L465" s="6" t="inlineStr"/>
@@ -23126,7 +23126,7 @@
       </c>
       <c r="K466" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L466" s="3" t="inlineStr"/>
@@ -23174,7 +23174,7 @@
       </c>
       <c r="K467" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L467" s="6" t="inlineStr"/>
@@ -23222,7 +23222,7 @@
       </c>
       <c r="K468" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L468" s="3" t="inlineStr"/>
@@ -23270,7 +23270,7 @@
       </c>
       <c r="K469" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L469" s="6" t="inlineStr"/>
@@ -23318,7 +23318,7 @@
       </c>
       <c r="K470" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L470" s="3" t="inlineStr"/>
@@ -23366,7 +23366,7 @@
       </c>
       <c r="K471" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L471" s="6" t="inlineStr"/>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="K472" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L472" s="3" t="inlineStr"/>
@@ -23462,7 +23462,7 @@
       </c>
       <c r="K473" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L473" s="6" t="inlineStr"/>
@@ -23510,7 +23510,7 @@
       </c>
       <c r="K474" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L474" s="3" t="inlineStr"/>
@@ -23558,7 +23558,7 @@
       </c>
       <c r="K475" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L475" s="6" t="inlineStr"/>
@@ -23606,7 +23606,7 @@
       </c>
       <c r="K476" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L476" s="3" t="inlineStr"/>
@@ -23654,7 +23654,7 @@
       </c>
       <c r="K477" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L477" s="6" t="inlineStr"/>
@@ -23702,7 +23702,7 @@
       </c>
       <c r="K478" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L478" s="3" t="inlineStr"/>
@@ -23750,7 +23750,7 @@
       </c>
       <c r="K479" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L479" s="6" t="inlineStr"/>
@@ -23798,7 +23798,7 @@
       </c>
       <c r="K480" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L480" s="3" t="inlineStr"/>
@@ -23846,7 +23846,7 @@
       </c>
       <c r="K481" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L481" s="6" t="inlineStr"/>
@@ -23894,7 +23894,7 @@
       </c>
       <c r="K482" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L482" s="3" t="inlineStr"/>
@@ -23942,7 +23942,7 @@
       </c>
       <c r="K483" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L483" s="6" t="inlineStr"/>
@@ -23990,7 +23990,7 @@
       </c>
       <c r="K484" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L484" s="3" t="inlineStr"/>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="K485" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L485" s="6" t="inlineStr"/>
@@ -24086,7 +24086,7 @@
       </c>
       <c r="K486" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L486" s="3" t="inlineStr"/>
@@ -24134,7 +24134,7 @@
       </c>
       <c r="K487" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L487" s="6" t="inlineStr"/>
@@ -24182,7 +24182,7 @@
       </c>
       <c r="K488" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L488" s="3" t="inlineStr"/>
@@ -24230,7 +24230,7 @@
       </c>
       <c r="K489" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L489" s="6" t="inlineStr"/>
@@ -24278,7 +24278,7 @@
       </c>
       <c r="K490" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L490" s="3" t="inlineStr"/>
@@ -24326,7 +24326,7 @@
       </c>
       <c r="K491" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L491" s="6" t="inlineStr"/>
@@ -24374,7 +24374,7 @@
       </c>
       <c r="K492" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L492" s="3" t="inlineStr"/>
@@ -24422,7 +24422,7 @@
       </c>
       <c r="K493" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L493" s="6" t="inlineStr"/>
@@ -24470,7 +24470,7 @@
       </c>
       <c r="K494" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L494" s="3" t="inlineStr"/>
@@ -24518,7 +24518,7 @@
       </c>
       <c r="K495" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L495" s="6" t="inlineStr"/>
@@ -24566,7 +24566,7 @@
       </c>
       <c r="K496" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L496" s="3" t="inlineStr"/>
@@ -24614,7 +24614,7 @@
       </c>
       <c r="K497" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L497" s="6" t="inlineStr"/>
@@ -24662,7 +24662,7 @@
       </c>
       <c r="K498" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L498" s="3" t="inlineStr"/>
@@ -24710,7 +24710,7 @@
       </c>
       <c r="K499" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L499" s="6" t="inlineStr"/>
@@ -24758,7 +24758,7 @@
       </c>
       <c r="K500" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L500" s="3" t="inlineStr"/>
@@ -24806,7 +24806,7 @@
       </c>
       <c r="K501" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L501" s="6" t="inlineStr"/>
@@ -24854,7 +24854,7 @@
       </c>
       <c r="K502" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L502" s="3" t="inlineStr"/>
@@ -24902,7 +24902,7 @@
       </c>
       <c r="K503" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L503" s="6" t="inlineStr"/>
@@ -24950,7 +24950,7 @@
       </c>
       <c r="K504" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L504" s="3" t="inlineStr"/>
@@ -24998,7 +24998,7 @@
       </c>
       <c r="K505" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L505" s="6" t="inlineStr"/>
@@ -25046,7 +25046,7 @@
       </c>
       <c r="K506" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L506" s="3" t="inlineStr"/>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="K507" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L507" s="6" t="inlineStr"/>
@@ -25142,7 +25142,7 @@
       </c>
       <c r="K508" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L508" s="3" t="inlineStr"/>
@@ -25190,7 +25190,7 @@
       </c>
       <c r="K509" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L509" s="6" t="inlineStr"/>
@@ -25238,7 +25238,7 @@
       </c>
       <c r="K510" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L510" s="3" t="inlineStr"/>
@@ -25286,7 +25286,7 @@
       </c>
       <c r="K511" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L511" s="6" t="inlineStr"/>
@@ -25334,7 +25334,7 @@
       </c>
       <c r="K512" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L512" s="3" t="inlineStr"/>
@@ -25382,7 +25382,7 @@
       </c>
       <c r="K513" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L513" s="6" t="inlineStr"/>
@@ -25430,7 +25430,7 @@
       </c>
       <c r="K514" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L514" s="3" t="inlineStr"/>
@@ -25478,7 +25478,7 @@
       </c>
       <c r="K515" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L515" s="6" t="inlineStr"/>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="K516" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L516" s="3" t="inlineStr"/>
@@ -25574,7 +25574,7 @@
       </c>
       <c r="K517" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L517" s="6" t="inlineStr"/>
@@ -25622,7 +25622,7 @@
       </c>
       <c r="K518" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L518" s="3" t="inlineStr"/>
@@ -25670,7 +25670,7 @@
       </c>
       <c r="K519" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L519" s="6" t="inlineStr"/>
@@ -25718,7 +25718,7 @@
       </c>
       <c r="K520" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L520" s="3" t="inlineStr"/>
@@ -25766,7 +25766,7 @@
       </c>
       <c r="K521" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L521" s="6" t="inlineStr"/>
@@ -25814,7 +25814,7 @@
       </c>
       <c r="K522" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L522" s="3" t="inlineStr"/>
@@ -25862,7 +25862,7 @@
       </c>
       <c r="K523" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L523" s="6" t="inlineStr"/>
@@ -25910,7 +25910,7 @@
       </c>
       <c r="K524" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L524" s="3" t="inlineStr"/>
@@ -25958,7 +25958,7 @@
       </c>
       <c r="K525" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L525" s="6" t="inlineStr"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K526" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L526" s="3" t="inlineStr"/>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="K527" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L527" s="6" t="inlineStr"/>
@@ -26102,7 +26102,7 @@
       </c>
       <c r="K528" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L528" s="3" t="inlineStr"/>
@@ -26150,7 +26150,7 @@
       </c>
       <c r="K529" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L529" s="6" t="inlineStr"/>
@@ -26198,7 +26198,7 @@
       </c>
       <c r="K530" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L530" s="3" t="inlineStr"/>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="K531" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L531" s="6" t="inlineStr"/>
@@ -26294,7 +26294,7 @@
       </c>
       <c r="K532" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L532" s="3" t="inlineStr"/>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="K533" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L533" s="6" t="inlineStr"/>
@@ -26390,7 +26390,7 @@
       </c>
       <c r="K534" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L534" s="3" t="inlineStr"/>
@@ -26438,7 +26438,7 @@
       </c>
       <c r="K535" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L535" s="6" t="inlineStr"/>
@@ -26486,7 +26486,7 @@
       </c>
       <c r="K536" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L536" s="3" t="inlineStr"/>
@@ -26534,7 +26534,7 @@
       </c>
       <c r="K537" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L537" s="6" t="inlineStr"/>
@@ -26582,7 +26582,7 @@
       </c>
       <c r="K538" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L538" s="3" t="inlineStr"/>
@@ -26630,7 +26630,7 @@
       </c>
       <c r="K539" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L539" s="6" t="inlineStr"/>
@@ -26678,7 +26678,7 @@
       </c>
       <c r="K540" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L540" s="3" t="inlineStr"/>
@@ -26726,7 +26726,7 @@
       </c>
       <c r="K541" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L541" s="6" t="inlineStr"/>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="K542" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L542" s="3" t="inlineStr"/>
@@ -26822,7 +26822,7 @@
       </c>
       <c r="K543" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L543" s="6" t="inlineStr"/>
@@ -26870,7 +26870,7 @@
       </c>
       <c r="K544" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L544" s="3" t="inlineStr"/>
@@ -26918,7 +26918,7 @@
       </c>
       <c r="K545" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L545" s="6" t="inlineStr"/>
@@ -26966,7 +26966,7 @@
       </c>
       <c r="K546" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L546" s="3" t="inlineStr"/>
@@ -27014,7 +27014,7 @@
       </c>
       <c r="K547" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L547" s="6" t="inlineStr"/>
@@ -27062,7 +27062,7 @@
       </c>
       <c r="K548" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L548" s="3" t="inlineStr"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K549" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L549" s="6" t="inlineStr"/>
@@ -27158,7 +27158,7 @@
       </c>
       <c r="K550" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L550" s="3" t="inlineStr"/>
@@ -27206,7 +27206,7 @@
       </c>
       <c r="K551" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L551" s="6" t="inlineStr"/>
@@ -27254,7 +27254,7 @@
       </c>
       <c r="K552" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L552" s="3" t="inlineStr"/>
@@ -27302,7 +27302,7 @@
       </c>
       <c r="K553" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L553" s="6" t="inlineStr"/>
@@ -27350,7 +27350,7 @@
       </c>
       <c r="K554" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L554" s="3" t="inlineStr"/>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="K555" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L555" s="6" t="inlineStr"/>
@@ -27446,7 +27446,7 @@
       </c>
       <c r="K556" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L556" s="3" t="inlineStr"/>
@@ -27494,7 +27494,7 @@
       </c>
       <c r="K557" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L557" s="6" t="inlineStr"/>
@@ -27542,7 +27542,7 @@
       </c>
       <c r="K558" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L558" s="3" t="inlineStr"/>
@@ -27590,7 +27590,7 @@
       </c>
       <c r="K559" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L559" s="6" t="inlineStr"/>
@@ -27638,7 +27638,7 @@
       </c>
       <c r="K560" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L560" s="3" t="inlineStr"/>
@@ -27686,7 +27686,7 @@
       </c>
       <c r="K561" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L561" s="6" t="inlineStr"/>
@@ -27734,7 +27734,7 @@
       </c>
       <c r="K562" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L562" s="3" t="inlineStr"/>
@@ -27782,7 +27782,7 @@
       </c>
       <c r="K563" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L563" s="6" t="inlineStr"/>
@@ -27830,7 +27830,7 @@
       </c>
       <c r="K564" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L564" s="3" t="inlineStr"/>
@@ -27878,7 +27878,7 @@
       </c>
       <c r="K565" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L565" s="6" t="inlineStr"/>
@@ -27926,7 +27926,7 @@
       </c>
       <c r="K566" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L566" s="3" t="inlineStr"/>
@@ -27974,7 +27974,7 @@
       </c>
       <c r="K567" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L567" s="6" t="inlineStr"/>
@@ -28022,7 +28022,7 @@
       </c>
       <c r="K568" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L568" s="3" t="inlineStr"/>
@@ -28070,7 +28070,7 @@
       </c>
       <c r="K569" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L569" s="6" t="inlineStr"/>
@@ -28118,7 +28118,7 @@
       </c>
       <c r="K570" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L570" s="3" t="inlineStr"/>
@@ -28166,7 +28166,7 @@
       </c>
       <c r="K571" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L571" s="6" t="inlineStr"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K572" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L572" s="3" t="inlineStr"/>
@@ -28262,7 +28262,7 @@
       </c>
       <c r="K573" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L573" s="6" t="inlineStr"/>
@@ -28310,7 +28310,7 @@
       </c>
       <c r="K574" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L574" s="3" t="inlineStr"/>
@@ -28358,7 +28358,7 @@
       </c>
       <c r="K575" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L575" s="6" t="inlineStr"/>
@@ -28406,7 +28406,7 @@
       </c>
       <c r="K576" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L576" s="3" t="inlineStr"/>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="K577" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L577" s="6" t="inlineStr"/>
@@ -28502,7 +28502,7 @@
       </c>
       <c r="K578" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L578" s="3" t="inlineStr"/>
@@ -28550,7 +28550,7 @@
       </c>
       <c r="K579" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L579" s="6" t="inlineStr"/>
@@ -28598,7 +28598,7 @@
       </c>
       <c r="K580" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L580" s="3" t="inlineStr"/>
@@ -28646,7 +28646,7 @@
       </c>
       <c r="K581" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L581" s="6" t="inlineStr"/>
@@ -28694,7 +28694,7 @@
       </c>
       <c r="K582" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L582" s="3" t="inlineStr"/>
@@ -28742,7 +28742,7 @@
       </c>
       <c r="K583" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L583" s="6" t="inlineStr"/>
@@ -28790,7 +28790,7 @@
       </c>
       <c r="K584" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L584" s="3" t="inlineStr"/>
@@ -28838,7 +28838,7 @@
       </c>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L585" s="6" t="inlineStr"/>
@@ -28886,7 +28886,7 @@
       </c>
       <c r="K586" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L586" s="3" t="inlineStr"/>
@@ -28934,7 +28934,7 @@
       </c>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L587" s="6" t="inlineStr"/>
@@ -28982,7 +28982,7 @@
       </c>
       <c r="K588" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L588" s="3" t="inlineStr"/>
@@ -29030,7 +29030,7 @@
       </c>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L589" s="6" t="inlineStr"/>
@@ -29078,7 +29078,7 @@
       </c>
       <c r="K590" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L590" s="3" t="inlineStr"/>
@@ -29126,7 +29126,7 @@
       </c>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L591" s="6" t="inlineStr"/>
@@ -29174,7 +29174,7 @@
       </c>
       <c r="K592" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L592" s="3" t="inlineStr"/>
@@ -29222,7 +29222,7 @@
       </c>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L593" s="6" t="inlineStr"/>
@@ -29270,7 +29270,7 @@
       </c>
       <c r="K594" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L594" s="3" t="inlineStr"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L595" s="6" t="inlineStr"/>
@@ -29366,7 +29366,7 @@
       </c>
       <c r="K596" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L596" s="3" t="inlineStr"/>
@@ -29414,7 +29414,7 @@
       </c>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L597" s="6" t="inlineStr"/>
@@ -29462,7 +29462,7 @@
       </c>
       <c r="K598" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L598" s="3" t="inlineStr"/>
@@ -29510,7 +29510,7 @@
       </c>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L599" s="6" t="inlineStr"/>
@@ -29558,7 +29558,7 @@
       </c>
       <c r="K600" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L600" s="3" t="inlineStr"/>
@@ -29606,7 +29606,7 @@
       </c>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L601" s="6" t="inlineStr"/>
@@ -29654,7 +29654,7 @@
       </c>
       <c r="K602" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L602" s="3" t="inlineStr"/>
@@ -29702,7 +29702,7 @@
       </c>
       <c r="K603" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L603" s="6" t="inlineStr"/>
@@ -29750,7 +29750,7 @@
       </c>
       <c r="K604" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L604" s="3" t="inlineStr"/>
@@ -29798,7 +29798,7 @@
       </c>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr"/>
@@ -29846,7 +29846,7 @@
       </c>
       <c r="K606" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L606" s="3" t="inlineStr"/>
@@ -29894,7 +29894,7 @@
       </c>
       <c r="K607" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L607" s="6" t="inlineStr"/>
@@ -29942,7 +29942,7 @@
       </c>
       <c r="K608" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L608" s="3" t="inlineStr"/>
@@ -29990,7 +29990,7 @@
       </c>
       <c r="K609" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L609" s="6" t="inlineStr"/>
@@ -30038,7 +30038,7 @@
       </c>
       <c r="K610" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L610" s="3" t="inlineStr"/>
@@ -30086,7 +30086,7 @@
       </c>
       <c r="K611" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L611" s="6" t="inlineStr"/>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="K612" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L612" s="3" t="inlineStr"/>
@@ -30182,7 +30182,7 @@
       </c>
       <c r="K613" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L613" s="6" t="inlineStr"/>
@@ -30230,7 +30230,7 @@
       </c>
       <c r="K614" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L614" s="3" t="inlineStr"/>
@@ -30278,7 +30278,7 @@
       </c>
       <c r="K615" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L615" s="6" t="inlineStr"/>
@@ -30326,7 +30326,7 @@
       </c>
       <c r="K616" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L616" s="3" t="inlineStr"/>
@@ -30374,7 +30374,7 @@
       </c>
       <c r="K617" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L617" s="6" t="inlineStr"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K618" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L618" s="3" t="inlineStr"/>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="K619" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L619" s="6" t="inlineStr"/>
@@ -30518,7 +30518,7 @@
       </c>
       <c r="K620" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L620" s="3" t="inlineStr"/>
@@ -30566,7 +30566,7 @@
       </c>
       <c r="K621" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L621" s="6" t="inlineStr"/>
@@ -30614,7 +30614,7 @@
       </c>
       <c r="K622" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L622" s="3" t="inlineStr"/>
@@ -30662,7 +30662,7 @@
       </c>
       <c r="K623" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L623" s="6" t="inlineStr"/>
@@ -30710,7 +30710,7 @@
       </c>
       <c r="K624" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L624" s="3" t="inlineStr"/>
@@ -30758,7 +30758,7 @@
       </c>
       <c r="K625" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L625" s="6" t="inlineStr"/>
@@ -30806,7 +30806,7 @@
       </c>
       <c r="K626" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L626" s="3" t="inlineStr"/>
@@ -30854,7 +30854,7 @@
       </c>
       <c r="K627" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L627" s="6" t="inlineStr"/>
@@ -30902,7 +30902,7 @@
       </c>
       <c r="K628" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L628" s="3" t="inlineStr"/>
@@ -30950,7 +30950,7 @@
       </c>
       <c r="K629" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L629" s="6" t="inlineStr"/>
@@ -30998,7 +30998,7 @@
       </c>
       <c r="K630" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L630" s="3" t="inlineStr"/>
@@ -31046,7 +31046,7 @@
       </c>
       <c r="K631" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L631" s="6" t="inlineStr"/>
@@ -31094,7 +31094,7 @@
       </c>
       <c r="K632" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L632" s="3" t="inlineStr"/>
@@ -31142,7 +31142,7 @@
       </c>
       <c r="K633" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L633" s="6" t="inlineStr"/>
@@ -31190,7 +31190,7 @@
       </c>
       <c r="K634" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L634" s="3" t="inlineStr"/>
@@ -31238,7 +31238,7 @@
       </c>
       <c r="K635" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L635" s="6" t="inlineStr"/>
@@ -31286,7 +31286,7 @@
       </c>
       <c r="K636" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L636" s="3" t="inlineStr"/>
@@ -31334,7 +31334,7 @@
       </c>
       <c r="K637" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L637" s="6" t="inlineStr"/>
@@ -31382,7 +31382,7 @@
       </c>
       <c r="K638" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L638" s="3" t="inlineStr"/>
@@ -31430,7 +31430,7 @@
       </c>
       <c r="K639" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L639" s="6" t="inlineStr"/>
@@ -31478,7 +31478,7 @@
       </c>
       <c r="K640" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L640" s="3" t="inlineStr"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K641" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L641" s="6" t="inlineStr"/>
@@ -31574,7 +31574,7 @@
       </c>
       <c r="K642" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L642" s="3" t="inlineStr"/>
@@ -31622,7 +31622,7 @@
       </c>
       <c r="K643" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L643" s="6" t="inlineStr"/>
@@ -31670,7 +31670,7 @@
       </c>
       <c r="K644" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L644" s="3" t="inlineStr"/>
@@ -31718,7 +31718,7 @@
       </c>
       <c r="K645" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L645" s="6" t="inlineStr"/>
@@ -31766,7 +31766,7 @@
       </c>
       <c r="K646" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L646" s="3" t="inlineStr"/>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="K647" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L647" s="6" t="inlineStr"/>
@@ -31862,7 +31862,7 @@
       </c>
       <c r="K648" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L648" s="3" t="inlineStr"/>
@@ -31910,7 +31910,7 @@
       </c>
       <c r="K649" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L649" s="6" t="inlineStr"/>
@@ -31958,7 +31958,7 @@
       </c>
       <c r="K650" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L650" s="3" t="inlineStr"/>
@@ -32006,7 +32006,7 @@
       </c>
       <c r="K651" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L651" s="6" t="inlineStr"/>
@@ -32054,7 +32054,7 @@
       </c>
       <c r="K652" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L652" s="3" t="inlineStr"/>
@@ -32102,7 +32102,7 @@
       </c>
       <c r="K653" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L653" s="6" t="inlineStr"/>
@@ -32150,7 +32150,7 @@
       </c>
       <c r="K654" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L654" s="3" t="inlineStr"/>
@@ -32198,7 +32198,7 @@
       </c>
       <c r="K655" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L655" s="6" t="inlineStr"/>
@@ -32246,7 +32246,7 @@
       </c>
       <c r="K656" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L656" s="3" t="inlineStr"/>
@@ -32294,7 +32294,7 @@
       </c>
       <c r="K657" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L657" s="6" t="inlineStr"/>
@@ -32342,7 +32342,7 @@
       </c>
       <c r="K658" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L658" s="3" t="inlineStr"/>
@@ -32390,7 +32390,7 @@
       </c>
       <c r="K659" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L659" s="6" t="inlineStr"/>
@@ -32438,7 +32438,7 @@
       </c>
       <c r="K660" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L660" s="3" t="inlineStr"/>
@@ -32486,7 +32486,7 @@
       </c>
       <c r="K661" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L661" s="6" t="inlineStr"/>
@@ -32534,7 +32534,7 @@
       </c>
       <c r="K662" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L662" s="3" t="inlineStr"/>
@@ -32582,7 +32582,7 @@
       </c>
       <c r="K663" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L663" s="6" t="inlineStr"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K664" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L664" s="3" t="inlineStr"/>
@@ -32678,7 +32678,7 @@
       </c>
       <c r="K665" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L665" s="6" t="inlineStr"/>
@@ -32726,7 +32726,7 @@
       </c>
       <c r="K666" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L666" s="3" t="inlineStr"/>
@@ -32774,7 +32774,7 @@
       </c>
       <c r="K667" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L667" s="6" t="inlineStr"/>
@@ -32822,7 +32822,7 @@
       </c>
       <c r="K668" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L668" s="3" t="inlineStr"/>
@@ -32870,7 +32870,7 @@
       </c>
       <c r="K669" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L669" s="6" t="inlineStr"/>
@@ -32918,7 +32918,7 @@
       </c>
       <c r="K670" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L670" s="3" t="inlineStr"/>
@@ -32966,7 +32966,7 @@
       </c>
       <c r="K671" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L671" s="6" t="inlineStr"/>
@@ -33014,7 +33014,7 @@
       </c>
       <c r="K672" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L672" s="3" t="inlineStr"/>
@@ -33062,7 +33062,7 @@
       </c>
       <c r="K673" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L673" s="6" t="inlineStr"/>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="K674" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L674" s="3" t="inlineStr"/>
@@ -33158,7 +33158,7 @@
       </c>
       <c r="K675" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L675" s="6" t="inlineStr"/>
@@ -33206,7 +33206,7 @@
       </c>
       <c r="K676" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L676" s="3" t="inlineStr"/>
@@ -33254,7 +33254,7 @@
       </c>
       <c r="K677" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L677" s="6" t="inlineStr"/>
@@ -33302,7 +33302,7 @@
       </c>
       <c r="K678" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L678" s="3" t="inlineStr"/>
@@ -33350,7 +33350,7 @@
       </c>
       <c r="K679" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L679" s="6" t="inlineStr"/>
@@ -33398,7 +33398,7 @@
       </c>
       <c r="K680" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L680" s="3" t="inlineStr"/>
@@ -33446,7 +33446,7 @@
       </c>
       <c r="K681" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L681" s="6" t="inlineStr"/>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="K682" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L682" s="3" t="inlineStr"/>
@@ -33542,7 +33542,7 @@
       </c>
       <c r="K683" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L683" s="6" t="inlineStr"/>
@@ -33590,7 +33590,7 @@
       </c>
       <c r="K684" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L684" s="3" t="inlineStr"/>
@@ -33638,7 +33638,7 @@
       </c>
       <c r="K685" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L685" s="6" t="inlineStr"/>
@@ -33686,7 +33686,7 @@
       </c>
       <c r="K686" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L686" s="3" t="inlineStr"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K687" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L687" s="6" t="inlineStr"/>
@@ -33782,7 +33782,7 @@
       </c>
       <c r="K688" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L688" s="3" t="inlineStr"/>
@@ -33830,7 +33830,7 @@
       </c>
       <c r="K689" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L689" s="6" t="inlineStr"/>
@@ -33878,7 +33878,7 @@
       </c>
       <c r="K690" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L690" s="3" t="inlineStr"/>
@@ -33926,7 +33926,7 @@
       </c>
       <c r="K691" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L691" s="6" t="inlineStr"/>
@@ -33974,7 +33974,7 @@
       </c>
       <c r="K692" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L692" s="3" t="inlineStr"/>
@@ -34022,7 +34022,7 @@
       </c>
       <c r="K693" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L693" s="6" t="inlineStr"/>
@@ -34070,7 +34070,7 @@
       </c>
       <c r="K694" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L694" s="3" t="inlineStr"/>
@@ -34118,7 +34118,7 @@
       </c>
       <c r="K695" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L695" s="6" t="inlineStr"/>
@@ -34166,7 +34166,7 @@
       </c>
       <c r="K696" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L696" s="3" t="inlineStr"/>
@@ -34214,7 +34214,7 @@
       </c>
       <c r="K697" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L697" s="6" t="inlineStr"/>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="K698" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L698" s="3" t="inlineStr"/>
@@ -34310,7 +34310,7 @@
       </c>
       <c r="K699" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L699" s="6" t="inlineStr"/>
@@ -34358,7 +34358,7 @@
       </c>
       <c r="K700" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L700" s="3" t="inlineStr"/>
@@ -34406,7 +34406,7 @@
       </c>
       <c r="K701" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L701" s="6" t="inlineStr"/>
@@ -34454,7 +34454,7 @@
       </c>
       <c r="K702" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L702" s="3" t="inlineStr"/>
@@ -34502,7 +34502,7 @@
       </c>
       <c r="K703" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L703" s="6" t="inlineStr"/>
@@ -34550,7 +34550,7 @@
       </c>
       <c r="K704" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L704" s="3" t="inlineStr"/>
@@ -34598,7 +34598,7 @@
       </c>
       <c r="K705" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L705" s="6" t="inlineStr"/>
@@ -34646,7 +34646,7 @@
       </c>
       <c r="K706" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L706" s="3" t="inlineStr"/>
@@ -34694,7 +34694,7 @@
       </c>
       <c r="K707" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L707" s="6" t="inlineStr"/>
@@ -34742,7 +34742,7 @@
       </c>
       <c r="K708" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L708" s="3" t="inlineStr"/>
@@ -34790,7 +34790,7 @@
       </c>
       <c r="K709" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L709" s="6" t="inlineStr"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K710" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L710" s="3" t="inlineStr"/>
@@ -34886,7 +34886,7 @@
       </c>
       <c r="K711" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L711" s="6" t="inlineStr"/>
@@ -34934,7 +34934,7 @@
       </c>
       <c r="K712" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L712" s="3" t="inlineStr"/>
@@ -34982,7 +34982,7 @@
       </c>
       <c r="K713" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L713" s="6" t="inlineStr"/>
@@ -35030,7 +35030,7 @@
       </c>
       <c r="K714" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L714" s="3" t="inlineStr"/>
@@ -35078,7 +35078,7 @@
       </c>
       <c r="K715" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L715" s="6" t="inlineStr"/>
@@ -35126,7 +35126,7 @@
       </c>
       <c r="K716" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L716" s="3" t="inlineStr"/>
@@ -35174,7 +35174,7 @@
       </c>
       <c r="K717" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L717" s="6" t="inlineStr"/>
@@ -35222,7 +35222,7 @@
       </c>
       <c r="K718" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L718" s="3" t="inlineStr"/>
@@ -35270,7 +35270,7 @@
       </c>
       <c r="K719" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L719" s="6" t="inlineStr"/>
@@ -35318,7 +35318,7 @@
       </c>
       <c r="K720" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L720" s="3" t="inlineStr"/>
@@ -35366,7 +35366,7 @@
       </c>
       <c r="K721" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L721" s="6" t="inlineStr"/>
@@ -35414,7 +35414,7 @@
       </c>
       <c r="K722" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L722" s="3" t="inlineStr"/>
@@ -35462,7 +35462,7 @@
       </c>
       <c r="K723" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L723" s="6" t="inlineStr"/>
@@ -35510,7 +35510,7 @@
       </c>
       <c r="K724" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L724" s="3" t="inlineStr"/>
@@ -35558,7 +35558,7 @@
       </c>
       <c r="K725" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L725" s="6" t="inlineStr"/>
@@ -35606,7 +35606,7 @@
       </c>
       <c r="K726" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L726" s="3" t="inlineStr"/>
@@ -35654,7 +35654,7 @@
       </c>
       <c r="K727" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L727" s="6" t="inlineStr"/>
@@ -35702,7 +35702,7 @@
       </c>
       <c r="K728" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L728" s="3" t="inlineStr"/>
@@ -35750,7 +35750,7 @@
       </c>
       <c r="K729" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L729" s="4" t="inlineStr">
@@ -35802,7 +35802,7 @@
       </c>
       <c r="K730" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L730" s="4" t="inlineStr">
@@ -35854,7 +35854,7 @@
       </c>
       <c r="K731" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L731" s="4" t="inlineStr">
@@ -35906,7 +35906,7 @@
       </c>
       <c r="K732" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L732" s="4" t="inlineStr">
@@ -35958,7 +35958,7 @@
       </c>
       <c r="K733" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L733" s="4" t="inlineStr">
@@ -36010,7 +36010,7 @@
       </c>
       <c r="K734" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L734" s="4" t="inlineStr">
@@ -36062,7 +36062,7 @@
       </c>
       <c r="K735" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L735" s="4" t="inlineStr">
@@ -36114,7 +36114,7 @@
       </c>
       <c r="K736" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L736" s="4" t="inlineStr">
@@ -36166,7 +36166,7 @@
       </c>
       <c r="K737" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L737" s="4" t="inlineStr">
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K738" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L738" s="4" t="inlineStr">
@@ -36270,7 +36270,7 @@
       </c>
       <c r="K739" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L739" s="4" t="inlineStr">
@@ -36322,7 +36322,7 @@
       </c>
       <c r="K740" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L740" s="4" t="inlineStr">
@@ -36374,7 +36374,7 @@
       </c>
       <c r="K741" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L741" s="4" t="inlineStr">
@@ -36426,7 +36426,7 @@
       </c>
       <c r="K742" s="3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L742" s="4" t="inlineStr">
@@ -36478,7 +36478,7 @@
       </c>
       <c r="K743" s="6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="L743" s="4" t="inlineStr">

--- a/public/loop-library.xlsx
+++ b/public/loop-library.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr"/>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr"/>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr"/>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr"/>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr"/>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr"/>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr"/>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr"/>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr"/>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr"/>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr"/>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr"/>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr"/>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr"/>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr"/>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr"/>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr"/>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr"/>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr"/>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr"/>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L93" s="6" t="inlineStr"/>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr"/>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L95" s="6" t="inlineStr"/>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr"/>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L97" s="6" t="inlineStr"/>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr"/>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr"/>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr"/>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr"/>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L102" s="3" t="inlineStr"/>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L103" s="6" t="inlineStr"/>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L104" s="3" t="inlineStr"/>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L105" s="6" t="inlineStr"/>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L106" s="3" t="inlineStr"/>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L107" s="6" t="inlineStr"/>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L108" s="3" t="inlineStr"/>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L109" s="6" t="inlineStr"/>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L110" s="3" t="inlineStr"/>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L111" s="6" t="inlineStr"/>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L112" s="3" t="inlineStr"/>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L113" s="6" t="inlineStr"/>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L114" s="3" t="inlineStr"/>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L115" s="6" t="inlineStr"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="K116" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L116" s="3" t="inlineStr"/>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L117" s="6" t="inlineStr"/>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="K118" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L118" s="3" t="inlineStr"/>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L119" s="6" t="inlineStr"/>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="K120" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L120" s="3" t="inlineStr"/>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L121" s="6" t="inlineStr"/>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="K122" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L122" s="3" t="inlineStr"/>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L123" s="6" t="inlineStr"/>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="K124" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L124" s="3" t="inlineStr"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="K125" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L125" s="6" t="inlineStr"/>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="K126" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L126" s="3" t="inlineStr"/>
@@ -6854,7 +6854,7 @@
       </c>
       <c r="K127" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L127" s="6" t="inlineStr"/>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L128" s="3" t="inlineStr"/>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="K129" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L129" s="6" t="inlineStr"/>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="K130" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L130" s="3" t="inlineStr"/>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="K131" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L131" s="6" t="inlineStr"/>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L132" s="3" t="inlineStr"/>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="K133" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L133" s="6" t="inlineStr"/>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="K134" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L134" s="3" t="inlineStr"/>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="K135" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L135" s="6" t="inlineStr"/>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="K136" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L136" s="3" t="inlineStr"/>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="K137" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L137" s="6" t="inlineStr"/>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="K138" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L138" s="3" t="inlineStr"/>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="K139" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L139" s="6" t="inlineStr"/>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="K140" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L140" s="3" t="inlineStr"/>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="K141" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L141" s="6" t="inlineStr"/>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L142" s="3" t="inlineStr"/>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="K143" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L143" s="6" t="inlineStr"/>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="K144" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L144" s="3" t="inlineStr"/>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="K145" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L145" s="6" t="inlineStr"/>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="K146" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L146" s="3" t="inlineStr"/>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="K147" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L147" s="6" t="inlineStr"/>
@@ -7862,7 +7862,7 @@
       </c>
       <c r="K148" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L148" s="3" t="inlineStr"/>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="K149" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L149" s="6" t="inlineStr"/>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="K150" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L150" s="3" t="inlineStr"/>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="K151" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L151" s="6" t="inlineStr"/>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="K152" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L152" s="3" t="inlineStr"/>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="K153" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L153" s="6" t="inlineStr"/>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="K154" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L154" s="3" t="inlineStr"/>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="K155" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L155" s="6" t="inlineStr"/>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="K156" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L156" s="3" t="inlineStr"/>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K157" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L157" s="6" t="inlineStr"/>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="K158" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L158" s="3" t="inlineStr"/>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="K159" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L159" s="6" t="inlineStr"/>
@@ -8438,7 +8438,7 @@
       </c>
       <c r="K160" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L160" s="3" t="inlineStr"/>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="K161" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L161" s="6" t="inlineStr"/>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="K162" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L162" s="3" t="inlineStr"/>
@@ -8582,7 +8582,7 @@
       </c>
       <c r="K163" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L163" s="6" t="inlineStr"/>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="K164" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L164" s="3" t="inlineStr"/>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="K165" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L165" s="6" t="inlineStr"/>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="K166" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L166" s="3" t="inlineStr"/>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="K167" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L167" s="6" t="inlineStr"/>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="K168" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L168" s="3" t="inlineStr"/>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="K169" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L169" s="6" t="inlineStr"/>
@@ -8918,7 +8918,7 @@
       </c>
       <c r="K170" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L170" s="3" t="inlineStr"/>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="K171" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L171" s="6" t="inlineStr"/>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="K172" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L172" s="3" t="inlineStr"/>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="K173" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L173" s="6" t="inlineStr"/>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="K174" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L174" s="3" t="inlineStr"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="K175" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L175" s="6" t="inlineStr"/>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="K176" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L176" s="3" t="inlineStr"/>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="K177" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L177" s="6" t="inlineStr"/>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="K178" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L178" s="3" t="inlineStr"/>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="K179" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L179" s="6" t="inlineStr"/>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="K180" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L180" s="3" t="inlineStr"/>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="K181" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L181" s="6" t="inlineStr"/>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="K182" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L182" s="3" t="inlineStr"/>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="K183" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L183" s="6" t="inlineStr"/>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="K184" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L184" s="3" t="inlineStr"/>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="K185" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L185" s="6" t="inlineStr"/>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="K186" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L186" s="3" t="inlineStr"/>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="K187" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L187" s="6" t="inlineStr"/>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="K188" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L188" s="3" t="inlineStr"/>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="K189" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L189" s="6" t="inlineStr"/>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="K190" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L190" s="3" t="inlineStr"/>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="K191" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L191" s="6" t="inlineStr"/>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="K192" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L192" s="3" t="inlineStr"/>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="K193" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L193" s="6" t="inlineStr"/>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="K194" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L194" s="3" t="inlineStr"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="K195" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L195" s="6" t="inlineStr"/>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="K196" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L196" s="3" t="inlineStr"/>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="K197" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L197" s="6" t="inlineStr"/>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="K198" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L198" s="3" t="inlineStr"/>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="K199" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L199" s="6" t="inlineStr"/>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="K200" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L200" s="3" t="inlineStr"/>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="K201" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L201" s="6" t="inlineStr"/>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="K202" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L202" s="3" t="inlineStr"/>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="K203" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L203" s="6" t="inlineStr"/>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="K204" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L204" s="3" t="inlineStr"/>
@@ -10598,7 +10598,7 @@
       </c>
       <c r="K205" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L205" s="6" t="inlineStr"/>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K206" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L206" s="3" t="inlineStr"/>
@@ -10694,7 +10694,7 @@
       </c>
       <c r="K207" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L207" s="6" t="inlineStr"/>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="K208" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L208" s="3" t="inlineStr"/>
@@ -10790,7 +10790,7 @@
       </c>
       <c r="K209" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L209" s="6" t="inlineStr"/>
@@ -10838,7 +10838,7 @@
       </c>
       <c r="K210" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L210" s="3" t="inlineStr"/>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="K211" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L211" s="6" t="inlineStr"/>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="K212" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L212" s="3" t="inlineStr"/>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="K213" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L213" s="6" t="inlineStr"/>
@@ -11030,7 +11030,7 @@
       </c>
       <c r="K214" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L214" s="3" t="inlineStr"/>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="K215" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L215" s="6" t="inlineStr"/>
@@ -11126,7 +11126,7 @@
       </c>
       <c r="K216" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L216" s="3" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="K217" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L217" s="6" t="inlineStr"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="K218" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L218" s="3" t="inlineStr"/>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="K219" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L219" s="6" t="inlineStr"/>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="K220" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L220" s="3" t="inlineStr"/>
@@ -11366,7 +11366,7 @@
       </c>
       <c r="K221" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L221" s="6" t="inlineStr"/>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="K222" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L222" s="3" t="inlineStr"/>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="K223" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L223" s="6" t="inlineStr"/>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="K224" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L224" s="3" t="inlineStr"/>
@@ -11558,7 +11558,7 @@
       </c>
       <c r="K225" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L225" s="6" t="inlineStr"/>
@@ -11606,7 +11606,7 @@
       </c>
       <c r="K226" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L226" s="3" t="inlineStr"/>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="K227" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L227" s="6" t="inlineStr"/>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="K228" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L228" s="3" t="inlineStr"/>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="K229" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L229" s="6" t="inlineStr"/>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="K230" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L230" s="3" t="inlineStr"/>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="K231" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L231" s="6" t="inlineStr"/>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="K232" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L232" s="3" t="inlineStr"/>
@@ -11942,7 +11942,7 @@
       </c>
       <c r="K233" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L233" s="6" t="inlineStr"/>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="K234" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L234" s="3" t="inlineStr"/>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="K235" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L235" s="6" t="inlineStr"/>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="K236" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L236" s="3" t="inlineStr"/>
@@ -12134,7 +12134,7 @@
       </c>
       <c r="K237" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L237" s="6" t="inlineStr"/>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="K238" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L238" s="3" t="inlineStr"/>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="K239" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L239" s="6" t="inlineStr"/>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="K240" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L240" s="3" t="inlineStr"/>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="K241" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L241" s="6" t="inlineStr"/>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="K242" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L242" s="3" t="inlineStr"/>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="K243" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L243" s="6" t="inlineStr"/>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="K244" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L244" s="3" t="inlineStr"/>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="K245" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L245" s="6" t="inlineStr"/>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="K246" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L246" s="3" t="inlineStr"/>
@@ -12614,7 +12614,7 @@
       </c>
       <c r="K247" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L247" s="6" t="inlineStr"/>
@@ -12662,7 +12662,7 @@
       </c>
       <c r="K248" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L248" s="3" t="inlineStr"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="K249" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L249" s="6" t="inlineStr"/>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="K250" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L250" s="3" t="inlineStr"/>
@@ -12806,7 +12806,7 @@
       </c>
       <c r="K251" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L251" s="6" t="inlineStr"/>
@@ -12854,7 +12854,7 @@
       </c>
       <c r="K252" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L252" s="3" t="inlineStr"/>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="K253" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L253" s="6" t="inlineStr"/>
@@ -12950,7 +12950,7 @@
       </c>
       <c r="K254" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L254" s="3" t="inlineStr"/>
@@ -12998,7 +12998,7 @@
       </c>
       <c r="K255" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L255" s="6" t="inlineStr"/>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="K256" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L256" s="3" t="inlineStr"/>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="K257" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L257" s="6" t="inlineStr"/>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="K258" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L258" s="3" t="inlineStr"/>
@@ -13190,7 +13190,7 @@
       </c>
       <c r="K259" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L259" s="6" t="inlineStr"/>
@@ -13238,7 +13238,7 @@
       </c>
       <c r="K260" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L260" s="3" t="inlineStr"/>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="K261" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L261" s="6" t="inlineStr"/>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="K262" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L262" s="3" t="inlineStr"/>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="K263" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L263" s="6" t="inlineStr"/>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="K264" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L264" s="3" t="inlineStr"/>
@@ -13478,7 +13478,7 @@
       </c>
       <c r="K265" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L265" s="6" t="inlineStr"/>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="K266" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L266" s="3" t="inlineStr"/>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="K267" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L267" s="6" t="inlineStr"/>
@@ -13622,7 +13622,7 @@
       </c>
       <c r="K268" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L268" s="3" t="inlineStr"/>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="K269" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L269" s="6" t="inlineStr"/>
@@ -13718,7 +13718,7 @@
       </c>
       <c r="K270" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L270" s="3" t="inlineStr"/>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="K271" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L271" s="6" t="inlineStr"/>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="K272" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L272" s="3" t="inlineStr"/>
@@ -13862,7 +13862,7 @@
       </c>
       <c r="K273" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L273" s="6" t="inlineStr"/>
@@ -13910,7 +13910,7 @@
       </c>
       <c r="K274" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L274" s="3" t="inlineStr"/>
@@ -13958,7 +13958,7 @@
       </c>
       <c r="K275" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L275" s="6" t="inlineStr"/>
@@ -14006,7 +14006,7 @@
       </c>
       <c r="K276" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L276" s="3" t="inlineStr"/>
@@ -14054,7 +14054,7 @@
       </c>
       <c r="K277" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L277" s="6" t="inlineStr"/>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="K278" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L278" s="3" t="inlineStr"/>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="K279" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L279" s="6" t="inlineStr"/>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="K280" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L280" s="3" t="inlineStr"/>
@@ -14246,7 +14246,7 @@
       </c>
       <c r="K281" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L281" s="6" t="inlineStr"/>
@@ -14294,7 +14294,7 @@
       </c>
       <c r="K282" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L282" s="3" t="inlineStr"/>
@@ -14342,7 +14342,7 @@
       </c>
       <c r="K283" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L283" s="6" t="inlineStr"/>
@@ -14390,7 +14390,7 @@
       </c>
       <c r="K284" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L284" s="3" t="inlineStr"/>
@@ -14438,7 +14438,7 @@
       </c>
       <c r="K285" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L285" s="6" t="inlineStr"/>
@@ -14486,7 +14486,7 @@
       </c>
       <c r="K286" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L286" s="3" t="inlineStr"/>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="K287" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L287" s="6" t="inlineStr"/>
@@ -14582,7 +14582,7 @@
       </c>
       <c r="K288" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L288" s="3" t="inlineStr"/>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="K289" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L289" s="6" t="inlineStr"/>
@@ -14678,7 +14678,7 @@
       </c>
       <c r="K290" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L290" s="3" t="inlineStr"/>
@@ -14726,7 +14726,7 @@
       </c>
       <c r="K291" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L291" s="6" t="inlineStr"/>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="K292" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L292" s="3" t="inlineStr"/>
@@ -14822,7 +14822,7 @@
       </c>
       <c r="K293" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L293" s="6" t="inlineStr"/>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="K294" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L294" s="3" t="inlineStr"/>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="K295" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L295" s="6" t="inlineStr"/>
@@ -14966,7 +14966,7 @@
       </c>
       <c r="K296" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L296" s="3" t="inlineStr"/>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="K297" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L297" s="6" t="inlineStr"/>
@@ -15062,7 +15062,7 @@
       </c>
       <c r="K298" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L298" s="3" t="inlineStr"/>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="K299" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L299" s="6" t="inlineStr"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="K300" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L300" s="3" t="inlineStr"/>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="K301" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L301" s="6" t="inlineStr"/>
@@ -15254,7 +15254,7 @@
       </c>
       <c r="K302" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L302" s="3" t="inlineStr"/>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="K303" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L303" s="6" t="inlineStr"/>
@@ -15350,7 +15350,7 @@
       </c>
       <c r="K304" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L304" s="3" t="inlineStr"/>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="K305" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L305" s="6" t="inlineStr"/>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="K306" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L306" s="3" t="inlineStr"/>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="K307" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L307" s="6" t="inlineStr"/>
@@ -15542,7 +15542,7 @@
       </c>
       <c r="K308" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L308" s="3" t="inlineStr"/>
@@ -15590,7 +15590,7 @@
       </c>
       <c r="K309" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L309" s="6" t="inlineStr"/>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="K310" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L310" s="3" t="inlineStr"/>
@@ -15686,7 +15686,7 @@
       </c>
       <c r="K311" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L311" s="6" t="inlineStr"/>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="K312" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L312" s="3" t="inlineStr"/>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="K313" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L313" s="6" t="inlineStr"/>
@@ -15830,7 +15830,7 @@
       </c>
       <c r="K314" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L314" s="3" t="inlineStr"/>
@@ -15878,7 +15878,7 @@
       </c>
       <c r="K315" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L315" s="6" t="inlineStr"/>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="K316" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L316" s="3" t="inlineStr"/>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="K317" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L317" s="6" t="inlineStr"/>
@@ -16022,7 +16022,7 @@
       </c>
       <c r="K318" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L318" s="3" t="inlineStr"/>
@@ -16070,7 +16070,7 @@
       </c>
       <c r="K319" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L319" s="6" t="inlineStr"/>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="K320" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L320" s="3" t="inlineStr"/>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="K321" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L321" s="6" t="inlineStr"/>
@@ -16214,7 +16214,7 @@
       </c>
       <c r="K322" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L322" s="3" t="inlineStr"/>
@@ -16262,7 +16262,7 @@
       </c>
       <c r="K323" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L323" s="6" t="inlineStr"/>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="K324" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L324" s="3" t="inlineStr"/>
@@ -16358,7 +16358,7 @@
       </c>
       <c r="K325" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L325" s="6" t="inlineStr"/>
@@ -16406,7 +16406,7 @@
       </c>
       <c r="K326" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L326" s="3" t="inlineStr"/>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="K327" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L327" s="6" t="inlineStr"/>
@@ -16502,7 +16502,7 @@
       </c>
       <c r="K328" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L328" s="3" t="inlineStr"/>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="K329" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L329" s="6" t="inlineStr"/>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="K330" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L330" s="3" t="inlineStr"/>
@@ -16646,7 +16646,7 @@
       </c>
       <c r="K331" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L331" s="6" t="inlineStr"/>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="K332" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L332" s="3" t="inlineStr"/>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="K333" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L333" s="6" t="inlineStr"/>
@@ -16790,7 +16790,7 @@
       </c>
       <c r="K334" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L334" s="3" t="inlineStr"/>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="K335" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L335" s="6" t="inlineStr"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="K336" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L336" s="3" t="inlineStr"/>
@@ -16934,7 +16934,7 @@
       </c>
       <c r="K337" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L337" s="6" t="inlineStr"/>
@@ -16982,7 +16982,7 @@
       </c>
       <c r="K338" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L338" s="3" t="inlineStr"/>
@@ -17030,7 +17030,7 @@
       </c>
       <c r="K339" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L339" s="6" t="inlineStr"/>
@@ -17078,7 +17078,7 @@
       </c>
       <c r="K340" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L340" s="3" t="inlineStr"/>
@@ -17126,7 +17126,7 @@
       </c>
       <c r="K341" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L341" s="6" t="inlineStr"/>
@@ -17174,7 +17174,7 @@
       </c>
       <c r="K342" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L342" s="3" t="inlineStr"/>
@@ -17222,7 +17222,7 @@
       </c>
       <c r="K343" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L343" s="6" t="inlineStr"/>
@@ -17270,7 +17270,7 @@
       </c>
       <c r="K344" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L344" s="3" t="inlineStr"/>
@@ -17318,7 +17318,7 @@
       </c>
       <c r="K345" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L345" s="6" t="inlineStr"/>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="K346" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L346" s="3" t="inlineStr"/>
@@ -17414,7 +17414,7 @@
       </c>
       <c r="K347" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L347" s="6" t="inlineStr"/>
@@ -17462,7 +17462,7 @@
       </c>
       <c r="K348" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L348" s="3" t="inlineStr"/>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="K349" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L349" s="6" t="inlineStr"/>
@@ -17558,7 +17558,7 @@
       </c>
       <c r="K350" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L350" s="3" t="inlineStr"/>
@@ -17606,7 +17606,7 @@
       </c>
       <c r="K351" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L351" s="6" t="inlineStr"/>
@@ -17654,7 +17654,7 @@
       </c>
       <c r="K352" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L352" s="3" t="inlineStr"/>
@@ -17702,7 +17702,7 @@
       </c>
       <c r="K353" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L353" s="6" t="inlineStr"/>
@@ -17750,7 +17750,7 @@
       </c>
       <c r="K354" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L354" s="3" t="inlineStr"/>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="K355" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L355" s="6" t="inlineStr"/>
@@ -17846,7 +17846,7 @@
       </c>
       <c r="K356" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L356" s="3" t="inlineStr"/>
@@ -17894,7 +17894,7 @@
       </c>
       <c r="K357" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L357" s="6" t="inlineStr"/>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="K358" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L358" s="3" t="inlineStr"/>
@@ -17990,7 +17990,7 @@
       </c>
       <c r="K359" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L359" s="6" t="inlineStr"/>
@@ -18038,7 +18038,7 @@
       </c>
       <c r="K360" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L360" s="3" t="inlineStr"/>
@@ -18086,7 +18086,7 @@
       </c>
       <c r="K361" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L361" s="6" t="inlineStr"/>
@@ -18134,7 +18134,7 @@
       </c>
       <c r="K362" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L362" s="3" t="inlineStr"/>
@@ -18182,7 +18182,7 @@
       </c>
       <c r="K363" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L363" s="6" t="inlineStr"/>
@@ -18230,7 +18230,7 @@
       </c>
       <c r="K364" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L364" s="3" t="inlineStr"/>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="K365" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L365" s="6" t="inlineStr"/>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="K366" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L366" s="3" t="inlineStr"/>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="K367" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L367" s="6" t="inlineStr"/>
@@ -18422,7 +18422,7 @@
       </c>
       <c r="K368" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L368" s="3" t="inlineStr"/>
@@ -18470,7 +18470,7 @@
       </c>
       <c r="K369" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L369" s="6" t="inlineStr"/>
@@ -18518,7 +18518,7 @@
       </c>
       <c r="K370" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L370" s="3" t="inlineStr"/>
@@ -18566,7 +18566,7 @@
       </c>
       <c r="K371" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L371" s="6" t="inlineStr"/>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="K372" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L372" s="3" t="inlineStr"/>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="K373" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L373" s="6" t="inlineStr"/>
@@ -18710,7 +18710,7 @@
       </c>
       <c r="K374" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L374" s="3" t="inlineStr"/>
@@ -18758,7 +18758,7 @@
       </c>
       <c r="K375" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L375" s="6" t="inlineStr"/>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="K376" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L376" s="3" t="inlineStr"/>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="K377" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L377" s="6" t="inlineStr"/>
@@ -18902,7 +18902,7 @@
       </c>
       <c r="K378" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L378" s="3" t="inlineStr"/>
@@ -18950,7 +18950,7 @@
       </c>
       <c r="K379" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L379" s="6" t="inlineStr"/>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="K380" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L380" s="3" t="inlineStr"/>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="K381" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L381" s="6" t="inlineStr"/>
@@ -19094,7 +19094,7 @@
       </c>
       <c r="K382" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L382" s="3" t="inlineStr"/>
@@ -19142,7 +19142,7 @@
       </c>
       <c r="K383" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L383" s="6" t="inlineStr"/>
@@ -19190,7 +19190,7 @@
       </c>
       <c r="K384" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L384" s="3" t="inlineStr"/>
@@ -19238,7 +19238,7 @@
       </c>
       <c r="K385" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L385" s="6" t="inlineStr"/>
@@ -19286,7 +19286,7 @@
       </c>
       <c r="K386" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L386" s="3" t="inlineStr"/>
@@ -19334,7 +19334,7 @@
       </c>
       <c r="K387" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L387" s="6" t="inlineStr"/>
@@ -19382,7 +19382,7 @@
       </c>
       <c r="K388" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L388" s="3" t="inlineStr"/>
@@ -19430,7 +19430,7 @@
       </c>
       <c r="K389" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L389" s="6" t="inlineStr"/>
@@ -19478,7 +19478,7 @@
       </c>
       <c r="K390" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L390" s="3" t="inlineStr"/>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="K391" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L391" s="6" t="inlineStr"/>
@@ -19574,7 +19574,7 @@
       </c>
       <c r="K392" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L392" s="3" t="inlineStr"/>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="K393" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L393" s="6" t="inlineStr"/>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="K394" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L394" s="3" t="inlineStr"/>
@@ -19718,7 +19718,7 @@
       </c>
       <c r="K395" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L395" s="6" t="inlineStr"/>
@@ -19766,7 +19766,7 @@
       </c>
       <c r="K396" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L396" s="3" t="inlineStr"/>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="K397" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L397" s="6" t="inlineStr"/>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="K398" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L398" s="3" t="inlineStr"/>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="K399" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L399" s="6" t="inlineStr"/>
@@ -19958,7 +19958,7 @@
       </c>
       <c r="K400" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L400" s="3" t="inlineStr"/>
@@ -20006,7 +20006,7 @@
       </c>
       <c r="K401" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L401" s="6" t="inlineStr"/>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="K402" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L402" s="3" t="inlineStr"/>
@@ -20102,7 +20102,7 @@
       </c>
       <c r="K403" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L403" s="6" t="inlineStr"/>
@@ -20150,7 +20150,7 @@
       </c>
       <c r="K404" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L404" s="3" t="inlineStr"/>
@@ -20198,7 +20198,7 @@
       </c>
       <c r="K405" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L405" s="6" t="inlineStr"/>
@@ -20246,7 +20246,7 @@
       </c>
       <c r="K406" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L406" s="3" t="inlineStr"/>
@@ -20294,7 +20294,7 @@
       </c>
       <c r="K407" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L407" s="6" t="inlineStr"/>
@@ -20342,7 +20342,7 @@
       </c>
       <c r="K408" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L408" s="3" t="inlineStr"/>
@@ -20390,7 +20390,7 @@
       </c>
       <c r="K409" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L409" s="6" t="inlineStr"/>
@@ -20438,7 +20438,7 @@
       </c>
       <c r="K410" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L410" s="3" t="inlineStr"/>
@@ -20486,7 +20486,7 @@
       </c>
       <c r="K411" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L411" s="6" t="inlineStr"/>
@@ -20534,7 +20534,7 @@
       </c>
       <c r="K412" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L412" s="3" t="inlineStr"/>
@@ -20582,7 +20582,7 @@
       </c>
       <c r="K413" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L413" s="6" t="inlineStr"/>
@@ -20630,7 +20630,7 @@
       </c>
       <c r="K414" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L414" s="3" t="inlineStr"/>
@@ -20678,7 +20678,7 @@
       </c>
       <c r="K415" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L415" s="6" t="inlineStr"/>
@@ -20726,7 +20726,7 @@
       </c>
       <c r="K416" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L416" s="3" t="inlineStr"/>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="K417" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L417" s="6" t="inlineStr"/>
@@ -20822,7 +20822,7 @@
       </c>
       <c r="K418" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L418" s="3" t="inlineStr"/>
@@ -20870,7 +20870,7 @@
       </c>
       <c r="K419" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L419" s="6" t="inlineStr"/>
@@ -20918,7 +20918,7 @@
       </c>
       <c r="K420" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L420" s="3" t="inlineStr"/>
@@ -20966,7 +20966,7 @@
       </c>
       <c r="K421" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L421" s="6" t="inlineStr"/>
@@ -21014,7 +21014,7 @@
       </c>
       <c r="K422" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L422" s="3" t="inlineStr"/>
@@ -21062,7 +21062,7 @@
       </c>
       <c r="K423" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L423" s="6" t="inlineStr"/>
@@ -21110,7 +21110,7 @@
       </c>
       <c r="K424" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L424" s="3" t="inlineStr"/>
@@ -21158,7 +21158,7 @@
       </c>
       <c r="K425" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L425" s="6" t="inlineStr"/>
@@ -21206,7 +21206,7 @@
       </c>
       <c r="K426" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L426" s="3" t="inlineStr"/>
@@ -21254,7 +21254,7 @@
       </c>
       <c r="K427" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L427" s="6" t="inlineStr"/>
@@ -21302,7 +21302,7 @@
       </c>
       <c r="K428" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L428" s="3" t="inlineStr"/>
@@ -21350,7 +21350,7 @@
       </c>
       <c r="K429" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L429" s="6" t="inlineStr"/>
@@ -21398,7 +21398,7 @@
       </c>
       <c r="K430" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L430" s="3" t="inlineStr"/>
@@ -21446,7 +21446,7 @@
       </c>
       <c r="K431" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L431" s="6" t="inlineStr"/>
@@ -21494,7 +21494,7 @@
       </c>
       <c r="K432" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L432" s="3" t="inlineStr"/>
@@ -21542,7 +21542,7 @@
       </c>
       <c r="K433" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L433" s="6" t="inlineStr"/>
@@ -21590,7 +21590,7 @@
       </c>
       <c r="K434" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L434" s="3" t="inlineStr"/>
@@ -21638,7 +21638,7 @@
       </c>
       <c r="K435" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L435" s="6" t="inlineStr"/>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="K436" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L436" s="3" t="inlineStr"/>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="K437" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L437" s="6" t="inlineStr"/>
@@ -21782,7 +21782,7 @@
       </c>
       <c r="K438" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L438" s="3" t="inlineStr"/>
@@ -21830,7 +21830,7 @@
       </c>
       <c r="K439" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L439" s="6" t="inlineStr"/>
@@ -21878,7 +21878,7 @@
       </c>
       <c r="K440" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L440" s="3" t="inlineStr"/>
@@ -21926,7 +21926,7 @@
       </c>
       <c r="K441" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L441" s="6" t="inlineStr"/>
@@ -21974,7 +21974,7 @@
       </c>
       <c r="K442" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L442" s="3" t="inlineStr"/>
@@ -22022,7 +22022,7 @@
       </c>
       <c r="K443" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L443" s="6" t="inlineStr"/>
@@ -22070,7 +22070,7 @@
       </c>
       <c r="K444" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L444" s="3" t="inlineStr"/>
@@ -22118,7 +22118,7 @@
       </c>
       <c r="K445" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L445" s="6" t="inlineStr"/>
@@ -22166,7 +22166,7 @@
       </c>
       <c r="K446" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L446" s="3" t="inlineStr"/>
@@ -22214,7 +22214,7 @@
       </c>
       <c r="K447" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L447" s="6" t="inlineStr"/>
@@ -22262,7 +22262,7 @@
       </c>
       <c r="K448" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L448" s="3" t="inlineStr"/>
@@ -22310,7 +22310,7 @@
       </c>
       <c r="K449" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L449" s="6" t="inlineStr"/>
@@ -22358,7 +22358,7 @@
       </c>
       <c r="K450" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L450" s="3" t="inlineStr"/>
@@ -22406,7 +22406,7 @@
       </c>
       <c r="K451" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L451" s="6" t="inlineStr"/>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="K452" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L452" s="3" t="inlineStr"/>
@@ -22502,7 +22502,7 @@
       </c>
       <c r="K453" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L453" s="6" t="inlineStr"/>
@@ -22550,7 +22550,7 @@
       </c>
       <c r="K454" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L454" s="3" t="inlineStr"/>
@@ -22598,7 +22598,7 @@
       </c>
       <c r="K455" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L455" s="6" t="inlineStr"/>
@@ -22646,7 +22646,7 @@
       </c>
       <c r="K456" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L456" s="3" t="inlineStr"/>
@@ -22694,7 +22694,7 @@
       </c>
       <c r="K457" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L457" s="6" t="inlineStr"/>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="K458" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L458" s="3" t="inlineStr"/>
@@ -22790,7 +22790,7 @@
       </c>
       <c r="K459" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L459" s="6" t="inlineStr"/>
@@ -22838,7 +22838,7 @@
       </c>
       <c r="K460" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L460" s="3" t="inlineStr"/>
@@ -22886,7 +22886,7 @@
       </c>
       <c r="K461" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L461" s="6" t="inlineStr"/>
@@ -22934,7 +22934,7 @@
       </c>
       <c r="K462" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L462" s="3" t="inlineStr"/>
@@ -22982,7 +22982,7 @@
       </c>
       <c r="K463" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L463" s="6" t="inlineStr"/>
@@ -23030,7 +23030,7 @@
       </c>
       <c r="K464" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L464" s="3" t="inlineStr"/>
@@ -23078,7 +23078,7 @@
       </c>
       <c r="K465" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L465" s="6" t="inlineStr"/>
@@ -23126,7 +23126,7 @@
       </c>
       <c r="K466" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L466" s="3" t="inlineStr"/>
@@ -23174,7 +23174,7 @@
       </c>
       <c r="K467" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L467" s="6" t="inlineStr"/>
@@ -23222,7 +23222,7 @@
       </c>
       <c r="K468" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L468" s="3" t="inlineStr"/>
@@ -23270,7 +23270,7 @@
       </c>
       <c r="K469" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L469" s="6" t="inlineStr"/>
@@ -23318,7 +23318,7 @@
       </c>
       <c r="K470" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L470" s="3" t="inlineStr"/>
@@ -23366,7 +23366,7 @@
       </c>
       <c r="K471" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L471" s="6" t="inlineStr"/>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="K472" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L472" s="3" t="inlineStr"/>
@@ -23462,7 +23462,7 @@
       </c>
       <c r="K473" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L473" s="6" t="inlineStr"/>
@@ -23510,7 +23510,7 @@
       </c>
       <c r="K474" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L474" s="3" t="inlineStr"/>
@@ -23558,7 +23558,7 @@
       </c>
       <c r="K475" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L475" s="6" t="inlineStr"/>
@@ -23606,7 +23606,7 @@
       </c>
       <c r="K476" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L476" s="3" t="inlineStr"/>
@@ -23654,7 +23654,7 @@
       </c>
       <c r="K477" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L477" s="6" t="inlineStr"/>
@@ -23702,7 +23702,7 @@
       </c>
       <c r="K478" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L478" s="3" t="inlineStr"/>
@@ -23750,7 +23750,7 @@
       </c>
       <c r="K479" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L479" s="6" t="inlineStr"/>
@@ -23798,7 +23798,7 @@
       </c>
       <c r="K480" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L480" s="3" t="inlineStr"/>
@@ -23846,7 +23846,7 @@
       </c>
       <c r="K481" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L481" s="6" t="inlineStr"/>
@@ -23894,7 +23894,7 @@
       </c>
       <c r="K482" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L482" s="3" t="inlineStr"/>
@@ -23942,7 +23942,7 @@
       </c>
       <c r="K483" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L483" s="6" t="inlineStr"/>
@@ -23990,7 +23990,7 @@
       </c>
       <c r="K484" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L484" s="3" t="inlineStr"/>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="K485" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L485" s="6" t="inlineStr"/>
@@ -24086,7 +24086,7 @@
       </c>
       <c r="K486" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L486" s="3" t="inlineStr"/>
@@ -24134,7 +24134,7 @@
       </c>
       <c r="K487" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L487" s="6" t="inlineStr"/>
@@ -24182,7 +24182,7 @@
       </c>
       <c r="K488" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L488" s="3" t="inlineStr"/>
@@ -24230,7 +24230,7 @@
       </c>
       <c r="K489" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L489" s="6" t="inlineStr"/>
@@ -24278,7 +24278,7 @@
       </c>
       <c r="K490" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L490" s="3" t="inlineStr"/>
@@ -24326,7 +24326,7 @@
       </c>
       <c r="K491" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L491" s="6" t="inlineStr"/>
@@ -24374,7 +24374,7 @@
       </c>
       <c r="K492" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L492" s="3" t="inlineStr"/>
@@ -24422,7 +24422,7 @@
       </c>
       <c r="K493" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L493" s="6" t="inlineStr"/>
@@ -24470,7 +24470,7 @@
       </c>
       <c r="K494" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L494" s="3" t="inlineStr"/>
@@ -24518,7 +24518,7 @@
       </c>
       <c r="K495" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L495" s="6" t="inlineStr"/>
@@ -24566,7 +24566,7 @@
       </c>
       <c r="K496" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L496" s="3" t="inlineStr"/>
@@ -24614,7 +24614,7 @@
       </c>
       <c r="K497" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L497" s="6" t="inlineStr"/>
@@ -24662,7 +24662,7 @@
       </c>
       <c r="K498" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L498" s="3" t="inlineStr"/>
@@ -24710,7 +24710,7 @@
       </c>
       <c r="K499" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L499" s="6" t="inlineStr"/>
@@ -24758,7 +24758,7 @@
       </c>
       <c r="K500" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L500" s="3" t="inlineStr"/>
@@ -24806,7 +24806,7 @@
       </c>
       <c r="K501" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L501" s="6" t="inlineStr"/>
@@ -24854,7 +24854,7 @@
       </c>
       <c r="K502" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L502" s="3" t="inlineStr"/>
@@ -24902,7 +24902,7 @@
       </c>
       <c r="K503" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L503" s="6" t="inlineStr"/>
@@ -24950,7 +24950,7 @@
       </c>
       <c r="K504" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L504" s="3" t="inlineStr"/>
@@ -24998,7 +24998,7 @@
       </c>
       <c r="K505" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L505" s="6" t="inlineStr"/>
@@ -25046,7 +25046,7 @@
       </c>
       <c r="K506" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L506" s="3" t="inlineStr"/>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="K507" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L507" s="6" t="inlineStr"/>
@@ -25142,7 +25142,7 @@
       </c>
       <c r="K508" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L508" s="3" t="inlineStr"/>
@@ -25190,7 +25190,7 @@
       </c>
       <c r="K509" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L509" s="6" t="inlineStr"/>
@@ -25238,7 +25238,7 @@
       </c>
       <c r="K510" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L510" s="3" t="inlineStr"/>
@@ -25286,7 +25286,7 @@
       </c>
       <c r="K511" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L511" s="6" t="inlineStr"/>
@@ -25334,7 +25334,7 @@
       </c>
       <c r="K512" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L512" s="3" t="inlineStr"/>
@@ -25382,7 +25382,7 @@
       </c>
       <c r="K513" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L513" s="6" t="inlineStr"/>
@@ -25430,7 +25430,7 @@
       </c>
       <c r="K514" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L514" s="3" t="inlineStr"/>
@@ -25478,7 +25478,7 @@
       </c>
       <c r="K515" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L515" s="6" t="inlineStr"/>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="K516" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L516" s="3" t="inlineStr"/>
@@ -25574,7 +25574,7 @@
       </c>
       <c r="K517" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L517" s="6" t="inlineStr"/>
@@ -25622,7 +25622,7 @@
       </c>
       <c r="K518" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L518" s="3" t="inlineStr"/>
@@ -25670,7 +25670,7 @@
       </c>
       <c r="K519" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L519" s="6" t="inlineStr"/>
@@ -25718,7 +25718,7 @@
       </c>
       <c r="K520" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L520" s="3" t="inlineStr"/>
@@ -25766,7 +25766,7 @@
       </c>
       <c r="K521" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L521" s="6" t="inlineStr"/>
@@ -25814,7 +25814,7 @@
       </c>
       <c r="K522" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L522" s="3" t="inlineStr"/>
@@ -25862,7 +25862,7 @@
       </c>
       <c r="K523" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L523" s="6" t="inlineStr"/>
@@ -25910,7 +25910,7 @@
       </c>
       <c r="K524" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L524" s="3" t="inlineStr"/>
@@ -25958,7 +25958,7 @@
       </c>
       <c r="K525" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L525" s="6" t="inlineStr"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K526" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L526" s="3" t="inlineStr"/>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="K527" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L527" s="6" t="inlineStr"/>
@@ -26102,7 +26102,7 @@
       </c>
       <c r="K528" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L528" s="3" t="inlineStr"/>
@@ -26150,7 +26150,7 @@
       </c>
       <c r="K529" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L529" s="6" t="inlineStr"/>
@@ -26198,7 +26198,7 @@
       </c>
       <c r="K530" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L530" s="3" t="inlineStr"/>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="K531" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L531" s="6" t="inlineStr"/>
@@ -26294,7 +26294,7 @@
       </c>
       <c r="K532" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L532" s="3" t="inlineStr"/>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="K533" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L533" s="6" t="inlineStr"/>
@@ -26390,7 +26390,7 @@
       </c>
       <c r="K534" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L534" s="3" t="inlineStr"/>
@@ -26438,7 +26438,7 @@
       </c>
       <c r="K535" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L535" s="6" t="inlineStr"/>
@@ -26486,7 +26486,7 @@
       </c>
       <c r="K536" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L536" s="3" t="inlineStr"/>
@@ -26534,7 +26534,7 @@
       </c>
       <c r="K537" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L537" s="6" t="inlineStr"/>
@@ -26582,7 +26582,7 @@
       </c>
       <c r="K538" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L538" s="3" t="inlineStr"/>
@@ -26630,7 +26630,7 @@
       </c>
       <c r="K539" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L539" s="6" t="inlineStr"/>
@@ -26678,7 +26678,7 @@
       </c>
       <c r="K540" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L540" s="3" t="inlineStr"/>
@@ -26726,7 +26726,7 @@
       </c>
       <c r="K541" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L541" s="6" t="inlineStr"/>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="K542" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L542" s="3" t="inlineStr"/>
@@ -26822,7 +26822,7 @@
       </c>
       <c r="K543" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L543" s="6" t="inlineStr"/>
@@ -26870,7 +26870,7 @@
       </c>
       <c r="K544" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L544" s="3" t="inlineStr"/>
@@ -26918,7 +26918,7 @@
       </c>
       <c r="K545" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L545" s="6" t="inlineStr"/>
@@ -26966,7 +26966,7 @@
       </c>
       <c r="K546" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L546" s="3" t="inlineStr"/>
@@ -27014,7 +27014,7 @@
       </c>
       <c r="K547" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L547" s="6" t="inlineStr"/>
@@ -27062,7 +27062,7 @@
       </c>
       <c r="K548" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L548" s="3" t="inlineStr"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K549" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L549" s="6" t="inlineStr"/>
@@ -27158,7 +27158,7 @@
       </c>
       <c r="K550" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L550" s="3" t="inlineStr"/>
@@ -27206,7 +27206,7 @@
       </c>
       <c r="K551" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L551" s="6" t="inlineStr"/>
@@ -27254,7 +27254,7 @@
       </c>
       <c r="K552" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L552" s="3" t="inlineStr"/>
@@ -27302,7 +27302,7 @@
       </c>
       <c r="K553" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L553" s="6" t="inlineStr"/>
@@ -27350,7 +27350,7 @@
       </c>
       <c r="K554" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L554" s="3" t="inlineStr"/>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="K555" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L555" s="6" t="inlineStr"/>
@@ -27446,7 +27446,7 @@
       </c>
       <c r="K556" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L556" s="3" t="inlineStr"/>
@@ -27494,7 +27494,7 @@
       </c>
       <c r="K557" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L557" s="6" t="inlineStr"/>
@@ -27542,7 +27542,7 @@
       </c>
       <c r="K558" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L558" s="3" t="inlineStr"/>
@@ -27590,7 +27590,7 @@
       </c>
       <c r="K559" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L559" s="6" t="inlineStr"/>
@@ -27638,7 +27638,7 @@
       </c>
       <c r="K560" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L560" s="3" t="inlineStr"/>
@@ -27686,7 +27686,7 @@
       </c>
       <c r="K561" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L561" s="6" t="inlineStr"/>
@@ -27734,7 +27734,7 @@
       </c>
       <c r="K562" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L562" s="3" t="inlineStr"/>
@@ -27782,7 +27782,7 @@
       </c>
       <c r="K563" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L563" s="6" t="inlineStr"/>
@@ -27830,7 +27830,7 @@
       </c>
       <c r="K564" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L564" s="3" t="inlineStr"/>
@@ -27878,7 +27878,7 @@
       </c>
       <c r="K565" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L565" s="6" t="inlineStr"/>
@@ -27926,7 +27926,7 @@
       </c>
       <c r="K566" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L566" s="3" t="inlineStr"/>
@@ -27974,7 +27974,7 @@
       </c>
       <c r="K567" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L567" s="6" t="inlineStr"/>
@@ -28022,7 +28022,7 @@
       </c>
       <c r="K568" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L568" s="3" t="inlineStr"/>
@@ -28070,7 +28070,7 @@
       </c>
       <c r="K569" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L569" s="6" t="inlineStr"/>
@@ -28118,7 +28118,7 @@
       </c>
       <c r="K570" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L570" s="3" t="inlineStr"/>
@@ -28166,7 +28166,7 @@
       </c>
       <c r="K571" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L571" s="6" t="inlineStr"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K572" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L572" s="3" t="inlineStr"/>
@@ -28262,7 +28262,7 @@
       </c>
       <c r="K573" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L573" s="6" t="inlineStr"/>
@@ -28310,7 +28310,7 @@
       </c>
       <c r="K574" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L574" s="3" t="inlineStr"/>
@@ -28358,7 +28358,7 @@
       </c>
       <c r="K575" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L575" s="6" t="inlineStr"/>
@@ -28406,7 +28406,7 @@
       </c>
       <c r="K576" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L576" s="3" t="inlineStr"/>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="K577" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L577" s="6" t="inlineStr"/>
@@ -28502,7 +28502,7 @@
       </c>
       <c r="K578" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L578" s="3" t="inlineStr"/>
@@ -28550,7 +28550,7 @@
       </c>
       <c r="K579" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L579" s="6" t="inlineStr"/>
@@ -28598,7 +28598,7 @@
       </c>
       <c r="K580" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L580" s="3" t="inlineStr"/>
@@ -28646,7 +28646,7 @@
       </c>
       <c r="K581" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L581" s="6" t="inlineStr"/>
@@ -28694,7 +28694,7 @@
       </c>
       <c r="K582" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L582" s="3" t="inlineStr"/>
@@ -28742,7 +28742,7 @@
       </c>
       <c r="K583" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L583" s="6" t="inlineStr"/>
@@ -28790,7 +28790,7 @@
       </c>
       <c r="K584" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L584" s="3" t="inlineStr"/>
@@ -28838,7 +28838,7 @@
       </c>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L585" s="6" t="inlineStr"/>
@@ -28886,7 +28886,7 @@
       </c>
       <c r="K586" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L586" s="3" t="inlineStr"/>
@@ -28934,7 +28934,7 @@
       </c>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L587" s="6" t="inlineStr"/>
@@ -28982,7 +28982,7 @@
       </c>
       <c r="K588" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L588" s="3" t="inlineStr"/>
@@ -29030,7 +29030,7 @@
       </c>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L589" s="6" t="inlineStr"/>
@@ -29078,7 +29078,7 @@
       </c>
       <c r="K590" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L590" s="3" t="inlineStr"/>
@@ -29126,7 +29126,7 @@
       </c>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L591" s="6" t="inlineStr"/>
@@ -29174,7 +29174,7 @@
       </c>
       <c r="K592" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L592" s="3" t="inlineStr"/>
@@ -29222,7 +29222,7 @@
       </c>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L593" s="6" t="inlineStr"/>
@@ -29270,7 +29270,7 @@
       </c>
       <c r="K594" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L594" s="3" t="inlineStr"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L595" s="6" t="inlineStr"/>
@@ -29366,7 +29366,7 @@
       </c>
       <c r="K596" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L596" s="3" t="inlineStr"/>
@@ -29414,7 +29414,7 @@
       </c>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L597" s="6" t="inlineStr"/>
@@ -29462,7 +29462,7 @@
       </c>
       <c r="K598" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L598" s="3" t="inlineStr"/>
@@ -29510,7 +29510,7 @@
       </c>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L599" s="6" t="inlineStr"/>
@@ -29558,7 +29558,7 @@
       </c>
       <c r="K600" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L600" s="3" t="inlineStr"/>
@@ -29606,7 +29606,7 @@
       </c>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L601" s="6" t="inlineStr"/>
@@ -29654,7 +29654,7 @@
       </c>
       <c r="K602" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L602" s="3" t="inlineStr"/>
@@ -29702,7 +29702,7 @@
       </c>
       <c r="K603" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L603" s="6" t="inlineStr"/>
@@ -29750,7 +29750,7 @@
       </c>
       <c r="K604" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L604" s="3" t="inlineStr"/>
@@ -29798,7 +29798,7 @@
       </c>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr"/>
@@ -29846,7 +29846,7 @@
       </c>
       <c r="K606" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L606" s="3" t="inlineStr"/>
@@ -29894,7 +29894,7 @@
       </c>
       <c r="K607" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L607" s="6" t="inlineStr"/>
@@ -29942,7 +29942,7 @@
       </c>
       <c r="K608" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L608" s="3" t="inlineStr"/>
@@ -29990,7 +29990,7 @@
       </c>
       <c r="K609" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L609" s="6" t="inlineStr"/>
@@ -30038,7 +30038,7 @@
       </c>
       <c r="K610" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L610" s="3" t="inlineStr"/>
@@ -30086,7 +30086,7 @@
       </c>
       <c r="K611" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L611" s="6" t="inlineStr"/>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="K612" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L612" s="3" t="inlineStr"/>
@@ -30182,7 +30182,7 @@
       </c>
       <c r="K613" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L613" s="6" t="inlineStr"/>
@@ -30230,7 +30230,7 @@
       </c>
       <c r="K614" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L614" s="3" t="inlineStr"/>
@@ -30278,7 +30278,7 @@
       </c>
       <c r="K615" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L615" s="6" t="inlineStr"/>
@@ -30326,7 +30326,7 @@
       </c>
       <c r="K616" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L616" s="3" t="inlineStr"/>
@@ -30374,7 +30374,7 @@
       </c>
       <c r="K617" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L617" s="6" t="inlineStr"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K618" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L618" s="3" t="inlineStr"/>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="K619" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L619" s="6" t="inlineStr"/>
@@ -30518,7 +30518,7 @@
       </c>
       <c r="K620" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L620" s="3" t="inlineStr"/>
@@ -30566,7 +30566,7 @@
       </c>
       <c r="K621" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L621" s="6" t="inlineStr"/>
@@ -30614,7 +30614,7 @@
       </c>
       <c r="K622" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L622" s="3" t="inlineStr"/>
@@ -30662,7 +30662,7 @@
       </c>
       <c r="K623" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L623" s="6" t="inlineStr"/>
@@ -30710,7 +30710,7 @@
       </c>
       <c r="K624" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L624" s="3" t="inlineStr"/>
@@ -30758,7 +30758,7 @@
       </c>
       <c r="K625" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L625" s="6" t="inlineStr"/>
@@ -30806,7 +30806,7 @@
       </c>
       <c r="K626" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L626" s="3" t="inlineStr"/>
@@ -30854,7 +30854,7 @@
       </c>
       <c r="K627" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L627" s="6" t="inlineStr"/>
@@ -30902,7 +30902,7 @@
       </c>
       <c r="K628" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L628" s="3" t="inlineStr"/>
@@ -30950,7 +30950,7 @@
       </c>
       <c r="K629" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L629" s="6" t="inlineStr"/>
@@ -30998,7 +30998,7 @@
       </c>
       <c r="K630" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L630" s="3" t="inlineStr"/>
@@ -31046,7 +31046,7 @@
       </c>
       <c r="K631" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L631" s="6" t="inlineStr"/>
@@ -31094,7 +31094,7 @@
       </c>
       <c r="K632" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L632" s="3" t="inlineStr"/>
@@ -31142,7 +31142,7 @@
       </c>
       <c r="K633" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L633" s="6" t="inlineStr"/>
@@ -31190,7 +31190,7 @@
       </c>
       <c r="K634" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L634" s="3" t="inlineStr"/>
@@ -31238,7 +31238,7 @@
       </c>
       <c r="K635" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L635" s="6" t="inlineStr"/>
@@ -31286,7 +31286,7 @@
       </c>
       <c r="K636" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L636" s="3" t="inlineStr"/>
@@ -31334,7 +31334,7 @@
       </c>
       <c r="K637" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L637" s="6" t="inlineStr"/>
@@ -31382,7 +31382,7 @@
       </c>
       <c r="K638" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L638" s="3" t="inlineStr"/>
@@ -31430,7 +31430,7 @@
       </c>
       <c r="K639" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L639" s="6" t="inlineStr"/>
@@ -31478,7 +31478,7 @@
       </c>
       <c r="K640" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L640" s="3" t="inlineStr"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K641" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L641" s="6" t="inlineStr"/>
@@ -31574,7 +31574,7 @@
       </c>
       <c r="K642" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L642" s="3" t="inlineStr"/>
@@ -31622,7 +31622,7 @@
       </c>
       <c r="K643" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L643" s="6" t="inlineStr"/>
@@ -31670,7 +31670,7 @@
       </c>
       <c r="K644" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L644" s="3" t="inlineStr"/>
@@ -31718,7 +31718,7 @@
       </c>
       <c r="K645" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L645" s="6" t="inlineStr"/>
@@ -31766,7 +31766,7 @@
       </c>
       <c r="K646" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L646" s="3" t="inlineStr"/>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="K647" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L647" s="6" t="inlineStr"/>
@@ -31862,7 +31862,7 @@
       </c>
       <c r="K648" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L648" s="3" t="inlineStr"/>
@@ -31910,7 +31910,7 @@
       </c>
       <c r="K649" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L649" s="6" t="inlineStr"/>
@@ -31958,7 +31958,7 @@
       </c>
       <c r="K650" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L650" s="3" t="inlineStr"/>
@@ -32006,7 +32006,7 @@
       </c>
       <c r="K651" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L651" s="6" t="inlineStr"/>
@@ -32054,7 +32054,7 @@
       </c>
       <c r="K652" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L652" s="3" t="inlineStr"/>
@@ -32102,7 +32102,7 @@
       </c>
       <c r="K653" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L653" s="6" t="inlineStr"/>
@@ -32150,7 +32150,7 @@
       </c>
       <c r="K654" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L654" s="3" t="inlineStr"/>
@@ -32198,7 +32198,7 @@
       </c>
       <c r="K655" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L655" s="6" t="inlineStr"/>
@@ -32246,7 +32246,7 @@
       </c>
       <c r="K656" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L656" s="3" t="inlineStr"/>
@@ -32294,7 +32294,7 @@
       </c>
       <c r="K657" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L657" s="6" t="inlineStr"/>
@@ -32342,7 +32342,7 @@
       </c>
       <c r="K658" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L658" s="3" t="inlineStr"/>
@@ -32390,7 +32390,7 @@
       </c>
       <c r="K659" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L659" s="6" t="inlineStr"/>
@@ -32438,7 +32438,7 @@
       </c>
       <c r="K660" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L660" s="3" t="inlineStr"/>
@@ -32486,7 +32486,7 @@
       </c>
       <c r="K661" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L661" s="6" t="inlineStr"/>
@@ -32534,7 +32534,7 @@
       </c>
       <c r="K662" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L662" s="3" t="inlineStr"/>
@@ -32582,7 +32582,7 @@
       </c>
       <c r="K663" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L663" s="6" t="inlineStr"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K664" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L664" s="3" t="inlineStr"/>
@@ -32678,7 +32678,7 @@
       </c>
       <c r="K665" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L665" s="6" t="inlineStr"/>
@@ -32726,7 +32726,7 @@
       </c>
       <c r="K666" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L666" s="3" t="inlineStr"/>
@@ -32774,7 +32774,7 @@
       </c>
       <c r="K667" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L667" s="6" t="inlineStr"/>
@@ -32822,7 +32822,7 @@
       </c>
       <c r="K668" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L668" s="3" t="inlineStr"/>
@@ -32870,7 +32870,7 @@
       </c>
       <c r="K669" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L669" s="6" t="inlineStr"/>
@@ -32918,7 +32918,7 @@
       </c>
       <c r="K670" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L670" s="3" t="inlineStr"/>
@@ -32966,7 +32966,7 @@
       </c>
       <c r="K671" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L671" s="6" t="inlineStr"/>
@@ -33014,7 +33014,7 @@
       </c>
       <c r="K672" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L672" s="3" t="inlineStr"/>
@@ -33062,7 +33062,7 @@
       </c>
       <c r="K673" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L673" s="6" t="inlineStr"/>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="K674" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L674" s="3" t="inlineStr"/>
@@ -33158,7 +33158,7 @@
       </c>
       <c r="K675" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L675" s="6" t="inlineStr"/>
@@ -33206,7 +33206,7 @@
       </c>
       <c r="K676" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L676" s="3" t="inlineStr"/>
@@ -33254,7 +33254,7 @@
       </c>
       <c r="K677" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L677" s="6" t="inlineStr"/>
@@ -33302,7 +33302,7 @@
       </c>
       <c r="K678" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L678" s="3" t="inlineStr"/>
@@ -33350,7 +33350,7 @@
       </c>
       <c r="K679" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L679" s="6" t="inlineStr"/>
@@ -33398,7 +33398,7 @@
       </c>
       <c r="K680" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L680" s="3" t="inlineStr"/>
@@ -33446,7 +33446,7 @@
       </c>
       <c r="K681" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L681" s="6" t="inlineStr"/>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="K682" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L682" s="3" t="inlineStr"/>
@@ -33542,7 +33542,7 @@
       </c>
       <c r="K683" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L683" s="6" t="inlineStr"/>
@@ -33590,7 +33590,7 @@
       </c>
       <c r="K684" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L684" s="3" t="inlineStr"/>
@@ -33638,7 +33638,7 @@
       </c>
       <c r="K685" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L685" s="6" t="inlineStr"/>
@@ -33686,7 +33686,7 @@
       </c>
       <c r="K686" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L686" s="3" t="inlineStr"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K687" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L687" s="6" t="inlineStr"/>
@@ -33782,7 +33782,7 @@
       </c>
       <c r="K688" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L688" s="3" t="inlineStr"/>
@@ -33830,7 +33830,7 @@
       </c>
       <c r="K689" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L689" s="6" t="inlineStr"/>
@@ -33878,7 +33878,7 @@
       </c>
       <c r="K690" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L690" s="3" t="inlineStr"/>
@@ -33926,7 +33926,7 @@
       </c>
       <c r="K691" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L691" s="6" t="inlineStr"/>
@@ -33974,7 +33974,7 @@
       </c>
       <c r="K692" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L692" s="3" t="inlineStr"/>
@@ -34022,7 +34022,7 @@
       </c>
       <c r="K693" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L693" s="6" t="inlineStr"/>
@@ -34070,7 +34070,7 @@
       </c>
       <c r="K694" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L694" s="3" t="inlineStr"/>
@@ -34118,7 +34118,7 @@
       </c>
       <c r="K695" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L695" s="6" t="inlineStr"/>
@@ -34166,7 +34166,7 @@
       </c>
       <c r="K696" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L696" s="3" t="inlineStr"/>
@@ -34214,7 +34214,7 @@
       </c>
       <c r="K697" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L697" s="6" t="inlineStr"/>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="K698" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L698" s="3" t="inlineStr"/>
@@ -34310,7 +34310,7 @@
       </c>
       <c r="K699" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L699" s="6" t="inlineStr"/>
@@ -34358,7 +34358,7 @@
       </c>
       <c r="K700" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L700" s="3" t="inlineStr"/>
@@ -34406,7 +34406,7 @@
       </c>
       <c r="K701" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L701" s="6" t="inlineStr"/>
@@ -34454,7 +34454,7 @@
       </c>
       <c r="K702" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L702" s="3" t="inlineStr"/>
@@ -34502,7 +34502,7 @@
       </c>
       <c r="K703" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L703" s="6" t="inlineStr"/>
@@ -34550,7 +34550,7 @@
       </c>
       <c r="K704" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L704" s="3" t="inlineStr"/>
@@ -34598,7 +34598,7 @@
       </c>
       <c r="K705" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L705" s="6" t="inlineStr"/>
@@ -34646,7 +34646,7 @@
       </c>
       <c r="K706" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L706" s="3" t="inlineStr"/>
@@ -34694,7 +34694,7 @@
       </c>
       <c r="K707" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L707" s="6" t="inlineStr"/>
@@ -34742,7 +34742,7 @@
       </c>
       <c r="K708" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L708" s="3" t="inlineStr"/>
@@ -34790,7 +34790,7 @@
       </c>
       <c r="K709" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L709" s="6" t="inlineStr"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K710" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L710" s="3" t="inlineStr"/>
@@ -34886,7 +34886,7 @@
       </c>
       <c r="K711" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L711" s="6" t="inlineStr"/>
@@ -34934,7 +34934,7 @@
       </c>
       <c r="K712" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L712" s="3" t="inlineStr"/>
@@ -34982,7 +34982,7 @@
       </c>
       <c r="K713" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L713" s="6" t="inlineStr"/>
@@ -35030,7 +35030,7 @@
       </c>
       <c r="K714" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L714" s="3" t="inlineStr"/>
@@ -35078,7 +35078,7 @@
       </c>
       <c r="K715" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L715" s="6" t="inlineStr"/>
@@ -35126,7 +35126,7 @@
       </c>
       <c r="K716" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L716" s="3" t="inlineStr"/>
@@ -35174,7 +35174,7 @@
       </c>
       <c r="K717" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L717" s="6" t="inlineStr"/>
@@ -35222,7 +35222,7 @@
       </c>
       <c r="K718" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L718" s="3" t="inlineStr"/>
@@ -35270,7 +35270,7 @@
       </c>
       <c r="K719" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L719" s="6" t="inlineStr"/>
@@ -35318,7 +35318,7 @@
       </c>
       <c r="K720" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L720" s="3" t="inlineStr"/>
@@ -35366,7 +35366,7 @@
       </c>
       <c r="K721" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L721" s="6" t="inlineStr"/>
@@ -35414,7 +35414,7 @@
       </c>
       <c r="K722" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L722" s="3" t="inlineStr"/>
@@ -35462,7 +35462,7 @@
       </c>
       <c r="K723" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L723" s="6" t="inlineStr"/>
@@ -35510,7 +35510,7 @@
       </c>
       <c r="K724" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L724" s="3" t="inlineStr"/>
@@ -35558,7 +35558,7 @@
       </c>
       <c r="K725" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L725" s="6" t="inlineStr"/>
@@ -35606,7 +35606,7 @@
       </c>
       <c r="K726" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L726" s="3" t="inlineStr"/>
@@ -35654,7 +35654,7 @@
       </c>
       <c r="K727" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L727" s="6" t="inlineStr"/>
@@ -35702,7 +35702,7 @@
       </c>
       <c r="K728" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L728" s="3" t="inlineStr"/>
@@ -35750,7 +35750,7 @@
       </c>
       <c r="K729" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L729" s="4" t="inlineStr">
@@ -35802,7 +35802,7 @@
       </c>
       <c r="K730" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L730" s="4" t="inlineStr">
@@ -35854,7 +35854,7 @@
       </c>
       <c r="K731" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L731" s="4" t="inlineStr">
@@ -35906,7 +35906,7 @@
       </c>
       <c r="K732" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L732" s="4" t="inlineStr">
@@ -35958,7 +35958,7 @@
       </c>
       <c r="K733" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L733" s="4" t="inlineStr">
@@ -36010,7 +36010,7 @@
       </c>
       <c r="K734" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L734" s="4" t="inlineStr">
@@ -36062,7 +36062,7 @@
       </c>
       <c r="K735" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L735" s="4" t="inlineStr">
@@ -36114,7 +36114,7 @@
       </c>
       <c r="K736" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L736" s="4" t="inlineStr">
@@ -36166,7 +36166,7 @@
       </c>
       <c r="K737" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L737" s="4" t="inlineStr">
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K738" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L738" s="4" t="inlineStr">
@@ -36270,7 +36270,7 @@
       </c>
       <c r="K739" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L739" s="4" t="inlineStr">
@@ -36322,7 +36322,7 @@
       </c>
       <c r="K740" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L740" s="4" t="inlineStr">
@@ -36374,7 +36374,7 @@
       </c>
       <c r="K741" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L741" s="4" t="inlineStr">
@@ -36426,7 +36426,7 @@
       </c>
       <c r="K742" s="3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L742" s="4" t="inlineStr">
@@ -36478,7 +36478,7 @@
       </c>
       <c r="K743" s="6" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-19</t>
         </is>
       </c>
       <c r="L743" s="4" t="inlineStr">

--- a/public/loop-library.xlsx
+++ b/public/loop-library.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr"/>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr"/>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr"/>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr"/>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr"/>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr"/>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr"/>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr"/>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr"/>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr"/>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr"/>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr"/>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr"/>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr"/>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr"/>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr"/>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr"/>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr"/>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr"/>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr"/>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L93" s="6" t="inlineStr"/>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr"/>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L95" s="6" t="inlineStr"/>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr"/>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L97" s="6" t="inlineStr"/>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr"/>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr"/>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr"/>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr"/>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L102" s="3" t="inlineStr"/>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L103" s="6" t="inlineStr"/>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L104" s="3" t="inlineStr"/>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L105" s="6" t="inlineStr"/>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L106" s="3" t="inlineStr"/>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L107" s="6" t="inlineStr"/>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L108" s="3" t="inlineStr"/>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L109" s="6" t="inlineStr"/>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L110" s="3" t="inlineStr"/>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L111" s="6" t="inlineStr"/>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L112" s="3" t="inlineStr"/>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L113" s="6" t="inlineStr"/>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L114" s="3" t="inlineStr"/>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L115" s="6" t="inlineStr"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="K116" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L116" s="3" t="inlineStr"/>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L117" s="6" t="inlineStr"/>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="K118" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L118" s="3" t="inlineStr"/>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L119" s="6" t="inlineStr"/>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="K120" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L120" s="3" t="inlineStr"/>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L121" s="6" t="inlineStr"/>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="K122" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L122" s="3" t="inlineStr"/>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L123" s="6" t="inlineStr"/>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="K124" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L124" s="3" t="inlineStr"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="K125" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L125" s="6" t="inlineStr"/>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="K126" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L126" s="3" t="inlineStr"/>
@@ -6854,7 +6854,7 @@
       </c>
       <c r="K127" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L127" s="6" t="inlineStr"/>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L128" s="3" t="inlineStr"/>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="K129" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L129" s="6" t="inlineStr"/>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="K130" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L130" s="3" t="inlineStr"/>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="K131" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L131" s="6" t="inlineStr"/>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L132" s="3" t="inlineStr"/>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="K133" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L133" s="6" t="inlineStr"/>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="K134" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L134" s="3" t="inlineStr"/>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="K135" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L135" s="6" t="inlineStr"/>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="K136" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L136" s="3" t="inlineStr"/>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="K137" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L137" s="6" t="inlineStr"/>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="K138" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L138" s="3" t="inlineStr"/>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="K139" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L139" s="6" t="inlineStr"/>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="K140" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L140" s="3" t="inlineStr"/>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="K141" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L141" s="6" t="inlineStr"/>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L142" s="3" t="inlineStr"/>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="K143" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L143" s="6" t="inlineStr"/>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="K144" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L144" s="3" t="inlineStr"/>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="K145" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L145" s="6" t="inlineStr"/>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="K146" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L146" s="3" t="inlineStr"/>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="K147" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L147" s="6" t="inlineStr"/>
@@ -7862,7 +7862,7 @@
       </c>
       <c r="K148" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L148" s="3" t="inlineStr"/>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="K149" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L149" s="6" t="inlineStr"/>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="K150" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L150" s="3" t="inlineStr"/>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="K151" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L151" s="6" t="inlineStr"/>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="K152" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L152" s="3" t="inlineStr"/>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="K153" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L153" s="6" t="inlineStr"/>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="K154" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L154" s="3" t="inlineStr"/>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="K155" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L155" s="6" t="inlineStr"/>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="K156" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L156" s="3" t="inlineStr"/>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K157" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L157" s="6" t="inlineStr"/>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="K158" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L158" s="3" t="inlineStr"/>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="K159" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L159" s="6" t="inlineStr"/>
@@ -8438,7 +8438,7 @@
       </c>
       <c r="K160" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L160" s="3" t="inlineStr"/>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="K161" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L161" s="6" t="inlineStr"/>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="K162" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L162" s="3" t="inlineStr"/>
@@ -8582,7 +8582,7 @@
       </c>
       <c r="K163" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L163" s="6" t="inlineStr"/>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="K164" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L164" s="3" t="inlineStr"/>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="K165" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L165" s="6" t="inlineStr"/>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="K166" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L166" s="3" t="inlineStr"/>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="K167" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L167" s="6" t="inlineStr"/>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="K168" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L168" s="3" t="inlineStr"/>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="K169" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L169" s="6" t="inlineStr"/>
@@ -8918,7 +8918,7 @@
       </c>
       <c r="K170" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L170" s="3" t="inlineStr"/>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="K171" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L171" s="6" t="inlineStr"/>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="K172" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L172" s="3" t="inlineStr"/>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="K173" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L173" s="6" t="inlineStr"/>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="K174" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L174" s="3" t="inlineStr"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="K175" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L175" s="6" t="inlineStr"/>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="K176" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L176" s="3" t="inlineStr"/>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="K177" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L177" s="6" t="inlineStr"/>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="K178" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L178" s="3" t="inlineStr"/>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="K179" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L179" s="6" t="inlineStr"/>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="K180" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L180" s="3" t="inlineStr"/>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="K181" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L181" s="6" t="inlineStr"/>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="K182" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L182" s="3" t="inlineStr"/>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="K183" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L183" s="6" t="inlineStr"/>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="K184" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L184" s="3" t="inlineStr"/>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="K185" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L185" s="6" t="inlineStr"/>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="K186" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L186" s="3" t="inlineStr"/>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="K187" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L187" s="6" t="inlineStr"/>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="K188" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L188" s="3" t="inlineStr"/>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="K189" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L189" s="6" t="inlineStr"/>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="K190" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L190" s="3" t="inlineStr"/>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="K191" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L191" s="6" t="inlineStr"/>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="K192" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L192" s="3" t="inlineStr"/>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="K193" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L193" s="6" t="inlineStr"/>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="K194" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L194" s="3" t="inlineStr"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="K195" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L195" s="6" t="inlineStr"/>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="K196" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L196" s="3" t="inlineStr"/>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="K197" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L197" s="6" t="inlineStr"/>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="K198" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L198" s="3" t="inlineStr"/>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="K199" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L199" s="6" t="inlineStr"/>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="K200" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L200" s="3" t="inlineStr"/>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="K201" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L201" s="6" t="inlineStr"/>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="K202" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L202" s="3" t="inlineStr"/>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="K203" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L203" s="6" t="inlineStr"/>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="K204" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L204" s="3" t="inlineStr"/>
@@ -10598,7 +10598,7 @@
       </c>
       <c r="K205" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L205" s="6" t="inlineStr"/>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K206" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L206" s="3" t="inlineStr"/>
@@ -10694,7 +10694,7 @@
       </c>
       <c r="K207" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L207" s="6" t="inlineStr"/>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="K208" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L208" s="3" t="inlineStr"/>
@@ -10790,7 +10790,7 @@
       </c>
       <c r="K209" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L209" s="6" t="inlineStr"/>
@@ -10838,7 +10838,7 @@
       </c>
       <c r="K210" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L210" s="3" t="inlineStr"/>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="K211" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L211" s="6" t="inlineStr"/>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="K212" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L212" s="3" t="inlineStr"/>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="K213" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L213" s="6" t="inlineStr"/>
@@ -11030,7 +11030,7 @@
       </c>
       <c r="K214" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L214" s="3" t="inlineStr"/>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="K215" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L215" s="6" t="inlineStr"/>
@@ -11126,7 +11126,7 @@
       </c>
       <c r="K216" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L216" s="3" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="K217" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L217" s="6" t="inlineStr"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="K218" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L218" s="3" t="inlineStr"/>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="K219" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L219" s="6" t="inlineStr"/>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="K220" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L220" s="3" t="inlineStr"/>
@@ -11366,7 +11366,7 @@
       </c>
       <c r="K221" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L221" s="6" t="inlineStr"/>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="K222" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L222" s="3" t="inlineStr"/>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="K223" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L223" s="6" t="inlineStr"/>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="K224" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L224" s="3" t="inlineStr"/>
@@ -11558,7 +11558,7 @@
       </c>
       <c r="K225" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L225" s="6" t="inlineStr"/>
@@ -11606,7 +11606,7 @@
       </c>
       <c r="K226" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L226" s="3" t="inlineStr"/>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="K227" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L227" s="6" t="inlineStr"/>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="K228" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L228" s="3" t="inlineStr"/>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="K229" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L229" s="6" t="inlineStr"/>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="K230" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L230" s="3" t="inlineStr"/>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="K231" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L231" s="6" t="inlineStr"/>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="K232" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L232" s="3" t="inlineStr"/>
@@ -11942,7 +11942,7 @@
       </c>
       <c r="K233" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L233" s="6" t="inlineStr"/>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="K234" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L234" s="3" t="inlineStr"/>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="K235" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L235" s="6" t="inlineStr"/>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="K236" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L236" s="3" t="inlineStr"/>
@@ -12134,7 +12134,7 @@
       </c>
       <c r="K237" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L237" s="6" t="inlineStr"/>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="K238" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L238" s="3" t="inlineStr"/>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="K239" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L239" s="6" t="inlineStr"/>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="K240" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L240" s="3" t="inlineStr"/>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="K241" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L241" s="6" t="inlineStr"/>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="K242" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L242" s="3" t="inlineStr"/>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="K243" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L243" s="6" t="inlineStr"/>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="K244" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L244" s="3" t="inlineStr"/>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="K245" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L245" s="6" t="inlineStr"/>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="K246" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L246" s="3" t="inlineStr"/>
@@ -12614,7 +12614,7 @@
       </c>
       <c r="K247" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L247" s="6" t="inlineStr"/>
@@ -12662,7 +12662,7 @@
       </c>
       <c r="K248" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L248" s="3" t="inlineStr"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="K249" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L249" s="6" t="inlineStr"/>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="K250" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L250" s="3" t="inlineStr"/>
@@ -12806,7 +12806,7 @@
       </c>
       <c r="K251" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L251" s="6" t="inlineStr"/>
@@ -12854,7 +12854,7 @@
       </c>
       <c r="K252" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L252" s="3" t="inlineStr"/>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="K253" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L253" s="6" t="inlineStr"/>
@@ -12950,7 +12950,7 @@
       </c>
       <c r="K254" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L254" s="3" t="inlineStr"/>
@@ -12998,7 +12998,7 @@
       </c>
       <c r="K255" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L255" s="6" t="inlineStr"/>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="K256" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L256" s="3" t="inlineStr"/>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="K257" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L257" s="6" t="inlineStr"/>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="K258" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L258" s="3" t="inlineStr"/>
@@ -13190,7 +13190,7 @@
       </c>
       <c r="K259" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L259" s="6" t="inlineStr"/>
@@ -13238,7 +13238,7 @@
       </c>
       <c r="K260" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L260" s="3" t="inlineStr"/>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="K261" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L261" s="6" t="inlineStr"/>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="K262" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L262" s="3" t="inlineStr"/>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="K263" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L263" s="6" t="inlineStr"/>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="K264" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L264" s="3" t="inlineStr"/>
@@ -13478,7 +13478,7 @@
       </c>
       <c r="K265" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L265" s="6" t="inlineStr"/>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="K266" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L266" s="3" t="inlineStr"/>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="K267" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L267" s="6" t="inlineStr"/>
@@ -13622,7 +13622,7 @@
       </c>
       <c r="K268" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L268" s="3" t="inlineStr"/>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="K269" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L269" s="6" t="inlineStr"/>
@@ -13718,7 +13718,7 @@
       </c>
       <c r="K270" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L270" s="3" t="inlineStr"/>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="K271" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L271" s="6" t="inlineStr"/>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="K272" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L272" s="3" t="inlineStr"/>
@@ -13862,7 +13862,7 @@
       </c>
       <c r="K273" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L273" s="6" t="inlineStr"/>
@@ -13910,7 +13910,7 @@
       </c>
       <c r="K274" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L274" s="3" t="inlineStr"/>
@@ -13958,7 +13958,7 @@
       </c>
       <c r="K275" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L275" s="6" t="inlineStr"/>
@@ -14006,7 +14006,7 @@
       </c>
       <c r="K276" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L276" s="3" t="inlineStr"/>
@@ -14054,7 +14054,7 @@
       </c>
       <c r="K277" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L277" s="6" t="inlineStr"/>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="K278" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L278" s="3" t="inlineStr"/>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="K279" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L279" s="6" t="inlineStr"/>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="K280" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L280" s="3" t="inlineStr"/>
@@ -14246,7 +14246,7 @@
       </c>
       <c r="K281" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L281" s="6" t="inlineStr"/>
@@ -14294,7 +14294,7 @@
       </c>
       <c r="K282" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L282" s="3" t="inlineStr"/>
@@ -14342,7 +14342,7 @@
       </c>
       <c r="K283" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L283" s="6" t="inlineStr"/>
@@ -14390,7 +14390,7 @@
       </c>
       <c r="K284" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L284" s="3" t="inlineStr"/>
@@ -14438,7 +14438,7 @@
       </c>
       <c r="K285" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L285" s="6" t="inlineStr"/>
@@ -14486,7 +14486,7 @@
       </c>
       <c r="K286" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L286" s="3" t="inlineStr"/>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="K287" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L287" s="6" t="inlineStr"/>
@@ -14582,7 +14582,7 @@
       </c>
       <c r="K288" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L288" s="3" t="inlineStr"/>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="K289" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L289" s="6" t="inlineStr"/>
@@ -14678,7 +14678,7 @@
       </c>
       <c r="K290" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L290" s="3" t="inlineStr"/>
@@ -14726,7 +14726,7 @@
       </c>
       <c r="K291" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L291" s="6" t="inlineStr"/>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="K292" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L292" s="3" t="inlineStr"/>
@@ -14822,7 +14822,7 @@
       </c>
       <c r="K293" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L293" s="6" t="inlineStr"/>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="K294" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L294" s="3" t="inlineStr"/>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="K295" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L295" s="6" t="inlineStr"/>
@@ -14966,7 +14966,7 @@
       </c>
       <c r="K296" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L296" s="3" t="inlineStr"/>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="K297" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L297" s="6" t="inlineStr"/>
@@ -15062,7 +15062,7 @@
       </c>
       <c r="K298" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L298" s="3" t="inlineStr"/>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="K299" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L299" s="6" t="inlineStr"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="K300" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L300" s="3" t="inlineStr"/>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="K301" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L301" s="6" t="inlineStr"/>
@@ -15254,7 +15254,7 @@
       </c>
       <c r="K302" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L302" s="3" t="inlineStr"/>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="K303" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L303" s="6" t="inlineStr"/>
@@ -15350,7 +15350,7 @@
       </c>
       <c r="K304" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L304" s="3" t="inlineStr"/>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="K305" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L305" s="6" t="inlineStr"/>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="K306" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L306" s="3" t="inlineStr"/>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="K307" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L307" s="6" t="inlineStr"/>
@@ -15542,7 +15542,7 @@
       </c>
       <c r="K308" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L308" s="3" t="inlineStr"/>
@@ -15590,7 +15590,7 @@
       </c>
       <c r="K309" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L309" s="6" t="inlineStr"/>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="K310" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L310" s="3" t="inlineStr"/>
@@ -15686,7 +15686,7 @@
       </c>
       <c r="K311" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L311" s="6" t="inlineStr"/>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="K312" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L312" s="3" t="inlineStr"/>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="K313" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L313" s="6" t="inlineStr"/>
@@ -15830,7 +15830,7 @@
       </c>
       <c r="K314" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L314" s="3" t="inlineStr"/>
@@ -15878,7 +15878,7 @@
       </c>
       <c r="K315" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L315" s="6" t="inlineStr"/>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="K316" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L316" s="3" t="inlineStr"/>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="K317" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L317" s="6" t="inlineStr"/>
@@ -16022,7 +16022,7 @@
       </c>
       <c r="K318" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L318" s="3" t="inlineStr"/>
@@ -16070,7 +16070,7 @@
       </c>
       <c r="K319" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L319" s="6" t="inlineStr"/>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="K320" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L320" s="3" t="inlineStr"/>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="K321" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L321" s="6" t="inlineStr"/>
@@ -16214,7 +16214,7 @@
       </c>
       <c r="K322" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L322" s="3" t="inlineStr"/>
@@ -16262,7 +16262,7 @@
       </c>
       <c r="K323" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L323" s="6" t="inlineStr"/>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="K324" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L324" s="3" t="inlineStr"/>
@@ -16358,7 +16358,7 @@
       </c>
       <c r="K325" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L325" s="6" t="inlineStr"/>
@@ -16406,7 +16406,7 @@
       </c>
       <c r="K326" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L326" s="3" t="inlineStr"/>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="K327" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L327" s="6" t="inlineStr"/>
@@ -16502,7 +16502,7 @@
       </c>
       <c r="K328" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L328" s="3" t="inlineStr"/>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="K329" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L329" s="6" t="inlineStr"/>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="K330" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L330" s="3" t="inlineStr"/>
@@ -16646,7 +16646,7 @@
       </c>
       <c r="K331" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L331" s="6" t="inlineStr"/>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="K332" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L332" s="3" t="inlineStr"/>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="K333" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L333" s="6" t="inlineStr"/>
@@ -16790,7 +16790,7 @@
       </c>
       <c r="K334" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L334" s="3" t="inlineStr"/>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="K335" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L335" s="6" t="inlineStr"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="K336" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L336" s="3" t="inlineStr"/>
@@ -16934,7 +16934,7 @@
       </c>
       <c r="K337" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L337" s="6" t="inlineStr"/>
@@ -16982,7 +16982,7 @@
       </c>
       <c r="K338" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L338" s="3" t="inlineStr"/>
@@ -17030,7 +17030,7 @@
       </c>
       <c r="K339" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L339" s="6" t="inlineStr"/>
@@ -17078,7 +17078,7 @@
       </c>
       <c r="K340" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L340" s="3" t="inlineStr"/>
@@ -17126,7 +17126,7 @@
       </c>
       <c r="K341" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L341" s="6" t="inlineStr"/>
@@ -17174,7 +17174,7 @@
       </c>
       <c r="K342" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L342" s="3" t="inlineStr"/>
@@ -17222,7 +17222,7 @@
       </c>
       <c r="K343" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L343" s="6" t="inlineStr"/>
@@ -17270,7 +17270,7 @@
       </c>
       <c r="K344" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L344" s="3" t="inlineStr"/>
@@ -17318,7 +17318,7 @@
       </c>
       <c r="K345" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L345" s="6" t="inlineStr"/>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="K346" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L346" s="3" t="inlineStr"/>
@@ -17414,7 +17414,7 @@
       </c>
       <c r="K347" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L347" s="6" t="inlineStr"/>
@@ -17462,7 +17462,7 @@
       </c>
       <c r="K348" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L348" s="3" t="inlineStr"/>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="K349" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L349" s="6" t="inlineStr"/>
@@ -17558,7 +17558,7 @@
       </c>
       <c r="K350" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L350" s="3" t="inlineStr"/>
@@ -17606,7 +17606,7 @@
       </c>
       <c r="K351" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L351" s="6" t="inlineStr"/>
@@ -17654,7 +17654,7 @@
       </c>
       <c r="K352" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L352" s="3" t="inlineStr"/>
@@ -17702,7 +17702,7 @@
       </c>
       <c r="K353" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L353" s="6" t="inlineStr"/>
@@ -17750,7 +17750,7 @@
       </c>
       <c r="K354" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L354" s="3" t="inlineStr"/>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="K355" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L355" s="6" t="inlineStr"/>
@@ -17846,7 +17846,7 @@
       </c>
       <c r="K356" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L356" s="3" t="inlineStr"/>
@@ -17894,7 +17894,7 @@
       </c>
       <c r="K357" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L357" s="6" t="inlineStr"/>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="K358" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L358" s="3" t="inlineStr"/>
@@ -17990,7 +17990,7 @@
       </c>
       <c r="K359" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L359" s="6" t="inlineStr"/>
@@ -18038,7 +18038,7 @@
       </c>
       <c r="K360" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L360" s="3" t="inlineStr"/>
@@ -18086,7 +18086,7 @@
       </c>
       <c r="K361" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L361" s="6" t="inlineStr"/>
@@ -18134,7 +18134,7 @@
       </c>
       <c r="K362" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L362" s="3" t="inlineStr"/>
@@ -18182,7 +18182,7 @@
       </c>
       <c r="K363" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L363" s="6" t="inlineStr"/>
@@ -18230,7 +18230,7 @@
       </c>
       <c r="K364" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L364" s="3" t="inlineStr"/>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="K365" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L365" s="6" t="inlineStr"/>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="K366" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L366" s="3" t="inlineStr"/>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="K367" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L367" s="6" t="inlineStr"/>
@@ -18422,7 +18422,7 @@
       </c>
       <c r="K368" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L368" s="3" t="inlineStr"/>
@@ -18470,7 +18470,7 @@
       </c>
       <c r="K369" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L369" s="6" t="inlineStr"/>
@@ -18518,7 +18518,7 @@
       </c>
       <c r="K370" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L370" s="3" t="inlineStr"/>
@@ -18566,7 +18566,7 @@
       </c>
       <c r="K371" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L371" s="6" t="inlineStr"/>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="K372" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L372" s="3" t="inlineStr"/>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="K373" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L373" s="6" t="inlineStr"/>
@@ -18710,7 +18710,7 @@
       </c>
       <c r="K374" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L374" s="3" t="inlineStr"/>
@@ -18758,7 +18758,7 @@
       </c>
       <c r="K375" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L375" s="6" t="inlineStr"/>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="K376" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L376" s="3" t="inlineStr"/>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="K377" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L377" s="6" t="inlineStr"/>
@@ -18902,7 +18902,7 @@
       </c>
       <c r="K378" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L378" s="3" t="inlineStr"/>
@@ -18950,7 +18950,7 @@
       </c>
       <c r="K379" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L379" s="6" t="inlineStr"/>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="K380" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L380" s="3" t="inlineStr"/>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="K381" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L381" s="6" t="inlineStr"/>
@@ -19094,7 +19094,7 @@
       </c>
       <c r="K382" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L382" s="3" t="inlineStr"/>
@@ -19142,7 +19142,7 @@
       </c>
       <c r="K383" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L383" s="6" t="inlineStr"/>
@@ -19190,7 +19190,7 @@
       </c>
       <c r="K384" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L384" s="3" t="inlineStr"/>
@@ -19238,7 +19238,7 @@
       </c>
       <c r="K385" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L385" s="6" t="inlineStr"/>
@@ -19286,7 +19286,7 @@
       </c>
       <c r="K386" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L386" s="3" t="inlineStr"/>
@@ -19334,7 +19334,7 @@
       </c>
       <c r="K387" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L387" s="6" t="inlineStr"/>
@@ -19382,7 +19382,7 @@
       </c>
       <c r="K388" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L388" s="3" t="inlineStr"/>
@@ -19430,7 +19430,7 @@
       </c>
       <c r="K389" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L389" s="6" t="inlineStr"/>
@@ -19478,7 +19478,7 @@
       </c>
       <c r="K390" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L390" s="3" t="inlineStr"/>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="K391" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L391" s="6" t="inlineStr"/>
@@ -19574,7 +19574,7 @@
       </c>
       <c r="K392" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L392" s="3" t="inlineStr"/>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="K393" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L393" s="6" t="inlineStr"/>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="K394" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L394" s="3" t="inlineStr"/>
@@ -19718,7 +19718,7 @@
       </c>
       <c r="K395" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L395" s="6" t="inlineStr"/>
@@ -19766,7 +19766,7 @@
       </c>
       <c r="K396" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L396" s="3" t="inlineStr"/>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="K397" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L397" s="6" t="inlineStr"/>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="K398" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L398" s="3" t="inlineStr"/>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="K399" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L399" s="6" t="inlineStr"/>
@@ -19958,7 +19958,7 @@
       </c>
       <c r="K400" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L400" s="3" t="inlineStr"/>
@@ -20006,7 +20006,7 @@
       </c>
       <c r="K401" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L401" s="6" t="inlineStr"/>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="K402" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L402" s="3" t="inlineStr"/>
@@ -20102,7 +20102,7 @@
       </c>
       <c r="K403" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L403" s="6" t="inlineStr"/>
@@ -20150,7 +20150,7 @@
       </c>
       <c r="K404" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L404" s="3" t="inlineStr"/>
@@ -20198,7 +20198,7 @@
       </c>
       <c r="K405" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L405" s="6" t="inlineStr"/>
@@ -20246,7 +20246,7 @@
       </c>
       <c r="K406" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L406" s="3" t="inlineStr"/>
@@ -20294,7 +20294,7 @@
       </c>
       <c r="K407" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L407" s="6" t="inlineStr"/>
@@ -20342,7 +20342,7 @@
       </c>
       <c r="K408" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L408" s="3" t="inlineStr"/>
@@ -20390,7 +20390,7 @@
       </c>
       <c r="K409" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L409" s="6" t="inlineStr"/>
@@ -20438,7 +20438,7 @@
       </c>
       <c r="K410" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L410" s="3" t="inlineStr"/>
@@ -20486,7 +20486,7 @@
       </c>
       <c r="K411" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L411" s="6" t="inlineStr"/>
@@ -20534,7 +20534,7 @@
       </c>
       <c r="K412" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L412" s="3" t="inlineStr"/>
@@ -20582,7 +20582,7 @@
       </c>
       <c r="K413" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L413" s="6" t="inlineStr"/>
@@ -20630,7 +20630,7 @@
       </c>
       <c r="K414" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L414" s="3" t="inlineStr"/>
@@ -20678,7 +20678,7 @@
       </c>
       <c r="K415" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L415" s="6" t="inlineStr"/>
@@ -20726,7 +20726,7 @@
       </c>
       <c r="K416" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L416" s="3" t="inlineStr"/>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="K417" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L417" s="6" t="inlineStr"/>
@@ -20822,7 +20822,7 @@
       </c>
       <c r="K418" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L418" s="3" t="inlineStr"/>
@@ -20870,7 +20870,7 @@
       </c>
       <c r="K419" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L419" s="6" t="inlineStr"/>
@@ -20918,7 +20918,7 @@
       </c>
       <c r="K420" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L420" s="3" t="inlineStr"/>
@@ -20966,7 +20966,7 @@
       </c>
       <c r="K421" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L421" s="6" t="inlineStr"/>
@@ -21014,7 +21014,7 @@
       </c>
       <c r="K422" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L422" s="3" t="inlineStr"/>
@@ -21062,7 +21062,7 @@
       </c>
       <c r="K423" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L423" s="6" t="inlineStr"/>
@@ -21110,7 +21110,7 @@
       </c>
       <c r="K424" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L424" s="3" t="inlineStr"/>
@@ -21158,7 +21158,7 @@
       </c>
       <c r="K425" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L425" s="6" t="inlineStr"/>
@@ -21206,7 +21206,7 @@
       </c>
       <c r="K426" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L426" s="3" t="inlineStr"/>
@@ -21254,7 +21254,7 @@
       </c>
       <c r="K427" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L427" s="6" t="inlineStr"/>
@@ -21302,7 +21302,7 @@
       </c>
       <c r="K428" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L428" s="3" t="inlineStr"/>
@@ -21350,7 +21350,7 @@
       </c>
       <c r="K429" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L429" s="6" t="inlineStr"/>
@@ -21398,7 +21398,7 @@
       </c>
       <c r="K430" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L430" s="3" t="inlineStr"/>
@@ -21446,7 +21446,7 @@
       </c>
       <c r="K431" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L431" s="6" t="inlineStr"/>
@@ -21494,7 +21494,7 @@
       </c>
       <c r="K432" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L432" s="3" t="inlineStr"/>
@@ -21542,7 +21542,7 @@
       </c>
       <c r="K433" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L433" s="6" t="inlineStr"/>
@@ -21590,7 +21590,7 @@
       </c>
       <c r="K434" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L434" s="3" t="inlineStr"/>
@@ -21638,7 +21638,7 @@
       </c>
       <c r="K435" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L435" s="6" t="inlineStr"/>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="K436" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L436" s="3" t="inlineStr"/>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="K437" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L437" s="6" t="inlineStr"/>
@@ -21782,7 +21782,7 @@
       </c>
       <c r="K438" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L438" s="3" t="inlineStr"/>
@@ -21830,7 +21830,7 @@
       </c>
       <c r="K439" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L439" s="6" t="inlineStr"/>
@@ -21878,7 +21878,7 @@
       </c>
       <c r="K440" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L440" s="3" t="inlineStr"/>
@@ -21926,7 +21926,7 @@
       </c>
       <c r="K441" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L441" s="6" t="inlineStr"/>
@@ -21974,7 +21974,7 @@
       </c>
       <c r="K442" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L442" s="3" t="inlineStr"/>
@@ -22022,7 +22022,7 @@
       </c>
       <c r="K443" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L443" s="6" t="inlineStr"/>
@@ -22070,7 +22070,7 @@
       </c>
       <c r="K444" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L444" s="3" t="inlineStr"/>
@@ -22118,7 +22118,7 @@
       </c>
       <c r="K445" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L445" s="6" t="inlineStr"/>
@@ -22166,7 +22166,7 @@
       </c>
       <c r="K446" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L446" s="3" t="inlineStr"/>
@@ -22214,7 +22214,7 @@
       </c>
       <c r="K447" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L447" s="6" t="inlineStr"/>
@@ -22262,7 +22262,7 @@
       </c>
       <c r="K448" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L448" s="3" t="inlineStr"/>
@@ -22310,7 +22310,7 @@
       </c>
       <c r="K449" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L449" s="6" t="inlineStr"/>
@@ -22358,7 +22358,7 @@
       </c>
       <c r="K450" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L450" s="3" t="inlineStr"/>
@@ -22406,7 +22406,7 @@
       </c>
       <c r="K451" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L451" s="6" t="inlineStr"/>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="K452" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L452" s="3" t="inlineStr"/>
@@ -22502,7 +22502,7 @@
       </c>
       <c r="K453" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L453" s="6" t="inlineStr"/>
@@ -22550,7 +22550,7 @@
       </c>
       <c r="K454" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L454" s="3" t="inlineStr"/>
@@ -22598,7 +22598,7 @@
       </c>
       <c r="K455" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L455" s="6" t="inlineStr"/>
@@ -22646,7 +22646,7 @@
       </c>
       <c r="K456" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L456" s="3" t="inlineStr"/>
@@ -22694,7 +22694,7 @@
       </c>
       <c r="K457" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L457" s="6" t="inlineStr"/>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="K458" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L458" s="3" t="inlineStr"/>
@@ -22790,7 +22790,7 @@
       </c>
       <c r="K459" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L459" s="6" t="inlineStr"/>
@@ -22838,7 +22838,7 @@
       </c>
       <c r="K460" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L460" s="3" t="inlineStr"/>
@@ -22886,7 +22886,7 @@
       </c>
       <c r="K461" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L461" s="6" t="inlineStr"/>
@@ -22934,7 +22934,7 @@
       </c>
       <c r="K462" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L462" s="3" t="inlineStr"/>
@@ -22982,7 +22982,7 @@
       </c>
       <c r="K463" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L463" s="6" t="inlineStr"/>
@@ -23030,7 +23030,7 @@
       </c>
       <c r="K464" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L464" s="3" t="inlineStr"/>
@@ -23078,7 +23078,7 @@
       </c>
       <c r="K465" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L465" s="6" t="inlineStr"/>
@@ -23126,7 +23126,7 @@
       </c>
       <c r="K466" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L466" s="3" t="inlineStr"/>
@@ -23174,7 +23174,7 @@
       </c>
       <c r="K467" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L467" s="6" t="inlineStr"/>
@@ -23222,7 +23222,7 @@
       </c>
       <c r="K468" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L468" s="3" t="inlineStr"/>
@@ -23270,7 +23270,7 @@
       </c>
       <c r="K469" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L469" s="6" t="inlineStr"/>
@@ -23318,7 +23318,7 @@
       </c>
       <c r="K470" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L470" s="3" t="inlineStr"/>
@@ -23366,7 +23366,7 @@
       </c>
       <c r="K471" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L471" s="6" t="inlineStr"/>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="K472" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L472" s="3" t="inlineStr"/>
@@ -23462,7 +23462,7 @@
       </c>
       <c r="K473" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L473" s="6" t="inlineStr"/>
@@ -23510,7 +23510,7 @@
       </c>
       <c r="K474" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L474" s="3" t="inlineStr"/>
@@ -23558,7 +23558,7 @@
       </c>
       <c r="K475" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L475" s="6" t="inlineStr"/>
@@ -23606,7 +23606,7 @@
       </c>
       <c r="K476" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L476" s="3" t="inlineStr"/>
@@ -23654,7 +23654,7 @@
       </c>
       <c r="K477" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L477" s="6" t="inlineStr"/>
@@ -23702,7 +23702,7 @@
       </c>
       <c r="K478" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L478" s="3" t="inlineStr"/>
@@ -23750,7 +23750,7 @@
       </c>
       <c r="K479" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L479" s="6" t="inlineStr"/>
@@ -23798,7 +23798,7 @@
       </c>
       <c r="K480" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L480" s="3" t="inlineStr"/>
@@ -23846,7 +23846,7 @@
       </c>
       <c r="K481" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L481" s="6" t="inlineStr"/>
@@ -23894,7 +23894,7 @@
       </c>
       <c r="K482" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L482" s="3" t="inlineStr"/>
@@ -23942,7 +23942,7 @@
       </c>
       <c r="K483" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L483" s="6" t="inlineStr"/>
@@ -23990,7 +23990,7 @@
       </c>
       <c r="K484" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L484" s="3" t="inlineStr"/>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="K485" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L485" s="6" t="inlineStr"/>
@@ -24086,7 +24086,7 @@
       </c>
       <c r="K486" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L486" s="3" t="inlineStr"/>
@@ -24134,7 +24134,7 @@
       </c>
       <c r="K487" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L487" s="6" t="inlineStr"/>
@@ -24182,7 +24182,7 @@
       </c>
       <c r="K488" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L488" s="3" t="inlineStr"/>
@@ -24230,7 +24230,7 @@
       </c>
       <c r="K489" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L489" s="6" t="inlineStr"/>
@@ -24278,7 +24278,7 @@
       </c>
       <c r="K490" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L490" s="3" t="inlineStr"/>
@@ -24326,7 +24326,7 @@
       </c>
       <c r="K491" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L491" s="6" t="inlineStr"/>
@@ -24374,7 +24374,7 @@
       </c>
       <c r="K492" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L492" s="3" t="inlineStr"/>
@@ -24422,7 +24422,7 @@
       </c>
       <c r="K493" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L493" s="6" t="inlineStr"/>
@@ -24470,7 +24470,7 @@
       </c>
       <c r="K494" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L494" s="3" t="inlineStr"/>
@@ -24518,7 +24518,7 @@
       </c>
       <c r="K495" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L495" s="6" t="inlineStr"/>
@@ -24566,7 +24566,7 @@
       </c>
       <c r="K496" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L496" s="3" t="inlineStr"/>
@@ -24614,7 +24614,7 @@
       </c>
       <c r="K497" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L497" s="6" t="inlineStr"/>
@@ -24662,7 +24662,7 @@
       </c>
       <c r="K498" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L498" s="3" t="inlineStr"/>
@@ -24710,7 +24710,7 @@
       </c>
       <c r="K499" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L499" s="6" t="inlineStr"/>
@@ -24758,7 +24758,7 @@
       </c>
       <c r="K500" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L500" s="3" t="inlineStr"/>
@@ -24806,7 +24806,7 @@
       </c>
       <c r="K501" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L501" s="6" t="inlineStr"/>
@@ -24854,7 +24854,7 @@
       </c>
       <c r="K502" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L502" s="3" t="inlineStr"/>
@@ -24902,7 +24902,7 @@
       </c>
       <c r="K503" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L503" s="6" t="inlineStr"/>
@@ -24950,7 +24950,7 @@
       </c>
       <c r="K504" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L504" s="3" t="inlineStr"/>
@@ -24998,7 +24998,7 @@
       </c>
       <c r="K505" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L505" s="6" t="inlineStr"/>
@@ -25046,7 +25046,7 @@
       </c>
       <c r="K506" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L506" s="3" t="inlineStr"/>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="K507" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L507" s="6" t="inlineStr"/>
@@ -25142,7 +25142,7 @@
       </c>
       <c r="K508" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L508" s="3" t="inlineStr"/>
@@ -25190,7 +25190,7 @@
       </c>
       <c r="K509" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L509" s="6" t="inlineStr"/>
@@ -25238,7 +25238,7 @@
       </c>
       <c r="K510" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L510" s="3" t="inlineStr"/>
@@ -25286,7 +25286,7 @@
       </c>
       <c r="K511" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L511" s="6" t="inlineStr"/>
@@ -25334,7 +25334,7 @@
       </c>
       <c r="K512" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L512" s="3" t="inlineStr"/>
@@ -25382,7 +25382,7 @@
       </c>
       <c r="K513" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L513" s="6" t="inlineStr"/>
@@ -25430,7 +25430,7 @@
       </c>
       <c r="K514" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L514" s="3" t="inlineStr"/>
@@ -25478,7 +25478,7 @@
       </c>
       <c r="K515" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L515" s="6" t="inlineStr"/>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="K516" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L516" s="3" t="inlineStr"/>
@@ -25574,7 +25574,7 @@
       </c>
       <c r="K517" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L517" s="6" t="inlineStr"/>
@@ -25622,7 +25622,7 @@
       </c>
       <c r="K518" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L518" s="3" t="inlineStr"/>
@@ -25670,7 +25670,7 @@
       </c>
       <c r="K519" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L519" s="6" t="inlineStr"/>
@@ -25718,7 +25718,7 @@
       </c>
       <c r="K520" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L520" s="3" t="inlineStr"/>
@@ -25766,7 +25766,7 @@
       </c>
       <c r="K521" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L521" s="6" t="inlineStr"/>
@@ -25814,7 +25814,7 @@
       </c>
       <c r="K522" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L522" s="3" t="inlineStr"/>
@@ -25862,7 +25862,7 @@
       </c>
       <c r="K523" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L523" s="6" t="inlineStr"/>
@@ -25910,7 +25910,7 @@
       </c>
       <c r="K524" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L524" s="3" t="inlineStr"/>
@@ -25958,7 +25958,7 @@
       </c>
       <c r="K525" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L525" s="6" t="inlineStr"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K526" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L526" s="3" t="inlineStr"/>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="K527" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L527" s="6" t="inlineStr"/>
@@ -26102,7 +26102,7 @@
       </c>
       <c r="K528" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L528" s="3" t="inlineStr"/>
@@ -26150,7 +26150,7 @@
       </c>
       <c r="K529" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L529" s="6" t="inlineStr"/>
@@ -26198,7 +26198,7 @@
       </c>
       <c r="K530" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L530" s="3" t="inlineStr"/>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="K531" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L531" s="6" t="inlineStr"/>
@@ -26294,7 +26294,7 @@
       </c>
       <c r="K532" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L532" s="3" t="inlineStr"/>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="K533" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L533" s="6" t="inlineStr"/>
@@ -26390,7 +26390,7 @@
       </c>
       <c r="K534" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L534" s="3" t="inlineStr"/>
@@ -26438,7 +26438,7 @@
       </c>
       <c r="K535" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L535" s="6" t="inlineStr"/>
@@ -26486,7 +26486,7 @@
       </c>
       <c r="K536" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L536" s="3" t="inlineStr"/>
@@ -26534,7 +26534,7 @@
       </c>
       <c r="K537" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L537" s="6" t="inlineStr"/>
@@ -26582,7 +26582,7 @@
       </c>
       <c r="K538" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L538" s="3" t="inlineStr"/>
@@ -26630,7 +26630,7 @@
       </c>
       <c r="K539" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L539" s="6" t="inlineStr"/>
@@ -26678,7 +26678,7 @@
       </c>
       <c r="K540" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L540" s="3" t="inlineStr"/>
@@ -26726,7 +26726,7 @@
       </c>
       <c r="K541" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L541" s="6" t="inlineStr"/>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="K542" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L542" s="3" t="inlineStr"/>
@@ -26822,7 +26822,7 @@
       </c>
       <c r="K543" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L543" s="6" t="inlineStr"/>
@@ -26870,7 +26870,7 @@
       </c>
       <c r="K544" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L544" s="3" t="inlineStr"/>
@@ -26918,7 +26918,7 @@
       </c>
       <c r="K545" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L545" s="6" t="inlineStr"/>
@@ -26966,7 +26966,7 @@
       </c>
       <c r="K546" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L546" s="3" t="inlineStr"/>
@@ -27014,7 +27014,7 @@
       </c>
       <c r="K547" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L547" s="6" t="inlineStr"/>
@@ -27062,7 +27062,7 @@
       </c>
       <c r="K548" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L548" s="3" t="inlineStr"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K549" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L549" s="6" t="inlineStr"/>
@@ -27158,7 +27158,7 @@
       </c>
       <c r="K550" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L550" s="3" t="inlineStr"/>
@@ -27206,7 +27206,7 @@
       </c>
       <c r="K551" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L551" s="6" t="inlineStr"/>
@@ -27254,7 +27254,7 @@
       </c>
       <c r="K552" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L552" s="3" t="inlineStr"/>
@@ -27302,7 +27302,7 @@
       </c>
       <c r="K553" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L553" s="6" t="inlineStr"/>
@@ -27350,7 +27350,7 @@
       </c>
       <c r="K554" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L554" s="3" t="inlineStr"/>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="K555" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L555" s="6" t="inlineStr"/>
@@ -27446,7 +27446,7 @@
       </c>
       <c r="K556" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L556" s="3" t="inlineStr"/>
@@ -27494,7 +27494,7 @@
       </c>
       <c r="K557" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L557" s="6" t="inlineStr"/>
@@ -27542,7 +27542,7 @@
       </c>
       <c r="K558" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L558" s="3" t="inlineStr"/>
@@ -27590,7 +27590,7 @@
       </c>
       <c r="K559" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L559" s="6" t="inlineStr"/>
@@ -27638,7 +27638,7 @@
       </c>
       <c r="K560" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L560" s="3" t="inlineStr"/>
@@ -27686,7 +27686,7 @@
       </c>
       <c r="K561" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L561" s="6" t="inlineStr"/>
@@ -27734,7 +27734,7 @@
       </c>
       <c r="K562" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L562" s="3" t="inlineStr"/>
@@ -27782,7 +27782,7 @@
       </c>
       <c r="K563" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L563" s="6" t="inlineStr"/>
@@ -27830,7 +27830,7 @@
       </c>
       <c r="K564" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L564" s="3" t="inlineStr"/>
@@ -27878,7 +27878,7 @@
       </c>
       <c r="K565" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L565" s="6" t="inlineStr"/>
@@ -27926,7 +27926,7 @@
       </c>
       <c r="K566" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L566" s="3" t="inlineStr"/>
@@ -27974,7 +27974,7 @@
       </c>
       <c r="K567" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L567" s="6" t="inlineStr"/>
@@ -28022,7 +28022,7 @@
       </c>
       <c r="K568" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L568" s="3" t="inlineStr"/>
@@ -28070,7 +28070,7 @@
       </c>
       <c r="K569" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L569" s="6" t="inlineStr"/>
@@ -28118,7 +28118,7 @@
       </c>
       <c r="K570" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L570" s="3" t="inlineStr"/>
@@ -28166,7 +28166,7 @@
       </c>
       <c r="K571" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L571" s="6" t="inlineStr"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K572" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L572" s="3" t="inlineStr"/>
@@ -28262,7 +28262,7 @@
       </c>
       <c r="K573" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L573" s="6" t="inlineStr"/>
@@ -28310,7 +28310,7 @@
       </c>
       <c r="K574" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L574" s="3" t="inlineStr"/>
@@ -28358,7 +28358,7 @@
       </c>
       <c r="K575" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L575" s="6" t="inlineStr"/>
@@ -28406,7 +28406,7 @@
       </c>
       <c r="K576" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L576" s="3" t="inlineStr"/>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="K577" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L577" s="6" t="inlineStr"/>
@@ -28502,7 +28502,7 @@
       </c>
       <c r="K578" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L578" s="3" t="inlineStr"/>
@@ -28550,7 +28550,7 @@
       </c>
       <c r="K579" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L579" s="6" t="inlineStr"/>
@@ -28598,7 +28598,7 @@
       </c>
       <c r="K580" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L580" s="3" t="inlineStr"/>
@@ -28646,7 +28646,7 @@
       </c>
       <c r="K581" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L581" s="6" t="inlineStr"/>
@@ -28694,7 +28694,7 @@
       </c>
       <c r="K582" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L582" s="3" t="inlineStr"/>
@@ -28742,7 +28742,7 @@
       </c>
       <c r="K583" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L583" s="6" t="inlineStr"/>
@@ -28790,7 +28790,7 @@
       </c>
       <c r="K584" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L584" s="3" t="inlineStr"/>
@@ -28838,7 +28838,7 @@
       </c>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L585" s="6" t="inlineStr"/>
@@ -28886,7 +28886,7 @@
       </c>
       <c r="K586" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L586" s="3" t="inlineStr"/>
@@ -28934,7 +28934,7 @@
       </c>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L587" s="6" t="inlineStr"/>
@@ -28982,7 +28982,7 @@
       </c>
       <c r="K588" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L588" s="3" t="inlineStr"/>
@@ -29030,7 +29030,7 @@
       </c>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L589" s="6" t="inlineStr"/>
@@ -29078,7 +29078,7 @@
       </c>
       <c r="K590" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L590" s="3" t="inlineStr"/>
@@ -29126,7 +29126,7 @@
       </c>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L591" s="6" t="inlineStr"/>
@@ -29174,7 +29174,7 @@
       </c>
       <c r="K592" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L592" s="3" t="inlineStr"/>
@@ -29222,7 +29222,7 @@
       </c>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L593" s="6" t="inlineStr"/>
@@ -29270,7 +29270,7 @@
       </c>
       <c r="K594" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L594" s="3" t="inlineStr"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L595" s="6" t="inlineStr"/>
@@ -29366,7 +29366,7 @@
       </c>
       <c r="K596" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L596" s="3" t="inlineStr"/>
@@ -29414,7 +29414,7 @@
       </c>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L597" s="6" t="inlineStr"/>
@@ -29462,7 +29462,7 @@
       </c>
       <c r="K598" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L598" s="3" t="inlineStr"/>
@@ -29510,7 +29510,7 @@
       </c>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L599" s="6" t="inlineStr"/>
@@ -29558,7 +29558,7 @@
       </c>
       <c r="K600" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L600" s="3" t="inlineStr"/>
@@ -29606,7 +29606,7 @@
       </c>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L601" s="6" t="inlineStr"/>
@@ -29654,7 +29654,7 @@
       </c>
       <c r="K602" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L602" s="3" t="inlineStr"/>
@@ -29702,7 +29702,7 @@
       </c>
       <c r="K603" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L603" s="6" t="inlineStr"/>
@@ -29750,7 +29750,7 @@
       </c>
       <c r="K604" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L604" s="3" t="inlineStr"/>
@@ -29798,7 +29798,7 @@
       </c>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr"/>
@@ -29846,7 +29846,7 @@
       </c>
       <c r="K606" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L606" s="3" t="inlineStr"/>
@@ -29894,7 +29894,7 @@
       </c>
       <c r="K607" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L607" s="6" t="inlineStr"/>
@@ -29942,7 +29942,7 @@
       </c>
       <c r="K608" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L608" s="3" t="inlineStr"/>
@@ -29990,7 +29990,7 @@
       </c>
       <c r="K609" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L609" s="6" t="inlineStr"/>
@@ -30038,7 +30038,7 @@
       </c>
       <c r="K610" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L610" s="3" t="inlineStr"/>
@@ -30086,7 +30086,7 @@
       </c>
       <c r="K611" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L611" s="6" t="inlineStr"/>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="K612" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L612" s="3" t="inlineStr"/>
@@ -30182,7 +30182,7 @@
       </c>
       <c r="K613" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L613" s="6" t="inlineStr"/>
@@ -30230,7 +30230,7 @@
       </c>
       <c r="K614" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L614" s="3" t="inlineStr"/>
@@ -30278,7 +30278,7 @@
       </c>
       <c r="K615" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L615" s="6" t="inlineStr"/>
@@ -30326,7 +30326,7 @@
       </c>
       <c r="K616" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L616" s="3" t="inlineStr"/>
@@ -30374,7 +30374,7 @@
       </c>
       <c r="K617" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L617" s="6" t="inlineStr"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K618" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L618" s="3" t="inlineStr"/>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="K619" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L619" s="6" t="inlineStr"/>
@@ -30518,7 +30518,7 @@
       </c>
       <c r="K620" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L620" s="3" t="inlineStr"/>
@@ -30566,7 +30566,7 @@
       </c>
       <c r="K621" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L621" s="6" t="inlineStr"/>
@@ -30614,7 +30614,7 @@
       </c>
       <c r="K622" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L622" s="3" t="inlineStr"/>
@@ -30662,7 +30662,7 @@
       </c>
       <c r="K623" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L623" s="6" t="inlineStr"/>
@@ -30710,7 +30710,7 @@
       </c>
       <c r="K624" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L624" s="3" t="inlineStr"/>
@@ -30758,7 +30758,7 @@
       </c>
       <c r="K625" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L625" s="6" t="inlineStr"/>
@@ -30806,7 +30806,7 @@
       </c>
       <c r="K626" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L626" s="3" t="inlineStr"/>
@@ -30854,7 +30854,7 @@
       </c>
       <c r="K627" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L627" s="6" t="inlineStr"/>
@@ -30902,7 +30902,7 @@
       </c>
       <c r="K628" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L628" s="3" t="inlineStr"/>
@@ -30950,7 +30950,7 @@
       </c>
       <c r="K629" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L629" s="6" t="inlineStr"/>
@@ -30998,7 +30998,7 @@
       </c>
       <c r="K630" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L630" s="3" t="inlineStr"/>
@@ -31046,7 +31046,7 @@
       </c>
       <c r="K631" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L631" s="6" t="inlineStr"/>
@@ -31094,7 +31094,7 @@
       </c>
       <c r="K632" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L632" s="3" t="inlineStr"/>
@@ -31142,7 +31142,7 @@
       </c>
       <c r="K633" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L633" s="6" t="inlineStr"/>
@@ -31190,7 +31190,7 @@
       </c>
       <c r="K634" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L634" s="3" t="inlineStr"/>
@@ -31238,7 +31238,7 @@
       </c>
       <c r="K635" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L635" s="6" t="inlineStr"/>
@@ -31286,7 +31286,7 @@
       </c>
       <c r="K636" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L636" s="3" t="inlineStr"/>
@@ -31334,7 +31334,7 @@
       </c>
       <c r="K637" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L637" s="6" t="inlineStr"/>
@@ -31382,7 +31382,7 @@
       </c>
       <c r="K638" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L638" s="3" t="inlineStr"/>
@@ -31430,7 +31430,7 @@
       </c>
       <c r="K639" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L639" s="6" t="inlineStr"/>
@@ -31478,7 +31478,7 @@
       </c>
       <c r="K640" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L640" s="3" t="inlineStr"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K641" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L641" s="6" t="inlineStr"/>
@@ -31574,7 +31574,7 @@
       </c>
       <c r="K642" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L642" s="3" t="inlineStr"/>
@@ -31622,7 +31622,7 @@
       </c>
       <c r="K643" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L643" s="6" t="inlineStr"/>
@@ -31670,7 +31670,7 @@
       </c>
       <c r="K644" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L644" s="3" t="inlineStr"/>
@@ -31718,7 +31718,7 @@
       </c>
       <c r="K645" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L645" s="6" t="inlineStr"/>
@@ -31766,7 +31766,7 @@
       </c>
       <c r="K646" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L646" s="3" t="inlineStr"/>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="K647" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L647" s="6" t="inlineStr"/>
@@ -31862,7 +31862,7 @@
       </c>
       <c r="K648" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L648" s="3" t="inlineStr"/>
@@ -31910,7 +31910,7 @@
       </c>
       <c r="K649" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L649" s="6" t="inlineStr"/>
@@ -31958,7 +31958,7 @@
       </c>
       <c r="K650" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L650" s="3" t="inlineStr"/>
@@ -32006,7 +32006,7 @@
       </c>
       <c r="K651" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L651" s="6" t="inlineStr"/>
@@ -32054,7 +32054,7 @@
       </c>
       <c r="K652" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L652" s="3" t="inlineStr"/>
@@ -32102,7 +32102,7 @@
       </c>
       <c r="K653" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L653" s="6" t="inlineStr"/>
@@ -32150,7 +32150,7 @@
       </c>
       <c r="K654" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L654" s="3" t="inlineStr"/>
@@ -32198,7 +32198,7 @@
       </c>
       <c r="K655" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L655" s="6" t="inlineStr"/>
@@ -32246,7 +32246,7 @@
       </c>
       <c r="K656" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L656" s="3" t="inlineStr"/>
@@ -32294,7 +32294,7 @@
       </c>
       <c r="K657" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L657" s="6" t="inlineStr"/>
@@ -32342,7 +32342,7 @@
       </c>
       <c r="K658" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L658" s="3" t="inlineStr"/>
@@ -32390,7 +32390,7 @@
       </c>
       <c r="K659" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L659" s="6" t="inlineStr"/>
@@ -32438,7 +32438,7 @@
       </c>
       <c r="K660" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L660" s="3" t="inlineStr"/>
@@ -32486,7 +32486,7 @@
       </c>
       <c r="K661" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L661" s="6" t="inlineStr"/>
@@ -32534,7 +32534,7 @@
       </c>
       <c r="K662" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L662" s="3" t="inlineStr"/>
@@ -32582,7 +32582,7 @@
       </c>
       <c r="K663" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L663" s="6" t="inlineStr"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K664" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L664" s="3" t="inlineStr"/>
@@ -32678,7 +32678,7 @@
       </c>
       <c r="K665" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L665" s="6" t="inlineStr"/>
@@ -32726,7 +32726,7 @@
       </c>
       <c r="K666" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L666" s="3" t="inlineStr"/>
@@ -32774,7 +32774,7 @@
       </c>
       <c r="K667" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L667" s="6" t="inlineStr"/>
@@ -32822,7 +32822,7 @@
       </c>
       <c r="K668" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L668" s="3" t="inlineStr"/>
@@ -32870,7 +32870,7 @@
       </c>
       <c r="K669" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L669" s="6" t="inlineStr"/>
@@ -32918,7 +32918,7 @@
       </c>
       <c r="K670" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L670" s="3" t="inlineStr"/>
@@ -32966,7 +32966,7 @@
       </c>
       <c r="K671" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L671" s="6" t="inlineStr"/>
@@ -33014,7 +33014,7 @@
       </c>
       <c r="K672" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L672" s="3" t="inlineStr"/>
@@ -33062,7 +33062,7 @@
       </c>
       <c r="K673" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L673" s="6" t="inlineStr"/>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="K674" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L674" s="3" t="inlineStr"/>
@@ -33158,7 +33158,7 @@
       </c>
       <c r="K675" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L675" s="6" t="inlineStr"/>
@@ -33206,7 +33206,7 @@
       </c>
       <c r="K676" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L676" s="3" t="inlineStr"/>
@@ -33254,7 +33254,7 @@
       </c>
       <c r="K677" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L677" s="6" t="inlineStr"/>
@@ -33302,7 +33302,7 @@
       </c>
       <c r="K678" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L678" s="3" t="inlineStr"/>
@@ -33350,7 +33350,7 @@
       </c>
       <c r="K679" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L679" s="6" t="inlineStr"/>
@@ -33398,7 +33398,7 @@
       </c>
       <c r="K680" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L680" s="3" t="inlineStr"/>
@@ -33446,7 +33446,7 @@
       </c>
       <c r="K681" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L681" s="6" t="inlineStr"/>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="K682" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L682" s="3" t="inlineStr"/>
@@ -33542,7 +33542,7 @@
       </c>
       <c r="K683" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L683" s="6" t="inlineStr"/>
@@ -33590,7 +33590,7 @@
       </c>
       <c r="K684" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L684" s="3" t="inlineStr"/>
@@ -33638,7 +33638,7 @@
       </c>
       <c r="K685" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L685" s="6" t="inlineStr"/>
@@ -33686,7 +33686,7 @@
       </c>
       <c r="K686" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L686" s="3" t="inlineStr"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K687" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L687" s="6" t="inlineStr"/>
@@ -33782,7 +33782,7 @@
       </c>
       <c r="K688" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L688" s="3" t="inlineStr"/>
@@ -33830,7 +33830,7 @@
       </c>
       <c r="K689" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L689" s="6" t="inlineStr"/>
@@ -33878,7 +33878,7 @@
       </c>
       <c r="K690" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L690" s="3" t="inlineStr"/>
@@ -33926,7 +33926,7 @@
       </c>
       <c r="K691" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L691" s="6" t="inlineStr"/>
@@ -33974,7 +33974,7 @@
       </c>
       <c r="K692" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L692" s="3" t="inlineStr"/>
@@ -34022,7 +34022,7 @@
       </c>
       <c r="K693" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L693" s="6" t="inlineStr"/>
@@ -34070,7 +34070,7 @@
       </c>
       <c r="K694" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L694" s="3" t="inlineStr"/>
@@ -34118,7 +34118,7 @@
       </c>
       <c r="K695" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L695" s="6" t="inlineStr"/>
@@ -34166,7 +34166,7 @@
       </c>
       <c r="K696" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L696" s="3" t="inlineStr"/>
@@ -34214,7 +34214,7 @@
       </c>
       <c r="K697" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L697" s="6" t="inlineStr"/>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="K698" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L698" s="3" t="inlineStr"/>
@@ -34310,7 +34310,7 @@
       </c>
       <c r="K699" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L699" s="6" t="inlineStr"/>
@@ -34358,7 +34358,7 @@
       </c>
       <c r="K700" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L700" s="3" t="inlineStr"/>
@@ -34406,7 +34406,7 @@
       </c>
       <c r="K701" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L701" s="6" t="inlineStr"/>
@@ -34454,7 +34454,7 @@
       </c>
       <c r="K702" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L702" s="3" t="inlineStr"/>
@@ -34502,7 +34502,7 @@
       </c>
       <c r="K703" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L703" s="6" t="inlineStr"/>
@@ -34550,7 +34550,7 @@
       </c>
       <c r="K704" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L704" s="3" t="inlineStr"/>
@@ -34598,7 +34598,7 @@
       </c>
       <c r="K705" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L705" s="6" t="inlineStr"/>
@@ -34646,7 +34646,7 @@
       </c>
       <c r="K706" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L706" s="3" t="inlineStr"/>
@@ -34694,7 +34694,7 @@
       </c>
       <c r="K707" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L707" s="6" t="inlineStr"/>
@@ -34742,7 +34742,7 @@
       </c>
       <c r="K708" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L708" s="3" t="inlineStr"/>
@@ -34790,7 +34790,7 @@
       </c>
       <c r="K709" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L709" s="6" t="inlineStr"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K710" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L710" s="3" t="inlineStr"/>
@@ -34886,7 +34886,7 @@
       </c>
       <c r="K711" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L711" s="6" t="inlineStr"/>
@@ -34934,7 +34934,7 @@
       </c>
       <c r="K712" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L712" s="3" t="inlineStr"/>
@@ -34982,7 +34982,7 @@
       </c>
       <c r="K713" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L713" s="6" t="inlineStr"/>
@@ -35030,7 +35030,7 @@
       </c>
       <c r="K714" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L714" s="3" t="inlineStr"/>
@@ -35078,7 +35078,7 @@
       </c>
       <c r="K715" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L715" s="6" t="inlineStr"/>
@@ -35126,7 +35126,7 @@
       </c>
       <c r="K716" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L716" s="3" t="inlineStr"/>
@@ -35174,7 +35174,7 @@
       </c>
       <c r="K717" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L717" s="6" t="inlineStr"/>
@@ -35222,7 +35222,7 @@
       </c>
       <c r="K718" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L718" s="3" t="inlineStr"/>
@@ -35270,7 +35270,7 @@
       </c>
       <c r="K719" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L719" s="6" t="inlineStr"/>
@@ -35318,7 +35318,7 @@
       </c>
       <c r="K720" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L720" s="3" t="inlineStr"/>
@@ -35366,7 +35366,7 @@
       </c>
       <c r="K721" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L721" s="6" t="inlineStr"/>
@@ -35414,7 +35414,7 @@
       </c>
       <c r="K722" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L722" s="3" t="inlineStr"/>
@@ -35462,7 +35462,7 @@
       </c>
       <c r="K723" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L723" s="6" t="inlineStr"/>
@@ -35510,7 +35510,7 @@
       </c>
       <c r="K724" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L724" s="3" t="inlineStr"/>
@@ -35558,7 +35558,7 @@
       </c>
       <c r="K725" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L725" s="6" t="inlineStr"/>
@@ -35606,7 +35606,7 @@
       </c>
       <c r="K726" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L726" s="3" t="inlineStr"/>
@@ -35654,7 +35654,7 @@
       </c>
       <c r="K727" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L727" s="6" t="inlineStr"/>
@@ -35702,7 +35702,7 @@
       </c>
       <c r="K728" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L728" s="3" t="inlineStr"/>
@@ -35750,7 +35750,7 @@
       </c>
       <c r="K729" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L729" s="4" t="inlineStr">
@@ -35802,7 +35802,7 @@
       </c>
       <c r="K730" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L730" s="4" t="inlineStr">
@@ -35854,7 +35854,7 @@
       </c>
       <c r="K731" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L731" s="4" t="inlineStr">
@@ -35906,7 +35906,7 @@
       </c>
       <c r="K732" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L732" s="4" t="inlineStr">
@@ -35958,7 +35958,7 @@
       </c>
       <c r="K733" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L733" s="4" t="inlineStr">
@@ -36010,7 +36010,7 @@
       </c>
       <c r="K734" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L734" s="4" t="inlineStr">
@@ -36062,7 +36062,7 @@
       </c>
       <c r="K735" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L735" s="4" t="inlineStr">
@@ -36114,7 +36114,7 @@
       </c>
       <c r="K736" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L736" s="4" t="inlineStr">
@@ -36166,7 +36166,7 @@
       </c>
       <c r="K737" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L737" s="4" t="inlineStr">
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K738" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L738" s="4" t="inlineStr">
@@ -36270,7 +36270,7 @@
       </c>
       <c r="K739" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L739" s="4" t="inlineStr">
@@ -36322,7 +36322,7 @@
       </c>
       <c r="K740" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L740" s="4" t="inlineStr">
@@ -36374,7 +36374,7 @@
       </c>
       <c r="K741" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L741" s="4" t="inlineStr">
@@ -36426,7 +36426,7 @@
       </c>
       <c r="K742" s="3" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L742" s="4" t="inlineStr">
@@ -36478,7 +36478,7 @@
       </c>
       <c r="K743" s="6" t="inlineStr">
         <is>
-          <t>2026-09-19</t>
+          <t>2026-09-20</t>
         </is>
       </c>
       <c r="L743" s="4" t="inlineStr">

--- a/public/loop-library.xlsx
+++ b/public/loop-library.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr"/>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr"/>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr"/>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr"/>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr"/>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr"/>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr"/>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr"/>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr"/>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr"/>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr"/>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr"/>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr"/>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr"/>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr"/>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr"/>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr"/>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr"/>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr"/>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr"/>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L93" s="6" t="inlineStr"/>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr"/>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L95" s="6" t="inlineStr"/>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr"/>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L97" s="6" t="inlineStr"/>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr"/>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr"/>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr"/>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr"/>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L102" s="3" t="inlineStr"/>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L103" s="6" t="inlineStr"/>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L104" s="3" t="inlineStr"/>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L105" s="6" t="inlineStr"/>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L106" s="3" t="inlineStr"/>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L107" s="6" t="inlineStr"/>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L108" s="3" t="inlineStr"/>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L109" s="6" t="inlineStr"/>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L110" s="3" t="inlineStr"/>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L111" s="6" t="inlineStr"/>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L112" s="3" t="inlineStr"/>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L113" s="6" t="inlineStr"/>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L114" s="3" t="inlineStr"/>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L115" s="6" t="inlineStr"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="K116" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L116" s="3" t="inlineStr"/>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L117" s="6" t="inlineStr"/>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="K118" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L118" s="3" t="inlineStr"/>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L119" s="6" t="inlineStr"/>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="K120" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L120" s="3" t="inlineStr"/>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L121" s="6" t="inlineStr"/>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="K122" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L122" s="3" t="inlineStr"/>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L123" s="6" t="inlineStr"/>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="K124" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L124" s="3" t="inlineStr"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="K125" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L125" s="6" t="inlineStr"/>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="K126" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L126" s="3" t="inlineStr"/>
@@ -6854,7 +6854,7 @@
       </c>
       <c r="K127" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L127" s="6" t="inlineStr"/>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L128" s="3" t="inlineStr"/>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="K129" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L129" s="6" t="inlineStr"/>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="K130" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L130" s="3" t="inlineStr"/>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="K131" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L131" s="6" t="inlineStr"/>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L132" s="3" t="inlineStr"/>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="K133" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L133" s="6" t="inlineStr"/>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="K134" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L134" s="3" t="inlineStr"/>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="K135" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L135" s="6" t="inlineStr"/>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="K136" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L136" s="3" t="inlineStr"/>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="K137" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L137" s="6" t="inlineStr"/>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="K138" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L138" s="3" t="inlineStr"/>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="K139" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L139" s="6" t="inlineStr"/>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="K140" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L140" s="3" t="inlineStr"/>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="K141" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L141" s="6" t="inlineStr"/>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L142" s="3" t="inlineStr"/>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="K143" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L143" s="6" t="inlineStr"/>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="K144" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L144" s="3" t="inlineStr"/>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="K145" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L145" s="6" t="inlineStr"/>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="K146" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L146" s="3" t="inlineStr"/>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="K147" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L147" s="6" t="inlineStr"/>
@@ -7862,7 +7862,7 @@
       </c>
       <c r="K148" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L148" s="3" t="inlineStr"/>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="K149" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L149" s="6" t="inlineStr"/>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="K150" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L150" s="3" t="inlineStr"/>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="K151" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L151" s="6" t="inlineStr"/>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="K152" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L152" s="3" t="inlineStr"/>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="K153" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L153" s="6" t="inlineStr"/>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="K154" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L154" s="3" t="inlineStr"/>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="K155" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L155" s="6" t="inlineStr"/>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="K156" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L156" s="3" t="inlineStr"/>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K157" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L157" s="6" t="inlineStr"/>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="K158" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L158" s="3" t="inlineStr"/>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="K159" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L159" s="6" t="inlineStr"/>
@@ -8438,7 +8438,7 @@
       </c>
       <c r="K160" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L160" s="3" t="inlineStr"/>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="K161" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L161" s="6" t="inlineStr"/>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="K162" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L162" s="3" t="inlineStr"/>
@@ -8582,7 +8582,7 @@
       </c>
       <c r="K163" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L163" s="6" t="inlineStr"/>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="K164" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L164" s="3" t="inlineStr"/>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="K165" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L165" s="6" t="inlineStr"/>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="K166" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L166" s="3" t="inlineStr"/>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="K167" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L167" s="6" t="inlineStr"/>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="K168" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L168" s="3" t="inlineStr"/>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="K169" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L169" s="6" t="inlineStr"/>
@@ -8918,7 +8918,7 @@
       </c>
       <c r="K170" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L170" s="3" t="inlineStr"/>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="K171" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L171" s="6" t="inlineStr"/>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="K172" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L172" s="3" t="inlineStr"/>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="K173" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L173" s="6" t="inlineStr"/>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="K174" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L174" s="3" t="inlineStr"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="K175" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L175" s="6" t="inlineStr"/>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="K176" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L176" s="3" t="inlineStr"/>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="K177" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L177" s="6" t="inlineStr"/>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="K178" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L178" s="3" t="inlineStr"/>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="K179" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L179" s="6" t="inlineStr"/>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="K180" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L180" s="3" t="inlineStr"/>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="K181" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L181" s="6" t="inlineStr"/>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="K182" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L182" s="3" t="inlineStr"/>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="K183" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L183" s="6" t="inlineStr"/>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="K184" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L184" s="3" t="inlineStr"/>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="K185" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L185" s="6" t="inlineStr"/>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="K186" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L186" s="3" t="inlineStr"/>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="K187" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L187" s="6" t="inlineStr"/>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="K188" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L188" s="3" t="inlineStr"/>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="K189" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L189" s="6" t="inlineStr"/>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="K190" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L190" s="3" t="inlineStr"/>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="K191" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L191" s="6" t="inlineStr"/>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="K192" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L192" s="3" t="inlineStr"/>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="K193" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L193" s="6" t="inlineStr"/>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="K194" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L194" s="3" t="inlineStr"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="K195" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L195" s="6" t="inlineStr"/>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="K196" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L196" s="3" t="inlineStr"/>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="K197" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L197" s="6" t="inlineStr"/>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="K198" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L198" s="3" t="inlineStr"/>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="K199" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L199" s="6" t="inlineStr"/>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="K200" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L200" s="3" t="inlineStr"/>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="K201" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L201" s="6" t="inlineStr"/>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="K202" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L202" s="3" t="inlineStr"/>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="K203" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L203" s="6" t="inlineStr"/>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="K204" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L204" s="3" t="inlineStr"/>
@@ -10598,7 +10598,7 @@
       </c>
       <c r="K205" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L205" s="6" t="inlineStr"/>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K206" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L206" s="3" t="inlineStr"/>
@@ -10694,7 +10694,7 @@
       </c>
       <c r="K207" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L207" s="6" t="inlineStr"/>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="K208" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L208" s="3" t="inlineStr"/>
@@ -10790,7 +10790,7 @@
       </c>
       <c r="K209" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L209" s="6" t="inlineStr"/>
@@ -10838,7 +10838,7 @@
       </c>
       <c r="K210" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L210" s="3" t="inlineStr"/>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="K211" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L211" s="6" t="inlineStr"/>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="K212" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L212" s="3" t="inlineStr"/>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="K213" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L213" s="6" t="inlineStr"/>
@@ -11030,7 +11030,7 @@
       </c>
       <c r="K214" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L214" s="3" t="inlineStr"/>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="K215" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L215" s="6" t="inlineStr"/>
@@ -11126,7 +11126,7 @@
       </c>
       <c r="K216" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L216" s="3" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="K217" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L217" s="6" t="inlineStr"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="K218" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L218" s="3" t="inlineStr"/>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="K219" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L219" s="6" t="inlineStr"/>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="K220" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L220" s="3" t="inlineStr"/>
@@ -11366,7 +11366,7 @@
       </c>
       <c r="K221" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L221" s="6" t="inlineStr"/>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="K222" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L222" s="3" t="inlineStr"/>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="K223" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L223" s="6" t="inlineStr"/>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="K224" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L224" s="3" t="inlineStr"/>
@@ -11558,7 +11558,7 @@
       </c>
       <c r="K225" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L225" s="6" t="inlineStr"/>
@@ -11606,7 +11606,7 @@
       </c>
       <c r="K226" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L226" s="3" t="inlineStr"/>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="K227" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L227" s="6" t="inlineStr"/>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="K228" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L228" s="3" t="inlineStr"/>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="K229" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L229" s="6" t="inlineStr"/>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="K230" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L230" s="3" t="inlineStr"/>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="K231" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L231" s="6" t="inlineStr"/>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="K232" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L232" s="3" t="inlineStr"/>
@@ -11942,7 +11942,7 @@
       </c>
       <c r="K233" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L233" s="6" t="inlineStr"/>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="K234" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L234" s="3" t="inlineStr"/>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="K235" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L235" s="6" t="inlineStr"/>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="K236" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L236" s="3" t="inlineStr"/>
@@ -12134,7 +12134,7 @@
       </c>
       <c r="K237" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L237" s="6" t="inlineStr"/>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="K238" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L238" s="3" t="inlineStr"/>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="K239" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L239" s="6" t="inlineStr"/>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="K240" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L240" s="3" t="inlineStr"/>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="K241" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L241" s="6" t="inlineStr"/>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="K242" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L242" s="3" t="inlineStr"/>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="K243" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L243" s="6" t="inlineStr"/>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="K244" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L244" s="3" t="inlineStr"/>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="K245" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L245" s="6" t="inlineStr"/>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="K246" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L246" s="3" t="inlineStr"/>
@@ -12614,7 +12614,7 @@
       </c>
       <c r="K247" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L247" s="6" t="inlineStr"/>
@@ -12662,7 +12662,7 @@
       </c>
       <c r="K248" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L248" s="3" t="inlineStr"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="K249" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L249" s="6" t="inlineStr"/>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="K250" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L250" s="3" t="inlineStr"/>
@@ -12806,7 +12806,7 @@
       </c>
       <c r="K251" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L251" s="6" t="inlineStr"/>
@@ -12854,7 +12854,7 @@
       </c>
       <c r="K252" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L252" s="3" t="inlineStr"/>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="K253" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L253" s="6" t="inlineStr"/>
@@ -12950,7 +12950,7 @@
       </c>
       <c r="K254" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L254" s="3" t="inlineStr"/>
@@ -12998,7 +12998,7 @@
       </c>
       <c r="K255" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L255" s="6" t="inlineStr"/>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="K256" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L256" s="3" t="inlineStr"/>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="K257" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L257" s="6" t="inlineStr"/>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="K258" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L258" s="3" t="inlineStr"/>
@@ -13190,7 +13190,7 @@
       </c>
       <c r="K259" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L259" s="6" t="inlineStr"/>
@@ -13238,7 +13238,7 @@
       </c>
       <c r="K260" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L260" s="3" t="inlineStr"/>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="K261" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L261" s="6" t="inlineStr"/>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="K262" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L262" s="3" t="inlineStr"/>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="K263" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L263" s="6" t="inlineStr"/>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="K264" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L264" s="3" t="inlineStr"/>
@@ -13478,7 +13478,7 @@
       </c>
       <c r="K265" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L265" s="6" t="inlineStr"/>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="K266" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L266" s="3" t="inlineStr"/>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="K267" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L267" s="6" t="inlineStr"/>
@@ -13622,7 +13622,7 @@
       </c>
       <c r="K268" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L268" s="3" t="inlineStr"/>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="K269" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L269" s="6" t="inlineStr"/>
@@ -13718,7 +13718,7 @@
       </c>
       <c r="K270" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L270" s="3" t="inlineStr"/>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="K271" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L271" s="6" t="inlineStr"/>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="K272" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L272" s="3" t="inlineStr"/>
@@ -13862,7 +13862,7 @@
       </c>
       <c r="K273" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L273" s="6" t="inlineStr"/>
@@ -13910,7 +13910,7 @@
       </c>
       <c r="K274" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L274" s="3" t="inlineStr"/>
@@ -13958,7 +13958,7 @@
       </c>
       <c r="K275" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L275" s="6" t="inlineStr"/>
@@ -14006,7 +14006,7 @@
       </c>
       <c r="K276" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L276" s="3" t="inlineStr"/>
@@ -14054,7 +14054,7 @@
       </c>
       <c r="K277" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L277" s="6" t="inlineStr"/>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="K278" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L278" s="3" t="inlineStr"/>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="K279" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L279" s="6" t="inlineStr"/>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="K280" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L280" s="3" t="inlineStr"/>
@@ -14246,7 +14246,7 @@
       </c>
       <c r="K281" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L281" s="6" t="inlineStr"/>
@@ -14294,7 +14294,7 @@
       </c>
       <c r="K282" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L282" s="3" t="inlineStr"/>
@@ -14342,7 +14342,7 @@
       </c>
       <c r="K283" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L283" s="6" t="inlineStr"/>
@@ -14390,7 +14390,7 @@
       </c>
       <c r="K284" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L284" s="3" t="inlineStr"/>
@@ -14438,7 +14438,7 @@
       </c>
       <c r="K285" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L285" s="6" t="inlineStr"/>
@@ -14486,7 +14486,7 @@
       </c>
       <c r="K286" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L286" s="3" t="inlineStr"/>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="K287" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L287" s="6" t="inlineStr"/>
@@ -14582,7 +14582,7 @@
       </c>
       <c r="K288" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L288" s="3" t="inlineStr"/>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="K289" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L289" s="6" t="inlineStr"/>
@@ -14678,7 +14678,7 @@
       </c>
       <c r="K290" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L290" s="3" t="inlineStr"/>
@@ -14726,7 +14726,7 @@
       </c>
       <c r="K291" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L291" s="6" t="inlineStr"/>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="K292" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L292" s="3" t="inlineStr"/>
@@ -14822,7 +14822,7 @@
       </c>
       <c r="K293" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L293" s="6" t="inlineStr"/>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="K294" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L294" s="3" t="inlineStr"/>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="K295" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L295" s="6" t="inlineStr"/>
@@ -14966,7 +14966,7 @@
       </c>
       <c r="K296" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L296" s="3" t="inlineStr"/>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="K297" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L297" s="6" t="inlineStr"/>
@@ -15062,7 +15062,7 @@
       </c>
       <c r="K298" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L298" s="3" t="inlineStr"/>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="K299" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L299" s="6" t="inlineStr"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="K300" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L300" s="3" t="inlineStr"/>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="K301" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L301" s="6" t="inlineStr"/>
@@ -15254,7 +15254,7 @@
       </c>
       <c r="K302" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L302" s="3" t="inlineStr"/>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="K303" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L303" s="6" t="inlineStr"/>
@@ -15350,7 +15350,7 @@
       </c>
       <c r="K304" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L304" s="3" t="inlineStr"/>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="K305" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L305" s="6" t="inlineStr"/>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="K306" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L306" s="3" t="inlineStr"/>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="K307" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L307" s="6" t="inlineStr"/>
@@ -15542,7 +15542,7 @@
       </c>
       <c r="K308" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L308" s="3" t="inlineStr"/>
@@ -15590,7 +15590,7 @@
       </c>
       <c r="K309" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L309" s="6" t="inlineStr"/>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="K310" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L310" s="3" t="inlineStr"/>
@@ -15686,7 +15686,7 @@
       </c>
       <c r="K311" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L311" s="6" t="inlineStr"/>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="K312" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L312" s="3" t="inlineStr"/>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="K313" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L313" s="6" t="inlineStr"/>
@@ -15830,7 +15830,7 @@
       </c>
       <c r="K314" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L314" s="3" t="inlineStr"/>
@@ -15878,7 +15878,7 @@
       </c>
       <c r="K315" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L315" s="6" t="inlineStr"/>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="K316" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L316" s="3" t="inlineStr"/>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="K317" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L317" s="6" t="inlineStr"/>
@@ -16022,7 +16022,7 @@
       </c>
       <c r="K318" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L318" s="3" t="inlineStr"/>
@@ -16070,7 +16070,7 @@
       </c>
       <c r="K319" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L319" s="6" t="inlineStr"/>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="K320" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L320" s="3" t="inlineStr"/>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="K321" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L321" s="6" t="inlineStr"/>
@@ -16214,7 +16214,7 @@
       </c>
       <c r="K322" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L322" s="3" t="inlineStr"/>
@@ -16262,7 +16262,7 @@
       </c>
       <c r="K323" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L323" s="6" t="inlineStr"/>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="K324" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L324" s="3" t="inlineStr"/>
@@ -16358,7 +16358,7 @@
       </c>
       <c r="K325" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L325" s="6" t="inlineStr"/>
@@ -16406,7 +16406,7 @@
       </c>
       <c r="K326" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L326" s="3" t="inlineStr"/>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="K327" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L327" s="6" t="inlineStr"/>
@@ -16502,7 +16502,7 @@
       </c>
       <c r="K328" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L328" s="3" t="inlineStr"/>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="K329" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L329" s="6" t="inlineStr"/>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="K330" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L330" s="3" t="inlineStr"/>
@@ -16646,7 +16646,7 @@
       </c>
       <c r="K331" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L331" s="6" t="inlineStr"/>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="K332" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L332" s="3" t="inlineStr"/>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="K333" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L333" s="6" t="inlineStr"/>
@@ -16790,7 +16790,7 @@
       </c>
       <c r="K334" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L334" s="3" t="inlineStr"/>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="K335" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L335" s="6" t="inlineStr"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="K336" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L336" s="3" t="inlineStr"/>
@@ -16934,7 +16934,7 @@
       </c>
       <c r="K337" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L337" s="6" t="inlineStr"/>
@@ -16982,7 +16982,7 @@
       </c>
       <c r="K338" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L338" s="3" t="inlineStr"/>
@@ -17030,7 +17030,7 @@
       </c>
       <c r="K339" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L339" s="6" t="inlineStr"/>
@@ -17078,7 +17078,7 @@
       </c>
       <c r="K340" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L340" s="3" t="inlineStr"/>
@@ -17126,7 +17126,7 @@
       </c>
       <c r="K341" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L341" s="6" t="inlineStr"/>
@@ -17174,7 +17174,7 @@
       </c>
       <c r="K342" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L342" s="3" t="inlineStr"/>
@@ -17222,7 +17222,7 @@
       </c>
       <c r="K343" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L343" s="6" t="inlineStr"/>
@@ -17270,7 +17270,7 @@
       </c>
       <c r="K344" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L344" s="3" t="inlineStr"/>
@@ -17318,7 +17318,7 @@
       </c>
       <c r="K345" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L345" s="6" t="inlineStr"/>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="K346" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L346" s="3" t="inlineStr"/>
@@ -17414,7 +17414,7 @@
       </c>
       <c r="K347" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L347" s="6" t="inlineStr"/>
@@ -17462,7 +17462,7 @@
       </c>
       <c r="K348" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L348" s="3" t="inlineStr"/>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="K349" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L349" s="6" t="inlineStr"/>
@@ -17558,7 +17558,7 @@
       </c>
       <c r="K350" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L350" s="3" t="inlineStr"/>
@@ -17606,7 +17606,7 @@
       </c>
       <c r="K351" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L351" s="6" t="inlineStr"/>
@@ -17654,7 +17654,7 @@
       </c>
       <c r="K352" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L352" s="3" t="inlineStr"/>
@@ -17702,7 +17702,7 @@
       </c>
       <c r="K353" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L353" s="6" t="inlineStr"/>
@@ -17750,7 +17750,7 @@
       </c>
       <c r="K354" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L354" s="3" t="inlineStr"/>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="K355" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L355" s="6" t="inlineStr"/>
@@ -17846,7 +17846,7 @@
       </c>
       <c r="K356" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L356" s="3" t="inlineStr"/>
@@ -17894,7 +17894,7 @@
       </c>
       <c r="K357" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L357" s="6" t="inlineStr"/>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="K358" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L358" s="3" t="inlineStr"/>
@@ -17990,7 +17990,7 @@
       </c>
       <c r="K359" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L359" s="6" t="inlineStr"/>
@@ -18038,7 +18038,7 @@
       </c>
       <c r="K360" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L360" s="3" t="inlineStr"/>
@@ -18086,7 +18086,7 @@
       </c>
       <c r="K361" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L361" s="6" t="inlineStr"/>
@@ -18134,7 +18134,7 @@
       </c>
       <c r="K362" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L362" s="3" t="inlineStr"/>
@@ -18182,7 +18182,7 @@
       </c>
       <c r="K363" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L363" s="6" t="inlineStr"/>
@@ -18230,7 +18230,7 @@
       </c>
       <c r="K364" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L364" s="3" t="inlineStr"/>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="K365" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L365" s="6" t="inlineStr"/>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="K366" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L366" s="3" t="inlineStr"/>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="K367" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L367" s="6" t="inlineStr"/>
@@ -18422,7 +18422,7 @@
       </c>
       <c r="K368" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L368" s="3" t="inlineStr"/>
@@ -18470,7 +18470,7 @@
       </c>
       <c r="K369" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L369" s="6" t="inlineStr"/>
@@ -18518,7 +18518,7 @@
       </c>
       <c r="K370" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L370" s="3" t="inlineStr"/>
@@ -18566,7 +18566,7 @@
       </c>
       <c r="K371" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L371" s="6" t="inlineStr"/>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="K372" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L372" s="3" t="inlineStr"/>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="K373" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L373" s="6" t="inlineStr"/>
@@ -18710,7 +18710,7 @@
       </c>
       <c r="K374" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L374" s="3" t="inlineStr"/>
@@ -18758,7 +18758,7 @@
       </c>
       <c r="K375" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L375" s="6" t="inlineStr"/>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="K376" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L376" s="3" t="inlineStr"/>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="K377" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L377" s="6" t="inlineStr"/>
@@ -18902,7 +18902,7 @@
       </c>
       <c r="K378" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L378" s="3" t="inlineStr"/>
@@ -18950,7 +18950,7 @@
       </c>
       <c r="K379" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L379" s="6" t="inlineStr"/>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="K380" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L380" s="3" t="inlineStr"/>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="K381" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L381" s="6" t="inlineStr"/>
@@ -19094,7 +19094,7 @@
       </c>
       <c r="K382" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L382" s="3" t="inlineStr"/>
@@ -19142,7 +19142,7 @@
       </c>
       <c r="K383" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L383" s="6" t="inlineStr"/>
@@ -19190,7 +19190,7 @@
       </c>
       <c r="K384" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L384" s="3" t="inlineStr"/>
@@ -19238,7 +19238,7 @@
       </c>
       <c r="K385" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L385" s="6" t="inlineStr"/>
@@ -19286,7 +19286,7 @@
       </c>
       <c r="K386" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L386" s="3" t="inlineStr"/>
@@ -19334,7 +19334,7 @@
       </c>
       <c r="K387" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L387" s="6" t="inlineStr"/>
@@ -19382,7 +19382,7 @@
       </c>
       <c r="K388" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L388" s="3" t="inlineStr"/>
@@ -19430,7 +19430,7 @@
       </c>
       <c r="K389" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L389" s="6" t="inlineStr"/>
@@ -19478,7 +19478,7 @@
       </c>
       <c r="K390" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L390" s="3" t="inlineStr"/>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="K391" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L391" s="6" t="inlineStr"/>
@@ -19574,7 +19574,7 @@
       </c>
       <c r="K392" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L392" s="3" t="inlineStr"/>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="K393" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L393" s="6" t="inlineStr"/>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="K394" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L394" s="3" t="inlineStr"/>
@@ -19718,7 +19718,7 @@
       </c>
       <c r="K395" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L395" s="6" t="inlineStr"/>
@@ -19766,7 +19766,7 @@
       </c>
       <c r="K396" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L396" s="3" t="inlineStr"/>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="K397" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L397" s="6" t="inlineStr"/>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="K398" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L398" s="3" t="inlineStr"/>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="K399" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L399" s="6" t="inlineStr"/>
@@ -19958,7 +19958,7 @@
       </c>
       <c r="K400" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L400" s="3" t="inlineStr"/>
@@ -20006,7 +20006,7 @@
       </c>
       <c r="K401" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L401" s="6" t="inlineStr"/>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="K402" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L402" s="3" t="inlineStr"/>
@@ -20102,7 +20102,7 @@
       </c>
       <c r="K403" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L403" s="6" t="inlineStr"/>
@@ -20150,7 +20150,7 @@
       </c>
       <c r="K404" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L404" s="3" t="inlineStr"/>
@@ -20198,7 +20198,7 @@
       </c>
       <c r="K405" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L405" s="6" t="inlineStr"/>
@@ -20246,7 +20246,7 @@
       </c>
       <c r="K406" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L406" s="3" t="inlineStr"/>
@@ -20294,7 +20294,7 @@
       </c>
       <c r="K407" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L407" s="6" t="inlineStr"/>
@@ -20342,7 +20342,7 @@
       </c>
       <c r="K408" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L408" s="3" t="inlineStr"/>
@@ -20390,7 +20390,7 @@
       </c>
       <c r="K409" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L409" s="6" t="inlineStr"/>
@@ -20438,7 +20438,7 @@
       </c>
       <c r="K410" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L410" s="3" t="inlineStr"/>
@@ -20486,7 +20486,7 @@
       </c>
       <c r="K411" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L411" s="6" t="inlineStr"/>
@@ -20534,7 +20534,7 @@
       </c>
       <c r="K412" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L412" s="3" t="inlineStr"/>
@@ -20582,7 +20582,7 @@
       </c>
       <c r="K413" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L413" s="6" t="inlineStr"/>
@@ -20630,7 +20630,7 @@
       </c>
       <c r="K414" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L414" s="3" t="inlineStr"/>
@@ -20678,7 +20678,7 @@
       </c>
       <c r="K415" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L415" s="6" t="inlineStr"/>
@@ -20726,7 +20726,7 @@
       </c>
       <c r="K416" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L416" s="3" t="inlineStr"/>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="K417" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L417" s="6" t="inlineStr"/>
@@ -20822,7 +20822,7 @@
       </c>
       <c r="K418" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L418" s="3" t="inlineStr"/>
@@ -20870,7 +20870,7 @@
       </c>
       <c r="K419" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L419" s="6" t="inlineStr"/>
@@ -20918,7 +20918,7 @@
       </c>
       <c r="K420" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L420" s="3" t="inlineStr"/>
@@ -20966,7 +20966,7 @@
       </c>
       <c r="K421" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L421" s="6" t="inlineStr"/>
@@ -21014,7 +21014,7 @@
       </c>
       <c r="K422" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L422" s="3" t="inlineStr"/>
@@ -21062,7 +21062,7 @@
       </c>
       <c r="K423" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L423" s="6" t="inlineStr"/>
@@ -21110,7 +21110,7 @@
       </c>
       <c r="K424" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L424" s="3" t="inlineStr"/>
@@ -21158,7 +21158,7 @@
       </c>
       <c r="K425" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L425" s="6" t="inlineStr"/>
@@ -21206,7 +21206,7 @@
       </c>
       <c r="K426" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L426" s="3" t="inlineStr"/>
@@ -21254,7 +21254,7 @@
       </c>
       <c r="K427" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L427" s="6" t="inlineStr"/>
@@ -21302,7 +21302,7 @@
       </c>
       <c r="K428" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L428" s="3" t="inlineStr"/>
@@ -21350,7 +21350,7 @@
       </c>
       <c r="K429" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L429" s="6" t="inlineStr"/>
@@ -21398,7 +21398,7 @@
       </c>
       <c r="K430" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L430" s="3" t="inlineStr"/>
@@ -21446,7 +21446,7 @@
       </c>
       <c r="K431" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L431" s="6" t="inlineStr"/>
@@ -21494,7 +21494,7 @@
       </c>
       <c r="K432" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L432" s="3" t="inlineStr"/>
@@ -21542,7 +21542,7 @@
       </c>
       <c r="K433" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L433" s="6" t="inlineStr"/>
@@ -21590,7 +21590,7 @@
       </c>
       <c r="K434" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L434" s="3" t="inlineStr"/>
@@ -21638,7 +21638,7 @@
       </c>
       <c r="K435" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L435" s="6" t="inlineStr"/>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="K436" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L436" s="3" t="inlineStr"/>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="K437" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L437" s="6" t="inlineStr"/>
@@ -21782,7 +21782,7 @@
       </c>
       <c r="K438" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L438" s="3" t="inlineStr"/>
@@ -21830,7 +21830,7 @@
       </c>
       <c r="K439" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L439" s="6" t="inlineStr"/>
@@ -21878,7 +21878,7 @@
       </c>
       <c r="K440" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L440" s="3" t="inlineStr"/>
@@ -21926,7 +21926,7 @@
       </c>
       <c r="K441" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L441" s="6" t="inlineStr"/>
@@ -21974,7 +21974,7 @@
       </c>
       <c r="K442" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L442" s="3" t="inlineStr"/>
@@ -22022,7 +22022,7 @@
       </c>
       <c r="K443" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L443" s="6" t="inlineStr"/>
@@ -22070,7 +22070,7 @@
       </c>
       <c r="K444" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L444" s="3" t="inlineStr"/>
@@ -22118,7 +22118,7 @@
       </c>
       <c r="K445" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L445" s="6" t="inlineStr"/>
@@ -22166,7 +22166,7 @@
       </c>
       <c r="K446" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L446" s="3" t="inlineStr"/>
@@ -22214,7 +22214,7 @@
       </c>
       <c r="K447" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L447" s="6" t="inlineStr"/>
@@ -22262,7 +22262,7 @@
       </c>
       <c r="K448" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L448" s="3" t="inlineStr"/>
@@ -22310,7 +22310,7 @@
       </c>
       <c r="K449" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L449" s="6" t="inlineStr"/>
@@ -22358,7 +22358,7 @@
       </c>
       <c r="K450" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L450" s="3" t="inlineStr"/>
@@ -22406,7 +22406,7 @@
       </c>
       <c r="K451" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L451" s="6" t="inlineStr"/>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="K452" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L452" s="3" t="inlineStr"/>
@@ -22502,7 +22502,7 @@
       </c>
       <c r="K453" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L453" s="6" t="inlineStr"/>
@@ -22550,7 +22550,7 @@
       </c>
       <c r="K454" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L454" s="3" t="inlineStr"/>
@@ -22598,7 +22598,7 @@
       </c>
       <c r="K455" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L455" s="6" t="inlineStr"/>
@@ -22646,7 +22646,7 @@
       </c>
       <c r="K456" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L456" s="3" t="inlineStr"/>
@@ -22694,7 +22694,7 @@
       </c>
       <c r="K457" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L457" s="6" t="inlineStr"/>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="K458" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L458" s="3" t="inlineStr"/>
@@ -22790,7 +22790,7 @@
       </c>
       <c r="K459" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L459" s="6" t="inlineStr"/>
@@ -22838,7 +22838,7 @@
       </c>
       <c r="K460" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L460" s="3" t="inlineStr"/>
@@ -22886,7 +22886,7 @@
       </c>
       <c r="K461" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L461" s="6" t="inlineStr"/>
@@ -22934,7 +22934,7 @@
       </c>
       <c r="K462" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L462" s="3" t="inlineStr"/>
@@ -22982,7 +22982,7 @@
       </c>
       <c r="K463" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L463" s="6" t="inlineStr"/>
@@ -23030,7 +23030,7 @@
       </c>
       <c r="K464" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L464" s="3" t="inlineStr"/>
@@ -23078,7 +23078,7 @@
       </c>
       <c r="K465" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L465" s="6" t="inlineStr"/>
@@ -23126,7 +23126,7 @@
       </c>
       <c r="K466" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L466" s="3" t="inlineStr"/>
@@ -23174,7 +23174,7 @@
       </c>
       <c r="K467" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L467" s="6" t="inlineStr"/>
@@ -23222,7 +23222,7 @@
       </c>
       <c r="K468" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L468" s="3" t="inlineStr"/>
@@ -23270,7 +23270,7 @@
       </c>
       <c r="K469" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L469" s="6" t="inlineStr"/>
@@ -23318,7 +23318,7 @@
       </c>
       <c r="K470" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L470" s="3" t="inlineStr"/>
@@ -23366,7 +23366,7 @@
       </c>
       <c r="K471" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L471" s="6" t="inlineStr"/>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="K472" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L472" s="3" t="inlineStr"/>
@@ -23462,7 +23462,7 @@
       </c>
       <c r="K473" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L473" s="6" t="inlineStr"/>
@@ -23510,7 +23510,7 @@
       </c>
       <c r="K474" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L474" s="3" t="inlineStr"/>
@@ -23558,7 +23558,7 @@
       </c>
       <c r="K475" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L475" s="6" t="inlineStr"/>
@@ -23606,7 +23606,7 @@
       </c>
       <c r="K476" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L476" s="3" t="inlineStr"/>
@@ -23654,7 +23654,7 @@
       </c>
       <c r="K477" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L477" s="6" t="inlineStr"/>
@@ -23702,7 +23702,7 @@
       </c>
       <c r="K478" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L478" s="3" t="inlineStr"/>
@@ -23750,7 +23750,7 @@
       </c>
       <c r="K479" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L479" s="6" t="inlineStr"/>
@@ -23798,7 +23798,7 @@
       </c>
       <c r="K480" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L480" s="3" t="inlineStr"/>
@@ -23846,7 +23846,7 @@
       </c>
       <c r="K481" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L481" s="6" t="inlineStr"/>
@@ -23894,7 +23894,7 @@
       </c>
       <c r="K482" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L482" s="3" t="inlineStr"/>
@@ -23942,7 +23942,7 @@
       </c>
       <c r="K483" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L483" s="6" t="inlineStr"/>
@@ -23990,7 +23990,7 @@
       </c>
       <c r="K484" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L484" s="3" t="inlineStr"/>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="K485" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L485" s="6" t="inlineStr"/>
@@ -24086,7 +24086,7 @@
       </c>
       <c r="K486" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L486" s="3" t="inlineStr"/>
@@ -24134,7 +24134,7 @@
       </c>
       <c r="K487" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L487" s="6" t="inlineStr"/>
@@ -24182,7 +24182,7 @@
       </c>
       <c r="K488" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L488" s="3" t="inlineStr"/>
@@ -24230,7 +24230,7 @@
       </c>
       <c r="K489" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L489" s="6" t="inlineStr"/>
@@ -24278,7 +24278,7 @@
       </c>
       <c r="K490" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L490" s="3" t="inlineStr"/>
@@ -24326,7 +24326,7 @@
       </c>
       <c r="K491" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L491" s="6" t="inlineStr"/>
@@ -24374,7 +24374,7 @@
       </c>
       <c r="K492" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L492" s="3" t="inlineStr"/>
@@ -24422,7 +24422,7 @@
       </c>
       <c r="K493" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L493" s="6" t="inlineStr"/>
@@ -24470,7 +24470,7 @@
       </c>
       <c r="K494" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L494" s="3" t="inlineStr"/>
@@ -24518,7 +24518,7 @@
       </c>
       <c r="K495" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L495" s="6" t="inlineStr"/>
@@ -24566,7 +24566,7 @@
       </c>
       <c r="K496" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L496" s="3" t="inlineStr"/>
@@ -24614,7 +24614,7 @@
       </c>
       <c r="K497" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L497" s="6" t="inlineStr"/>
@@ -24662,7 +24662,7 @@
       </c>
       <c r="K498" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L498" s="3" t="inlineStr"/>
@@ -24710,7 +24710,7 @@
       </c>
       <c r="K499" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L499" s="6" t="inlineStr"/>
@@ -24758,7 +24758,7 @@
       </c>
       <c r="K500" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L500" s="3" t="inlineStr"/>
@@ -24806,7 +24806,7 @@
       </c>
       <c r="K501" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L501" s="6" t="inlineStr"/>
@@ -24854,7 +24854,7 @@
       </c>
       <c r="K502" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L502" s="3" t="inlineStr"/>
@@ -24902,7 +24902,7 @@
       </c>
       <c r="K503" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L503" s="6" t="inlineStr"/>
@@ -24950,7 +24950,7 @@
       </c>
       <c r="K504" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L504" s="3" t="inlineStr"/>
@@ -24998,7 +24998,7 @@
       </c>
       <c r="K505" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L505" s="6" t="inlineStr"/>
@@ -25046,7 +25046,7 @@
       </c>
       <c r="K506" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L506" s="3" t="inlineStr"/>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="K507" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L507" s="6" t="inlineStr"/>
@@ -25142,7 +25142,7 @@
       </c>
       <c r="K508" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L508" s="3" t="inlineStr"/>
@@ -25190,7 +25190,7 @@
       </c>
       <c r="K509" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L509" s="6" t="inlineStr"/>
@@ -25238,7 +25238,7 @@
       </c>
       <c r="K510" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L510" s="3" t="inlineStr"/>
@@ -25286,7 +25286,7 @@
       </c>
       <c r="K511" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L511" s="6" t="inlineStr"/>
@@ -25334,7 +25334,7 @@
       </c>
       <c r="K512" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L512" s="3" t="inlineStr"/>
@@ -25382,7 +25382,7 @@
       </c>
       <c r="K513" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L513" s="6" t="inlineStr"/>
@@ -25430,7 +25430,7 @@
       </c>
       <c r="K514" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L514" s="3" t="inlineStr"/>
@@ -25478,7 +25478,7 @@
       </c>
       <c r="K515" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L515" s="6" t="inlineStr"/>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="K516" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L516" s="3" t="inlineStr"/>
@@ -25574,7 +25574,7 @@
       </c>
       <c r="K517" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L517" s="6" t="inlineStr"/>
@@ -25622,7 +25622,7 @@
       </c>
       <c r="K518" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L518" s="3" t="inlineStr"/>
@@ -25670,7 +25670,7 @@
       </c>
       <c r="K519" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L519" s="6" t="inlineStr"/>
@@ -25718,7 +25718,7 @@
       </c>
       <c r="K520" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L520" s="3" t="inlineStr"/>
@@ -25766,7 +25766,7 @@
       </c>
       <c r="K521" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L521" s="6" t="inlineStr"/>
@@ -25814,7 +25814,7 @@
       </c>
       <c r="K522" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L522" s="3" t="inlineStr"/>
@@ -25862,7 +25862,7 @@
       </c>
       <c r="K523" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L523" s="6" t="inlineStr"/>
@@ -25910,7 +25910,7 @@
       </c>
       <c r="K524" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L524" s="3" t="inlineStr"/>
@@ -25958,7 +25958,7 @@
       </c>
       <c r="K525" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L525" s="6" t="inlineStr"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K526" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L526" s="3" t="inlineStr"/>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="K527" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L527" s="6" t="inlineStr"/>
@@ -26102,7 +26102,7 @@
       </c>
       <c r="K528" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L528" s="3" t="inlineStr"/>
@@ -26150,7 +26150,7 @@
       </c>
       <c r="K529" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L529" s="6" t="inlineStr"/>
@@ -26198,7 +26198,7 @@
       </c>
       <c r="K530" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L530" s="3" t="inlineStr"/>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="K531" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L531" s="6" t="inlineStr"/>
@@ -26294,7 +26294,7 @@
       </c>
       <c r="K532" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L532" s="3" t="inlineStr"/>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="K533" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L533" s="6" t="inlineStr"/>
@@ -26390,7 +26390,7 @@
       </c>
       <c r="K534" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L534" s="3" t="inlineStr"/>
@@ -26438,7 +26438,7 @@
       </c>
       <c r="K535" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L535" s="6" t="inlineStr"/>
@@ -26486,7 +26486,7 @@
       </c>
       <c r="K536" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L536" s="3" t="inlineStr"/>
@@ -26534,7 +26534,7 @@
       </c>
       <c r="K537" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L537" s="6" t="inlineStr"/>
@@ -26582,7 +26582,7 @@
       </c>
       <c r="K538" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L538" s="3" t="inlineStr"/>
@@ -26630,7 +26630,7 @@
       </c>
       <c r="K539" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L539" s="6" t="inlineStr"/>
@@ -26678,7 +26678,7 @@
       </c>
       <c r="K540" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L540" s="3" t="inlineStr"/>
@@ -26726,7 +26726,7 @@
       </c>
       <c r="K541" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L541" s="6" t="inlineStr"/>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="K542" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L542" s="3" t="inlineStr"/>
@@ -26822,7 +26822,7 @@
       </c>
       <c r="K543" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L543" s="6" t="inlineStr"/>
@@ -26870,7 +26870,7 @@
       </c>
       <c r="K544" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L544" s="3" t="inlineStr"/>
@@ -26918,7 +26918,7 @@
       </c>
       <c r="K545" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L545" s="6" t="inlineStr"/>
@@ -26966,7 +26966,7 @@
       </c>
       <c r="K546" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L546" s="3" t="inlineStr"/>
@@ -27014,7 +27014,7 @@
       </c>
       <c r="K547" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L547" s="6" t="inlineStr"/>
@@ -27062,7 +27062,7 @@
       </c>
       <c r="K548" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L548" s="3" t="inlineStr"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K549" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L549" s="6" t="inlineStr"/>
@@ -27158,7 +27158,7 @@
       </c>
       <c r="K550" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L550" s="3" t="inlineStr"/>
@@ -27206,7 +27206,7 @@
       </c>
       <c r="K551" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L551" s="6" t="inlineStr"/>
@@ -27254,7 +27254,7 @@
       </c>
       <c r="K552" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L552" s="3" t="inlineStr"/>
@@ -27302,7 +27302,7 @@
       </c>
       <c r="K553" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L553" s="6" t="inlineStr"/>
@@ -27350,7 +27350,7 @@
       </c>
       <c r="K554" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L554" s="3" t="inlineStr"/>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="K555" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L555" s="6" t="inlineStr"/>
@@ -27446,7 +27446,7 @@
       </c>
       <c r="K556" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L556" s="3" t="inlineStr"/>
@@ -27494,7 +27494,7 @@
       </c>
       <c r="K557" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L557" s="6" t="inlineStr"/>
@@ -27542,7 +27542,7 @@
       </c>
       <c r="K558" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L558" s="3" t="inlineStr"/>
@@ -27590,7 +27590,7 @@
       </c>
       <c r="K559" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L559" s="6" t="inlineStr"/>
@@ -27638,7 +27638,7 @@
       </c>
       <c r="K560" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L560" s="3" t="inlineStr"/>
@@ -27686,7 +27686,7 @@
       </c>
       <c r="K561" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L561" s="6" t="inlineStr"/>
@@ -27734,7 +27734,7 @@
       </c>
       <c r="K562" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L562" s="3" t="inlineStr"/>
@@ -27782,7 +27782,7 @@
       </c>
       <c r="K563" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L563" s="6" t="inlineStr"/>
@@ -27830,7 +27830,7 @@
       </c>
       <c r="K564" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L564" s="3" t="inlineStr"/>
@@ -27878,7 +27878,7 @@
       </c>
       <c r="K565" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L565" s="6" t="inlineStr"/>
@@ -27926,7 +27926,7 @@
       </c>
       <c r="K566" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L566" s="3" t="inlineStr"/>
@@ -27974,7 +27974,7 @@
       </c>
       <c r="K567" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L567" s="6" t="inlineStr"/>
@@ -28022,7 +28022,7 @@
       </c>
       <c r="K568" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L568" s="3" t="inlineStr"/>
@@ -28070,7 +28070,7 @@
       </c>
       <c r="K569" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L569" s="6" t="inlineStr"/>
@@ -28118,7 +28118,7 @@
       </c>
       <c r="K570" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L570" s="3" t="inlineStr"/>
@@ -28166,7 +28166,7 @@
       </c>
       <c r="K571" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L571" s="6" t="inlineStr"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K572" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L572" s="3" t="inlineStr"/>
@@ -28262,7 +28262,7 @@
       </c>
       <c r="K573" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L573" s="6" t="inlineStr"/>
@@ -28310,7 +28310,7 @@
       </c>
       <c r="K574" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L574" s="3" t="inlineStr"/>
@@ -28358,7 +28358,7 @@
       </c>
       <c r="K575" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L575" s="6" t="inlineStr"/>
@@ -28406,7 +28406,7 @@
       </c>
       <c r="K576" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L576" s="3" t="inlineStr"/>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="K577" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L577" s="6" t="inlineStr"/>
@@ -28502,7 +28502,7 @@
       </c>
       <c r="K578" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L578" s="3" t="inlineStr"/>
@@ -28550,7 +28550,7 @@
       </c>
       <c r="K579" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L579" s="6" t="inlineStr"/>
@@ -28598,7 +28598,7 @@
       </c>
       <c r="K580" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L580" s="3" t="inlineStr"/>
@@ -28646,7 +28646,7 @@
       </c>
       <c r="K581" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L581" s="6" t="inlineStr"/>
@@ -28694,7 +28694,7 @@
       </c>
       <c r="K582" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L582" s="3" t="inlineStr"/>
@@ -28742,7 +28742,7 @@
       </c>
       <c r="K583" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L583" s="6" t="inlineStr"/>
@@ -28790,7 +28790,7 @@
       </c>
       <c r="K584" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L584" s="3" t="inlineStr"/>
@@ -28838,7 +28838,7 @@
       </c>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L585" s="6" t="inlineStr"/>
@@ -28886,7 +28886,7 @@
       </c>
       <c r="K586" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L586" s="3" t="inlineStr"/>
@@ -28934,7 +28934,7 @@
       </c>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L587" s="6" t="inlineStr"/>
@@ -28982,7 +28982,7 @@
       </c>
       <c r="K588" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L588" s="3" t="inlineStr"/>
@@ -29030,7 +29030,7 @@
       </c>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L589" s="6" t="inlineStr"/>
@@ -29078,7 +29078,7 @@
       </c>
       <c r="K590" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L590" s="3" t="inlineStr"/>
@@ -29126,7 +29126,7 @@
       </c>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L591" s="6" t="inlineStr"/>
@@ -29174,7 +29174,7 @@
       </c>
       <c r="K592" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L592" s="3" t="inlineStr"/>
@@ -29222,7 +29222,7 @@
       </c>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L593" s="6" t="inlineStr"/>
@@ -29270,7 +29270,7 @@
       </c>
       <c r="K594" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L594" s="3" t="inlineStr"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L595" s="6" t="inlineStr"/>
@@ -29366,7 +29366,7 @@
       </c>
       <c r="K596" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L596" s="3" t="inlineStr"/>
@@ -29414,7 +29414,7 @@
       </c>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L597" s="6" t="inlineStr"/>
@@ -29462,7 +29462,7 @@
       </c>
       <c r="K598" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L598" s="3" t="inlineStr"/>
@@ -29510,7 +29510,7 @@
       </c>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L599" s="6" t="inlineStr"/>
@@ -29558,7 +29558,7 @@
       </c>
       <c r="K600" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L600" s="3" t="inlineStr"/>
@@ -29606,7 +29606,7 @@
       </c>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L601" s="6" t="inlineStr"/>
@@ -29654,7 +29654,7 @@
       </c>
       <c r="K602" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L602" s="3" t="inlineStr"/>
@@ -29702,7 +29702,7 @@
       </c>
       <c r="K603" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L603" s="6" t="inlineStr"/>
@@ -29750,7 +29750,7 @@
       </c>
       <c r="K604" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L604" s="3" t="inlineStr"/>
@@ -29798,7 +29798,7 @@
       </c>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr"/>
@@ -29846,7 +29846,7 @@
       </c>
       <c r="K606" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L606" s="3" t="inlineStr"/>
@@ -29894,7 +29894,7 @@
       </c>
       <c r="K607" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L607" s="6" t="inlineStr"/>
@@ -29942,7 +29942,7 @@
       </c>
       <c r="K608" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L608" s="3" t="inlineStr"/>
@@ -29990,7 +29990,7 @@
       </c>
       <c r="K609" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L609" s="6" t="inlineStr"/>
@@ -30038,7 +30038,7 @@
       </c>
       <c r="K610" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L610" s="3" t="inlineStr"/>
@@ -30086,7 +30086,7 @@
       </c>
       <c r="K611" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L611" s="6" t="inlineStr"/>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="K612" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L612" s="3" t="inlineStr"/>
@@ -30182,7 +30182,7 @@
       </c>
       <c r="K613" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L613" s="6" t="inlineStr"/>
@@ -30230,7 +30230,7 @@
       </c>
       <c r="K614" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L614" s="3" t="inlineStr"/>
@@ -30278,7 +30278,7 @@
       </c>
       <c r="K615" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L615" s="6" t="inlineStr"/>
@@ -30326,7 +30326,7 @@
       </c>
       <c r="K616" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L616" s="3" t="inlineStr"/>
@@ -30374,7 +30374,7 @@
       </c>
       <c r="K617" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L617" s="6" t="inlineStr"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K618" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L618" s="3" t="inlineStr"/>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="K619" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L619" s="6" t="inlineStr"/>
@@ -30518,7 +30518,7 @@
       </c>
       <c r="K620" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L620" s="3" t="inlineStr"/>
@@ -30566,7 +30566,7 @@
       </c>
       <c r="K621" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L621" s="6" t="inlineStr"/>
@@ -30614,7 +30614,7 @@
       </c>
       <c r="K622" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L622" s="3" t="inlineStr"/>
@@ -30662,7 +30662,7 @@
       </c>
       <c r="K623" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L623" s="6" t="inlineStr"/>
@@ -30710,7 +30710,7 @@
       </c>
       <c r="K624" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L624" s="3" t="inlineStr"/>
@@ -30758,7 +30758,7 @@
       </c>
       <c r="K625" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L625" s="6" t="inlineStr"/>
@@ -30806,7 +30806,7 @@
       </c>
       <c r="K626" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L626" s="3" t="inlineStr"/>
@@ -30854,7 +30854,7 @@
       </c>
       <c r="K627" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L627" s="6" t="inlineStr"/>
@@ -30902,7 +30902,7 @@
       </c>
       <c r="K628" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L628" s="3" t="inlineStr"/>
@@ -30950,7 +30950,7 @@
       </c>
       <c r="K629" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L629" s="6" t="inlineStr"/>
@@ -30998,7 +30998,7 @@
       </c>
       <c r="K630" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L630" s="3" t="inlineStr"/>
@@ -31046,7 +31046,7 @@
       </c>
       <c r="K631" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L631" s="6" t="inlineStr"/>
@@ -31094,7 +31094,7 @@
       </c>
       <c r="K632" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L632" s="3" t="inlineStr"/>
@@ -31142,7 +31142,7 @@
       </c>
       <c r="K633" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L633" s="6" t="inlineStr"/>
@@ -31190,7 +31190,7 @@
       </c>
       <c r="K634" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L634" s="3" t="inlineStr"/>
@@ -31238,7 +31238,7 @@
       </c>
       <c r="K635" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L635" s="6" t="inlineStr"/>
@@ -31286,7 +31286,7 @@
       </c>
       <c r="K636" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L636" s="3" t="inlineStr"/>
@@ -31334,7 +31334,7 @@
       </c>
       <c r="K637" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L637" s="6" t="inlineStr"/>
@@ -31382,7 +31382,7 @@
       </c>
       <c r="K638" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L638" s="3" t="inlineStr"/>
@@ -31430,7 +31430,7 @@
       </c>
       <c r="K639" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L639" s="6" t="inlineStr"/>
@@ -31478,7 +31478,7 @@
       </c>
       <c r="K640" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L640" s="3" t="inlineStr"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K641" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L641" s="6" t="inlineStr"/>
@@ -31574,7 +31574,7 @@
       </c>
       <c r="K642" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L642" s="3" t="inlineStr"/>
@@ -31622,7 +31622,7 @@
       </c>
       <c r="K643" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L643" s="6" t="inlineStr"/>
@@ -31670,7 +31670,7 @@
       </c>
       <c r="K644" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L644" s="3" t="inlineStr"/>
@@ -31718,7 +31718,7 @@
       </c>
       <c r="K645" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L645" s="6" t="inlineStr"/>
@@ -31766,7 +31766,7 @@
       </c>
       <c r="K646" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L646" s="3" t="inlineStr"/>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="K647" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L647" s="6" t="inlineStr"/>
@@ -31862,7 +31862,7 @@
       </c>
       <c r="K648" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L648" s="3" t="inlineStr"/>
@@ -31910,7 +31910,7 @@
       </c>
       <c r="K649" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L649" s="6" t="inlineStr"/>
@@ -31958,7 +31958,7 @@
       </c>
       <c r="K650" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L650" s="3" t="inlineStr"/>
@@ -32006,7 +32006,7 @@
       </c>
       <c r="K651" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L651" s="6" t="inlineStr"/>
@@ -32054,7 +32054,7 @@
       </c>
       <c r="K652" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L652" s="3" t="inlineStr"/>
@@ -32102,7 +32102,7 @@
       </c>
       <c r="K653" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L653" s="6" t="inlineStr"/>
@@ -32150,7 +32150,7 @@
       </c>
       <c r="K654" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L654" s="3" t="inlineStr"/>
@@ -32198,7 +32198,7 @@
       </c>
       <c r="K655" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L655" s="6" t="inlineStr"/>
@@ -32246,7 +32246,7 @@
       </c>
       <c r="K656" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L656" s="3" t="inlineStr"/>
@@ -32294,7 +32294,7 @@
       </c>
       <c r="K657" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L657" s="6" t="inlineStr"/>
@@ -32342,7 +32342,7 @@
       </c>
       <c r="K658" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L658" s="3" t="inlineStr"/>
@@ -32390,7 +32390,7 @@
       </c>
       <c r="K659" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L659" s="6" t="inlineStr"/>
@@ -32438,7 +32438,7 @@
       </c>
       <c r="K660" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L660" s="3" t="inlineStr"/>
@@ -32486,7 +32486,7 @@
       </c>
       <c r="K661" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L661" s="6" t="inlineStr"/>
@@ -32534,7 +32534,7 @@
       </c>
       <c r="K662" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L662" s="3" t="inlineStr"/>
@@ -32582,7 +32582,7 @@
       </c>
       <c r="K663" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L663" s="6" t="inlineStr"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K664" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L664" s="3" t="inlineStr"/>
@@ -32678,7 +32678,7 @@
       </c>
       <c r="K665" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L665" s="6" t="inlineStr"/>
@@ -32726,7 +32726,7 @@
       </c>
       <c r="K666" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L666" s="3" t="inlineStr"/>
@@ -32774,7 +32774,7 @@
       </c>
       <c r="K667" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L667" s="6" t="inlineStr"/>
@@ -32822,7 +32822,7 @@
       </c>
       <c r="K668" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L668" s="3" t="inlineStr"/>
@@ -32870,7 +32870,7 @@
       </c>
       <c r="K669" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L669" s="6" t="inlineStr"/>
@@ -32918,7 +32918,7 @@
       </c>
       <c r="K670" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L670" s="3" t="inlineStr"/>
@@ -32966,7 +32966,7 @@
       </c>
       <c r="K671" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L671" s="6" t="inlineStr"/>
@@ -33014,7 +33014,7 @@
       </c>
       <c r="K672" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L672" s="3" t="inlineStr"/>
@@ -33062,7 +33062,7 @@
       </c>
       <c r="K673" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L673" s="6" t="inlineStr"/>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="K674" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L674" s="3" t="inlineStr"/>
@@ -33158,7 +33158,7 @@
       </c>
       <c r="K675" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L675" s="6" t="inlineStr"/>
@@ -33206,7 +33206,7 @@
       </c>
       <c r="K676" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L676" s="3" t="inlineStr"/>
@@ -33254,7 +33254,7 @@
       </c>
       <c r="K677" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L677" s="6" t="inlineStr"/>
@@ -33302,7 +33302,7 @@
       </c>
       <c r="K678" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L678" s="3" t="inlineStr"/>
@@ -33350,7 +33350,7 @@
       </c>
       <c r="K679" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L679" s="6" t="inlineStr"/>
@@ -33398,7 +33398,7 @@
       </c>
       <c r="K680" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L680" s="3" t="inlineStr"/>
@@ -33446,7 +33446,7 @@
       </c>
       <c r="K681" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L681" s="6" t="inlineStr"/>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="K682" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L682" s="3" t="inlineStr"/>
@@ -33542,7 +33542,7 @@
       </c>
       <c r="K683" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L683" s="6" t="inlineStr"/>
@@ -33590,7 +33590,7 @@
       </c>
       <c r="K684" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L684" s="3" t="inlineStr"/>
@@ -33638,7 +33638,7 @@
       </c>
       <c r="K685" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L685" s="6" t="inlineStr"/>
@@ -33686,7 +33686,7 @@
       </c>
       <c r="K686" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L686" s="3" t="inlineStr"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K687" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L687" s="6" t="inlineStr"/>
@@ -33782,7 +33782,7 @@
       </c>
       <c r="K688" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L688" s="3" t="inlineStr"/>
@@ -33830,7 +33830,7 @@
       </c>
       <c r="K689" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L689" s="6" t="inlineStr"/>
@@ -33878,7 +33878,7 @@
       </c>
       <c r="K690" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L690" s="3" t="inlineStr"/>
@@ -33926,7 +33926,7 @@
       </c>
       <c r="K691" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L691" s="6" t="inlineStr"/>
@@ -33974,7 +33974,7 @@
       </c>
       <c r="K692" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L692" s="3" t="inlineStr"/>
@@ -34022,7 +34022,7 @@
       </c>
       <c r="K693" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L693" s="6" t="inlineStr"/>
@@ -34070,7 +34070,7 @@
       </c>
       <c r="K694" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L694" s="3" t="inlineStr"/>
@@ -34118,7 +34118,7 @@
       </c>
       <c r="K695" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L695" s="6" t="inlineStr"/>
@@ -34166,7 +34166,7 @@
       </c>
       <c r="K696" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L696" s="3" t="inlineStr"/>
@@ -34214,7 +34214,7 @@
       </c>
       <c r="K697" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L697" s="6" t="inlineStr"/>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="K698" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L698" s="3" t="inlineStr"/>
@@ -34310,7 +34310,7 @@
       </c>
       <c r="K699" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L699" s="6" t="inlineStr"/>
@@ -34358,7 +34358,7 @@
       </c>
       <c r="K700" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L700" s="3" t="inlineStr"/>
@@ -34406,7 +34406,7 @@
       </c>
       <c r="K701" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L701" s="6" t="inlineStr"/>
@@ -34454,7 +34454,7 @@
       </c>
       <c r="K702" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L702" s="3" t="inlineStr"/>
@@ -34502,7 +34502,7 @@
       </c>
       <c r="K703" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L703" s="6" t="inlineStr"/>
@@ -34550,7 +34550,7 @@
       </c>
       <c r="K704" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L704" s="3" t="inlineStr"/>
@@ -34598,7 +34598,7 @@
       </c>
       <c r="K705" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L705" s="6" t="inlineStr"/>
@@ -34646,7 +34646,7 @@
       </c>
       <c r="K706" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L706" s="3" t="inlineStr"/>
@@ -34694,7 +34694,7 @@
       </c>
       <c r="K707" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L707" s="6" t="inlineStr"/>
@@ -34742,7 +34742,7 @@
       </c>
       <c r="K708" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L708" s="3" t="inlineStr"/>
@@ -34790,7 +34790,7 @@
       </c>
       <c r="K709" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L709" s="6" t="inlineStr"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K710" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L710" s="3" t="inlineStr"/>
@@ -34886,7 +34886,7 @@
       </c>
       <c r="K711" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L711" s="6" t="inlineStr"/>
@@ -34934,7 +34934,7 @@
       </c>
       <c r="K712" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L712" s="3" t="inlineStr"/>
@@ -34982,7 +34982,7 @@
       </c>
       <c r="K713" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L713" s="6" t="inlineStr"/>
@@ -35030,7 +35030,7 @@
       </c>
       <c r="K714" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L714" s="3" t="inlineStr"/>
@@ -35078,7 +35078,7 @@
       </c>
       <c r="K715" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L715" s="6" t="inlineStr"/>
@@ -35126,7 +35126,7 @@
       </c>
       <c r="K716" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L716" s="3" t="inlineStr"/>
@@ -35174,7 +35174,7 @@
       </c>
       <c r="K717" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L717" s="6" t="inlineStr"/>
@@ -35222,7 +35222,7 @@
       </c>
       <c r="K718" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L718" s="3" t="inlineStr"/>
@@ -35270,7 +35270,7 @@
       </c>
       <c r="K719" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L719" s="6" t="inlineStr"/>
@@ -35318,7 +35318,7 @@
       </c>
       <c r="K720" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L720" s="3" t="inlineStr"/>
@@ -35366,7 +35366,7 @@
       </c>
       <c r="K721" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L721" s="6" t="inlineStr"/>
@@ -35414,7 +35414,7 @@
       </c>
       <c r="K722" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L722" s="3" t="inlineStr"/>
@@ -35462,7 +35462,7 @@
       </c>
       <c r="K723" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L723" s="6" t="inlineStr"/>
@@ -35510,7 +35510,7 @@
       </c>
       <c r="K724" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L724" s="3" t="inlineStr"/>
@@ -35558,7 +35558,7 @@
       </c>
       <c r="K725" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L725" s="6" t="inlineStr"/>
@@ -35606,7 +35606,7 @@
       </c>
       <c r="K726" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L726" s="3" t="inlineStr"/>
@@ -35654,7 +35654,7 @@
       </c>
       <c r="K727" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L727" s="6" t="inlineStr"/>
@@ -35702,7 +35702,7 @@
       </c>
       <c r="K728" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L728" s="3" t="inlineStr"/>
@@ -35750,7 +35750,7 @@
       </c>
       <c r="K729" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L729" s="4" t="inlineStr">
@@ -35802,7 +35802,7 @@
       </c>
       <c r="K730" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L730" s="4" t="inlineStr">
@@ -35854,7 +35854,7 @@
       </c>
       <c r="K731" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L731" s="4" t="inlineStr">
@@ -35906,7 +35906,7 @@
       </c>
       <c r="K732" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L732" s="4" t="inlineStr">
@@ -35958,7 +35958,7 @@
       </c>
       <c r="K733" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L733" s="4" t="inlineStr">
@@ -36010,7 +36010,7 @@
       </c>
       <c r="K734" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L734" s="4" t="inlineStr">
@@ -36062,7 +36062,7 @@
       </c>
       <c r="K735" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L735" s="4" t="inlineStr">
@@ -36114,7 +36114,7 @@
       </c>
       <c r="K736" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L736" s="4" t="inlineStr">
@@ -36166,7 +36166,7 @@
       </c>
       <c r="K737" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L737" s="4" t="inlineStr">
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K738" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L738" s="4" t="inlineStr">
@@ -36270,7 +36270,7 @@
       </c>
       <c r="K739" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L739" s="4" t="inlineStr">
@@ -36322,7 +36322,7 @@
       </c>
       <c r="K740" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L740" s="4" t="inlineStr">
@@ -36374,7 +36374,7 @@
       </c>
       <c r="K741" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L741" s="4" t="inlineStr">
@@ -36426,7 +36426,7 @@
       </c>
       <c r="K742" s="3" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L742" s="4" t="inlineStr">
@@ -36478,7 +36478,7 @@
       </c>
       <c r="K743" s="6" t="inlineStr">
         <is>
-          <t>2026-09-20</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="L743" s="4" t="inlineStr">

--- a/public/loop-library.xlsx
+++ b/public/loop-library.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr"/>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr"/>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr"/>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr"/>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr"/>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr"/>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr"/>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr"/>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr"/>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr"/>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr"/>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr"/>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr"/>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr"/>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr"/>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr"/>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr"/>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr"/>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr"/>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr"/>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L93" s="6" t="inlineStr"/>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr"/>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L95" s="6" t="inlineStr"/>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr"/>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L97" s="6" t="inlineStr"/>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr"/>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr"/>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr"/>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr"/>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L102" s="3" t="inlineStr"/>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L103" s="6" t="inlineStr"/>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L104" s="3" t="inlineStr"/>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L105" s="6" t="inlineStr"/>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L106" s="3" t="inlineStr"/>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L107" s="6" t="inlineStr"/>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L108" s="3" t="inlineStr"/>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L109" s="6" t="inlineStr"/>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L110" s="3" t="inlineStr"/>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L111" s="6" t="inlineStr"/>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L112" s="3" t="inlineStr"/>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L113" s="6" t="inlineStr"/>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L114" s="3" t="inlineStr"/>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L115" s="6" t="inlineStr"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="K116" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L116" s="3" t="inlineStr"/>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L117" s="6" t="inlineStr"/>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="K118" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L118" s="3" t="inlineStr"/>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L119" s="6" t="inlineStr"/>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="K120" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L120" s="3" t="inlineStr"/>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L121" s="6" t="inlineStr"/>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="K122" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L122" s="3" t="inlineStr"/>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L123" s="6" t="inlineStr"/>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="K124" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L124" s="3" t="inlineStr"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="K125" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L125" s="6" t="inlineStr"/>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="K126" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L126" s="3" t="inlineStr"/>
@@ -6854,7 +6854,7 @@
       </c>
       <c r="K127" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L127" s="6" t="inlineStr"/>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L128" s="3" t="inlineStr"/>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="K129" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L129" s="6" t="inlineStr"/>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="K130" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L130" s="3" t="inlineStr"/>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="K131" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L131" s="6" t="inlineStr"/>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L132" s="3" t="inlineStr"/>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="K133" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L133" s="6" t="inlineStr"/>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="K134" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L134" s="3" t="inlineStr"/>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="K135" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L135" s="6" t="inlineStr"/>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="K136" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L136" s="3" t="inlineStr"/>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="K137" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L137" s="6" t="inlineStr"/>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="K138" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L138" s="3" t="inlineStr"/>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="K139" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L139" s="6" t="inlineStr"/>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="K140" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L140" s="3" t="inlineStr"/>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="K141" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L141" s="6" t="inlineStr"/>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L142" s="3" t="inlineStr"/>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="K143" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L143" s="6" t="inlineStr"/>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="K144" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L144" s="3" t="inlineStr"/>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="K145" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L145" s="6" t="inlineStr"/>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="K146" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L146" s="3" t="inlineStr"/>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="K147" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L147" s="6" t="inlineStr"/>
@@ -7862,7 +7862,7 @@
       </c>
       <c r="K148" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L148" s="3" t="inlineStr"/>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="K149" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L149" s="6" t="inlineStr"/>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="K150" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L150" s="3" t="inlineStr"/>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="K151" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L151" s="6" t="inlineStr"/>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="K152" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L152" s="3" t="inlineStr"/>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="K153" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L153" s="6" t="inlineStr"/>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="K154" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L154" s="3" t="inlineStr"/>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="K155" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L155" s="6" t="inlineStr"/>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="K156" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L156" s="3" t="inlineStr"/>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K157" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L157" s="6" t="inlineStr"/>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="K158" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L158" s="3" t="inlineStr"/>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="K159" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L159" s="6" t="inlineStr"/>
@@ -8438,7 +8438,7 @@
       </c>
       <c r="K160" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L160" s="3" t="inlineStr"/>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="K161" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L161" s="6" t="inlineStr"/>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="K162" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L162" s="3" t="inlineStr"/>
@@ -8582,7 +8582,7 @@
       </c>
       <c r="K163" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L163" s="6" t="inlineStr"/>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="K164" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L164" s="3" t="inlineStr"/>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="K165" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L165" s="6" t="inlineStr"/>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="K166" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L166" s="3" t="inlineStr"/>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="K167" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L167" s="6" t="inlineStr"/>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="K168" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L168" s="3" t="inlineStr"/>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="K169" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L169" s="6" t="inlineStr"/>
@@ -8918,7 +8918,7 @@
       </c>
       <c r="K170" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L170" s="3" t="inlineStr"/>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="K171" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L171" s="6" t="inlineStr"/>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="K172" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L172" s="3" t="inlineStr"/>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="K173" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L173" s="6" t="inlineStr"/>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="K174" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L174" s="3" t="inlineStr"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="K175" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L175" s="6" t="inlineStr"/>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="K176" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L176" s="3" t="inlineStr"/>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="K177" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L177" s="6" t="inlineStr"/>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="K178" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L178" s="3" t="inlineStr"/>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="K179" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L179" s="6" t="inlineStr"/>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="K180" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L180" s="3" t="inlineStr"/>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="K181" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L181" s="6" t="inlineStr"/>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="K182" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L182" s="3" t="inlineStr"/>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="K183" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L183" s="6" t="inlineStr"/>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="K184" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L184" s="3" t="inlineStr"/>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="K185" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L185" s="6" t="inlineStr"/>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="K186" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L186" s="3" t="inlineStr"/>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="K187" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L187" s="6" t="inlineStr"/>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="K188" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L188" s="3" t="inlineStr"/>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="K189" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L189" s="6" t="inlineStr"/>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="K190" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L190" s="3" t="inlineStr"/>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="K191" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L191" s="6" t="inlineStr"/>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="K192" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L192" s="3" t="inlineStr"/>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="K193" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L193" s="6" t="inlineStr"/>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="K194" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L194" s="3" t="inlineStr"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="K195" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L195" s="6" t="inlineStr"/>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="K196" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L196" s="3" t="inlineStr"/>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="K197" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L197" s="6" t="inlineStr"/>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="K198" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L198" s="3" t="inlineStr"/>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="K199" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L199" s="6" t="inlineStr"/>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="K200" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L200" s="3" t="inlineStr"/>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="K201" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L201" s="6" t="inlineStr"/>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="K202" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L202" s="3" t="inlineStr"/>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="K203" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L203" s="6" t="inlineStr"/>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="K204" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L204" s="3" t="inlineStr"/>
@@ -10598,7 +10598,7 @@
       </c>
       <c r="K205" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L205" s="6" t="inlineStr"/>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K206" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L206" s="3" t="inlineStr"/>
@@ -10694,7 +10694,7 @@
       </c>
       <c r="K207" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L207" s="6" t="inlineStr"/>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="K208" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L208" s="3" t="inlineStr"/>
@@ -10790,7 +10790,7 @@
       </c>
       <c r="K209" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L209" s="6" t="inlineStr"/>
@@ -10838,7 +10838,7 @@
       </c>
       <c r="K210" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L210" s="3" t="inlineStr"/>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="K211" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L211" s="6" t="inlineStr"/>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="K212" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L212" s="3" t="inlineStr"/>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="K213" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L213" s="6" t="inlineStr"/>
@@ -11030,7 +11030,7 @@
       </c>
       <c r="K214" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L214" s="3" t="inlineStr"/>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="K215" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L215" s="6" t="inlineStr"/>
@@ -11126,7 +11126,7 @@
       </c>
       <c r="K216" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L216" s="3" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="K217" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L217" s="6" t="inlineStr"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="K218" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L218" s="3" t="inlineStr"/>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="K219" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L219" s="6" t="inlineStr"/>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="K220" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L220" s="3" t="inlineStr"/>
@@ -11366,7 +11366,7 @@
       </c>
       <c r="K221" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L221" s="6" t="inlineStr"/>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="K222" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L222" s="3" t="inlineStr"/>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="K223" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L223" s="6" t="inlineStr"/>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="K224" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L224" s="3" t="inlineStr"/>
@@ -11558,7 +11558,7 @@
       </c>
       <c r="K225" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L225" s="6" t="inlineStr"/>
@@ -11606,7 +11606,7 @@
       </c>
       <c r="K226" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L226" s="3" t="inlineStr"/>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="K227" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L227" s="6" t="inlineStr"/>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="K228" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L228" s="3" t="inlineStr"/>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="K229" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L229" s="6" t="inlineStr"/>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="K230" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L230" s="3" t="inlineStr"/>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="K231" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L231" s="6" t="inlineStr"/>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="K232" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L232" s="3" t="inlineStr"/>
@@ -11942,7 +11942,7 @@
       </c>
       <c r="K233" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L233" s="6" t="inlineStr"/>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="K234" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L234" s="3" t="inlineStr"/>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="K235" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L235" s="6" t="inlineStr"/>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="K236" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L236" s="3" t="inlineStr"/>
@@ -12134,7 +12134,7 @@
       </c>
       <c r="K237" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L237" s="6" t="inlineStr"/>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="K238" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L238" s="3" t="inlineStr"/>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="K239" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L239" s="6" t="inlineStr"/>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="K240" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L240" s="3" t="inlineStr"/>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="K241" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L241" s="6" t="inlineStr"/>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="K242" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L242" s="3" t="inlineStr"/>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="K243" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L243" s="6" t="inlineStr"/>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="K244" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L244" s="3" t="inlineStr"/>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="K245" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L245" s="6" t="inlineStr"/>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="K246" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L246" s="3" t="inlineStr"/>
@@ -12614,7 +12614,7 @@
       </c>
       <c r="K247" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L247" s="6" t="inlineStr"/>
@@ -12662,7 +12662,7 @@
       </c>
       <c r="K248" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L248" s="3" t="inlineStr"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="K249" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L249" s="6" t="inlineStr"/>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="K250" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L250" s="3" t="inlineStr"/>
@@ -12806,7 +12806,7 @@
       </c>
       <c r="K251" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L251" s="6" t="inlineStr"/>
@@ -12854,7 +12854,7 @@
       </c>
       <c r="K252" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L252" s="3" t="inlineStr"/>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="K253" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L253" s="6" t="inlineStr"/>
@@ -12950,7 +12950,7 @@
       </c>
       <c r="K254" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L254" s="3" t="inlineStr"/>
@@ -12998,7 +12998,7 @@
       </c>
       <c r="K255" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L255" s="6" t="inlineStr"/>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="K256" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L256" s="3" t="inlineStr"/>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="K257" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L257" s="6" t="inlineStr"/>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="K258" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L258" s="3" t="inlineStr"/>
@@ -13190,7 +13190,7 @@
       </c>
       <c r="K259" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L259" s="6" t="inlineStr"/>
@@ -13238,7 +13238,7 @@
       </c>
       <c r="K260" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L260" s="3" t="inlineStr"/>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="K261" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L261" s="6" t="inlineStr"/>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="K262" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L262" s="3" t="inlineStr"/>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="K263" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L263" s="6" t="inlineStr"/>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="K264" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L264" s="3" t="inlineStr"/>
@@ -13478,7 +13478,7 @@
       </c>
       <c r="K265" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L265" s="6" t="inlineStr"/>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="K266" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L266" s="3" t="inlineStr"/>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="K267" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L267" s="6" t="inlineStr"/>
@@ -13622,7 +13622,7 @@
       </c>
       <c r="K268" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L268" s="3" t="inlineStr"/>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="K269" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L269" s="6" t="inlineStr"/>
@@ -13718,7 +13718,7 @@
       </c>
       <c r="K270" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L270" s="3" t="inlineStr"/>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="K271" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L271" s="6" t="inlineStr"/>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="K272" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L272" s="3" t="inlineStr"/>
@@ -13862,7 +13862,7 @@
       </c>
       <c r="K273" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L273" s="6" t="inlineStr"/>
@@ -13910,7 +13910,7 @@
       </c>
       <c r="K274" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L274" s="3" t="inlineStr"/>
@@ -13958,7 +13958,7 @@
       </c>
       <c r="K275" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L275" s="6" t="inlineStr"/>
@@ -14006,7 +14006,7 @@
       </c>
       <c r="K276" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L276" s="3" t="inlineStr"/>
@@ -14054,7 +14054,7 @@
       </c>
       <c r="K277" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L277" s="6" t="inlineStr"/>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="K278" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L278" s="3" t="inlineStr"/>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="K279" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L279" s="6" t="inlineStr"/>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="K280" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L280" s="3" t="inlineStr"/>
@@ -14246,7 +14246,7 @@
       </c>
       <c r="K281" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L281" s="6" t="inlineStr"/>
@@ -14294,7 +14294,7 @@
       </c>
       <c r="K282" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L282" s="3" t="inlineStr"/>
@@ -14342,7 +14342,7 @@
       </c>
       <c r="K283" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L283" s="6" t="inlineStr"/>
@@ -14390,7 +14390,7 @@
       </c>
       <c r="K284" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L284" s="3" t="inlineStr"/>
@@ -14438,7 +14438,7 @@
       </c>
       <c r="K285" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L285" s="6" t="inlineStr"/>
@@ -14486,7 +14486,7 @@
       </c>
       <c r="K286" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L286" s="3" t="inlineStr"/>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="K287" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L287" s="6" t="inlineStr"/>
@@ -14582,7 +14582,7 @@
       </c>
       <c r="K288" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L288" s="3" t="inlineStr"/>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="K289" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L289" s="6" t="inlineStr"/>
@@ -14678,7 +14678,7 @@
       </c>
       <c r="K290" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L290" s="3" t="inlineStr"/>
@@ -14726,7 +14726,7 @@
       </c>
       <c r="K291" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L291" s="6" t="inlineStr"/>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="K292" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L292" s="3" t="inlineStr"/>
@@ -14822,7 +14822,7 @@
       </c>
       <c r="K293" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L293" s="6" t="inlineStr"/>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="K294" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L294" s="3" t="inlineStr"/>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="K295" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L295" s="6" t="inlineStr"/>
@@ -14966,7 +14966,7 @@
       </c>
       <c r="K296" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L296" s="3" t="inlineStr"/>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="K297" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L297" s="6" t="inlineStr"/>
@@ -15062,7 +15062,7 @@
       </c>
       <c r="K298" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L298" s="3" t="inlineStr"/>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="K299" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L299" s="6" t="inlineStr"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="K300" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L300" s="3" t="inlineStr"/>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="K301" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L301" s="6" t="inlineStr"/>
@@ -15254,7 +15254,7 @@
       </c>
       <c r="K302" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L302" s="3" t="inlineStr"/>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="K303" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L303" s="6" t="inlineStr"/>
@@ -15350,7 +15350,7 @@
       </c>
       <c r="K304" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L304" s="3" t="inlineStr"/>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="K305" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L305" s="6" t="inlineStr"/>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="K306" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L306" s="3" t="inlineStr"/>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="K307" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L307" s="6" t="inlineStr"/>
@@ -15542,7 +15542,7 @@
       </c>
       <c r="K308" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L308" s="3" t="inlineStr"/>
@@ -15590,7 +15590,7 @@
       </c>
       <c r="K309" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L309" s="6" t="inlineStr"/>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="K310" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L310" s="3" t="inlineStr"/>
@@ -15686,7 +15686,7 @@
       </c>
       <c r="K311" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L311" s="6" t="inlineStr"/>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="K312" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L312" s="3" t="inlineStr"/>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="K313" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L313" s="6" t="inlineStr"/>
@@ -15830,7 +15830,7 @@
       </c>
       <c r="K314" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L314" s="3" t="inlineStr"/>
@@ -15878,7 +15878,7 @@
       </c>
       <c r="K315" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L315" s="6" t="inlineStr"/>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="K316" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L316" s="3" t="inlineStr"/>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="K317" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L317" s="6" t="inlineStr"/>
@@ -16022,7 +16022,7 @@
       </c>
       <c r="K318" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L318" s="3" t="inlineStr"/>
@@ -16070,7 +16070,7 @@
       </c>
       <c r="K319" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L319" s="6" t="inlineStr"/>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="K320" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L320" s="3" t="inlineStr"/>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="K321" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L321" s="6" t="inlineStr"/>
@@ -16214,7 +16214,7 @@
       </c>
       <c r="K322" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L322" s="3" t="inlineStr"/>
@@ -16262,7 +16262,7 @@
       </c>
       <c r="K323" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L323" s="6" t="inlineStr"/>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="K324" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L324" s="3" t="inlineStr"/>
@@ -16358,7 +16358,7 @@
       </c>
       <c r="K325" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L325" s="6" t="inlineStr"/>
@@ -16406,7 +16406,7 @@
       </c>
       <c r="K326" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L326" s="3" t="inlineStr"/>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="K327" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L327" s="6" t="inlineStr"/>
@@ -16502,7 +16502,7 @@
       </c>
       <c r="K328" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L328" s="3" t="inlineStr"/>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="K329" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L329" s="6" t="inlineStr"/>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="K330" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L330" s="3" t="inlineStr"/>
@@ -16646,7 +16646,7 @@
       </c>
       <c r="K331" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L331" s="6" t="inlineStr"/>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="K332" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L332" s="3" t="inlineStr"/>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="K333" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L333" s="6" t="inlineStr"/>
@@ -16790,7 +16790,7 @@
       </c>
       <c r="K334" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L334" s="3" t="inlineStr"/>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="K335" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L335" s="6" t="inlineStr"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="K336" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L336" s="3" t="inlineStr"/>
@@ -16934,7 +16934,7 @@
       </c>
       <c r="K337" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L337" s="6" t="inlineStr"/>
@@ -16982,7 +16982,7 @@
       </c>
       <c r="K338" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L338" s="3" t="inlineStr"/>
@@ -17030,7 +17030,7 @@
       </c>
       <c r="K339" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L339" s="6" t="inlineStr"/>
@@ -17078,7 +17078,7 @@
       </c>
       <c r="K340" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L340" s="3" t="inlineStr"/>
@@ -17126,7 +17126,7 @@
       </c>
       <c r="K341" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L341" s="6" t="inlineStr"/>
@@ -17174,7 +17174,7 @@
       </c>
       <c r="K342" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L342" s="3" t="inlineStr"/>
@@ -17222,7 +17222,7 @@
       </c>
       <c r="K343" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L343" s="6" t="inlineStr"/>
@@ -17270,7 +17270,7 @@
       </c>
       <c r="K344" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L344" s="3" t="inlineStr"/>
@@ -17318,7 +17318,7 @@
       </c>
       <c r="K345" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L345" s="6" t="inlineStr"/>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="K346" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L346" s="3" t="inlineStr"/>
@@ -17414,7 +17414,7 @@
       </c>
       <c r="K347" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L347" s="6" t="inlineStr"/>
@@ -17462,7 +17462,7 @@
       </c>
       <c r="K348" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L348" s="3" t="inlineStr"/>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="K349" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L349" s="6" t="inlineStr"/>
@@ -17558,7 +17558,7 @@
       </c>
       <c r="K350" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L350" s="3" t="inlineStr"/>
@@ -17606,7 +17606,7 @@
       </c>
       <c r="K351" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L351" s="6" t="inlineStr"/>
@@ -17654,7 +17654,7 @@
       </c>
       <c r="K352" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L352" s="3" t="inlineStr"/>
@@ -17702,7 +17702,7 @@
       </c>
       <c r="K353" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L353" s="6" t="inlineStr"/>
@@ -17750,7 +17750,7 @@
       </c>
       <c r="K354" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L354" s="3" t="inlineStr"/>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="K355" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L355" s="6" t="inlineStr"/>
@@ -17846,7 +17846,7 @@
       </c>
       <c r="K356" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L356" s="3" t="inlineStr"/>
@@ -17894,7 +17894,7 @@
       </c>
       <c r="K357" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L357" s="6" t="inlineStr"/>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="K358" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L358" s="3" t="inlineStr"/>
@@ -17990,7 +17990,7 @@
       </c>
       <c r="K359" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L359" s="6" t="inlineStr"/>
@@ -18038,7 +18038,7 @@
       </c>
       <c r="K360" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L360" s="3" t="inlineStr"/>
@@ -18086,7 +18086,7 @@
       </c>
       <c r="K361" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L361" s="6" t="inlineStr"/>
@@ -18134,7 +18134,7 @@
       </c>
       <c r="K362" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L362" s="3" t="inlineStr"/>
@@ -18182,7 +18182,7 @@
       </c>
       <c r="K363" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L363" s="6" t="inlineStr"/>
@@ -18230,7 +18230,7 @@
       </c>
       <c r="K364" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L364" s="3" t="inlineStr"/>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="K365" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L365" s="6" t="inlineStr"/>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="K366" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L366" s="3" t="inlineStr"/>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="K367" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L367" s="6" t="inlineStr"/>
@@ -18422,7 +18422,7 @@
       </c>
       <c r="K368" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L368" s="3" t="inlineStr"/>
@@ -18470,7 +18470,7 @@
       </c>
       <c r="K369" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L369" s="6" t="inlineStr"/>
@@ -18518,7 +18518,7 @@
       </c>
       <c r="K370" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L370" s="3" t="inlineStr"/>
@@ -18566,7 +18566,7 @@
       </c>
       <c r="K371" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L371" s="6" t="inlineStr"/>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="K372" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L372" s="3" t="inlineStr"/>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="K373" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L373" s="6" t="inlineStr"/>
@@ -18710,7 +18710,7 @@
       </c>
       <c r="K374" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L374" s="3" t="inlineStr"/>
@@ -18758,7 +18758,7 @@
       </c>
       <c r="K375" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L375" s="6" t="inlineStr"/>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="K376" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L376" s="3" t="inlineStr"/>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="K377" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L377" s="6" t="inlineStr"/>
@@ -18902,7 +18902,7 @@
       </c>
       <c r="K378" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L378" s="3" t="inlineStr"/>
@@ -18950,7 +18950,7 @@
       </c>
       <c r="K379" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L379" s="6" t="inlineStr"/>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="K380" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L380" s="3" t="inlineStr"/>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="K381" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L381" s="6" t="inlineStr"/>
@@ -19094,7 +19094,7 @@
       </c>
       <c r="K382" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L382" s="3" t="inlineStr"/>
@@ -19142,7 +19142,7 @@
       </c>
       <c r="K383" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L383" s="6" t="inlineStr"/>
@@ -19190,7 +19190,7 @@
       </c>
       <c r="K384" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L384" s="3" t="inlineStr"/>
@@ -19238,7 +19238,7 @@
       </c>
       <c r="K385" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L385" s="6" t="inlineStr"/>
@@ -19286,7 +19286,7 @@
       </c>
       <c r="K386" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L386" s="3" t="inlineStr"/>
@@ -19334,7 +19334,7 @@
       </c>
       <c r="K387" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L387" s="6" t="inlineStr"/>
@@ -19382,7 +19382,7 @@
       </c>
       <c r="K388" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L388" s="3" t="inlineStr"/>
@@ -19430,7 +19430,7 @@
       </c>
       <c r="K389" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L389" s="6" t="inlineStr"/>
@@ -19478,7 +19478,7 @@
       </c>
       <c r="K390" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L390" s="3" t="inlineStr"/>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="K391" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L391" s="6" t="inlineStr"/>
@@ -19574,7 +19574,7 @@
       </c>
       <c r="K392" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L392" s="3" t="inlineStr"/>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="K393" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L393" s="6" t="inlineStr"/>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="K394" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L394" s="3" t="inlineStr"/>
@@ -19718,7 +19718,7 @@
       </c>
       <c r="K395" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L395" s="6" t="inlineStr"/>
@@ -19766,7 +19766,7 @@
       </c>
       <c r="K396" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L396" s="3" t="inlineStr"/>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="K397" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L397" s="6" t="inlineStr"/>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="K398" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L398" s="3" t="inlineStr"/>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="K399" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L399" s="6" t="inlineStr"/>
@@ -19958,7 +19958,7 @@
       </c>
       <c r="K400" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L400" s="3" t="inlineStr"/>
@@ -20006,7 +20006,7 @@
       </c>
       <c r="K401" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L401" s="6" t="inlineStr"/>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="K402" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L402" s="3" t="inlineStr"/>
@@ -20102,7 +20102,7 @@
       </c>
       <c r="K403" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L403" s="6" t="inlineStr"/>
@@ -20150,7 +20150,7 @@
       </c>
       <c r="K404" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L404" s="3" t="inlineStr"/>
@@ -20198,7 +20198,7 @@
       </c>
       <c r="K405" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L405" s="6" t="inlineStr"/>
@@ -20246,7 +20246,7 @@
       </c>
       <c r="K406" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L406" s="3" t="inlineStr"/>
@@ -20294,7 +20294,7 @@
       </c>
       <c r="K407" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L407" s="6" t="inlineStr"/>
@@ -20342,7 +20342,7 @@
       </c>
       <c r="K408" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L408" s="3" t="inlineStr"/>
@@ -20390,7 +20390,7 @@
       </c>
       <c r="K409" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L409" s="6" t="inlineStr"/>
@@ -20438,7 +20438,7 @@
       </c>
       <c r="K410" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L410" s="3" t="inlineStr"/>
@@ -20486,7 +20486,7 @@
       </c>
       <c r="K411" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L411" s="6" t="inlineStr"/>
@@ -20534,7 +20534,7 @@
       </c>
       <c r="K412" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L412" s="3" t="inlineStr"/>
@@ -20582,7 +20582,7 @@
       </c>
       <c r="K413" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L413" s="6" t="inlineStr"/>
@@ -20630,7 +20630,7 @@
       </c>
       <c r="K414" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L414" s="3" t="inlineStr"/>
@@ -20678,7 +20678,7 @@
       </c>
       <c r="K415" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L415" s="6" t="inlineStr"/>
@@ -20726,7 +20726,7 @@
       </c>
       <c r="K416" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L416" s="3" t="inlineStr"/>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="K417" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L417" s="6" t="inlineStr"/>
@@ -20822,7 +20822,7 @@
       </c>
       <c r="K418" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L418" s="3" t="inlineStr"/>
@@ -20870,7 +20870,7 @@
       </c>
       <c r="K419" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L419" s="6" t="inlineStr"/>
@@ -20918,7 +20918,7 @@
       </c>
       <c r="K420" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L420" s="3" t="inlineStr"/>
@@ -20966,7 +20966,7 @@
       </c>
       <c r="K421" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L421" s="6" t="inlineStr"/>
@@ -21014,7 +21014,7 @@
       </c>
       <c r="K422" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L422" s="3" t="inlineStr"/>
@@ -21062,7 +21062,7 @@
       </c>
       <c r="K423" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L423" s="6" t="inlineStr"/>
@@ -21110,7 +21110,7 @@
       </c>
       <c r="K424" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L424" s="3" t="inlineStr"/>
@@ -21158,7 +21158,7 @@
       </c>
       <c r="K425" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L425" s="6" t="inlineStr"/>
@@ -21206,7 +21206,7 @@
       </c>
       <c r="K426" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L426" s="3" t="inlineStr"/>
@@ -21254,7 +21254,7 @@
       </c>
       <c r="K427" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L427" s="6" t="inlineStr"/>
@@ -21302,7 +21302,7 @@
       </c>
       <c r="K428" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L428" s="3" t="inlineStr"/>
@@ -21350,7 +21350,7 @@
       </c>
       <c r="K429" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L429" s="6" t="inlineStr"/>
@@ -21398,7 +21398,7 @@
       </c>
       <c r="K430" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L430" s="3" t="inlineStr"/>
@@ -21446,7 +21446,7 @@
       </c>
       <c r="K431" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L431" s="6" t="inlineStr"/>
@@ -21494,7 +21494,7 @@
       </c>
       <c r="K432" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L432" s="3" t="inlineStr"/>
@@ -21542,7 +21542,7 @@
       </c>
       <c r="K433" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L433" s="6" t="inlineStr"/>
@@ -21590,7 +21590,7 @@
       </c>
       <c r="K434" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L434" s="3" t="inlineStr"/>
@@ -21638,7 +21638,7 @@
       </c>
       <c r="K435" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L435" s="6" t="inlineStr"/>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="K436" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L436" s="3" t="inlineStr"/>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="K437" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L437" s="6" t="inlineStr"/>
@@ -21782,7 +21782,7 @@
       </c>
       <c r="K438" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L438" s="3" t="inlineStr"/>
@@ -21830,7 +21830,7 @@
       </c>
       <c r="K439" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L439" s="6" t="inlineStr"/>
@@ -21878,7 +21878,7 @@
       </c>
       <c r="K440" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L440" s="3" t="inlineStr"/>
@@ -21926,7 +21926,7 @@
       </c>
       <c r="K441" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L441" s="6" t="inlineStr"/>
@@ -21974,7 +21974,7 @@
       </c>
       <c r="K442" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L442" s="3" t="inlineStr"/>
@@ -22022,7 +22022,7 @@
       </c>
       <c r="K443" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L443" s="6" t="inlineStr"/>
@@ -22070,7 +22070,7 @@
       </c>
       <c r="K444" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L444" s="3" t="inlineStr"/>
@@ -22118,7 +22118,7 @@
       </c>
       <c r="K445" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L445" s="6" t="inlineStr"/>
@@ -22166,7 +22166,7 @@
       </c>
       <c r="K446" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L446" s="3" t="inlineStr"/>
@@ -22214,7 +22214,7 @@
       </c>
       <c r="K447" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L447" s="6" t="inlineStr"/>
@@ -22262,7 +22262,7 @@
       </c>
       <c r="K448" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L448" s="3" t="inlineStr"/>
@@ -22310,7 +22310,7 @@
       </c>
       <c r="K449" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L449" s="6" t="inlineStr"/>
@@ -22358,7 +22358,7 @@
       </c>
       <c r="K450" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L450" s="3" t="inlineStr"/>
@@ -22406,7 +22406,7 @@
       </c>
       <c r="K451" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L451" s="6" t="inlineStr"/>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="K452" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L452" s="3" t="inlineStr"/>
@@ -22502,7 +22502,7 @@
       </c>
       <c r="K453" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L453" s="6" t="inlineStr"/>
@@ -22550,7 +22550,7 @@
       </c>
       <c r="K454" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L454" s="3" t="inlineStr"/>
@@ -22598,7 +22598,7 @@
       </c>
       <c r="K455" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L455" s="6" t="inlineStr"/>
@@ -22646,7 +22646,7 @@
       </c>
       <c r="K456" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L456" s="3" t="inlineStr"/>
@@ -22694,7 +22694,7 @@
       </c>
       <c r="K457" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L457" s="6" t="inlineStr"/>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="K458" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L458" s="3" t="inlineStr"/>
@@ -22790,7 +22790,7 @@
       </c>
       <c r="K459" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L459" s="6" t="inlineStr"/>
@@ -22838,7 +22838,7 @@
       </c>
       <c r="K460" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L460" s="3" t="inlineStr"/>
@@ -22886,7 +22886,7 @@
       </c>
       <c r="K461" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L461" s="6" t="inlineStr"/>
@@ -22934,7 +22934,7 @@
       </c>
       <c r="K462" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L462" s="3" t="inlineStr"/>
@@ -22982,7 +22982,7 @@
       </c>
       <c r="K463" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L463" s="6" t="inlineStr"/>
@@ -23030,7 +23030,7 @@
       </c>
       <c r="K464" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L464" s="3" t="inlineStr"/>
@@ -23078,7 +23078,7 @@
       </c>
       <c r="K465" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L465" s="6" t="inlineStr"/>
@@ -23126,7 +23126,7 @@
       </c>
       <c r="K466" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L466" s="3" t="inlineStr"/>
@@ -23174,7 +23174,7 @@
       </c>
       <c r="K467" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L467" s="6" t="inlineStr"/>
@@ -23222,7 +23222,7 @@
       </c>
       <c r="K468" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L468" s="3" t="inlineStr"/>
@@ -23270,7 +23270,7 @@
       </c>
       <c r="K469" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L469" s="6" t="inlineStr"/>
@@ -23318,7 +23318,7 @@
       </c>
       <c r="K470" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L470" s="3" t="inlineStr"/>
@@ -23366,7 +23366,7 @@
       </c>
       <c r="K471" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L471" s="6" t="inlineStr"/>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="K472" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L472" s="3" t="inlineStr"/>
@@ -23462,7 +23462,7 @@
       </c>
       <c r="K473" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L473" s="6" t="inlineStr"/>
@@ -23510,7 +23510,7 @@
       </c>
       <c r="K474" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L474" s="3" t="inlineStr"/>
@@ -23558,7 +23558,7 @@
       </c>
       <c r="K475" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L475" s="6" t="inlineStr"/>
@@ -23606,7 +23606,7 @@
       </c>
       <c r="K476" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L476" s="3" t="inlineStr"/>
@@ -23654,7 +23654,7 @@
       </c>
       <c r="K477" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L477" s="6" t="inlineStr"/>
@@ -23702,7 +23702,7 @@
       </c>
       <c r="K478" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L478" s="3" t="inlineStr"/>
@@ -23750,7 +23750,7 @@
       </c>
       <c r="K479" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L479" s="6" t="inlineStr"/>
@@ -23798,7 +23798,7 @@
       </c>
       <c r="K480" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L480" s="3" t="inlineStr"/>
@@ -23846,7 +23846,7 @@
       </c>
       <c r="K481" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L481" s="6" t="inlineStr"/>
@@ -23894,7 +23894,7 @@
       </c>
       <c r="K482" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L482" s="3" t="inlineStr"/>
@@ -23942,7 +23942,7 @@
       </c>
       <c r="K483" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L483" s="6" t="inlineStr"/>
@@ -23990,7 +23990,7 @@
       </c>
       <c r="K484" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L484" s="3" t="inlineStr"/>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="K485" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L485" s="6" t="inlineStr"/>
@@ -24086,7 +24086,7 @@
       </c>
       <c r="K486" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L486" s="3" t="inlineStr"/>
@@ -24134,7 +24134,7 @@
       </c>
       <c r="K487" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L487" s="6" t="inlineStr"/>
@@ -24182,7 +24182,7 @@
       </c>
       <c r="K488" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L488" s="3" t="inlineStr"/>
@@ -24230,7 +24230,7 @@
       </c>
       <c r="K489" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L489" s="6" t="inlineStr"/>
@@ -24278,7 +24278,7 @@
       </c>
       <c r="K490" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L490" s="3" t="inlineStr"/>
@@ -24326,7 +24326,7 @@
       </c>
       <c r="K491" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L491" s="6" t="inlineStr"/>
@@ -24374,7 +24374,7 @@
       </c>
       <c r="K492" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L492" s="3" t="inlineStr"/>
@@ -24422,7 +24422,7 @@
       </c>
       <c r="K493" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L493" s="6" t="inlineStr"/>
@@ -24470,7 +24470,7 @@
       </c>
       <c r="K494" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L494" s="3" t="inlineStr"/>
@@ -24518,7 +24518,7 @@
       </c>
       <c r="K495" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L495" s="6" t="inlineStr"/>
@@ -24566,7 +24566,7 @@
       </c>
       <c r="K496" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L496" s="3" t="inlineStr"/>
@@ -24614,7 +24614,7 @@
       </c>
       <c r="K497" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L497" s="6" t="inlineStr"/>
@@ -24662,7 +24662,7 @@
       </c>
       <c r="K498" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L498" s="3" t="inlineStr"/>
@@ -24710,7 +24710,7 @@
       </c>
       <c r="K499" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L499" s="6" t="inlineStr"/>
@@ -24758,7 +24758,7 @@
       </c>
       <c r="K500" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L500" s="3" t="inlineStr"/>
@@ -24806,7 +24806,7 @@
       </c>
       <c r="K501" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L501" s="6" t="inlineStr"/>
@@ -24854,7 +24854,7 @@
       </c>
       <c r="K502" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L502" s="3" t="inlineStr"/>
@@ -24902,7 +24902,7 @@
       </c>
       <c r="K503" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L503" s="6" t="inlineStr"/>
@@ -24950,7 +24950,7 @@
       </c>
       <c r="K504" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L504" s="3" t="inlineStr"/>
@@ -24998,7 +24998,7 @@
       </c>
       <c r="K505" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L505" s="6" t="inlineStr"/>
@@ -25046,7 +25046,7 @@
       </c>
       <c r="K506" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L506" s="3" t="inlineStr"/>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="K507" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L507" s="6" t="inlineStr"/>
@@ -25142,7 +25142,7 @@
       </c>
       <c r="K508" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L508" s="3" t="inlineStr"/>
@@ -25190,7 +25190,7 @@
       </c>
       <c r="K509" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L509" s="6" t="inlineStr"/>
@@ -25238,7 +25238,7 @@
       </c>
       <c r="K510" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L510" s="3" t="inlineStr"/>
@@ -25286,7 +25286,7 @@
       </c>
       <c r="K511" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L511" s="6" t="inlineStr"/>
@@ -25334,7 +25334,7 @@
       </c>
       <c r="K512" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L512" s="3" t="inlineStr"/>
@@ -25382,7 +25382,7 @@
       </c>
       <c r="K513" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L513" s="6" t="inlineStr"/>
@@ -25430,7 +25430,7 @@
       </c>
       <c r="K514" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L514" s="3" t="inlineStr"/>
@@ -25478,7 +25478,7 @@
       </c>
       <c r="K515" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L515" s="6" t="inlineStr"/>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="K516" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L516" s="3" t="inlineStr"/>
@@ -25574,7 +25574,7 @@
       </c>
       <c r="K517" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L517" s="6" t="inlineStr"/>
@@ -25622,7 +25622,7 @@
       </c>
       <c r="K518" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L518" s="3" t="inlineStr"/>
@@ -25670,7 +25670,7 @@
       </c>
       <c r="K519" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L519" s="6" t="inlineStr"/>
@@ -25718,7 +25718,7 @@
       </c>
       <c r="K520" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L520" s="3" t="inlineStr"/>
@@ -25766,7 +25766,7 @@
       </c>
       <c r="K521" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L521" s="6" t="inlineStr"/>
@@ -25814,7 +25814,7 @@
       </c>
       <c r="K522" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L522" s="3" t="inlineStr"/>
@@ -25862,7 +25862,7 @@
       </c>
       <c r="K523" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L523" s="6" t="inlineStr"/>
@@ -25910,7 +25910,7 @@
       </c>
       <c r="K524" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L524" s="3" t="inlineStr"/>
@@ -25958,7 +25958,7 @@
       </c>
       <c r="K525" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L525" s="6" t="inlineStr"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K526" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L526" s="3" t="inlineStr"/>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="K527" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L527" s="6" t="inlineStr"/>
@@ -26102,7 +26102,7 @@
       </c>
       <c r="K528" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L528" s="3" t="inlineStr"/>
@@ -26150,7 +26150,7 @@
       </c>
       <c r="K529" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L529" s="6" t="inlineStr"/>
@@ -26198,7 +26198,7 @@
       </c>
       <c r="K530" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L530" s="3" t="inlineStr"/>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="K531" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L531" s="6" t="inlineStr"/>
@@ -26294,7 +26294,7 @@
       </c>
       <c r="K532" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L532" s="3" t="inlineStr"/>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="K533" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L533" s="6" t="inlineStr"/>
@@ -26390,7 +26390,7 @@
       </c>
       <c r="K534" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L534" s="3" t="inlineStr"/>
@@ -26438,7 +26438,7 @@
       </c>
       <c r="K535" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L535" s="6" t="inlineStr"/>
@@ -26486,7 +26486,7 @@
       </c>
       <c r="K536" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L536" s="3" t="inlineStr"/>
@@ -26534,7 +26534,7 @@
       </c>
       <c r="K537" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L537" s="6" t="inlineStr"/>
@@ -26582,7 +26582,7 @@
       </c>
       <c r="K538" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L538" s="3" t="inlineStr"/>
@@ -26630,7 +26630,7 @@
       </c>
       <c r="K539" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L539" s="6" t="inlineStr"/>
@@ -26678,7 +26678,7 @@
       </c>
       <c r="K540" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L540" s="3" t="inlineStr"/>
@@ -26726,7 +26726,7 @@
       </c>
       <c r="K541" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L541" s="6" t="inlineStr"/>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="K542" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L542" s="3" t="inlineStr"/>
@@ -26822,7 +26822,7 @@
       </c>
       <c r="K543" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L543" s="6" t="inlineStr"/>
@@ -26870,7 +26870,7 @@
       </c>
       <c r="K544" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L544" s="3" t="inlineStr"/>
@@ -26918,7 +26918,7 @@
       </c>
       <c r="K545" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L545" s="6" t="inlineStr"/>
@@ -26966,7 +26966,7 @@
       </c>
       <c r="K546" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L546" s="3" t="inlineStr"/>
@@ -27014,7 +27014,7 @@
       </c>
       <c r="K547" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L547" s="6" t="inlineStr"/>
@@ -27062,7 +27062,7 @@
       </c>
       <c r="K548" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L548" s="3" t="inlineStr"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K549" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L549" s="6" t="inlineStr"/>
@@ -27158,7 +27158,7 @@
       </c>
       <c r="K550" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L550" s="3" t="inlineStr"/>
@@ -27206,7 +27206,7 @@
       </c>
       <c r="K551" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L551" s="6" t="inlineStr"/>
@@ -27254,7 +27254,7 @@
       </c>
       <c r="K552" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L552" s="3" t="inlineStr"/>
@@ -27302,7 +27302,7 @@
       </c>
       <c r="K553" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L553" s="6" t="inlineStr"/>
@@ -27350,7 +27350,7 @@
       </c>
       <c r="K554" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L554" s="3" t="inlineStr"/>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="K555" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L555" s="6" t="inlineStr"/>
@@ -27446,7 +27446,7 @@
       </c>
       <c r="K556" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L556" s="3" t="inlineStr"/>
@@ -27494,7 +27494,7 @@
       </c>
       <c r="K557" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L557" s="6" t="inlineStr"/>
@@ -27542,7 +27542,7 @@
       </c>
       <c r="K558" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L558" s="3" t="inlineStr"/>
@@ -27590,7 +27590,7 @@
       </c>
       <c r="K559" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L559" s="6" t="inlineStr"/>
@@ -27638,7 +27638,7 @@
       </c>
       <c r="K560" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L560" s="3" t="inlineStr"/>
@@ -27686,7 +27686,7 @@
       </c>
       <c r="K561" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L561" s="6" t="inlineStr"/>
@@ -27734,7 +27734,7 @@
       </c>
       <c r="K562" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L562" s="3" t="inlineStr"/>
@@ -27782,7 +27782,7 @@
       </c>
       <c r="K563" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L563" s="6" t="inlineStr"/>
@@ -27830,7 +27830,7 @@
       </c>
       <c r="K564" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L564" s="3" t="inlineStr"/>
@@ -27878,7 +27878,7 @@
       </c>
       <c r="K565" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L565" s="6" t="inlineStr"/>
@@ -27926,7 +27926,7 @@
       </c>
       <c r="K566" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L566" s="3" t="inlineStr"/>
@@ -27974,7 +27974,7 @@
       </c>
       <c r="K567" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L567" s="6" t="inlineStr"/>
@@ -28022,7 +28022,7 @@
       </c>
       <c r="K568" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L568" s="3" t="inlineStr"/>
@@ -28070,7 +28070,7 @@
       </c>
       <c r="K569" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L569" s="6" t="inlineStr"/>
@@ -28118,7 +28118,7 @@
       </c>
       <c r="K570" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L570" s="3" t="inlineStr"/>
@@ -28166,7 +28166,7 @@
       </c>
       <c r="K571" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L571" s="6" t="inlineStr"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K572" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L572" s="3" t="inlineStr"/>
@@ -28262,7 +28262,7 @@
       </c>
       <c r="K573" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L573" s="6" t="inlineStr"/>
@@ -28310,7 +28310,7 @@
       </c>
       <c r="K574" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L574" s="3" t="inlineStr"/>
@@ -28358,7 +28358,7 @@
       </c>
       <c r="K575" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L575" s="6" t="inlineStr"/>
@@ -28406,7 +28406,7 @@
       </c>
       <c r="K576" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L576" s="3" t="inlineStr"/>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="K577" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L577" s="6" t="inlineStr"/>
@@ -28502,7 +28502,7 @@
       </c>
       <c r="K578" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L578" s="3" t="inlineStr"/>
@@ -28550,7 +28550,7 @@
       </c>
       <c r="K579" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L579" s="6" t="inlineStr"/>
@@ -28598,7 +28598,7 @@
       </c>
       <c r="K580" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L580" s="3" t="inlineStr"/>
@@ -28646,7 +28646,7 @@
       </c>
       <c r="K581" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L581" s="6" t="inlineStr"/>
@@ -28694,7 +28694,7 @@
       </c>
       <c r="K582" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L582" s="3" t="inlineStr"/>
@@ -28742,7 +28742,7 @@
       </c>
       <c r="K583" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L583" s="6" t="inlineStr"/>
@@ -28790,7 +28790,7 @@
       </c>
       <c r="K584" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L584" s="3" t="inlineStr"/>
@@ -28838,7 +28838,7 @@
       </c>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L585" s="6" t="inlineStr"/>
@@ -28886,7 +28886,7 @@
       </c>
       <c r="K586" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L586" s="3" t="inlineStr"/>
@@ -28934,7 +28934,7 @@
       </c>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L587" s="6" t="inlineStr"/>
@@ -28982,7 +28982,7 @@
       </c>
       <c r="K588" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L588" s="3" t="inlineStr"/>
@@ -29030,7 +29030,7 @@
       </c>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L589" s="6" t="inlineStr"/>
@@ -29078,7 +29078,7 @@
       </c>
       <c r="K590" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L590" s="3" t="inlineStr"/>
@@ -29126,7 +29126,7 @@
       </c>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L591" s="6" t="inlineStr"/>
@@ -29174,7 +29174,7 @@
       </c>
       <c r="K592" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L592" s="3" t="inlineStr"/>
@@ -29222,7 +29222,7 @@
       </c>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L593" s="6" t="inlineStr"/>
@@ -29270,7 +29270,7 @@
       </c>
       <c r="K594" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L594" s="3" t="inlineStr"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L595" s="6" t="inlineStr"/>
@@ -29366,7 +29366,7 @@
       </c>
       <c r="K596" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L596" s="3" t="inlineStr"/>
@@ -29414,7 +29414,7 @@
       </c>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L597" s="6" t="inlineStr"/>
@@ -29462,7 +29462,7 @@
       </c>
       <c r="K598" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L598" s="3" t="inlineStr"/>
@@ -29510,7 +29510,7 @@
       </c>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L599" s="6" t="inlineStr"/>
@@ -29558,7 +29558,7 @@
       </c>
       <c r="K600" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L600" s="3" t="inlineStr"/>
@@ -29606,7 +29606,7 @@
       </c>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L601" s="6" t="inlineStr"/>
@@ -29654,7 +29654,7 @@
       </c>
       <c r="K602" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L602" s="3" t="inlineStr"/>
@@ -29702,7 +29702,7 @@
       </c>
       <c r="K603" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L603" s="6" t="inlineStr"/>
@@ -29750,7 +29750,7 @@
       </c>
       <c r="K604" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L604" s="3" t="inlineStr"/>
@@ -29798,7 +29798,7 @@
       </c>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr"/>
@@ -29846,7 +29846,7 @@
       </c>
       <c r="K606" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L606" s="3" t="inlineStr"/>
@@ -29894,7 +29894,7 @@
       </c>
       <c r="K607" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L607" s="6" t="inlineStr"/>
@@ -29942,7 +29942,7 @@
       </c>
       <c r="K608" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L608" s="3" t="inlineStr"/>
@@ -29990,7 +29990,7 @@
       </c>
       <c r="K609" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L609" s="6" t="inlineStr"/>
@@ -30038,7 +30038,7 @@
       </c>
       <c r="K610" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L610" s="3" t="inlineStr"/>
@@ -30086,7 +30086,7 @@
       </c>
       <c r="K611" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L611" s="6" t="inlineStr"/>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="K612" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L612" s="3" t="inlineStr"/>
@@ -30182,7 +30182,7 @@
       </c>
       <c r="K613" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L613" s="6" t="inlineStr"/>
@@ -30230,7 +30230,7 @@
       </c>
       <c r="K614" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L614" s="3" t="inlineStr"/>
@@ -30278,7 +30278,7 @@
       </c>
       <c r="K615" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L615" s="6" t="inlineStr"/>
@@ -30326,7 +30326,7 @@
       </c>
       <c r="K616" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L616" s="3" t="inlineStr"/>
@@ -30374,7 +30374,7 @@
       </c>
       <c r="K617" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L617" s="6" t="inlineStr"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K618" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L618" s="3" t="inlineStr"/>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="K619" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L619" s="6" t="inlineStr"/>
@@ -30518,7 +30518,7 @@
       </c>
       <c r="K620" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L620" s="3" t="inlineStr"/>
@@ -30566,7 +30566,7 @@
       </c>
       <c r="K621" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L621" s="6" t="inlineStr"/>
@@ -30614,7 +30614,7 @@
       </c>
       <c r="K622" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L622" s="3" t="inlineStr"/>
@@ -30662,7 +30662,7 @@
       </c>
       <c r="K623" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L623" s="6" t="inlineStr"/>
@@ -30710,7 +30710,7 @@
       </c>
       <c r="K624" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L624" s="3" t="inlineStr"/>
@@ -30758,7 +30758,7 @@
       </c>
       <c r="K625" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L625" s="6" t="inlineStr"/>
@@ -30806,7 +30806,7 @@
       </c>
       <c r="K626" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L626" s="3" t="inlineStr"/>
@@ -30854,7 +30854,7 @@
       </c>
       <c r="K627" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L627" s="6" t="inlineStr"/>
@@ -30902,7 +30902,7 @@
       </c>
       <c r="K628" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L628" s="3" t="inlineStr"/>
@@ -30950,7 +30950,7 @@
       </c>
       <c r="K629" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L629" s="6" t="inlineStr"/>
@@ -30998,7 +30998,7 @@
       </c>
       <c r="K630" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L630" s="3" t="inlineStr"/>
@@ -31046,7 +31046,7 @@
       </c>
       <c r="K631" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L631" s="6" t="inlineStr"/>
@@ -31094,7 +31094,7 @@
       </c>
       <c r="K632" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L632" s="3" t="inlineStr"/>
@@ -31142,7 +31142,7 @@
       </c>
       <c r="K633" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L633" s="6" t="inlineStr"/>
@@ -31190,7 +31190,7 @@
       </c>
       <c r="K634" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L634" s="3" t="inlineStr"/>
@@ -31238,7 +31238,7 @@
       </c>
       <c r="K635" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L635" s="6" t="inlineStr"/>
@@ -31286,7 +31286,7 @@
       </c>
       <c r="K636" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L636" s="3" t="inlineStr"/>
@@ -31334,7 +31334,7 @@
       </c>
       <c r="K637" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L637" s="6" t="inlineStr"/>
@@ -31382,7 +31382,7 @@
       </c>
       <c r="K638" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L638" s="3" t="inlineStr"/>
@@ -31430,7 +31430,7 @@
       </c>
       <c r="K639" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L639" s="6" t="inlineStr"/>
@@ -31478,7 +31478,7 @@
       </c>
       <c r="K640" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L640" s="3" t="inlineStr"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K641" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L641" s="6" t="inlineStr"/>
@@ -31574,7 +31574,7 @@
       </c>
       <c r="K642" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L642" s="3" t="inlineStr"/>
@@ -31622,7 +31622,7 @@
       </c>
       <c r="K643" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L643" s="6" t="inlineStr"/>
@@ -31670,7 +31670,7 @@
       </c>
       <c r="K644" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L644" s="3" t="inlineStr"/>
@@ -31718,7 +31718,7 @@
       </c>
       <c r="K645" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L645" s="6" t="inlineStr"/>
@@ -31766,7 +31766,7 @@
       </c>
       <c r="K646" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L646" s="3" t="inlineStr"/>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="K647" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L647" s="6" t="inlineStr"/>
@@ -31862,7 +31862,7 @@
       </c>
       <c r="K648" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L648" s="3" t="inlineStr"/>
@@ -31910,7 +31910,7 @@
       </c>
       <c r="K649" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L649" s="6" t="inlineStr"/>
@@ -31958,7 +31958,7 @@
       </c>
       <c r="K650" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L650" s="3" t="inlineStr"/>
@@ -32006,7 +32006,7 @@
       </c>
       <c r="K651" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L651" s="6" t="inlineStr"/>
@@ -32054,7 +32054,7 @@
       </c>
       <c r="K652" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L652" s="3" t="inlineStr"/>
@@ -32102,7 +32102,7 @@
       </c>
       <c r="K653" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L653" s="6" t="inlineStr"/>
@@ -32150,7 +32150,7 @@
       </c>
       <c r="K654" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L654" s="3" t="inlineStr"/>
@@ -32198,7 +32198,7 @@
       </c>
       <c r="K655" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L655" s="6" t="inlineStr"/>
@@ -32246,7 +32246,7 @@
       </c>
       <c r="K656" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L656" s="3" t="inlineStr"/>
@@ -32294,7 +32294,7 @@
       </c>
       <c r="K657" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L657" s="6" t="inlineStr"/>
@@ -32342,7 +32342,7 @@
       </c>
       <c r="K658" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L658" s="3" t="inlineStr"/>
@@ -32390,7 +32390,7 @@
       </c>
       <c r="K659" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L659" s="6" t="inlineStr"/>
@@ -32438,7 +32438,7 @@
       </c>
       <c r="K660" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L660" s="3" t="inlineStr"/>
@@ -32486,7 +32486,7 @@
       </c>
       <c r="K661" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L661" s="6" t="inlineStr"/>
@@ -32534,7 +32534,7 @@
       </c>
       <c r="K662" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L662" s="3" t="inlineStr"/>
@@ -32582,7 +32582,7 @@
       </c>
       <c r="K663" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L663" s="6" t="inlineStr"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K664" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L664" s="3" t="inlineStr"/>
@@ -32678,7 +32678,7 @@
       </c>
       <c r="K665" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L665" s="6" t="inlineStr"/>
@@ -32726,7 +32726,7 @@
       </c>
       <c r="K666" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L666" s="3" t="inlineStr"/>
@@ -32774,7 +32774,7 @@
       </c>
       <c r="K667" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L667" s="6" t="inlineStr"/>
@@ -32822,7 +32822,7 @@
       </c>
       <c r="K668" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L668" s="3" t="inlineStr"/>
@@ -32870,7 +32870,7 @@
       </c>
       <c r="K669" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L669" s="6" t="inlineStr"/>
@@ -32918,7 +32918,7 @@
       </c>
       <c r="K670" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L670" s="3" t="inlineStr"/>
@@ -32966,7 +32966,7 @@
       </c>
       <c r="K671" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L671" s="6" t="inlineStr"/>
@@ -33014,7 +33014,7 @@
       </c>
       <c r="K672" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L672" s="3" t="inlineStr"/>
@@ -33062,7 +33062,7 @@
       </c>
       <c r="K673" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L673" s="6" t="inlineStr"/>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="K674" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L674" s="3" t="inlineStr"/>
@@ -33158,7 +33158,7 @@
       </c>
       <c r="K675" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L675" s="6" t="inlineStr"/>
@@ -33206,7 +33206,7 @@
       </c>
       <c r="K676" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L676" s="3" t="inlineStr"/>
@@ -33254,7 +33254,7 @@
       </c>
       <c r="K677" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L677" s="6" t="inlineStr"/>
@@ -33302,7 +33302,7 @@
       </c>
       <c r="K678" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L678" s="3" t="inlineStr"/>
@@ -33350,7 +33350,7 @@
       </c>
       <c r="K679" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L679" s="6" t="inlineStr"/>
@@ -33398,7 +33398,7 @@
       </c>
       <c r="K680" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L680" s="3" t="inlineStr"/>
@@ -33446,7 +33446,7 @@
       </c>
       <c r="K681" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L681" s="6" t="inlineStr"/>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="K682" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L682" s="3" t="inlineStr"/>
@@ -33542,7 +33542,7 @@
       </c>
       <c r="K683" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L683" s="6" t="inlineStr"/>
@@ -33590,7 +33590,7 @@
       </c>
       <c r="K684" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L684" s="3" t="inlineStr"/>
@@ -33638,7 +33638,7 @@
       </c>
       <c r="K685" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L685" s="6" t="inlineStr"/>
@@ -33686,7 +33686,7 @@
       </c>
       <c r="K686" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L686" s="3" t="inlineStr"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K687" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L687" s="6" t="inlineStr"/>
@@ -33782,7 +33782,7 @@
       </c>
       <c r="K688" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L688" s="3" t="inlineStr"/>
@@ -33830,7 +33830,7 @@
       </c>
       <c r="K689" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L689" s="6" t="inlineStr"/>
@@ -33878,7 +33878,7 @@
       </c>
       <c r="K690" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L690" s="3" t="inlineStr"/>
@@ -33926,7 +33926,7 @@
       </c>
       <c r="K691" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L691" s="6" t="inlineStr"/>
@@ -33974,7 +33974,7 @@
       </c>
       <c r="K692" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L692" s="3" t="inlineStr"/>
@@ -34022,7 +34022,7 @@
       </c>
       <c r="K693" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L693" s="6" t="inlineStr"/>
@@ -34070,7 +34070,7 @@
       </c>
       <c r="K694" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L694" s="3" t="inlineStr"/>
@@ -34118,7 +34118,7 @@
       </c>
       <c r="K695" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L695" s="6" t="inlineStr"/>
@@ -34166,7 +34166,7 @@
       </c>
       <c r="K696" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L696" s="3" t="inlineStr"/>
@@ -34214,7 +34214,7 @@
       </c>
       <c r="K697" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L697" s="6" t="inlineStr"/>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="K698" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L698" s="3" t="inlineStr"/>
@@ -34310,7 +34310,7 @@
       </c>
       <c r="K699" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L699" s="6" t="inlineStr"/>
@@ -34358,7 +34358,7 @@
       </c>
       <c r="K700" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L700" s="3" t="inlineStr"/>
@@ -34406,7 +34406,7 @@
       </c>
       <c r="K701" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L701" s="6" t="inlineStr"/>
@@ -34454,7 +34454,7 @@
       </c>
       <c r="K702" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L702" s="3" t="inlineStr"/>
@@ -34502,7 +34502,7 @@
       </c>
       <c r="K703" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L703" s="6" t="inlineStr"/>
@@ -34550,7 +34550,7 @@
       </c>
       <c r="K704" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L704" s="3" t="inlineStr"/>
@@ -34598,7 +34598,7 @@
       </c>
       <c r="K705" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L705" s="6" t="inlineStr"/>
@@ -34646,7 +34646,7 @@
       </c>
       <c r="K706" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L706" s="3" t="inlineStr"/>
@@ -34694,7 +34694,7 @@
       </c>
       <c r="K707" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L707" s="6" t="inlineStr"/>
@@ -34742,7 +34742,7 @@
       </c>
       <c r="K708" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L708" s="3" t="inlineStr"/>
@@ -34790,7 +34790,7 @@
       </c>
       <c r="K709" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L709" s="6" t="inlineStr"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K710" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L710" s="3" t="inlineStr"/>
@@ -34886,7 +34886,7 @@
       </c>
       <c r="K711" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L711" s="6" t="inlineStr"/>
@@ -34934,7 +34934,7 @@
       </c>
       <c r="K712" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L712" s="3" t="inlineStr"/>
@@ -34982,7 +34982,7 @@
       </c>
       <c r="K713" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L713" s="6" t="inlineStr"/>
@@ -35030,7 +35030,7 @@
       </c>
       <c r="K714" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L714" s="3" t="inlineStr"/>
@@ -35078,7 +35078,7 @@
       </c>
       <c r="K715" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L715" s="6" t="inlineStr"/>
@@ -35126,7 +35126,7 @@
       </c>
       <c r="K716" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L716" s="3" t="inlineStr"/>
@@ -35174,7 +35174,7 @@
       </c>
       <c r="K717" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L717" s="6" t="inlineStr"/>
@@ -35222,7 +35222,7 @@
       </c>
       <c r="K718" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L718" s="3" t="inlineStr"/>
@@ -35270,7 +35270,7 @@
       </c>
       <c r="K719" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L719" s="6" t="inlineStr"/>
@@ -35318,7 +35318,7 @@
       </c>
       <c r="K720" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L720" s="3" t="inlineStr"/>
@@ -35366,7 +35366,7 @@
       </c>
       <c r="K721" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L721" s="6" t="inlineStr"/>
@@ -35414,7 +35414,7 @@
       </c>
       <c r="K722" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L722" s="3" t="inlineStr"/>
@@ -35462,7 +35462,7 @@
       </c>
       <c r="K723" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L723" s="6" t="inlineStr"/>
@@ -35510,7 +35510,7 @@
       </c>
       <c r="K724" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L724" s="3" t="inlineStr"/>
@@ -35558,7 +35558,7 @@
       </c>
       <c r="K725" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L725" s="6" t="inlineStr"/>
@@ -35606,7 +35606,7 @@
       </c>
       <c r="K726" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L726" s="3" t="inlineStr"/>
@@ -35654,7 +35654,7 @@
       </c>
       <c r="K727" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L727" s="6" t="inlineStr"/>
@@ -35702,7 +35702,7 @@
       </c>
       <c r="K728" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L728" s="3" t="inlineStr"/>
@@ -35750,7 +35750,7 @@
       </c>
       <c r="K729" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L729" s="4" t="inlineStr">
@@ -35802,7 +35802,7 @@
       </c>
       <c r="K730" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L730" s="4" t="inlineStr">
@@ -35854,7 +35854,7 @@
       </c>
       <c r="K731" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L731" s="4" t="inlineStr">
@@ -35906,7 +35906,7 @@
       </c>
       <c r="K732" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L732" s="4" t="inlineStr">
@@ -35958,7 +35958,7 @@
       </c>
       <c r="K733" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L733" s="4" t="inlineStr">
@@ -36010,7 +36010,7 @@
       </c>
       <c r="K734" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L734" s="4" t="inlineStr">
@@ -36062,7 +36062,7 @@
       </c>
       <c r="K735" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L735" s="4" t="inlineStr">
@@ -36114,7 +36114,7 @@
       </c>
       <c r="K736" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L736" s="4" t="inlineStr">
@@ -36166,7 +36166,7 @@
       </c>
       <c r="K737" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L737" s="4" t="inlineStr">
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K738" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L738" s="4" t="inlineStr">
@@ -36270,7 +36270,7 @@
       </c>
       <c r="K739" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L739" s="4" t="inlineStr">
@@ -36322,7 +36322,7 @@
       </c>
       <c r="K740" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L740" s="4" t="inlineStr">
@@ -36374,7 +36374,7 @@
       </c>
       <c r="K741" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L741" s="4" t="inlineStr">
@@ -36426,7 +36426,7 @@
       </c>
       <c r="K742" s="3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L742" s="4" t="inlineStr">
@@ -36478,7 +36478,7 @@
       </c>
       <c r="K743" s="6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="L743" s="4" t="inlineStr">

--- a/public/loop-library.xlsx
+++ b/public/loop-library.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr"/>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr"/>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr"/>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr"/>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr"/>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr"/>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr"/>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr"/>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr"/>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr"/>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr"/>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr"/>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr"/>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr"/>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr"/>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr"/>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr"/>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr"/>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr"/>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr"/>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L93" s="6" t="inlineStr"/>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr"/>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L95" s="6" t="inlineStr"/>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr"/>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L97" s="6" t="inlineStr"/>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr"/>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr"/>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr"/>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr"/>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L102" s="3" t="inlineStr"/>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L103" s="6" t="inlineStr"/>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L104" s="3" t="inlineStr"/>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L105" s="6" t="inlineStr"/>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L106" s="3" t="inlineStr"/>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L107" s="6" t="inlineStr"/>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L108" s="3" t="inlineStr"/>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L109" s="6" t="inlineStr"/>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L110" s="3" t="inlineStr"/>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L111" s="6" t="inlineStr"/>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L112" s="3" t="inlineStr"/>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L113" s="6" t="inlineStr"/>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L114" s="3" t="inlineStr"/>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L115" s="6" t="inlineStr"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="K116" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L116" s="3" t="inlineStr"/>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L117" s="6" t="inlineStr"/>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="K118" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L118" s="3" t="inlineStr"/>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L119" s="6" t="inlineStr"/>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="K120" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L120" s="3" t="inlineStr"/>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L121" s="6" t="inlineStr"/>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="K122" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L122" s="3" t="inlineStr"/>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L123" s="6" t="inlineStr"/>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="K124" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L124" s="3" t="inlineStr"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="K125" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L125" s="6" t="inlineStr"/>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="K126" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L126" s="3" t="inlineStr"/>
@@ -6854,7 +6854,7 @@
       </c>
       <c r="K127" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L127" s="6" t="inlineStr"/>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L128" s="3" t="inlineStr"/>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="K129" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L129" s="6" t="inlineStr"/>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="K130" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L130" s="3" t="inlineStr"/>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="K131" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L131" s="6" t="inlineStr"/>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L132" s="3" t="inlineStr"/>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="K133" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L133" s="6" t="inlineStr"/>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="K134" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L134" s="3" t="inlineStr"/>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="K135" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L135" s="6" t="inlineStr"/>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="K136" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L136" s="3" t="inlineStr"/>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="K137" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L137" s="6" t="inlineStr"/>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="K138" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L138" s="3" t="inlineStr"/>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="K139" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L139" s="6" t="inlineStr"/>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="K140" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L140" s="3" t="inlineStr"/>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="K141" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L141" s="6" t="inlineStr"/>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L142" s="3" t="inlineStr"/>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="K143" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L143" s="6" t="inlineStr"/>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="K144" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L144" s="3" t="inlineStr"/>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="K145" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L145" s="6" t="inlineStr"/>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="K146" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L146" s="3" t="inlineStr"/>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="K147" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L147" s="6" t="inlineStr"/>
@@ -7862,7 +7862,7 @@
       </c>
       <c r="K148" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L148" s="3" t="inlineStr"/>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="K149" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L149" s="6" t="inlineStr"/>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="K150" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L150" s="3" t="inlineStr"/>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="K151" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L151" s="6" t="inlineStr"/>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="K152" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L152" s="3" t="inlineStr"/>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="K153" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L153" s="6" t="inlineStr"/>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="K154" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L154" s="3" t="inlineStr"/>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="K155" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L155" s="6" t="inlineStr"/>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="K156" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L156" s="3" t="inlineStr"/>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K157" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L157" s="6" t="inlineStr"/>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="K158" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L158" s="3" t="inlineStr"/>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="K159" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L159" s="6" t="inlineStr"/>
@@ -8438,7 +8438,7 @@
       </c>
       <c r="K160" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L160" s="3" t="inlineStr"/>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="K161" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L161" s="6" t="inlineStr"/>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="K162" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L162" s="3" t="inlineStr"/>
@@ -8582,7 +8582,7 @@
       </c>
       <c r="K163" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L163" s="6" t="inlineStr"/>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="K164" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L164" s="3" t="inlineStr"/>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="K165" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L165" s="6" t="inlineStr"/>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="K166" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L166" s="3" t="inlineStr"/>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="K167" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L167" s="6" t="inlineStr"/>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="K168" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L168" s="3" t="inlineStr"/>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="K169" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L169" s="6" t="inlineStr"/>
@@ -8918,7 +8918,7 @@
       </c>
       <c r="K170" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L170" s="3" t="inlineStr"/>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="K171" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L171" s="6" t="inlineStr"/>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="K172" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L172" s="3" t="inlineStr"/>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="K173" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L173" s="6" t="inlineStr"/>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="K174" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L174" s="3" t="inlineStr"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="K175" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L175" s="6" t="inlineStr"/>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="K176" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L176" s="3" t="inlineStr"/>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="K177" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L177" s="6" t="inlineStr"/>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="K178" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L178" s="3" t="inlineStr"/>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="K179" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L179" s="6" t="inlineStr"/>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="K180" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L180" s="3" t="inlineStr"/>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="K181" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L181" s="6" t="inlineStr"/>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="K182" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L182" s="3" t="inlineStr"/>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="K183" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L183" s="6" t="inlineStr"/>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="K184" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L184" s="3" t="inlineStr"/>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="K185" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L185" s="6" t="inlineStr"/>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="K186" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L186" s="3" t="inlineStr"/>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="K187" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L187" s="6" t="inlineStr"/>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="K188" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L188" s="3" t="inlineStr"/>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="K189" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L189" s="6" t="inlineStr"/>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="K190" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L190" s="3" t="inlineStr"/>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="K191" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L191" s="6" t="inlineStr"/>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="K192" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L192" s="3" t="inlineStr"/>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="K193" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L193" s="6" t="inlineStr"/>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="K194" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L194" s="3" t="inlineStr"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="K195" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L195" s="6" t="inlineStr"/>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="K196" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L196" s="3" t="inlineStr"/>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="K197" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L197" s="6" t="inlineStr"/>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="K198" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L198" s="3" t="inlineStr"/>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="K199" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L199" s="6" t="inlineStr"/>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="K200" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L200" s="3" t="inlineStr"/>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="K201" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L201" s="6" t="inlineStr"/>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="K202" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L202" s="3" t="inlineStr"/>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="K203" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L203" s="6" t="inlineStr"/>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="K204" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L204" s="3" t="inlineStr"/>
@@ -10598,7 +10598,7 @@
       </c>
       <c r="K205" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L205" s="6" t="inlineStr"/>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K206" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L206" s="3" t="inlineStr"/>
@@ -10694,7 +10694,7 @@
       </c>
       <c r="K207" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L207" s="6" t="inlineStr"/>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="K208" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L208" s="3" t="inlineStr"/>
@@ -10790,7 +10790,7 @@
       </c>
       <c r="K209" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L209" s="6" t="inlineStr"/>
@@ -10838,7 +10838,7 @@
       </c>
       <c r="K210" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L210" s="3" t="inlineStr"/>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="K211" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L211" s="6" t="inlineStr"/>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="K212" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L212" s="3" t="inlineStr"/>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="K213" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L213" s="6" t="inlineStr"/>
@@ -11030,7 +11030,7 @@
       </c>
       <c r="K214" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L214" s="3" t="inlineStr"/>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="K215" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L215" s="6" t="inlineStr"/>
@@ -11126,7 +11126,7 @@
       </c>
       <c r="K216" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L216" s="3" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="K217" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L217" s="6" t="inlineStr"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="K218" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L218" s="3" t="inlineStr"/>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="K219" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L219" s="6" t="inlineStr"/>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="K220" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L220" s="3" t="inlineStr"/>
@@ -11366,7 +11366,7 @@
       </c>
       <c r="K221" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L221" s="6" t="inlineStr"/>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="K222" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L222" s="3" t="inlineStr"/>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="K223" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L223" s="6" t="inlineStr"/>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="K224" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L224" s="3" t="inlineStr"/>
@@ -11558,7 +11558,7 @@
       </c>
       <c r="K225" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L225" s="6" t="inlineStr"/>
@@ -11606,7 +11606,7 @@
       </c>
       <c r="K226" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L226" s="3" t="inlineStr"/>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="K227" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L227" s="6" t="inlineStr"/>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="K228" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L228" s="3" t="inlineStr"/>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="K229" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L229" s="6" t="inlineStr"/>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="K230" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L230" s="3" t="inlineStr"/>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="K231" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L231" s="6" t="inlineStr"/>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="K232" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L232" s="3" t="inlineStr"/>
@@ -11942,7 +11942,7 @@
       </c>
       <c r="K233" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L233" s="6" t="inlineStr"/>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="K234" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L234" s="3" t="inlineStr"/>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="K235" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L235" s="6" t="inlineStr"/>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="K236" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L236" s="3" t="inlineStr"/>
@@ -12134,7 +12134,7 @@
       </c>
       <c r="K237" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L237" s="6" t="inlineStr"/>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="K238" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L238" s="3" t="inlineStr"/>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="K239" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L239" s="6" t="inlineStr"/>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="K240" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L240" s="3" t="inlineStr"/>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="K241" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L241" s="6" t="inlineStr"/>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="K242" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L242" s="3" t="inlineStr"/>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="K243" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L243" s="6" t="inlineStr"/>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="K244" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L244" s="3" t="inlineStr"/>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="K245" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L245" s="6" t="inlineStr"/>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="K246" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L246" s="3" t="inlineStr"/>
@@ -12614,7 +12614,7 @@
       </c>
       <c r="K247" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L247" s="6" t="inlineStr"/>
@@ -12662,7 +12662,7 @@
       </c>
       <c r="K248" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L248" s="3" t="inlineStr"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="K249" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L249" s="6" t="inlineStr"/>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="K250" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L250" s="3" t="inlineStr"/>
@@ -12806,7 +12806,7 @@
       </c>
       <c r="K251" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L251" s="6" t="inlineStr"/>
@@ -12854,7 +12854,7 @@
       </c>
       <c r="K252" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L252" s="3" t="inlineStr"/>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="K253" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L253" s="6" t="inlineStr"/>
@@ -12950,7 +12950,7 @@
       </c>
       <c r="K254" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L254" s="3" t="inlineStr"/>
@@ -12998,7 +12998,7 @@
       </c>
       <c r="K255" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L255" s="6" t="inlineStr"/>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="K256" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L256" s="3" t="inlineStr"/>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="K257" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L257" s="6" t="inlineStr"/>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="K258" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L258" s="3" t="inlineStr"/>
@@ -13190,7 +13190,7 @@
       </c>
       <c r="K259" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L259" s="6" t="inlineStr"/>
@@ -13238,7 +13238,7 @@
       </c>
       <c r="K260" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L260" s="3" t="inlineStr"/>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="K261" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L261" s="6" t="inlineStr"/>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="K262" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L262" s="3" t="inlineStr"/>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="K263" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L263" s="6" t="inlineStr"/>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="K264" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L264" s="3" t="inlineStr"/>
@@ -13478,7 +13478,7 @@
       </c>
       <c r="K265" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L265" s="6" t="inlineStr"/>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="K266" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L266" s="3" t="inlineStr"/>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="K267" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L267" s="6" t="inlineStr"/>
@@ -13622,7 +13622,7 @@
       </c>
       <c r="K268" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L268" s="3" t="inlineStr"/>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="K269" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L269" s="6" t="inlineStr"/>
@@ -13718,7 +13718,7 @@
       </c>
       <c r="K270" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L270" s="3" t="inlineStr"/>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="K271" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L271" s="6" t="inlineStr"/>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="K272" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L272" s="3" t="inlineStr"/>
@@ -13862,7 +13862,7 @@
       </c>
       <c r="K273" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L273" s="6" t="inlineStr"/>
@@ -13910,7 +13910,7 @@
       </c>
       <c r="K274" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L274" s="3" t="inlineStr"/>
@@ -13958,7 +13958,7 @@
       </c>
       <c r="K275" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L275" s="6" t="inlineStr"/>
@@ -14006,7 +14006,7 @@
       </c>
       <c r="K276" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L276" s="3" t="inlineStr"/>
@@ -14054,7 +14054,7 @@
       </c>
       <c r="K277" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L277" s="6" t="inlineStr"/>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="K278" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L278" s="3" t="inlineStr"/>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="K279" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L279" s="6" t="inlineStr"/>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="K280" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L280" s="3" t="inlineStr"/>
@@ -14246,7 +14246,7 @@
       </c>
       <c r="K281" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L281" s="6" t="inlineStr"/>
@@ -14294,7 +14294,7 @@
       </c>
       <c r="K282" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L282" s="3" t="inlineStr"/>
@@ -14342,7 +14342,7 @@
       </c>
       <c r="K283" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L283" s="6" t="inlineStr"/>
@@ -14390,7 +14390,7 @@
       </c>
       <c r="K284" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L284" s="3" t="inlineStr"/>
@@ -14438,7 +14438,7 @@
       </c>
       <c r="K285" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L285" s="6" t="inlineStr"/>
@@ -14486,7 +14486,7 @@
       </c>
       <c r="K286" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L286" s="3" t="inlineStr"/>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="K287" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L287" s="6" t="inlineStr"/>
@@ -14582,7 +14582,7 @@
       </c>
       <c r="K288" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L288" s="3" t="inlineStr"/>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="K289" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L289" s="6" t="inlineStr"/>
@@ -14678,7 +14678,7 @@
       </c>
       <c r="K290" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L290" s="3" t="inlineStr"/>
@@ -14726,7 +14726,7 @@
       </c>
       <c r="K291" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L291" s="6" t="inlineStr"/>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="K292" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L292" s="3" t="inlineStr"/>
@@ -14822,7 +14822,7 @@
       </c>
       <c r="K293" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L293" s="6" t="inlineStr"/>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="K294" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L294" s="3" t="inlineStr"/>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="K295" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L295" s="6" t="inlineStr"/>
@@ -14966,7 +14966,7 @@
       </c>
       <c r="K296" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L296" s="3" t="inlineStr"/>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="K297" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L297" s="6" t="inlineStr"/>
@@ -15062,7 +15062,7 @@
       </c>
       <c r="K298" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L298" s="3" t="inlineStr"/>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="K299" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L299" s="6" t="inlineStr"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="K300" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L300" s="3" t="inlineStr"/>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="K301" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L301" s="6" t="inlineStr"/>
@@ -15254,7 +15254,7 @@
       </c>
       <c r="K302" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L302" s="3" t="inlineStr"/>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="K303" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L303" s="6" t="inlineStr"/>
@@ -15350,7 +15350,7 @@
       </c>
       <c r="K304" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L304" s="3" t="inlineStr"/>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="K305" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L305" s="6" t="inlineStr"/>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="K306" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L306" s="3" t="inlineStr"/>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="K307" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L307" s="6" t="inlineStr"/>
@@ -15542,7 +15542,7 @@
       </c>
       <c r="K308" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L308" s="3" t="inlineStr"/>
@@ -15590,7 +15590,7 @@
       </c>
       <c r="K309" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L309" s="6" t="inlineStr"/>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="K310" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L310" s="3" t="inlineStr"/>
@@ -15686,7 +15686,7 @@
       </c>
       <c r="K311" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L311" s="6" t="inlineStr"/>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="K312" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L312" s="3" t="inlineStr"/>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="K313" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L313" s="6" t="inlineStr"/>
@@ -15830,7 +15830,7 @@
       </c>
       <c r="K314" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L314" s="3" t="inlineStr"/>
@@ -15878,7 +15878,7 @@
       </c>
       <c r="K315" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L315" s="6" t="inlineStr"/>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="K316" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L316" s="3" t="inlineStr"/>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="K317" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L317" s="6" t="inlineStr"/>
@@ -16022,7 +16022,7 @@
       </c>
       <c r="K318" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L318" s="3" t="inlineStr"/>
@@ -16070,7 +16070,7 @@
       </c>
       <c r="K319" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L319" s="6" t="inlineStr"/>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="K320" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L320" s="3" t="inlineStr"/>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="K321" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L321" s="6" t="inlineStr"/>
@@ -16214,7 +16214,7 @@
       </c>
       <c r="K322" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L322" s="3" t="inlineStr"/>
@@ -16262,7 +16262,7 @@
       </c>
       <c r="K323" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L323" s="6" t="inlineStr"/>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="K324" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L324" s="3" t="inlineStr"/>
@@ -16358,7 +16358,7 @@
       </c>
       <c r="K325" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L325" s="6" t="inlineStr"/>
@@ -16406,7 +16406,7 @@
       </c>
       <c r="K326" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L326" s="3" t="inlineStr"/>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="K327" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L327" s="6" t="inlineStr"/>
@@ -16502,7 +16502,7 @@
       </c>
       <c r="K328" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L328" s="3" t="inlineStr"/>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="K329" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L329" s="6" t="inlineStr"/>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="K330" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L330" s="3" t="inlineStr"/>
@@ -16646,7 +16646,7 @@
       </c>
       <c r="K331" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L331" s="6" t="inlineStr"/>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="K332" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L332" s="3" t="inlineStr"/>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="K333" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L333" s="6" t="inlineStr"/>
@@ -16790,7 +16790,7 @@
       </c>
       <c r="K334" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L334" s="3" t="inlineStr"/>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="K335" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L335" s="6" t="inlineStr"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="K336" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L336" s="3" t="inlineStr"/>
@@ -16934,7 +16934,7 @@
       </c>
       <c r="K337" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L337" s="6" t="inlineStr"/>
@@ -16982,7 +16982,7 @@
       </c>
       <c r="K338" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L338" s="3" t="inlineStr"/>
@@ -17030,7 +17030,7 @@
       </c>
       <c r="K339" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L339" s="6" t="inlineStr"/>
@@ -17078,7 +17078,7 @@
       </c>
       <c r="K340" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L340" s="3" t="inlineStr"/>
@@ -17126,7 +17126,7 @@
       </c>
       <c r="K341" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L341" s="6" t="inlineStr"/>
@@ -17174,7 +17174,7 @@
       </c>
       <c r="K342" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L342" s="3" t="inlineStr"/>
@@ -17222,7 +17222,7 @@
       </c>
       <c r="K343" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L343" s="6" t="inlineStr"/>
@@ -17270,7 +17270,7 @@
       </c>
       <c r="K344" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L344" s="3" t="inlineStr"/>
@@ -17318,7 +17318,7 @@
       </c>
       <c r="K345" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L345" s="6" t="inlineStr"/>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="K346" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L346" s="3" t="inlineStr"/>
@@ -17414,7 +17414,7 @@
       </c>
       <c r="K347" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L347" s="6" t="inlineStr"/>
@@ -17462,7 +17462,7 @@
       </c>
       <c r="K348" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L348" s="3" t="inlineStr"/>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="K349" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L349" s="6" t="inlineStr"/>
@@ -17558,7 +17558,7 @@
       </c>
       <c r="K350" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L350" s="3" t="inlineStr"/>
@@ -17606,7 +17606,7 @@
       </c>
       <c r="K351" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L351" s="6" t="inlineStr"/>
@@ -17654,7 +17654,7 @@
       </c>
       <c r="K352" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L352" s="3" t="inlineStr"/>
@@ -17702,7 +17702,7 @@
       </c>
       <c r="K353" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L353" s="6" t="inlineStr"/>
@@ -17750,7 +17750,7 @@
       </c>
       <c r="K354" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L354" s="3" t="inlineStr"/>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="K355" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L355" s="6" t="inlineStr"/>
@@ -17846,7 +17846,7 @@
       </c>
       <c r="K356" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L356" s="3" t="inlineStr"/>
@@ -17894,7 +17894,7 @@
       </c>
       <c r="K357" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L357" s="6" t="inlineStr"/>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="K358" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L358" s="3" t="inlineStr"/>
@@ -17990,7 +17990,7 @@
       </c>
       <c r="K359" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L359" s="6" t="inlineStr"/>
@@ -18038,7 +18038,7 @@
       </c>
       <c r="K360" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L360" s="3" t="inlineStr"/>
@@ -18086,7 +18086,7 @@
       </c>
       <c r="K361" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L361" s="6" t="inlineStr"/>
@@ -18134,7 +18134,7 @@
       </c>
       <c r="K362" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L362" s="3" t="inlineStr"/>
@@ -18182,7 +18182,7 @@
       </c>
       <c r="K363" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L363" s="6" t="inlineStr"/>
@@ -18230,7 +18230,7 @@
       </c>
       <c r="K364" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L364" s="3" t="inlineStr"/>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="K365" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L365" s="6" t="inlineStr"/>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="K366" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L366" s="3" t="inlineStr"/>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="K367" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L367" s="6" t="inlineStr"/>
@@ -18422,7 +18422,7 @@
       </c>
       <c r="K368" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L368" s="3" t="inlineStr"/>
@@ -18470,7 +18470,7 @@
       </c>
       <c r="K369" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L369" s="6" t="inlineStr"/>
@@ -18518,7 +18518,7 @@
       </c>
       <c r="K370" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L370" s="3" t="inlineStr"/>
@@ -18566,7 +18566,7 @@
       </c>
       <c r="K371" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L371" s="6" t="inlineStr"/>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="K372" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L372" s="3" t="inlineStr"/>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="K373" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L373" s="6" t="inlineStr"/>
@@ -18710,7 +18710,7 @@
       </c>
       <c r="K374" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L374" s="3" t="inlineStr"/>
@@ -18758,7 +18758,7 @@
       </c>
       <c r="K375" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L375" s="6" t="inlineStr"/>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="K376" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L376" s="3" t="inlineStr"/>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="K377" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L377" s="6" t="inlineStr"/>
@@ -18902,7 +18902,7 @@
       </c>
       <c r="K378" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L378" s="3" t="inlineStr"/>
@@ -18950,7 +18950,7 @@
       </c>
       <c r="K379" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L379" s="6" t="inlineStr"/>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="K380" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L380" s="3" t="inlineStr"/>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="K381" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L381" s="6" t="inlineStr"/>
@@ -19094,7 +19094,7 @@
       </c>
       <c r="K382" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L382" s="3" t="inlineStr"/>
@@ -19142,7 +19142,7 @@
       </c>
       <c r="K383" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L383" s="6" t="inlineStr"/>
@@ -19190,7 +19190,7 @@
       </c>
       <c r="K384" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L384" s="3" t="inlineStr"/>
@@ -19238,7 +19238,7 @@
       </c>
       <c r="K385" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L385" s="6" t="inlineStr"/>
@@ -19286,7 +19286,7 @@
       </c>
       <c r="K386" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L386" s="3" t="inlineStr"/>
@@ -19334,7 +19334,7 @@
       </c>
       <c r="K387" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L387" s="6" t="inlineStr"/>
@@ -19382,7 +19382,7 @@
       </c>
       <c r="K388" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L388" s="3" t="inlineStr"/>
@@ -19430,7 +19430,7 @@
       </c>
       <c r="K389" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L389" s="6" t="inlineStr"/>
@@ -19478,7 +19478,7 @@
       </c>
       <c r="K390" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L390" s="3" t="inlineStr"/>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="K391" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L391" s="6" t="inlineStr"/>
@@ -19574,7 +19574,7 @@
       </c>
       <c r="K392" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L392" s="3" t="inlineStr"/>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="K393" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L393" s="6" t="inlineStr"/>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="K394" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L394" s="3" t="inlineStr"/>
@@ -19718,7 +19718,7 @@
       </c>
       <c r="K395" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L395" s="6" t="inlineStr"/>
@@ -19766,7 +19766,7 @@
       </c>
       <c r="K396" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L396" s="3" t="inlineStr"/>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="K397" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L397" s="6" t="inlineStr"/>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="K398" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L398" s="3" t="inlineStr"/>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="K399" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L399" s="6" t="inlineStr"/>
@@ -19958,7 +19958,7 @@
       </c>
       <c r="K400" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L400" s="3" t="inlineStr"/>
@@ -20006,7 +20006,7 @@
       </c>
       <c r="K401" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L401" s="6" t="inlineStr"/>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="K402" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L402" s="3" t="inlineStr"/>
@@ -20102,7 +20102,7 @@
       </c>
       <c r="K403" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L403" s="6" t="inlineStr"/>
@@ -20150,7 +20150,7 @@
       </c>
       <c r="K404" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L404" s="3" t="inlineStr"/>
@@ -20198,7 +20198,7 @@
       </c>
       <c r="K405" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L405" s="6" t="inlineStr"/>
@@ -20246,7 +20246,7 @@
       </c>
       <c r="K406" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L406" s="3" t="inlineStr"/>
@@ -20294,7 +20294,7 @@
       </c>
       <c r="K407" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L407" s="6" t="inlineStr"/>
@@ -20342,7 +20342,7 @@
       </c>
       <c r="K408" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L408" s="3" t="inlineStr"/>
@@ -20390,7 +20390,7 @@
       </c>
       <c r="K409" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L409" s="6" t="inlineStr"/>
@@ -20438,7 +20438,7 @@
       </c>
       <c r="K410" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L410" s="3" t="inlineStr"/>
@@ -20486,7 +20486,7 @@
       </c>
       <c r="K411" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L411" s="6" t="inlineStr"/>
@@ -20534,7 +20534,7 @@
       </c>
       <c r="K412" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L412" s="3" t="inlineStr"/>
@@ -20582,7 +20582,7 @@
       </c>
       <c r="K413" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L413" s="6" t="inlineStr"/>
@@ -20630,7 +20630,7 @@
       </c>
       <c r="K414" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L414" s="3" t="inlineStr"/>
@@ -20678,7 +20678,7 @@
       </c>
       <c r="K415" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L415" s="6" t="inlineStr"/>
@@ -20726,7 +20726,7 @@
       </c>
       <c r="K416" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L416" s="3" t="inlineStr"/>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="K417" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L417" s="6" t="inlineStr"/>
@@ -20822,7 +20822,7 @@
       </c>
       <c r="K418" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L418" s="3" t="inlineStr"/>
@@ -20870,7 +20870,7 @@
       </c>
       <c r="K419" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L419" s="6" t="inlineStr"/>
@@ -20918,7 +20918,7 @@
       </c>
       <c r="K420" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L420" s="3" t="inlineStr"/>
@@ -20966,7 +20966,7 @@
       </c>
       <c r="K421" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L421" s="6" t="inlineStr"/>
@@ -21014,7 +21014,7 @@
       </c>
       <c r="K422" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L422" s="3" t="inlineStr"/>
@@ -21062,7 +21062,7 @@
       </c>
       <c r="K423" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L423" s="6" t="inlineStr"/>
@@ -21110,7 +21110,7 @@
       </c>
       <c r="K424" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L424" s="3" t="inlineStr"/>
@@ -21158,7 +21158,7 @@
       </c>
       <c r="K425" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L425" s="6" t="inlineStr"/>
@@ -21206,7 +21206,7 @@
       </c>
       <c r="K426" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L426" s="3" t="inlineStr"/>
@@ -21254,7 +21254,7 @@
       </c>
       <c r="K427" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L427" s="6" t="inlineStr"/>
@@ -21302,7 +21302,7 @@
       </c>
       <c r="K428" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L428" s="3" t="inlineStr"/>
@@ -21350,7 +21350,7 @@
       </c>
       <c r="K429" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L429" s="6" t="inlineStr"/>
@@ -21398,7 +21398,7 @@
       </c>
       <c r="K430" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L430" s="3" t="inlineStr"/>
@@ -21446,7 +21446,7 @@
       </c>
       <c r="K431" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L431" s="6" t="inlineStr"/>
@@ -21494,7 +21494,7 @@
       </c>
       <c r="K432" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L432" s="3" t="inlineStr"/>
@@ -21542,7 +21542,7 @@
       </c>
       <c r="K433" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L433" s="6" t="inlineStr"/>
@@ -21590,7 +21590,7 @@
       </c>
       <c r="K434" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L434" s="3" t="inlineStr"/>
@@ -21638,7 +21638,7 @@
       </c>
       <c r="K435" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L435" s="6" t="inlineStr"/>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="K436" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L436" s="3" t="inlineStr"/>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="K437" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L437" s="6" t="inlineStr"/>
@@ -21782,7 +21782,7 @@
       </c>
       <c r="K438" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L438" s="3" t="inlineStr"/>
@@ -21830,7 +21830,7 @@
       </c>
       <c r="K439" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L439" s="6" t="inlineStr"/>
@@ -21878,7 +21878,7 @@
       </c>
       <c r="K440" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L440" s="3" t="inlineStr"/>
@@ -21926,7 +21926,7 @@
       </c>
       <c r="K441" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L441" s="6" t="inlineStr"/>
@@ -21974,7 +21974,7 @@
       </c>
       <c r="K442" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L442" s="3" t="inlineStr"/>
@@ -22022,7 +22022,7 @@
       </c>
       <c r="K443" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L443" s="6" t="inlineStr"/>
@@ -22070,7 +22070,7 @@
       </c>
       <c r="K444" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L444" s="3" t="inlineStr"/>
@@ -22118,7 +22118,7 @@
       </c>
       <c r="K445" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L445" s="6" t="inlineStr"/>
@@ -22166,7 +22166,7 @@
       </c>
       <c r="K446" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L446" s="3" t="inlineStr"/>
@@ -22214,7 +22214,7 @@
       </c>
       <c r="K447" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L447" s="6" t="inlineStr"/>
@@ -22262,7 +22262,7 @@
       </c>
       <c r="K448" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L448" s="3" t="inlineStr"/>
@@ -22310,7 +22310,7 @@
       </c>
       <c r="K449" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L449" s="6" t="inlineStr"/>
@@ -22358,7 +22358,7 @@
       </c>
       <c r="K450" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L450" s="3" t="inlineStr"/>
@@ -22406,7 +22406,7 @@
       </c>
       <c r="K451" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L451" s="6" t="inlineStr"/>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="K452" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L452" s="3" t="inlineStr"/>
@@ -22502,7 +22502,7 @@
       </c>
       <c r="K453" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L453" s="6" t="inlineStr"/>
@@ -22550,7 +22550,7 @@
       </c>
       <c r="K454" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L454" s="3" t="inlineStr"/>
@@ -22598,7 +22598,7 @@
       </c>
       <c r="K455" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L455" s="6" t="inlineStr"/>
@@ -22646,7 +22646,7 @@
       </c>
       <c r="K456" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L456" s="3" t="inlineStr"/>
@@ -22694,7 +22694,7 @@
       </c>
       <c r="K457" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L457" s="6" t="inlineStr"/>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="K458" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L458" s="3" t="inlineStr"/>
@@ -22790,7 +22790,7 @@
       </c>
       <c r="K459" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L459" s="6" t="inlineStr"/>
@@ -22838,7 +22838,7 @@
       </c>
       <c r="K460" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L460" s="3" t="inlineStr"/>
@@ -22886,7 +22886,7 @@
       </c>
       <c r="K461" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L461" s="6" t="inlineStr"/>
@@ -22934,7 +22934,7 @@
       </c>
       <c r="K462" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L462" s="3" t="inlineStr"/>
@@ -22982,7 +22982,7 @@
       </c>
       <c r="K463" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L463" s="6" t="inlineStr"/>
@@ -23030,7 +23030,7 @@
       </c>
       <c r="K464" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L464" s="3" t="inlineStr"/>
@@ -23078,7 +23078,7 @@
       </c>
       <c r="K465" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L465" s="6" t="inlineStr"/>
@@ -23126,7 +23126,7 @@
       </c>
       <c r="K466" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L466" s="3" t="inlineStr"/>
@@ -23174,7 +23174,7 @@
       </c>
       <c r="K467" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L467" s="6" t="inlineStr"/>
@@ -23222,7 +23222,7 @@
       </c>
       <c r="K468" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L468" s="3" t="inlineStr"/>
@@ -23270,7 +23270,7 @@
       </c>
       <c r="K469" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L469" s="6" t="inlineStr"/>
@@ -23318,7 +23318,7 @@
       </c>
       <c r="K470" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L470" s="3" t="inlineStr"/>
@@ -23366,7 +23366,7 @@
       </c>
       <c r="K471" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L471" s="6" t="inlineStr"/>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="K472" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L472" s="3" t="inlineStr"/>
@@ -23462,7 +23462,7 @@
       </c>
       <c r="K473" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L473" s="6" t="inlineStr"/>
@@ -23510,7 +23510,7 @@
       </c>
       <c r="K474" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L474" s="3" t="inlineStr"/>
@@ -23558,7 +23558,7 @@
       </c>
       <c r="K475" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L475" s="6" t="inlineStr"/>
@@ -23606,7 +23606,7 @@
       </c>
       <c r="K476" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L476" s="3" t="inlineStr"/>
@@ -23654,7 +23654,7 @@
       </c>
       <c r="K477" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L477" s="6" t="inlineStr"/>
@@ -23702,7 +23702,7 @@
       </c>
       <c r="K478" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L478" s="3" t="inlineStr"/>
@@ -23750,7 +23750,7 @@
       </c>
       <c r="K479" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L479" s="6" t="inlineStr"/>
@@ -23798,7 +23798,7 @@
       </c>
       <c r="K480" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L480" s="3" t="inlineStr"/>
@@ -23846,7 +23846,7 @@
       </c>
       <c r="K481" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L481" s="6" t="inlineStr"/>
@@ -23894,7 +23894,7 @@
       </c>
       <c r="K482" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L482" s="3" t="inlineStr"/>
@@ -23942,7 +23942,7 @@
       </c>
       <c r="K483" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L483" s="6" t="inlineStr"/>
@@ -23990,7 +23990,7 @@
       </c>
       <c r="K484" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L484" s="3" t="inlineStr"/>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="K485" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L485" s="6" t="inlineStr"/>
@@ -24086,7 +24086,7 @@
       </c>
       <c r="K486" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L486" s="3" t="inlineStr"/>
@@ -24134,7 +24134,7 @@
       </c>
       <c r="K487" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L487" s="6" t="inlineStr"/>
@@ -24182,7 +24182,7 @@
       </c>
       <c r="K488" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L488" s="3" t="inlineStr"/>
@@ -24230,7 +24230,7 @@
       </c>
       <c r="K489" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L489" s="6" t="inlineStr"/>
@@ -24278,7 +24278,7 @@
       </c>
       <c r="K490" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L490" s="3" t="inlineStr"/>
@@ -24326,7 +24326,7 @@
       </c>
       <c r="K491" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L491" s="6" t="inlineStr"/>
@@ -24374,7 +24374,7 @@
       </c>
       <c r="K492" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L492" s="3" t="inlineStr"/>
@@ -24422,7 +24422,7 @@
       </c>
       <c r="K493" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L493" s="6" t="inlineStr"/>
@@ -24470,7 +24470,7 @@
       </c>
       <c r="K494" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L494" s="3" t="inlineStr"/>
@@ -24518,7 +24518,7 @@
       </c>
       <c r="K495" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L495" s="6" t="inlineStr"/>
@@ -24566,7 +24566,7 @@
       </c>
       <c r="K496" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L496" s="3" t="inlineStr"/>
@@ -24614,7 +24614,7 @@
       </c>
       <c r="K497" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L497" s="6" t="inlineStr"/>
@@ -24662,7 +24662,7 @@
       </c>
       <c r="K498" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L498" s="3" t="inlineStr"/>
@@ -24710,7 +24710,7 @@
       </c>
       <c r="K499" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L499" s="6" t="inlineStr"/>
@@ -24758,7 +24758,7 @@
       </c>
       <c r="K500" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L500" s="3" t="inlineStr"/>
@@ -24806,7 +24806,7 @@
       </c>
       <c r="K501" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L501" s="6" t="inlineStr"/>
@@ -24854,7 +24854,7 @@
       </c>
       <c r="K502" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L502" s="3" t="inlineStr"/>
@@ -24902,7 +24902,7 @@
       </c>
       <c r="K503" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L503" s="6" t="inlineStr"/>
@@ -24950,7 +24950,7 @@
       </c>
       <c r="K504" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L504" s="3" t="inlineStr"/>
@@ -24998,7 +24998,7 @@
       </c>
       <c r="K505" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L505" s="6" t="inlineStr"/>
@@ -25046,7 +25046,7 @@
       </c>
       <c r="K506" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L506" s="3" t="inlineStr"/>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="K507" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L507" s="6" t="inlineStr"/>
@@ -25142,7 +25142,7 @@
       </c>
       <c r="K508" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L508" s="3" t="inlineStr"/>
@@ -25190,7 +25190,7 @@
       </c>
       <c r="K509" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L509" s="6" t="inlineStr"/>
@@ -25238,7 +25238,7 @@
       </c>
       <c r="K510" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L510" s="3" t="inlineStr"/>
@@ -25286,7 +25286,7 @@
       </c>
       <c r="K511" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L511" s="6" t="inlineStr"/>
@@ -25334,7 +25334,7 @@
       </c>
       <c r="K512" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L512" s="3" t="inlineStr"/>
@@ -25382,7 +25382,7 @@
       </c>
       <c r="K513" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L513" s="6" t="inlineStr"/>
@@ -25430,7 +25430,7 @@
       </c>
       <c r="K514" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L514" s="3" t="inlineStr"/>
@@ -25478,7 +25478,7 @@
       </c>
       <c r="K515" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L515" s="6" t="inlineStr"/>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="K516" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L516" s="3" t="inlineStr"/>
@@ -25574,7 +25574,7 @@
       </c>
       <c r="K517" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L517" s="6" t="inlineStr"/>
@@ -25622,7 +25622,7 @@
       </c>
       <c r="K518" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L518" s="3" t="inlineStr"/>
@@ -25670,7 +25670,7 @@
       </c>
       <c r="K519" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L519" s="6" t="inlineStr"/>
@@ -25718,7 +25718,7 @@
       </c>
       <c r="K520" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L520" s="3" t="inlineStr"/>
@@ -25766,7 +25766,7 @@
       </c>
       <c r="K521" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L521" s="6" t="inlineStr"/>
@@ -25814,7 +25814,7 @@
       </c>
       <c r="K522" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L522" s="3" t="inlineStr"/>
@@ -25862,7 +25862,7 @@
       </c>
       <c r="K523" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L523" s="6" t="inlineStr"/>
@@ -25910,7 +25910,7 @@
       </c>
       <c r="K524" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L524" s="3" t="inlineStr"/>
@@ -25958,7 +25958,7 @@
       </c>
       <c r="K525" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L525" s="6" t="inlineStr"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K526" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L526" s="3" t="inlineStr"/>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="K527" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L527" s="6" t="inlineStr"/>
@@ -26102,7 +26102,7 @@
       </c>
       <c r="K528" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L528" s="3" t="inlineStr"/>
@@ -26150,7 +26150,7 @@
       </c>
       <c r="K529" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L529" s="6" t="inlineStr"/>
@@ -26198,7 +26198,7 @@
       </c>
       <c r="K530" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L530" s="3" t="inlineStr"/>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="K531" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L531" s="6" t="inlineStr"/>
@@ -26294,7 +26294,7 @@
       </c>
       <c r="K532" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L532" s="3" t="inlineStr"/>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="K533" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L533" s="6" t="inlineStr"/>
@@ -26390,7 +26390,7 @@
       </c>
       <c r="K534" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L534" s="3" t="inlineStr"/>
@@ -26438,7 +26438,7 @@
       </c>
       <c r="K535" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L535" s="6" t="inlineStr"/>
@@ -26486,7 +26486,7 @@
       </c>
       <c r="K536" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L536" s="3" t="inlineStr"/>
@@ -26534,7 +26534,7 @@
       </c>
       <c r="K537" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L537" s="6" t="inlineStr"/>
@@ -26582,7 +26582,7 @@
       </c>
       <c r="K538" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L538" s="3" t="inlineStr"/>
@@ -26630,7 +26630,7 @@
       </c>
       <c r="K539" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L539" s="6" t="inlineStr"/>
@@ -26678,7 +26678,7 @@
       </c>
       <c r="K540" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L540" s="3" t="inlineStr"/>
@@ -26726,7 +26726,7 @@
       </c>
       <c r="K541" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L541" s="6" t="inlineStr"/>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="K542" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L542" s="3" t="inlineStr"/>
@@ -26822,7 +26822,7 @@
       </c>
       <c r="K543" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L543" s="6" t="inlineStr"/>
@@ -26870,7 +26870,7 @@
       </c>
       <c r="K544" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L544" s="3" t="inlineStr"/>
@@ -26918,7 +26918,7 @@
       </c>
       <c r="K545" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L545" s="6" t="inlineStr"/>
@@ -26966,7 +26966,7 @@
       </c>
       <c r="K546" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L546" s="3" t="inlineStr"/>
@@ -27014,7 +27014,7 @@
       </c>
       <c r="K547" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L547" s="6" t="inlineStr"/>
@@ -27062,7 +27062,7 @@
       </c>
       <c r="K548" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L548" s="3" t="inlineStr"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K549" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L549" s="6" t="inlineStr"/>
@@ -27158,7 +27158,7 @@
       </c>
       <c r="K550" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L550" s="3" t="inlineStr"/>
@@ -27206,7 +27206,7 @@
       </c>
       <c r="K551" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L551" s="6" t="inlineStr"/>
@@ -27254,7 +27254,7 @@
       </c>
       <c r="K552" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L552" s="3" t="inlineStr"/>
@@ -27302,7 +27302,7 @@
       </c>
       <c r="K553" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L553" s="6" t="inlineStr"/>
@@ -27350,7 +27350,7 @@
       </c>
       <c r="K554" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L554" s="3" t="inlineStr"/>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="K555" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L555" s="6" t="inlineStr"/>
@@ -27446,7 +27446,7 @@
       </c>
       <c r="K556" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L556" s="3" t="inlineStr"/>
@@ -27494,7 +27494,7 @@
       </c>
       <c r="K557" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L557" s="6" t="inlineStr"/>
@@ -27542,7 +27542,7 @@
       </c>
       <c r="K558" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L558" s="3" t="inlineStr"/>
@@ -27590,7 +27590,7 @@
       </c>
       <c r="K559" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L559" s="6" t="inlineStr"/>
@@ -27638,7 +27638,7 @@
       </c>
       <c r="K560" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L560" s="3" t="inlineStr"/>
@@ -27686,7 +27686,7 @@
       </c>
       <c r="K561" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L561" s="6" t="inlineStr"/>
@@ -27734,7 +27734,7 @@
       </c>
       <c r="K562" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L562" s="3" t="inlineStr"/>
@@ -27782,7 +27782,7 @@
       </c>
       <c r="K563" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L563" s="6" t="inlineStr"/>
@@ -27830,7 +27830,7 @@
       </c>
       <c r="K564" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L564" s="3" t="inlineStr"/>
@@ -27878,7 +27878,7 @@
       </c>
       <c r="K565" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L565" s="6" t="inlineStr"/>
@@ -27926,7 +27926,7 @@
       </c>
       <c r="K566" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L566" s="3" t="inlineStr"/>
@@ -27974,7 +27974,7 @@
       </c>
       <c r="K567" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L567" s="6" t="inlineStr"/>
@@ -28022,7 +28022,7 @@
       </c>
       <c r="K568" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L568" s="3" t="inlineStr"/>
@@ -28070,7 +28070,7 @@
       </c>
       <c r="K569" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L569" s="6" t="inlineStr"/>
@@ -28118,7 +28118,7 @@
       </c>
       <c r="K570" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L570" s="3" t="inlineStr"/>
@@ -28166,7 +28166,7 @@
       </c>
       <c r="K571" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L571" s="6" t="inlineStr"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K572" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L572" s="3" t="inlineStr"/>
@@ -28262,7 +28262,7 @@
       </c>
       <c r="K573" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L573" s="6" t="inlineStr"/>
@@ -28310,7 +28310,7 @@
       </c>
       <c r="K574" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L574" s="3" t="inlineStr"/>
@@ -28358,7 +28358,7 @@
       </c>
       <c r="K575" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L575" s="6" t="inlineStr"/>
@@ -28406,7 +28406,7 @@
       </c>
       <c r="K576" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L576" s="3" t="inlineStr"/>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="K577" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L577" s="6" t="inlineStr"/>
@@ -28502,7 +28502,7 @@
       </c>
       <c r="K578" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L578" s="3" t="inlineStr"/>
@@ -28550,7 +28550,7 @@
       </c>
       <c r="K579" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L579" s="6" t="inlineStr"/>
@@ -28598,7 +28598,7 @@
       </c>
       <c r="K580" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L580" s="3" t="inlineStr"/>
@@ -28646,7 +28646,7 @@
       </c>
       <c r="K581" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L581" s="6" t="inlineStr"/>
@@ -28694,7 +28694,7 @@
       </c>
       <c r="K582" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L582" s="3" t="inlineStr"/>
@@ -28742,7 +28742,7 @@
       </c>
       <c r="K583" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L583" s="6" t="inlineStr"/>
@@ -28790,7 +28790,7 @@
       </c>
       <c r="K584" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L584" s="3" t="inlineStr"/>
@@ -28838,7 +28838,7 @@
       </c>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L585" s="6" t="inlineStr"/>
@@ -28886,7 +28886,7 @@
       </c>
       <c r="K586" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L586" s="3" t="inlineStr"/>
@@ -28934,7 +28934,7 @@
       </c>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L587" s="6" t="inlineStr"/>
@@ -28982,7 +28982,7 @@
       </c>
       <c r="K588" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L588" s="3" t="inlineStr"/>
@@ -29030,7 +29030,7 @@
       </c>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L589" s="6" t="inlineStr"/>
@@ -29078,7 +29078,7 @@
       </c>
       <c r="K590" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L590" s="3" t="inlineStr"/>
@@ -29126,7 +29126,7 @@
       </c>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L591" s="6" t="inlineStr"/>
@@ -29174,7 +29174,7 @@
       </c>
       <c r="K592" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L592" s="3" t="inlineStr"/>
@@ -29222,7 +29222,7 @@
       </c>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L593" s="6" t="inlineStr"/>
@@ -29270,7 +29270,7 @@
       </c>
       <c r="K594" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L594" s="3" t="inlineStr"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L595" s="6" t="inlineStr"/>
@@ -29366,7 +29366,7 @@
       </c>
       <c r="K596" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L596" s="3" t="inlineStr"/>
@@ -29414,7 +29414,7 @@
       </c>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L597" s="6" t="inlineStr"/>
@@ -29462,7 +29462,7 @@
       </c>
       <c r="K598" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L598" s="3" t="inlineStr"/>
@@ -29510,7 +29510,7 @@
       </c>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L599" s="6" t="inlineStr"/>
@@ -29558,7 +29558,7 @@
       </c>
       <c r="K600" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L600" s="3" t="inlineStr"/>
@@ -29606,7 +29606,7 @@
       </c>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L601" s="6" t="inlineStr"/>
@@ -29654,7 +29654,7 @@
       </c>
       <c r="K602" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L602" s="3" t="inlineStr"/>
@@ -29702,7 +29702,7 @@
       </c>
       <c r="K603" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L603" s="6" t="inlineStr"/>
@@ -29750,7 +29750,7 @@
       </c>
       <c r="K604" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L604" s="3" t="inlineStr"/>
@@ -29798,7 +29798,7 @@
       </c>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr"/>
@@ -29846,7 +29846,7 @@
       </c>
       <c r="K606" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L606" s="3" t="inlineStr"/>
@@ -29894,7 +29894,7 @@
       </c>
       <c r="K607" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L607" s="6" t="inlineStr"/>
@@ -29942,7 +29942,7 @@
       </c>
       <c r="K608" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L608" s="3" t="inlineStr"/>
@@ -29990,7 +29990,7 @@
       </c>
       <c r="K609" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L609" s="6" t="inlineStr"/>
@@ -30038,7 +30038,7 @@
       </c>
       <c r="K610" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L610" s="3" t="inlineStr"/>
@@ -30086,7 +30086,7 @@
       </c>
       <c r="K611" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L611" s="6" t="inlineStr"/>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="K612" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L612" s="3" t="inlineStr"/>
@@ -30182,7 +30182,7 @@
       </c>
       <c r="K613" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L613" s="6" t="inlineStr"/>
@@ -30230,7 +30230,7 @@
       </c>
       <c r="K614" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L614" s="3" t="inlineStr"/>
@@ -30278,7 +30278,7 @@
       </c>
       <c r="K615" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L615" s="6" t="inlineStr"/>
@@ -30326,7 +30326,7 @@
       </c>
       <c r="K616" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L616" s="3" t="inlineStr"/>
@@ -30374,7 +30374,7 @@
       </c>
       <c r="K617" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L617" s="6" t="inlineStr"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K618" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L618" s="3" t="inlineStr"/>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="K619" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L619" s="6" t="inlineStr"/>
@@ -30518,7 +30518,7 @@
       </c>
       <c r="K620" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L620" s="3" t="inlineStr"/>
@@ -30566,7 +30566,7 @@
       </c>
       <c r="K621" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L621" s="6" t="inlineStr"/>
@@ -30614,7 +30614,7 @@
       </c>
       <c r="K622" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L622" s="3" t="inlineStr"/>
@@ -30662,7 +30662,7 @@
       </c>
       <c r="K623" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L623" s="6" t="inlineStr"/>
@@ -30710,7 +30710,7 @@
       </c>
       <c r="K624" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L624" s="3" t="inlineStr"/>
@@ -30758,7 +30758,7 @@
       </c>
       <c r="K625" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L625" s="6" t="inlineStr"/>
@@ -30806,7 +30806,7 @@
       </c>
       <c r="K626" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L626" s="3" t="inlineStr"/>
@@ -30854,7 +30854,7 @@
       </c>
       <c r="K627" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L627" s="6" t="inlineStr"/>
@@ -30902,7 +30902,7 @@
       </c>
       <c r="K628" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L628" s="3" t="inlineStr"/>
@@ -30950,7 +30950,7 @@
       </c>
       <c r="K629" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L629" s="6" t="inlineStr"/>
@@ -30998,7 +30998,7 @@
       </c>
       <c r="K630" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L630" s="3" t="inlineStr"/>
@@ -31046,7 +31046,7 @@
       </c>
       <c r="K631" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L631" s="6" t="inlineStr"/>
@@ -31094,7 +31094,7 @@
       </c>
       <c r="K632" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L632" s="3" t="inlineStr"/>
@@ -31142,7 +31142,7 @@
       </c>
       <c r="K633" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L633" s="6" t="inlineStr"/>
@@ -31190,7 +31190,7 @@
       </c>
       <c r="K634" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L634" s="3" t="inlineStr"/>
@@ -31238,7 +31238,7 @@
       </c>
       <c r="K635" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L635" s="6" t="inlineStr"/>
@@ -31286,7 +31286,7 @@
       </c>
       <c r="K636" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L636" s="3" t="inlineStr"/>
@@ -31334,7 +31334,7 @@
       </c>
       <c r="K637" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L637" s="6" t="inlineStr"/>
@@ -31382,7 +31382,7 @@
       </c>
       <c r="K638" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L638" s="3" t="inlineStr"/>
@@ -31430,7 +31430,7 @@
       </c>
       <c r="K639" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L639" s="6" t="inlineStr"/>
@@ -31478,7 +31478,7 @@
       </c>
       <c r="K640" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L640" s="3" t="inlineStr"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K641" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L641" s="6" t="inlineStr"/>
@@ -31574,7 +31574,7 @@
       </c>
       <c r="K642" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L642" s="3" t="inlineStr"/>
@@ -31622,7 +31622,7 @@
       </c>
       <c r="K643" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L643" s="6" t="inlineStr"/>
@@ -31670,7 +31670,7 @@
       </c>
       <c r="K644" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L644" s="3" t="inlineStr"/>
@@ -31718,7 +31718,7 @@
       </c>
       <c r="K645" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L645" s="6" t="inlineStr"/>
@@ -31766,7 +31766,7 @@
       </c>
       <c r="K646" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L646" s="3" t="inlineStr"/>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="K647" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L647" s="6" t="inlineStr"/>
@@ -31862,7 +31862,7 @@
       </c>
       <c r="K648" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L648" s="3" t="inlineStr"/>
@@ -31910,7 +31910,7 @@
       </c>
       <c r="K649" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L649" s="6" t="inlineStr"/>
@@ -31958,7 +31958,7 @@
       </c>
       <c r="K650" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L650" s="3" t="inlineStr"/>
@@ -32006,7 +32006,7 @@
       </c>
       <c r="K651" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L651" s="6" t="inlineStr"/>
@@ -32054,7 +32054,7 @@
       </c>
       <c r="K652" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L652" s="3" t="inlineStr"/>
@@ -32102,7 +32102,7 @@
       </c>
       <c r="K653" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L653" s="6" t="inlineStr"/>
@@ -32150,7 +32150,7 @@
       </c>
       <c r="K654" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L654" s="3" t="inlineStr"/>
@@ -32198,7 +32198,7 @@
       </c>
       <c r="K655" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L655" s="6" t="inlineStr"/>
@@ -32246,7 +32246,7 @@
       </c>
       <c r="K656" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L656" s="3" t="inlineStr"/>
@@ -32294,7 +32294,7 @@
       </c>
       <c r="K657" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L657" s="6" t="inlineStr"/>
@@ -32342,7 +32342,7 @@
       </c>
       <c r="K658" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L658" s="3" t="inlineStr"/>
@@ -32390,7 +32390,7 @@
       </c>
       <c r="K659" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L659" s="6" t="inlineStr"/>
@@ -32438,7 +32438,7 @@
       </c>
       <c r="K660" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L660" s="3" t="inlineStr"/>
@@ -32486,7 +32486,7 @@
       </c>
       <c r="K661" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L661" s="6" t="inlineStr"/>
@@ -32534,7 +32534,7 @@
       </c>
       <c r="K662" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L662" s="3" t="inlineStr"/>
@@ -32582,7 +32582,7 @@
       </c>
       <c r="K663" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L663" s="6" t="inlineStr"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K664" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L664" s="3" t="inlineStr"/>
@@ -32678,7 +32678,7 @@
       </c>
       <c r="K665" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L665" s="6" t="inlineStr"/>
@@ -32726,7 +32726,7 @@
       </c>
       <c r="K666" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L666" s="3" t="inlineStr"/>
@@ -32774,7 +32774,7 @@
       </c>
       <c r="K667" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L667" s="6" t="inlineStr"/>
@@ -32822,7 +32822,7 @@
       </c>
       <c r="K668" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L668" s="3" t="inlineStr"/>
@@ -32870,7 +32870,7 @@
       </c>
       <c r="K669" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L669" s="6" t="inlineStr"/>
@@ -32918,7 +32918,7 @@
       </c>
       <c r="K670" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L670" s="3" t="inlineStr"/>
@@ -32966,7 +32966,7 @@
       </c>
       <c r="K671" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L671" s="6" t="inlineStr"/>
@@ -33014,7 +33014,7 @@
       </c>
       <c r="K672" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L672" s="3" t="inlineStr"/>
@@ -33062,7 +33062,7 @@
       </c>
       <c r="K673" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L673" s="6" t="inlineStr"/>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="K674" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L674" s="3" t="inlineStr"/>
@@ -33158,7 +33158,7 @@
       </c>
       <c r="K675" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L675" s="6" t="inlineStr"/>
@@ -33206,7 +33206,7 @@
       </c>
       <c r="K676" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L676" s="3" t="inlineStr"/>
@@ -33254,7 +33254,7 @@
       </c>
       <c r="K677" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L677" s="6" t="inlineStr"/>
@@ -33302,7 +33302,7 @@
       </c>
       <c r="K678" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L678" s="3" t="inlineStr"/>
@@ -33350,7 +33350,7 @@
       </c>
       <c r="K679" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L679" s="6" t="inlineStr"/>
@@ -33398,7 +33398,7 @@
       </c>
       <c r="K680" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L680" s="3" t="inlineStr"/>
@@ -33446,7 +33446,7 @@
       </c>
       <c r="K681" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L681" s="6" t="inlineStr"/>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="K682" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L682" s="3" t="inlineStr"/>
@@ -33542,7 +33542,7 @@
       </c>
       <c r="K683" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L683" s="6" t="inlineStr"/>
@@ -33590,7 +33590,7 @@
       </c>
       <c r="K684" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L684" s="3" t="inlineStr"/>
@@ -33638,7 +33638,7 @@
       </c>
       <c r="K685" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L685" s="6" t="inlineStr"/>
@@ -33686,7 +33686,7 @@
       </c>
       <c r="K686" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L686" s="3" t="inlineStr"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K687" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L687" s="6" t="inlineStr"/>
@@ -33782,7 +33782,7 @@
       </c>
       <c r="K688" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L688" s="3" t="inlineStr"/>
@@ -33830,7 +33830,7 @@
       </c>
       <c r="K689" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L689" s="6" t="inlineStr"/>
@@ -33878,7 +33878,7 @@
       </c>
       <c r="K690" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L690" s="3" t="inlineStr"/>
@@ -33926,7 +33926,7 @@
       </c>
       <c r="K691" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L691" s="6" t="inlineStr"/>
@@ -33974,7 +33974,7 @@
       </c>
       <c r="K692" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L692" s="3" t="inlineStr"/>
@@ -34022,7 +34022,7 @@
       </c>
       <c r="K693" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L693" s="6" t="inlineStr"/>
@@ -34070,7 +34070,7 @@
       </c>
       <c r="K694" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L694" s="3" t="inlineStr"/>
@@ -34118,7 +34118,7 @@
       </c>
       <c r="K695" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L695" s="6" t="inlineStr"/>
@@ -34166,7 +34166,7 @@
       </c>
       <c r="K696" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L696" s="3" t="inlineStr"/>
@@ -34214,7 +34214,7 @@
       </c>
       <c r="K697" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L697" s="6" t="inlineStr"/>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="K698" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L698" s="3" t="inlineStr"/>
@@ -34310,7 +34310,7 @@
       </c>
       <c r="K699" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L699" s="6" t="inlineStr"/>
@@ -34358,7 +34358,7 @@
       </c>
       <c r="K700" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L700" s="3" t="inlineStr"/>
@@ -34406,7 +34406,7 @@
       </c>
       <c r="K701" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L701" s="6" t="inlineStr"/>
@@ -34454,7 +34454,7 @@
       </c>
       <c r="K702" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L702" s="3" t="inlineStr"/>
@@ -34502,7 +34502,7 @@
       </c>
       <c r="K703" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L703" s="6" t="inlineStr"/>
@@ -34550,7 +34550,7 @@
       </c>
       <c r="K704" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L704" s="3" t="inlineStr"/>
@@ -34598,7 +34598,7 @@
       </c>
       <c r="K705" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L705" s="6" t="inlineStr"/>
@@ -34646,7 +34646,7 @@
       </c>
       <c r="K706" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L706" s="3" t="inlineStr"/>
@@ -34694,7 +34694,7 @@
       </c>
       <c r="K707" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L707" s="6" t="inlineStr"/>
@@ -34742,7 +34742,7 @@
       </c>
       <c r="K708" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L708" s="3" t="inlineStr"/>
@@ -34790,7 +34790,7 @@
       </c>
       <c r="K709" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L709" s="6" t="inlineStr"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K710" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L710" s="3" t="inlineStr"/>
@@ -34886,7 +34886,7 @@
       </c>
       <c r="K711" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L711" s="6" t="inlineStr"/>
@@ -34934,7 +34934,7 @@
       </c>
       <c r="K712" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L712" s="3" t="inlineStr"/>
@@ -34982,7 +34982,7 @@
       </c>
       <c r="K713" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L713" s="6" t="inlineStr"/>
@@ -35030,7 +35030,7 @@
       </c>
       <c r="K714" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L714" s="3" t="inlineStr"/>
@@ -35078,7 +35078,7 @@
       </c>
       <c r="K715" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L715" s="6" t="inlineStr"/>
@@ -35126,7 +35126,7 @@
       </c>
       <c r="K716" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L716" s="3" t="inlineStr"/>
@@ -35174,7 +35174,7 @@
       </c>
       <c r="K717" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L717" s="6" t="inlineStr"/>
@@ -35222,7 +35222,7 @@
       </c>
       <c r="K718" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L718" s="3" t="inlineStr"/>
@@ -35270,7 +35270,7 @@
       </c>
       <c r="K719" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L719" s="6" t="inlineStr"/>
@@ -35318,7 +35318,7 @@
       </c>
       <c r="K720" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L720" s="3" t="inlineStr"/>
@@ -35366,7 +35366,7 @@
       </c>
       <c r="K721" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L721" s="6" t="inlineStr"/>
@@ -35414,7 +35414,7 @@
       </c>
       <c r="K722" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L722" s="3" t="inlineStr"/>
@@ -35462,7 +35462,7 @@
       </c>
       <c r="K723" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L723" s="6" t="inlineStr"/>
@@ -35510,7 +35510,7 @@
       </c>
       <c r="K724" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L724" s="3" t="inlineStr"/>
@@ -35558,7 +35558,7 @@
       </c>
       <c r="K725" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L725" s="6" t="inlineStr"/>
@@ -35606,7 +35606,7 @@
       </c>
       <c r="K726" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L726" s="3" t="inlineStr"/>
@@ -35654,7 +35654,7 @@
       </c>
       <c r="K727" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L727" s="6" t="inlineStr"/>
@@ -35702,7 +35702,7 @@
       </c>
       <c r="K728" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L728" s="3" t="inlineStr"/>
@@ -35750,7 +35750,7 @@
       </c>
       <c r="K729" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L729" s="4" t="inlineStr">
@@ -35802,7 +35802,7 @@
       </c>
       <c r="K730" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L730" s="4" t="inlineStr">
@@ -35854,7 +35854,7 @@
       </c>
       <c r="K731" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L731" s="4" t="inlineStr">
@@ -35906,7 +35906,7 @@
       </c>
       <c r="K732" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L732" s="4" t="inlineStr">
@@ -35958,7 +35958,7 @@
       </c>
       <c r="K733" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L733" s="4" t="inlineStr">
@@ -36010,7 +36010,7 @@
       </c>
       <c r="K734" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L734" s="4" t="inlineStr">
@@ -36062,7 +36062,7 @@
       </c>
       <c r="K735" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L735" s="4" t="inlineStr">
@@ -36114,7 +36114,7 @@
       </c>
       <c r="K736" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L736" s="4" t="inlineStr">
@@ -36166,7 +36166,7 @@
       </c>
       <c r="K737" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L737" s="4" t="inlineStr">
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K738" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L738" s="4" t="inlineStr">
@@ -36270,7 +36270,7 @@
       </c>
       <c r="K739" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L739" s="4" t="inlineStr">
@@ -36322,7 +36322,7 @@
       </c>
       <c r="K740" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L740" s="4" t="inlineStr">
@@ -36374,7 +36374,7 @@
       </c>
       <c r="K741" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L741" s="4" t="inlineStr">
@@ -36426,7 +36426,7 @@
       </c>
       <c r="K742" s="3" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L742" s="4" t="inlineStr">
@@ -36478,7 +36478,7 @@
       </c>
       <c r="K743" s="6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="L743" s="4" t="inlineStr">

--- a/public/loop-library.xlsx
+++ b/public/loop-library.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr"/>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr"/>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr"/>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr"/>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr"/>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr"/>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr"/>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr"/>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr"/>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr"/>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr"/>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr"/>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr"/>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr"/>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr"/>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr"/>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr"/>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr"/>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr"/>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr"/>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L93" s="6" t="inlineStr"/>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr"/>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L95" s="6" t="inlineStr"/>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr"/>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L97" s="6" t="inlineStr"/>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr"/>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr"/>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr"/>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr"/>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L102" s="3" t="inlineStr"/>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L103" s="6" t="inlineStr"/>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L104" s="3" t="inlineStr"/>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L105" s="6" t="inlineStr"/>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L106" s="3" t="inlineStr"/>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L107" s="6" t="inlineStr"/>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L108" s="3" t="inlineStr"/>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L109" s="6" t="inlineStr"/>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L110" s="3" t="inlineStr"/>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L111" s="6" t="inlineStr"/>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L112" s="3" t="inlineStr"/>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L113" s="6" t="inlineStr"/>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L114" s="3" t="inlineStr"/>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L115" s="6" t="inlineStr"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="K116" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L116" s="3" t="inlineStr"/>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L117" s="6" t="inlineStr"/>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="K118" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L118" s="3" t="inlineStr"/>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L119" s="6" t="inlineStr"/>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="K120" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L120" s="3" t="inlineStr"/>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L121" s="6" t="inlineStr"/>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="K122" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L122" s="3" t="inlineStr"/>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L123" s="6" t="inlineStr"/>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="K124" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L124" s="3" t="inlineStr"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="K125" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L125" s="6" t="inlineStr"/>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="K126" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L126" s="3" t="inlineStr"/>
@@ -6854,7 +6854,7 @@
       </c>
       <c r="K127" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L127" s="6" t="inlineStr"/>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L128" s="3" t="inlineStr"/>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="K129" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L129" s="6" t="inlineStr"/>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="K130" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L130" s="3" t="inlineStr"/>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="K131" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L131" s="6" t="inlineStr"/>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L132" s="3" t="inlineStr"/>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="K133" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L133" s="6" t="inlineStr"/>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="K134" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L134" s="3" t="inlineStr"/>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="K135" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L135" s="6" t="inlineStr"/>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="K136" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L136" s="3" t="inlineStr"/>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="K137" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L137" s="6" t="inlineStr"/>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="K138" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L138" s="3" t="inlineStr"/>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="K139" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L139" s="6" t="inlineStr"/>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="K140" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L140" s="3" t="inlineStr"/>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="K141" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L141" s="6" t="inlineStr"/>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L142" s="3" t="inlineStr"/>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="K143" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L143" s="6" t="inlineStr"/>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="K144" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L144" s="3" t="inlineStr"/>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="K145" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L145" s="6" t="inlineStr"/>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="K146" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L146" s="3" t="inlineStr"/>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="K147" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L147" s="6" t="inlineStr"/>
@@ -7862,7 +7862,7 @@
       </c>
       <c r="K148" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L148" s="3" t="inlineStr"/>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="K149" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L149" s="6" t="inlineStr"/>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="K150" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L150" s="3" t="inlineStr"/>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="K151" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L151" s="6" t="inlineStr"/>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="K152" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L152" s="3" t="inlineStr"/>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="K153" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L153" s="6" t="inlineStr"/>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="K154" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L154" s="3" t="inlineStr"/>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="K155" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L155" s="6" t="inlineStr"/>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="K156" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L156" s="3" t="inlineStr"/>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K157" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L157" s="6" t="inlineStr"/>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="K158" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L158" s="3" t="inlineStr"/>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="K159" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L159" s="6" t="inlineStr"/>
@@ -8438,7 +8438,7 @@
       </c>
       <c r="K160" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L160" s="3" t="inlineStr"/>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="K161" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L161" s="6" t="inlineStr"/>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="K162" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L162" s="3" t="inlineStr"/>
@@ -8582,7 +8582,7 @@
       </c>
       <c r="K163" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L163" s="6" t="inlineStr"/>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="K164" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L164" s="3" t="inlineStr"/>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="K165" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L165" s="6" t="inlineStr"/>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="K166" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L166" s="3" t="inlineStr"/>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="K167" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L167" s="6" t="inlineStr"/>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="K168" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L168" s="3" t="inlineStr"/>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="K169" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L169" s="6" t="inlineStr"/>
@@ -8918,7 +8918,7 @@
       </c>
       <c r="K170" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L170" s="3" t="inlineStr"/>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="K171" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L171" s="6" t="inlineStr"/>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="K172" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L172" s="3" t="inlineStr"/>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="K173" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L173" s="6" t="inlineStr"/>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="K174" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L174" s="3" t="inlineStr"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="K175" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L175" s="6" t="inlineStr"/>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="K176" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L176" s="3" t="inlineStr"/>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="K177" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L177" s="6" t="inlineStr"/>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="K178" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L178" s="3" t="inlineStr"/>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="K179" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L179" s="6" t="inlineStr"/>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="K180" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L180" s="3" t="inlineStr"/>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="K181" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L181" s="6" t="inlineStr"/>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="K182" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L182" s="3" t="inlineStr"/>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="K183" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L183" s="6" t="inlineStr"/>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="K184" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L184" s="3" t="inlineStr"/>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="K185" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L185" s="6" t="inlineStr"/>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="K186" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L186" s="3" t="inlineStr"/>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="K187" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L187" s="6" t="inlineStr"/>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="K188" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L188" s="3" t="inlineStr"/>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="K189" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L189" s="6" t="inlineStr"/>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="K190" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L190" s="3" t="inlineStr"/>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="K191" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L191" s="6" t="inlineStr"/>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="K192" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L192" s="3" t="inlineStr"/>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="K193" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L193" s="6" t="inlineStr"/>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="K194" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L194" s="3" t="inlineStr"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="K195" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L195" s="6" t="inlineStr"/>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="K196" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L196" s="3" t="inlineStr"/>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="K197" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L197" s="6" t="inlineStr"/>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="K198" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L198" s="3" t="inlineStr"/>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="K199" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L199" s="6" t="inlineStr"/>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="K200" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L200" s="3" t="inlineStr"/>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="K201" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L201" s="6" t="inlineStr"/>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="K202" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L202" s="3" t="inlineStr"/>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="K203" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L203" s="6" t="inlineStr"/>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="K204" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L204" s="3" t="inlineStr"/>
@@ -10598,7 +10598,7 @@
       </c>
       <c r="K205" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L205" s="6" t="inlineStr"/>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K206" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L206" s="3" t="inlineStr"/>
@@ -10694,7 +10694,7 @@
       </c>
       <c r="K207" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L207" s="6" t="inlineStr"/>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="K208" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L208" s="3" t="inlineStr"/>
@@ -10790,7 +10790,7 @@
       </c>
       <c r="K209" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L209" s="6" t="inlineStr"/>
@@ -10838,7 +10838,7 @@
       </c>
       <c r="K210" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L210" s="3" t="inlineStr"/>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="K211" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L211" s="6" t="inlineStr"/>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="K212" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L212" s="3" t="inlineStr"/>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="K213" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L213" s="6" t="inlineStr"/>
@@ -11030,7 +11030,7 @@
       </c>
       <c r="K214" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L214" s="3" t="inlineStr"/>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="K215" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L215" s="6" t="inlineStr"/>
@@ -11126,7 +11126,7 @@
       </c>
       <c r="K216" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L216" s="3" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="K217" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L217" s="6" t="inlineStr"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="K218" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L218" s="3" t="inlineStr"/>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="K219" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L219" s="6" t="inlineStr"/>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="K220" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L220" s="3" t="inlineStr"/>
@@ -11366,7 +11366,7 @@
       </c>
       <c r="K221" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L221" s="6" t="inlineStr"/>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="K222" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L222" s="3" t="inlineStr"/>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="K223" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L223" s="6" t="inlineStr"/>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="K224" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L224" s="3" t="inlineStr"/>
@@ -11558,7 +11558,7 @@
       </c>
       <c r="K225" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L225" s="6" t="inlineStr"/>
@@ -11606,7 +11606,7 @@
       </c>
       <c r="K226" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L226" s="3" t="inlineStr"/>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="K227" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L227" s="6" t="inlineStr"/>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="K228" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L228" s="3" t="inlineStr"/>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="K229" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L229" s="6" t="inlineStr"/>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="K230" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L230" s="3" t="inlineStr"/>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="K231" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L231" s="6" t="inlineStr"/>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="K232" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L232" s="3" t="inlineStr"/>
@@ -11942,7 +11942,7 @@
       </c>
       <c r="K233" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L233" s="6" t="inlineStr"/>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="K234" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L234" s="3" t="inlineStr"/>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="K235" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L235" s="6" t="inlineStr"/>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="K236" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L236" s="3" t="inlineStr"/>
@@ -12134,7 +12134,7 @@
       </c>
       <c r="K237" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L237" s="6" t="inlineStr"/>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="K238" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L238" s="3" t="inlineStr"/>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="K239" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L239" s="6" t="inlineStr"/>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="K240" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L240" s="3" t="inlineStr"/>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="K241" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L241" s="6" t="inlineStr"/>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="K242" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L242" s="3" t="inlineStr"/>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="K243" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L243" s="6" t="inlineStr"/>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="K244" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L244" s="3" t="inlineStr"/>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="K245" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L245" s="6" t="inlineStr"/>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="K246" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L246" s="3" t="inlineStr"/>
@@ -12614,7 +12614,7 @@
       </c>
       <c r="K247" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L247" s="6" t="inlineStr"/>
@@ -12662,7 +12662,7 @@
       </c>
       <c r="K248" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L248" s="3" t="inlineStr"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="K249" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L249" s="6" t="inlineStr"/>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="K250" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L250" s="3" t="inlineStr"/>
@@ -12806,7 +12806,7 @@
       </c>
       <c r="K251" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L251" s="6" t="inlineStr"/>
@@ -12854,7 +12854,7 @@
       </c>
       <c r="K252" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L252" s="3" t="inlineStr"/>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="K253" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L253" s="6" t="inlineStr"/>
@@ -12950,7 +12950,7 @@
       </c>
       <c r="K254" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L254" s="3" t="inlineStr"/>
@@ -12998,7 +12998,7 @@
       </c>
       <c r="K255" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L255" s="6" t="inlineStr"/>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="K256" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L256" s="3" t="inlineStr"/>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="K257" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L257" s="6" t="inlineStr"/>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="K258" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L258" s="3" t="inlineStr"/>
@@ -13190,7 +13190,7 @@
       </c>
       <c r="K259" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L259" s="6" t="inlineStr"/>
@@ -13238,7 +13238,7 @@
       </c>
       <c r="K260" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L260" s="3" t="inlineStr"/>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="K261" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L261" s="6" t="inlineStr"/>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="K262" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L262" s="3" t="inlineStr"/>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="K263" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L263" s="6" t="inlineStr"/>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="K264" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L264" s="3" t="inlineStr"/>
@@ -13478,7 +13478,7 @@
       </c>
       <c r="K265" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L265" s="6" t="inlineStr"/>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="K266" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L266" s="3" t="inlineStr"/>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="K267" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L267" s="6" t="inlineStr"/>
@@ -13622,7 +13622,7 @@
       </c>
       <c r="K268" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L268" s="3" t="inlineStr"/>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="K269" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L269" s="6" t="inlineStr"/>
@@ -13718,7 +13718,7 @@
       </c>
       <c r="K270" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L270" s="3" t="inlineStr"/>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="K271" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L271" s="6" t="inlineStr"/>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="K272" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L272" s="3" t="inlineStr"/>
@@ -13862,7 +13862,7 @@
       </c>
       <c r="K273" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L273" s="6" t="inlineStr"/>
@@ -13910,7 +13910,7 @@
       </c>
       <c r="K274" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L274" s="3" t="inlineStr"/>
@@ -13958,7 +13958,7 @@
       </c>
       <c r="K275" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L275" s="6" t="inlineStr"/>
@@ -14006,7 +14006,7 @@
       </c>
       <c r="K276" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L276" s="3" t="inlineStr"/>
@@ -14054,7 +14054,7 @@
       </c>
       <c r="K277" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L277" s="6" t="inlineStr"/>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="K278" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L278" s="3" t="inlineStr"/>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="K279" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L279" s="6" t="inlineStr"/>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="K280" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L280" s="3" t="inlineStr"/>
@@ -14246,7 +14246,7 @@
       </c>
       <c r="K281" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L281" s="6" t="inlineStr"/>
@@ -14294,7 +14294,7 @@
       </c>
       <c r="K282" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L282" s="3" t="inlineStr"/>
@@ -14342,7 +14342,7 @@
       </c>
       <c r="K283" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L283" s="6" t="inlineStr"/>
@@ -14390,7 +14390,7 @@
       </c>
       <c r="K284" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L284" s="3" t="inlineStr"/>
@@ -14438,7 +14438,7 @@
       </c>
       <c r="K285" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L285" s="6" t="inlineStr"/>
@@ -14486,7 +14486,7 @@
       </c>
       <c r="K286" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L286" s="3" t="inlineStr"/>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="K287" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L287" s="6" t="inlineStr"/>
@@ -14582,7 +14582,7 @@
       </c>
       <c r="K288" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L288" s="3" t="inlineStr"/>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="K289" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L289" s="6" t="inlineStr"/>
@@ -14678,7 +14678,7 @@
       </c>
       <c r="K290" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L290" s="3" t="inlineStr"/>
@@ -14726,7 +14726,7 @@
       </c>
       <c r="K291" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L291" s="6" t="inlineStr"/>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="K292" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L292" s="3" t="inlineStr"/>
@@ -14822,7 +14822,7 @@
       </c>
       <c r="K293" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L293" s="6" t="inlineStr"/>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="K294" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L294" s="3" t="inlineStr"/>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="K295" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L295" s="6" t="inlineStr"/>
@@ -14966,7 +14966,7 @@
       </c>
       <c r="K296" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L296" s="3" t="inlineStr"/>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="K297" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L297" s="6" t="inlineStr"/>
@@ -15062,7 +15062,7 @@
       </c>
       <c r="K298" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L298" s="3" t="inlineStr"/>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="K299" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L299" s="6" t="inlineStr"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="K300" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L300" s="3" t="inlineStr"/>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="K301" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L301" s="6" t="inlineStr"/>
@@ -15254,7 +15254,7 @@
       </c>
       <c r="K302" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L302" s="3" t="inlineStr"/>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="K303" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L303" s="6" t="inlineStr"/>
@@ -15350,7 +15350,7 @@
       </c>
       <c r="K304" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L304" s="3" t="inlineStr"/>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="K305" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L305" s="6" t="inlineStr"/>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="K306" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L306" s="3" t="inlineStr"/>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="K307" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L307" s="6" t="inlineStr"/>
@@ -15542,7 +15542,7 @@
       </c>
       <c r="K308" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L308" s="3" t="inlineStr"/>
@@ -15590,7 +15590,7 @@
       </c>
       <c r="K309" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L309" s="6" t="inlineStr"/>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="K310" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L310" s="3" t="inlineStr"/>
@@ -15686,7 +15686,7 @@
       </c>
       <c r="K311" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L311" s="6" t="inlineStr"/>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="K312" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L312" s="3" t="inlineStr"/>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="K313" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L313" s="6" t="inlineStr"/>
@@ -15830,7 +15830,7 @@
       </c>
       <c r="K314" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L314" s="3" t="inlineStr"/>
@@ -15878,7 +15878,7 @@
       </c>
       <c r="K315" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L315" s="6" t="inlineStr"/>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="K316" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L316" s="3" t="inlineStr"/>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="K317" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L317" s="6" t="inlineStr"/>
@@ -16022,7 +16022,7 @@
       </c>
       <c r="K318" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L318" s="3" t="inlineStr"/>
@@ -16070,7 +16070,7 @@
       </c>
       <c r="K319" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L319" s="6" t="inlineStr"/>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="K320" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L320" s="3" t="inlineStr"/>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="K321" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L321" s="6" t="inlineStr"/>
@@ -16214,7 +16214,7 @@
       </c>
       <c r="K322" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L322" s="3" t="inlineStr"/>
@@ -16262,7 +16262,7 @@
       </c>
       <c r="K323" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L323" s="6" t="inlineStr"/>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="K324" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L324" s="3" t="inlineStr"/>
@@ -16358,7 +16358,7 @@
       </c>
       <c r="K325" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L325" s="6" t="inlineStr"/>
@@ -16406,7 +16406,7 @@
       </c>
       <c r="K326" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L326" s="3" t="inlineStr"/>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="K327" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L327" s="6" t="inlineStr"/>
@@ -16502,7 +16502,7 @@
       </c>
       <c r="K328" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L328" s="3" t="inlineStr"/>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="K329" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L329" s="6" t="inlineStr"/>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="K330" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L330" s="3" t="inlineStr"/>
@@ -16646,7 +16646,7 @@
       </c>
       <c r="K331" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L331" s="6" t="inlineStr"/>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="K332" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L332" s="3" t="inlineStr"/>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="K333" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L333" s="6" t="inlineStr"/>
@@ -16790,7 +16790,7 @@
       </c>
       <c r="K334" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L334" s="3" t="inlineStr"/>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="K335" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L335" s="6" t="inlineStr"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="K336" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L336" s="3" t="inlineStr"/>
@@ -16934,7 +16934,7 @@
       </c>
       <c r="K337" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L337" s="6" t="inlineStr"/>
@@ -16982,7 +16982,7 @@
       </c>
       <c r="K338" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L338" s="3" t="inlineStr"/>
@@ -17030,7 +17030,7 @@
       </c>
       <c r="K339" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L339" s="6" t="inlineStr"/>
@@ -17078,7 +17078,7 @@
       </c>
       <c r="K340" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L340" s="3" t="inlineStr"/>
@@ -17126,7 +17126,7 @@
       </c>
       <c r="K341" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L341" s="6" t="inlineStr"/>
@@ -17174,7 +17174,7 @@
       </c>
       <c r="K342" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L342" s="3" t="inlineStr"/>
@@ -17222,7 +17222,7 @@
       </c>
       <c r="K343" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L343" s="6" t="inlineStr"/>
@@ -17270,7 +17270,7 @@
       </c>
       <c r="K344" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L344" s="3" t="inlineStr"/>
@@ -17318,7 +17318,7 @@
       </c>
       <c r="K345" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L345" s="6" t="inlineStr"/>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="K346" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L346" s="3" t="inlineStr"/>
@@ -17414,7 +17414,7 @@
       </c>
       <c r="K347" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L347" s="6" t="inlineStr"/>
@@ -17462,7 +17462,7 @@
       </c>
       <c r="K348" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L348" s="3" t="inlineStr"/>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="K349" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L349" s="6" t="inlineStr"/>
@@ -17558,7 +17558,7 @@
       </c>
       <c r="K350" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L350" s="3" t="inlineStr"/>
@@ -17606,7 +17606,7 @@
       </c>
       <c r="K351" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L351" s="6" t="inlineStr"/>
@@ -17654,7 +17654,7 @@
       </c>
       <c r="K352" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L352" s="3" t="inlineStr"/>
@@ -17702,7 +17702,7 @@
       </c>
       <c r="K353" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L353" s="6" t="inlineStr"/>
@@ -17750,7 +17750,7 @@
       </c>
       <c r="K354" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L354" s="3" t="inlineStr"/>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="K355" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L355" s="6" t="inlineStr"/>
@@ -17846,7 +17846,7 @@
       </c>
       <c r="K356" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L356" s="3" t="inlineStr"/>
@@ -17894,7 +17894,7 @@
       </c>
       <c r="K357" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L357" s="6" t="inlineStr"/>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="K358" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L358" s="3" t="inlineStr"/>
@@ -17990,7 +17990,7 @@
       </c>
       <c r="K359" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L359" s="6" t="inlineStr"/>
@@ -18038,7 +18038,7 @@
       </c>
       <c r="K360" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L360" s="3" t="inlineStr"/>
@@ -18086,7 +18086,7 @@
       </c>
       <c r="K361" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L361" s="6" t="inlineStr"/>
@@ -18134,7 +18134,7 @@
       </c>
       <c r="K362" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L362" s="3" t="inlineStr"/>
@@ -18182,7 +18182,7 @@
       </c>
       <c r="K363" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L363" s="6" t="inlineStr"/>
@@ -18230,7 +18230,7 @@
       </c>
       <c r="K364" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L364" s="3" t="inlineStr"/>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="K365" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L365" s="6" t="inlineStr"/>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="K366" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L366" s="3" t="inlineStr"/>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="K367" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L367" s="6" t="inlineStr"/>
@@ -18422,7 +18422,7 @@
       </c>
       <c r="K368" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L368" s="3" t="inlineStr"/>
@@ -18470,7 +18470,7 @@
       </c>
       <c r="K369" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L369" s="6" t="inlineStr"/>
@@ -18518,7 +18518,7 @@
       </c>
       <c r="K370" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L370" s="3" t="inlineStr"/>
@@ -18566,7 +18566,7 @@
       </c>
       <c r="K371" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L371" s="6" t="inlineStr"/>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="K372" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L372" s="3" t="inlineStr"/>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="K373" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L373" s="6" t="inlineStr"/>
@@ -18710,7 +18710,7 @@
       </c>
       <c r="K374" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L374" s="3" t="inlineStr"/>
@@ -18758,7 +18758,7 @@
       </c>
       <c r="K375" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L375" s="6" t="inlineStr"/>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="K376" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L376" s="3" t="inlineStr"/>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="K377" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L377" s="6" t="inlineStr"/>
@@ -18902,7 +18902,7 @@
       </c>
       <c r="K378" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L378" s="3" t="inlineStr"/>
@@ -18950,7 +18950,7 @@
       </c>
       <c r="K379" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L379" s="6" t="inlineStr"/>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="K380" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L380" s="3" t="inlineStr"/>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="K381" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L381" s="6" t="inlineStr"/>
@@ -19094,7 +19094,7 @@
       </c>
       <c r="K382" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L382" s="3" t="inlineStr"/>
@@ -19142,7 +19142,7 @@
       </c>
       <c r="K383" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L383" s="6" t="inlineStr"/>
@@ -19190,7 +19190,7 @@
       </c>
       <c r="K384" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L384" s="3" t="inlineStr"/>
@@ -19238,7 +19238,7 @@
       </c>
       <c r="K385" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L385" s="6" t="inlineStr"/>
@@ -19286,7 +19286,7 @@
       </c>
       <c r="K386" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L386" s="3" t="inlineStr"/>
@@ -19334,7 +19334,7 @@
       </c>
       <c r="K387" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L387" s="6" t="inlineStr"/>
@@ -19382,7 +19382,7 @@
       </c>
       <c r="K388" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L388" s="3" t="inlineStr"/>
@@ -19430,7 +19430,7 @@
       </c>
       <c r="K389" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L389" s="6" t="inlineStr"/>
@@ -19478,7 +19478,7 @@
       </c>
       <c r="K390" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L390" s="3" t="inlineStr"/>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="K391" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L391" s="6" t="inlineStr"/>
@@ -19574,7 +19574,7 @@
       </c>
       <c r="K392" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L392" s="3" t="inlineStr"/>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="K393" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L393" s="6" t="inlineStr"/>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="K394" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L394" s="3" t="inlineStr"/>
@@ -19718,7 +19718,7 @@
       </c>
       <c r="K395" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L395" s="6" t="inlineStr"/>
@@ -19766,7 +19766,7 @@
       </c>
       <c r="K396" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L396" s="3" t="inlineStr"/>
@@ -19814,7 +19814,7 @@
       </c>
       <c r="K397" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L397" s="6" t="inlineStr"/>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="K398" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L398" s="3" t="inlineStr"/>
@@ -19910,7 +19910,7 @@
       </c>
       <c r="K399" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L399" s="6" t="inlineStr"/>
@@ -19958,7 +19958,7 @@
       </c>
       <c r="K400" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L400" s="3" t="inlineStr"/>
@@ -20006,7 +20006,7 @@
       </c>
       <c r="K401" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L401" s="6" t="inlineStr"/>
@@ -20054,7 +20054,7 @@
       </c>
       <c r="K402" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L402" s="3" t="inlineStr"/>
@@ -20102,7 +20102,7 @@
       </c>
       <c r="K403" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L403" s="6" t="inlineStr"/>
@@ -20150,7 +20150,7 @@
       </c>
       <c r="K404" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L404" s="3" t="inlineStr"/>
@@ -20198,7 +20198,7 @@
       </c>
       <c r="K405" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L405" s="6" t="inlineStr"/>
@@ -20246,7 +20246,7 @@
       </c>
       <c r="K406" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L406" s="3" t="inlineStr"/>
@@ -20294,7 +20294,7 @@
       </c>
       <c r="K407" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L407" s="6" t="inlineStr"/>
@@ -20342,7 +20342,7 @@
       </c>
       <c r="K408" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L408" s="3" t="inlineStr"/>
@@ -20390,7 +20390,7 @@
       </c>
       <c r="K409" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L409" s="6" t="inlineStr"/>
@@ -20438,7 +20438,7 @@
       </c>
       <c r="K410" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L410" s="3" t="inlineStr"/>
@@ -20486,7 +20486,7 @@
       </c>
       <c r="K411" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L411" s="6" t="inlineStr"/>
@@ -20534,7 +20534,7 @@
       </c>
       <c r="K412" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L412" s="3" t="inlineStr"/>
@@ -20582,7 +20582,7 @@
       </c>
       <c r="K413" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L413" s="6" t="inlineStr"/>
@@ -20630,7 +20630,7 @@
       </c>
       <c r="K414" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L414" s="3" t="inlineStr"/>
@@ -20678,7 +20678,7 @@
       </c>
       <c r="K415" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L415" s="6" t="inlineStr"/>
@@ -20726,7 +20726,7 @@
       </c>
       <c r="K416" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L416" s="3" t="inlineStr"/>
@@ -20774,7 +20774,7 @@
       </c>
       <c r="K417" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L417" s="6" t="inlineStr"/>
@@ -20822,7 +20822,7 @@
       </c>
       <c r="K418" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L418" s="3" t="inlineStr"/>
@@ -20870,7 +20870,7 @@
       </c>
       <c r="K419" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L419" s="6" t="inlineStr"/>
@@ -20918,7 +20918,7 @@
       </c>
       <c r="K420" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L420" s="3" t="inlineStr"/>
@@ -20966,7 +20966,7 @@
       </c>
       <c r="K421" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L421" s="6" t="inlineStr"/>
@@ -21014,7 +21014,7 @@
       </c>
       <c r="K422" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L422" s="3" t="inlineStr"/>
@@ -21062,7 +21062,7 @@
       </c>
       <c r="K423" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L423" s="6" t="inlineStr"/>
@@ -21110,7 +21110,7 @@
       </c>
       <c r="K424" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L424" s="3" t="inlineStr"/>
@@ -21158,7 +21158,7 @@
       </c>
       <c r="K425" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L425" s="6" t="inlineStr"/>
@@ -21206,7 +21206,7 @@
       </c>
       <c r="K426" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L426" s="3" t="inlineStr"/>
@@ -21254,7 +21254,7 @@
       </c>
       <c r="K427" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L427" s="6" t="inlineStr"/>
@@ -21302,7 +21302,7 @@
       </c>
       <c r="K428" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L428" s="3" t="inlineStr"/>
@@ -21350,7 +21350,7 @@
       </c>
       <c r="K429" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L429" s="6" t="inlineStr"/>
@@ -21398,7 +21398,7 @@
       </c>
       <c r="K430" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L430" s="3" t="inlineStr"/>
@@ -21446,7 +21446,7 @@
       </c>
       <c r="K431" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L431" s="6" t="inlineStr"/>
@@ -21494,7 +21494,7 @@
       </c>
       <c r="K432" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L432" s="3" t="inlineStr"/>
@@ -21542,7 +21542,7 @@
       </c>
       <c r="K433" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L433" s="6" t="inlineStr"/>
@@ -21590,7 +21590,7 @@
       </c>
       <c r="K434" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L434" s="3" t="inlineStr"/>
@@ -21638,7 +21638,7 @@
       </c>
       <c r="K435" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L435" s="6" t="inlineStr"/>
@@ -21686,7 +21686,7 @@
       </c>
       <c r="K436" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L436" s="3" t="inlineStr"/>
@@ -21734,7 +21734,7 @@
       </c>
       <c r="K437" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L437" s="6" t="inlineStr"/>
@@ -21782,7 +21782,7 @@
       </c>
       <c r="K438" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L438" s="3" t="inlineStr"/>
@@ -21830,7 +21830,7 @@
       </c>
       <c r="K439" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L439" s="6" t="inlineStr"/>
@@ -21878,7 +21878,7 @@
       </c>
       <c r="K440" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L440" s="3" t="inlineStr"/>
@@ -21926,7 +21926,7 @@
       </c>
       <c r="K441" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L441" s="6" t="inlineStr"/>
@@ -21974,7 +21974,7 @@
       </c>
       <c r="K442" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L442" s="3" t="inlineStr"/>
@@ -22022,7 +22022,7 @@
       </c>
       <c r="K443" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L443" s="6" t="inlineStr"/>
@@ -22070,7 +22070,7 @@
       </c>
       <c r="K444" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L444" s="3" t="inlineStr"/>
@@ -22118,7 +22118,7 @@
       </c>
       <c r="K445" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L445" s="6" t="inlineStr"/>
@@ -22166,7 +22166,7 @@
       </c>
       <c r="K446" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L446" s="3" t="inlineStr"/>
@@ -22214,7 +22214,7 @@
       </c>
       <c r="K447" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L447" s="6" t="inlineStr"/>
@@ -22262,7 +22262,7 @@
       </c>
       <c r="K448" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L448" s="3" t="inlineStr"/>
@@ -22310,7 +22310,7 @@
       </c>
       <c r="K449" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L449" s="6" t="inlineStr"/>
@@ -22358,7 +22358,7 @@
       </c>
       <c r="K450" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L450" s="3" t="inlineStr"/>
@@ -22406,7 +22406,7 @@
       </c>
       <c r="K451" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L451" s="6" t="inlineStr"/>
@@ -22454,7 +22454,7 @@
       </c>
       <c r="K452" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L452" s="3" t="inlineStr"/>
@@ -22502,7 +22502,7 @@
       </c>
       <c r="K453" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L453" s="6" t="inlineStr"/>
@@ -22550,7 +22550,7 @@
       </c>
       <c r="K454" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L454" s="3" t="inlineStr"/>
@@ -22598,7 +22598,7 @@
       </c>
       <c r="K455" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L455" s="6" t="inlineStr"/>
@@ -22646,7 +22646,7 @@
       </c>
       <c r="K456" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L456" s="3" t="inlineStr"/>
@@ -22694,7 +22694,7 @@
       </c>
       <c r="K457" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L457" s="6" t="inlineStr"/>
@@ -22742,7 +22742,7 @@
       </c>
       <c r="K458" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L458" s="3" t="inlineStr"/>
@@ -22790,7 +22790,7 @@
       </c>
       <c r="K459" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L459" s="6" t="inlineStr"/>
@@ -22838,7 +22838,7 @@
       </c>
       <c r="K460" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L460" s="3" t="inlineStr"/>
@@ -22886,7 +22886,7 @@
       </c>
       <c r="K461" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L461" s="6" t="inlineStr"/>
@@ -22934,7 +22934,7 @@
       </c>
       <c r="K462" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L462" s="3" t="inlineStr"/>
@@ -22982,7 +22982,7 @@
       </c>
       <c r="K463" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L463" s="6" t="inlineStr"/>
@@ -23030,7 +23030,7 @@
       </c>
       <c r="K464" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L464" s="3" t="inlineStr"/>
@@ -23078,7 +23078,7 @@
       </c>
       <c r="K465" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L465" s="6" t="inlineStr"/>
@@ -23126,7 +23126,7 @@
       </c>
       <c r="K466" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L466" s="3" t="inlineStr"/>
@@ -23174,7 +23174,7 @@
       </c>
       <c r="K467" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L467" s="6" t="inlineStr"/>
@@ -23222,7 +23222,7 @@
       </c>
       <c r="K468" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L468" s="3" t="inlineStr"/>
@@ -23270,7 +23270,7 @@
       </c>
       <c r="K469" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L469" s="6" t="inlineStr"/>
@@ -23318,7 +23318,7 @@
       </c>
       <c r="K470" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L470" s="3" t="inlineStr"/>
@@ -23366,7 +23366,7 @@
       </c>
       <c r="K471" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L471" s="6" t="inlineStr"/>
@@ -23414,7 +23414,7 @@
       </c>
       <c r="K472" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L472" s="3" t="inlineStr"/>
@@ -23462,7 +23462,7 @@
       </c>
       <c r="K473" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L473" s="6" t="inlineStr"/>
@@ -23510,7 +23510,7 @@
       </c>
       <c r="K474" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L474" s="3" t="inlineStr"/>
@@ -23558,7 +23558,7 @@
       </c>
       <c r="K475" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L475" s="6" t="inlineStr"/>
@@ -23606,7 +23606,7 @@
       </c>
       <c r="K476" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L476" s="3" t="inlineStr"/>
@@ -23654,7 +23654,7 @@
       </c>
       <c r="K477" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L477" s="6" t="inlineStr"/>
@@ -23702,7 +23702,7 @@
       </c>
       <c r="K478" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L478" s="3" t="inlineStr"/>
@@ -23750,7 +23750,7 @@
       </c>
       <c r="K479" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L479" s="6" t="inlineStr"/>
@@ -23798,7 +23798,7 @@
       </c>
       <c r="K480" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L480" s="3" t="inlineStr"/>
@@ -23846,7 +23846,7 @@
       </c>
       <c r="K481" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L481" s="6" t="inlineStr"/>
@@ -23894,7 +23894,7 @@
       </c>
       <c r="K482" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L482" s="3" t="inlineStr"/>
@@ -23942,7 +23942,7 @@
       </c>
       <c r="K483" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L483" s="6" t="inlineStr"/>
@@ -23990,7 +23990,7 @@
       </c>
       <c r="K484" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L484" s="3" t="inlineStr"/>
@@ -24038,7 +24038,7 @@
       </c>
       <c r="K485" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L485" s="6" t="inlineStr"/>
@@ -24086,7 +24086,7 @@
       </c>
       <c r="K486" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L486" s="3" t="inlineStr"/>
@@ -24134,7 +24134,7 @@
       </c>
       <c r="K487" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L487" s="6" t="inlineStr"/>
@@ -24182,7 +24182,7 @@
       </c>
       <c r="K488" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L488" s="3" t="inlineStr"/>
@@ -24230,7 +24230,7 @@
       </c>
       <c r="K489" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L489" s="6" t="inlineStr"/>
@@ -24278,7 +24278,7 @@
       </c>
       <c r="K490" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L490" s="3" t="inlineStr"/>
@@ -24326,7 +24326,7 @@
       </c>
       <c r="K491" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L491" s="6" t="inlineStr"/>
@@ -24374,7 +24374,7 @@
       </c>
       <c r="K492" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L492" s="3" t="inlineStr"/>
@@ -24422,7 +24422,7 @@
       </c>
       <c r="K493" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L493" s="6" t="inlineStr"/>
@@ -24470,7 +24470,7 @@
       </c>
       <c r="K494" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L494" s="3" t="inlineStr"/>
@@ -24518,7 +24518,7 @@
       </c>
       <c r="K495" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L495" s="6" t="inlineStr"/>
@@ -24566,7 +24566,7 @@
       </c>
       <c r="K496" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L496" s="3" t="inlineStr"/>
@@ -24614,7 +24614,7 @@
       </c>
       <c r="K497" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L497" s="6" t="inlineStr"/>
@@ -24662,7 +24662,7 @@
       </c>
       <c r="K498" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L498" s="3" t="inlineStr"/>
@@ -24710,7 +24710,7 @@
       </c>
       <c r="K499" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L499" s="6" t="inlineStr"/>
@@ -24758,7 +24758,7 @@
       </c>
       <c r="K500" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L500" s="3" t="inlineStr"/>
@@ -24806,7 +24806,7 @@
       </c>
       <c r="K501" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L501" s="6" t="inlineStr"/>
@@ -24854,7 +24854,7 @@
       </c>
       <c r="K502" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L502" s="3" t="inlineStr"/>
@@ -24902,7 +24902,7 @@
       </c>
       <c r="K503" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L503" s="6" t="inlineStr"/>
@@ -24950,7 +24950,7 @@
       </c>
       <c r="K504" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L504" s="3" t="inlineStr"/>
@@ -24998,7 +24998,7 @@
       </c>
       <c r="K505" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L505" s="6" t="inlineStr"/>
@@ -25046,7 +25046,7 @@
       </c>
       <c r="K506" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L506" s="3" t="inlineStr"/>
@@ -25094,7 +25094,7 @@
       </c>
       <c r="K507" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L507" s="6" t="inlineStr"/>
@@ -25142,7 +25142,7 @@
       </c>
       <c r="K508" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L508" s="3" t="inlineStr"/>
@@ -25190,7 +25190,7 @@
       </c>
       <c r="K509" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L509" s="6" t="inlineStr"/>
@@ -25238,7 +25238,7 @@
       </c>
       <c r="K510" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L510" s="3" t="inlineStr"/>
@@ -25286,7 +25286,7 @@
       </c>
       <c r="K511" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L511" s="6" t="inlineStr"/>
@@ -25334,7 +25334,7 @@
       </c>
       <c r="K512" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L512" s="3" t="inlineStr"/>
@@ -25382,7 +25382,7 @@
       </c>
       <c r="K513" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L513" s="6" t="inlineStr"/>
@@ -25430,7 +25430,7 @@
       </c>
       <c r="K514" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L514" s="3" t="inlineStr"/>
@@ -25478,7 +25478,7 @@
       </c>
       <c r="K515" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L515" s="6" t="inlineStr"/>
@@ -25526,7 +25526,7 @@
       </c>
       <c r="K516" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L516" s="3" t="inlineStr"/>
@@ -25574,7 +25574,7 @@
       </c>
       <c r="K517" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L517" s="6" t="inlineStr"/>
@@ -25622,7 +25622,7 @@
       </c>
       <c r="K518" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L518" s="3" t="inlineStr"/>
@@ -25670,7 +25670,7 @@
       </c>
       <c r="K519" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L519" s="6" t="inlineStr"/>
@@ -25718,7 +25718,7 @@
       </c>
       <c r="K520" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L520" s="3" t="inlineStr"/>
@@ -25766,7 +25766,7 @@
       </c>
       <c r="K521" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L521" s="6" t="inlineStr"/>
@@ -25814,7 +25814,7 @@
       </c>
       <c r="K522" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L522" s="3" t="inlineStr"/>
@@ -25862,7 +25862,7 @@
       </c>
       <c r="K523" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L523" s="6" t="inlineStr"/>
@@ -25910,7 +25910,7 @@
       </c>
       <c r="K524" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L524" s="3" t="inlineStr"/>
@@ -25958,7 +25958,7 @@
       </c>
       <c r="K525" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L525" s="6" t="inlineStr"/>
@@ -26006,7 +26006,7 @@
       </c>
       <c r="K526" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L526" s="3" t="inlineStr"/>
@@ -26054,7 +26054,7 @@
       </c>
       <c r="K527" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L527" s="6" t="inlineStr"/>
@@ -26102,7 +26102,7 @@
       </c>
       <c r="K528" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L528" s="3" t="inlineStr"/>
@@ -26150,7 +26150,7 @@
       </c>
       <c r="K529" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L529" s="6" t="inlineStr"/>
@@ -26198,7 +26198,7 @@
       </c>
       <c r="K530" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L530" s="3" t="inlineStr"/>
@@ -26246,7 +26246,7 @@
       </c>
       <c r="K531" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L531" s="6" t="inlineStr"/>
@@ -26294,7 +26294,7 @@
       </c>
       <c r="K532" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L532" s="3" t="inlineStr"/>
@@ -26342,7 +26342,7 @@
       </c>
       <c r="K533" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L533" s="6" t="inlineStr"/>
@@ -26390,7 +26390,7 @@
       </c>
       <c r="K534" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L534" s="3" t="inlineStr"/>
@@ -26438,7 +26438,7 @@
       </c>
       <c r="K535" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L535" s="6" t="inlineStr"/>
@@ -26486,7 +26486,7 @@
       </c>
       <c r="K536" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L536" s="3" t="inlineStr"/>
@@ -26534,7 +26534,7 @@
       </c>
       <c r="K537" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L537" s="6" t="inlineStr"/>
@@ -26582,7 +26582,7 @@
       </c>
       <c r="K538" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L538" s="3" t="inlineStr"/>
@@ -26630,7 +26630,7 @@
       </c>
       <c r="K539" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L539" s="6" t="inlineStr"/>
@@ -26678,7 +26678,7 @@
       </c>
       <c r="K540" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L540" s="3" t="inlineStr"/>
@@ -26726,7 +26726,7 @@
       </c>
       <c r="K541" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L541" s="6" t="inlineStr"/>
@@ -26774,7 +26774,7 @@
       </c>
       <c r="K542" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L542" s="3" t="inlineStr"/>
@@ -26822,7 +26822,7 @@
       </c>
       <c r="K543" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L543" s="6" t="inlineStr"/>
@@ -26870,7 +26870,7 @@
       </c>
       <c r="K544" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L544" s="3" t="inlineStr"/>
@@ -26918,7 +26918,7 @@
       </c>
       <c r="K545" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L545" s="6" t="inlineStr"/>
@@ -26966,7 +26966,7 @@
       </c>
       <c r="K546" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L546" s="3" t="inlineStr"/>
@@ -27014,7 +27014,7 @@
       </c>
       <c r="K547" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L547" s="6" t="inlineStr"/>
@@ -27062,7 +27062,7 @@
       </c>
       <c r="K548" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L548" s="3" t="inlineStr"/>
@@ -27110,7 +27110,7 @@
       </c>
       <c r="K549" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L549" s="6" t="inlineStr"/>
@@ -27158,7 +27158,7 @@
       </c>
       <c r="K550" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L550" s="3" t="inlineStr"/>
@@ -27206,7 +27206,7 @@
       </c>
       <c r="K551" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L551" s="6" t="inlineStr"/>
@@ -27254,7 +27254,7 @@
       </c>
       <c r="K552" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L552" s="3" t="inlineStr"/>
@@ -27302,7 +27302,7 @@
       </c>
       <c r="K553" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L553" s="6" t="inlineStr"/>
@@ -27350,7 +27350,7 @@
       </c>
       <c r="K554" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L554" s="3" t="inlineStr"/>
@@ -27398,7 +27398,7 @@
       </c>
       <c r="K555" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L555" s="6" t="inlineStr"/>
@@ -27446,7 +27446,7 @@
       </c>
       <c r="K556" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L556" s="3" t="inlineStr"/>
@@ -27494,7 +27494,7 @@
       </c>
       <c r="K557" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L557" s="6" t="inlineStr"/>
@@ -27542,7 +27542,7 @@
       </c>
       <c r="K558" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L558" s="3" t="inlineStr"/>
@@ -27590,7 +27590,7 @@
       </c>
       <c r="K559" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L559" s="6" t="inlineStr"/>
@@ -27638,7 +27638,7 @@
       </c>
       <c r="K560" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L560" s="3" t="inlineStr"/>
@@ -27686,7 +27686,7 @@
       </c>
       <c r="K561" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L561" s="6" t="inlineStr"/>
@@ -27734,7 +27734,7 @@
       </c>
       <c r="K562" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L562" s="3" t="inlineStr"/>
@@ -27782,7 +27782,7 @@
       </c>
       <c r="K563" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L563" s="6" t="inlineStr"/>
@@ -27830,7 +27830,7 @@
       </c>
       <c r="K564" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L564" s="3" t="inlineStr"/>
@@ -27878,7 +27878,7 @@
       </c>
       <c r="K565" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L565" s="6" t="inlineStr"/>
@@ -27926,7 +27926,7 @@
       </c>
       <c r="K566" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L566" s="3" t="inlineStr"/>
@@ -27974,7 +27974,7 @@
       </c>
       <c r="K567" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L567" s="6" t="inlineStr"/>
@@ -28022,7 +28022,7 @@
       </c>
       <c r="K568" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L568" s="3" t="inlineStr"/>
@@ -28070,7 +28070,7 @@
       </c>
       <c r="K569" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L569" s="6" t="inlineStr"/>
@@ -28118,7 +28118,7 @@
       </c>
       <c r="K570" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L570" s="3" t="inlineStr"/>
@@ -28166,7 +28166,7 @@
       </c>
       <c r="K571" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L571" s="6" t="inlineStr"/>
@@ -28214,7 +28214,7 @@
       </c>
       <c r="K572" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L572" s="3" t="inlineStr"/>
@@ -28262,7 +28262,7 @@
       </c>
       <c r="K573" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L573" s="6" t="inlineStr"/>
@@ -28310,7 +28310,7 @@
       </c>
       <c r="K574" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L574" s="3" t="inlineStr"/>
@@ -28358,7 +28358,7 @@
       </c>
       <c r="K575" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L575" s="6" t="inlineStr"/>
@@ -28406,7 +28406,7 @@
       </c>
       <c r="K576" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L576" s="3" t="inlineStr"/>
@@ -28454,7 +28454,7 @@
       </c>
       <c r="K577" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L577" s="6" t="inlineStr"/>
@@ -28502,7 +28502,7 @@
       </c>
       <c r="K578" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L578" s="3" t="inlineStr"/>
@@ -28550,7 +28550,7 @@
       </c>
       <c r="K579" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L579" s="6" t="inlineStr"/>
@@ -28598,7 +28598,7 @@
       </c>
       <c r="K580" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L580" s="3" t="inlineStr"/>
@@ -28646,7 +28646,7 @@
       </c>
       <c r="K581" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L581" s="6" t="inlineStr"/>
@@ -28694,7 +28694,7 @@
       </c>
       <c r="K582" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L582" s="3" t="inlineStr"/>
@@ -28742,7 +28742,7 @@
       </c>
       <c r="K583" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L583" s="6" t="inlineStr"/>
@@ -28790,7 +28790,7 @@
       </c>
       <c r="K584" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L584" s="3" t="inlineStr"/>
@@ -28838,7 +28838,7 @@
       </c>
       <c r="K585" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L585" s="6" t="inlineStr"/>
@@ -28886,7 +28886,7 @@
       </c>
       <c r="K586" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L586" s="3" t="inlineStr"/>
@@ -28934,7 +28934,7 @@
       </c>
       <c r="K587" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L587" s="6" t="inlineStr"/>
@@ -28982,7 +28982,7 @@
       </c>
       <c r="K588" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L588" s="3" t="inlineStr"/>
@@ -29030,7 +29030,7 @@
       </c>
       <c r="K589" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L589" s="6" t="inlineStr"/>
@@ -29078,7 +29078,7 @@
       </c>
       <c r="K590" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L590" s="3" t="inlineStr"/>
@@ -29126,7 +29126,7 @@
       </c>
       <c r="K591" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L591" s="6" t="inlineStr"/>
@@ -29174,7 +29174,7 @@
       </c>
       <c r="K592" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L592" s="3" t="inlineStr"/>
@@ -29222,7 +29222,7 @@
       </c>
       <c r="K593" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L593" s="6" t="inlineStr"/>
@@ -29270,7 +29270,7 @@
       </c>
       <c r="K594" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L594" s="3" t="inlineStr"/>
@@ -29318,7 +29318,7 @@
       </c>
       <c r="K595" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L595" s="6" t="inlineStr"/>
@@ -29366,7 +29366,7 @@
       </c>
       <c r="K596" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L596" s="3" t="inlineStr"/>
@@ -29414,7 +29414,7 @@
       </c>
       <c r="K597" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L597" s="6" t="inlineStr"/>
@@ -29462,7 +29462,7 @@
       </c>
       <c r="K598" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L598" s="3" t="inlineStr"/>
@@ -29510,7 +29510,7 @@
       </c>
       <c r="K599" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L599" s="6" t="inlineStr"/>
@@ -29558,7 +29558,7 @@
       </c>
       <c r="K600" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L600" s="3" t="inlineStr"/>
@@ -29606,7 +29606,7 @@
       </c>
       <c r="K601" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L601" s="6" t="inlineStr"/>
@@ -29654,7 +29654,7 @@
       </c>
       <c r="K602" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L602" s="3" t="inlineStr"/>
@@ -29702,7 +29702,7 @@
       </c>
       <c r="K603" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L603" s="6" t="inlineStr"/>
@@ -29750,7 +29750,7 @@
       </c>
       <c r="K604" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L604" s="3" t="inlineStr"/>
@@ -29798,7 +29798,7 @@
       </c>
       <c r="K605" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L605" s="6" t="inlineStr"/>
@@ -29846,7 +29846,7 @@
       </c>
       <c r="K606" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L606" s="3" t="inlineStr"/>
@@ -29894,7 +29894,7 @@
       </c>
       <c r="K607" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L607" s="6" t="inlineStr"/>
@@ -29942,7 +29942,7 @@
       </c>
       <c r="K608" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L608" s="3" t="inlineStr"/>
@@ -29990,7 +29990,7 @@
       </c>
       <c r="K609" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L609" s="6" t="inlineStr"/>
@@ -30038,7 +30038,7 @@
       </c>
       <c r="K610" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L610" s="3" t="inlineStr"/>
@@ -30086,7 +30086,7 @@
       </c>
       <c r="K611" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L611" s="6" t="inlineStr"/>
@@ -30134,7 +30134,7 @@
       </c>
       <c r="K612" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L612" s="3" t="inlineStr"/>
@@ -30182,7 +30182,7 @@
       </c>
       <c r="K613" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L613" s="6" t="inlineStr"/>
@@ -30230,7 +30230,7 @@
       </c>
       <c r="K614" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L614" s="3" t="inlineStr"/>
@@ -30278,7 +30278,7 @@
       </c>
       <c r="K615" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L615" s="6" t="inlineStr"/>
@@ -30326,7 +30326,7 @@
       </c>
       <c r="K616" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L616" s="3" t="inlineStr"/>
@@ -30374,7 +30374,7 @@
       </c>
       <c r="K617" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L617" s="6" t="inlineStr"/>
@@ -30422,7 +30422,7 @@
       </c>
       <c r="K618" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L618" s="3" t="inlineStr"/>
@@ -30470,7 +30470,7 @@
       </c>
       <c r="K619" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L619" s="6" t="inlineStr"/>
@@ -30518,7 +30518,7 @@
       </c>
       <c r="K620" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L620" s="3" t="inlineStr"/>
@@ -30566,7 +30566,7 @@
       </c>
       <c r="K621" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L621" s="6" t="inlineStr"/>
@@ -30614,7 +30614,7 @@
       </c>
       <c r="K622" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L622" s="3" t="inlineStr"/>
@@ -30662,7 +30662,7 @@
       </c>
       <c r="K623" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L623" s="6" t="inlineStr"/>
@@ -30710,7 +30710,7 @@
       </c>
       <c r="K624" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L624" s="3" t="inlineStr"/>
@@ -30758,7 +30758,7 @@
       </c>
       <c r="K625" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L625" s="6" t="inlineStr"/>
@@ -30806,7 +30806,7 @@
       </c>
       <c r="K626" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L626" s="3" t="inlineStr"/>
@@ -30854,7 +30854,7 @@
       </c>
       <c r="K627" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L627" s="6" t="inlineStr"/>
@@ -30902,7 +30902,7 @@
       </c>
       <c r="K628" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L628" s="3" t="inlineStr"/>
@@ -30950,7 +30950,7 @@
       </c>
       <c r="K629" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L629" s="6" t="inlineStr"/>
@@ -30998,7 +30998,7 @@
       </c>
       <c r="K630" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L630" s="3" t="inlineStr"/>
@@ -31046,7 +31046,7 @@
       </c>
       <c r="K631" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L631" s="6" t="inlineStr"/>
@@ -31094,7 +31094,7 @@
       </c>
       <c r="K632" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L632" s="3" t="inlineStr"/>
@@ -31142,7 +31142,7 @@
       </c>
       <c r="K633" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L633" s="6" t="inlineStr"/>
@@ -31190,7 +31190,7 @@
       </c>
       <c r="K634" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L634" s="3" t="inlineStr"/>
@@ -31238,7 +31238,7 @@
       </c>
       <c r="K635" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L635" s="6" t="inlineStr"/>
@@ -31286,7 +31286,7 @@
       </c>
       <c r="K636" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L636" s="3" t="inlineStr"/>
@@ -31334,7 +31334,7 @@
       </c>
       <c r="K637" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L637" s="6" t="inlineStr"/>
@@ -31382,7 +31382,7 @@
       </c>
       <c r="K638" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L638" s="3" t="inlineStr"/>
@@ -31430,7 +31430,7 @@
       </c>
       <c r="K639" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L639" s="6" t="inlineStr"/>
@@ -31478,7 +31478,7 @@
       </c>
       <c r="K640" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L640" s="3" t="inlineStr"/>
@@ -31526,7 +31526,7 @@
       </c>
       <c r="K641" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L641" s="6" t="inlineStr"/>
@@ -31574,7 +31574,7 @@
       </c>
       <c r="K642" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L642" s="3" t="inlineStr"/>
@@ -31622,7 +31622,7 @@
       </c>
       <c r="K643" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L643" s="6" t="inlineStr"/>
@@ -31670,7 +31670,7 @@
       </c>
       <c r="K644" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L644" s="3" t="inlineStr"/>
@@ -31718,7 +31718,7 @@
       </c>
       <c r="K645" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L645" s="6" t="inlineStr"/>
@@ -31766,7 +31766,7 @@
       </c>
       <c r="K646" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L646" s="3" t="inlineStr"/>
@@ -31814,7 +31814,7 @@
       </c>
       <c r="K647" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L647" s="6" t="inlineStr"/>
@@ -31862,7 +31862,7 @@
       </c>
       <c r="K648" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L648" s="3" t="inlineStr"/>
@@ -31910,7 +31910,7 @@
       </c>
       <c r="K649" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L649" s="6" t="inlineStr"/>
@@ -31958,7 +31958,7 @@
       </c>
       <c r="K650" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L650" s="3" t="inlineStr"/>
@@ -32006,7 +32006,7 @@
       </c>
       <c r="K651" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L651" s="6" t="inlineStr"/>
@@ -32054,7 +32054,7 @@
       </c>
       <c r="K652" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L652" s="3" t="inlineStr"/>
@@ -32102,7 +32102,7 @@
       </c>
       <c r="K653" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L653" s="6" t="inlineStr"/>
@@ -32150,7 +32150,7 @@
       </c>
       <c r="K654" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L654" s="3" t="inlineStr"/>
@@ -32198,7 +32198,7 @@
       </c>
       <c r="K655" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L655" s="6" t="inlineStr"/>
@@ -32246,7 +32246,7 @@
       </c>
       <c r="K656" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L656" s="3" t="inlineStr"/>
@@ -32294,7 +32294,7 @@
       </c>
       <c r="K657" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L657" s="6" t="inlineStr"/>
@@ -32342,7 +32342,7 @@
       </c>
       <c r="K658" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L658" s="3" t="inlineStr"/>
@@ -32390,7 +32390,7 @@
       </c>
       <c r="K659" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L659" s="6" t="inlineStr"/>
@@ -32438,7 +32438,7 @@
       </c>
       <c r="K660" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L660" s="3" t="inlineStr"/>
@@ -32486,7 +32486,7 @@
       </c>
       <c r="K661" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L661" s="6" t="inlineStr"/>
@@ -32534,7 +32534,7 @@
       </c>
       <c r="K662" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L662" s="3" t="inlineStr"/>
@@ -32582,7 +32582,7 @@
       </c>
       <c r="K663" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L663" s="6" t="inlineStr"/>
@@ -32630,7 +32630,7 @@
       </c>
       <c r="K664" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L664" s="3" t="inlineStr"/>
@@ -32678,7 +32678,7 @@
       </c>
       <c r="K665" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L665" s="6" t="inlineStr"/>
@@ -32726,7 +32726,7 @@
       </c>
       <c r="K666" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L666" s="3" t="inlineStr"/>
@@ -32774,7 +32774,7 @@
       </c>
       <c r="K667" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L667" s="6" t="inlineStr"/>
@@ -32822,7 +32822,7 @@
       </c>
       <c r="K668" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L668" s="3" t="inlineStr"/>
@@ -32870,7 +32870,7 @@
       </c>
       <c r="K669" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L669" s="6" t="inlineStr"/>
@@ -32918,7 +32918,7 @@
       </c>
       <c r="K670" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L670" s="3" t="inlineStr"/>
@@ -32966,7 +32966,7 @@
       </c>
       <c r="K671" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L671" s="6" t="inlineStr"/>
@@ -33014,7 +33014,7 @@
       </c>
       <c r="K672" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L672" s="3" t="inlineStr"/>
@@ -33062,7 +33062,7 @@
       </c>
       <c r="K673" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L673" s="6" t="inlineStr"/>
@@ -33110,7 +33110,7 @@
       </c>
       <c r="K674" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L674" s="3" t="inlineStr"/>
@@ -33158,7 +33158,7 @@
       </c>
       <c r="K675" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L675" s="6" t="inlineStr"/>
@@ -33206,7 +33206,7 @@
       </c>
       <c r="K676" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L676" s="3" t="inlineStr"/>
@@ -33254,7 +33254,7 @@
       </c>
       <c r="K677" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L677" s="6" t="inlineStr"/>
@@ -33302,7 +33302,7 @@
       </c>
       <c r="K678" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L678" s="3" t="inlineStr"/>
@@ -33350,7 +33350,7 @@
       </c>
       <c r="K679" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L679" s="6" t="inlineStr"/>
@@ -33398,7 +33398,7 @@
       </c>
       <c r="K680" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L680" s="3" t="inlineStr"/>
@@ -33446,7 +33446,7 @@
       </c>
       <c r="K681" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L681" s="6" t="inlineStr"/>
@@ -33494,7 +33494,7 @@
       </c>
       <c r="K682" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L682" s="3" t="inlineStr"/>
@@ -33542,7 +33542,7 @@
       </c>
       <c r="K683" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L683" s="6" t="inlineStr"/>
@@ -33590,7 +33590,7 @@
       </c>
       <c r="K684" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L684" s="3" t="inlineStr"/>
@@ -33638,7 +33638,7 @@
       </c>
       <c r="K685" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L685" s="6" t="inlineStr"/>
@@ -33686,7 +33686,7 @@
       </c>
       <c r="K686" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L686" s="3" t="inlineStr"/>
@@ -33734,7 +33734,7 @@
       </c>
       <c r="K687" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L687" s="6" t="inlineStr"/>
@@ -33782,7 +33782,7 @@
       </c>
       <c r="K688" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L688" s="3" t="inlineStr"/>
@@ -33830,7 +33830,7 @@
       </c>
       <c r="K689" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L689" s="6" t="inlineStr"/>
@@ -33878,7 +33878,7 @@
       </c>
       <c r="K690" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L690" s="3" t="inlineStr"/>
@@ -33926,7 +33926,7 @@
       </c>
       <c r="K691" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L691" s="6" t="inlineStr"/>
@@ -33974,7 +33974,7 @@
       </c>
       <c r="K692" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L692" s="3" t="inlineStr"/>
@@ -34022,7 +34022,7 @@
       </c>
       <c r="K693" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L693" s="6" t="inlineStr"/>
@@ -34070,7 +34070,7 @@
       </c>
       <c r="K694" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L694" s="3" t="inlineStr"/>
@@ -34118,7 +34118,7 @@
       </c>
       <c r="K695" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L695" s="6" t="inlineStr"/>
@@ -34166,7 +34166,7 @@
       </c>
       <c r="K696" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L696" s="3" t="inlineStr"/>
@@ -34214,7 +34214,7 @@
       </c>
       <c r="K697" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L697" s="6" t="inlineStr"/>
@@ -34262,7 +34262,7 @@
       </c>
       <c r="K698" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L698" s="3" t="inlineStr"/>
@@ -34310,7 +34310,7 @@
       </c>
       <c r="K699" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L699" s="6" t="inlineStr"/>
@@ -34358,7 +34358,7 @@
       </c>
       <c r="K700" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L700" s="3" t="inlineStr"/>
@@ -34406,7 +34406,7 @@
       </c>
       <c r="K701" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L701" s="6" t="inlineStr"/>
@@ -34454,7 +34454,7 @@
       </c>
       <c r="K702" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L702" s="3" t="inlineStr"/>
@@ -34502,7 +34502,7 @@
       </c>
       <c r="K703" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L703" s="6" t="inlineStr"/>
@@ -34550,7 +34550,7 @@
       </c>
       <c r="K704" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L704" s="3" t="inlineStr"/>
@@ -34598,7 +34598,7 @@
       </c>
       <c r="K705" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L705" s="6" t="inlineStr"/>
@@ -34646,7 +34646,7 @@
       </c>
       <c r="K706" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L706" s="3" t="inlineStr"/>
@@ -34694,7 +34694,7 @@
       </c>
       <c r="K707" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L707" s="6" t="inlineStr"/>
@@ -34742,7 +34742,7 @@
       </c>
       <c r="K708" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L708" s="3" t="inlineStr"/>
@@ -34790,7 +34790,7 @@
       </c>
       <c r="K709" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L709" s="6" t="inlineStr"/>
@@ -34838,7 +34838,7 @@
       </c>
       <c r="K710" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L710" s="3" t="inlineStr"/>
@@ -34886,7 +34886,7 @@
       </c>
       <c r="K711" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L711" s="6" t="inlineStr"/>
@@ -34934,7 +34934,7 @@
       </c>
       <c r="K712" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L712" s="3" t="inlineStr"/>
@@ -34982,7 +34982,7 @@
       </c>
       <c r="K713" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L713" s="6" t="inlineStr"/>
@@ -35030,7 +35030,7 @@
       </c>
       <c r="K714" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L714" s="3" t="inlineStr"/>
@@ -35078,7 +35078,7 @@
       </c>
       <c r="K715" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L715" s="6" t="inlineStr"/>
@@ -35126,7 +35126,7 @@
       </c>
       <c r="K716" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L716" s="3" t="inlineStr"/>
@@ -35174,7 +35174,7 @@
       </c>
       <c r="K717" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L717" s="6" t="inlineStr"/>
@@ -35222,7 +35222,7 @@
       </c>
       <c r="K718" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L718" s="3" t="inlineStr"/>
@@ -35270,7 +35270,7 @@
       </c>
       <c r="K719" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L719" s="6" t="inlineStr"/>
@@ -35318,7 +35318,7 @@
       </c>
       <c r="K720" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L720" s="3" t="inlineStr"/>
@@ -35366,7 +35366,7 @@
       </c>
       <c r="K721" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L721" s="6" t="inlineStr"/>
@@ -35414,7 +35414,7 @@
       </c>
       <c r="K722" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L722" s="3" t="inlineStr"/>
@@ -35462,7 +35462,7 @@
       </c>
       <c r="K723" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L723" s="6" t="inlineStr"/>
@@ -35510,7 +35510,7 @@
       </c>
       <c r="K724" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L724" s="3" t="inlineStr"/>
@@ -35558,7 +35558,7 @@
       </c>
       <c r="K725" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L725" s="6" t="inlineStr"/>
@@ -35606,7 +35606,7 @@
       </c>
       <c r="K726" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L726" s="3" t="inlineStr"/>
@@ -35654,7 +35654,7 @@
       </c>
       <c r="K727" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L727" s="6" t="inlineStr"/>
@@ -35702,7 +35702,7 @@
       </c>
       <c r="K728" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L728" s="3" t="inlineStr"/>
@@ -35750,7 +35750,7 @@
       </c>
       <c r="K729" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L729" s="4" t="inlineStr">
@@ -35802,7 +35802,7 @@
       </c>
       <c r="K730" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L730" s="4" t="inlineStr">
@@ -35854,7 +35854,7 @@
       </c>
       <c r="K731" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L731" s="4" t="inlineStr">
@@ -35906,7 +35906,7 @@
       </c>
       <c r="K732" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L732" s="4" t="inlineStr">
@@ -35958,7 +35958,7 @@
       </c>
       <c r="K733" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L733" s="4" t="inlineStr">
@@ -36010,7 +36010,7 @@
       </c>
       <c r="K734" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L734" s="4" t="inlineStr">
@@ -36062,7 +36062,7 @@
       </c>
       <c r="K735" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L735" s="4" t="inlineStr">
@@ -36114,7 +36114,7 @@
       </c>
       <c r="K736" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L736" s="4" t="inlineStr">
@@ -36166,7 +36166,7 @@
       </c>
       <c r="K737" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L737" s="4" t="inlineStr">
@@ -36218,7 +36218,7 @@
       </c>
       <c r="K738" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L738" s="4" t="inlineStr">
@@ -36270,7 +36270,7 @@
       </c>
       <c r="K739" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L739" s="4" t="inlineStr">
@@ -36322,7 +36322,7 @@
       </c>
       <c r="K740" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L740" s="4" t="inlineStr">
@@ -36374,7 +36374,7 @@
       </c>
       <c r="K741" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L741" s="4" t="inlineStr">
@@ -36426,7 +36426,7 @@
       </c>
       <c r="K742" s="3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L742" s="4" t="inlineStr">
@@ -36478,7 +36478,7 @@
       </c>
       <c r="K743" s="6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="L743" s="4" t="inlineStr">

--- a/public/loop-library.xlsx
+++ b/public/loop-library.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L2" s="4" t="inlineStr">
@@ -626,7 +626,7 @@
       </c>
       <c r="K3" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L3" s="4" t="inlineStr">
@@ -678,7 +678,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L4" s="4" t="inlineStr">
@@ -730,7 +730,7 @@
       </c>
       <c r="K5" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L5" s="4" t="inlineStr">
@@ -782,7 +782,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="K7" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="K9" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
@@ -990,7 +990,7 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="K11" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="K13" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
@@ -1250,7 +1250,7 @@
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
@@ -1302,7 +1302,7 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="K17" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="K19" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="K21" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="K23" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
@@ -1718,7 +1718,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="K25" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
@@ -1822,7 +1822,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="K27" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="K29" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
@@ -2030,7 +2030,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="K31" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="K33" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="K35" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
@@ -2342,7 +2342,7 @@
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="K37" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K39" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
@@ -2550,7 +2550,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
@@ -2602,7 +2602,7 @@
       </c>
       <c r="K41" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
@@ -2654,7 +2654,7 @@
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
@@ -2706,7 +2706,7 @@
       </c>
       <c r="K43" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
@@ -2758,7 +2758,7 @@
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="K45" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="K47" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="K48" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="K49" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="K50" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
@@ -3122,7 +3122,7 @@
       </c>
       <c r="K51" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
@@ -3174,7 +3174,7 @@
       </c>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="K53" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
@@ -3278,7 +3278,7 @@
       </c>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
@@ -3330,7 +3330,7 @@
       </c>
       <c r="K55" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
@@ -3382,7 +3382,7 @@
       </c>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
@@ -3434,7 +3434,7 @@
       </c>
       <c r="K57" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
@@ -3486,7 +3486,7 @@
       </c>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="K59" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
@@ -3642,7 +3642,7 @@
       </c>
       <c r="K61" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
@@ -3694,7 +3694,7 @@
       </c>
       <c r="K62" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
@@ -3746,7 +3746,7 @@
       </c>
       <c r="K63" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
@@ -3798,7 +3798,7 @@
       </c>
       <c r="K64" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
@@ -3850,7 +3850,7 @@
       </c>
       <c r="K65" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L65" s="4" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="K66" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L66" s="4" t="inlineStr">
@@ -3954,7 +3954,7 @@
       </c>
       <c r="K67" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L67" s="4" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="K68" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L68" s="4" t="inlineStr">
@@ -4058,7 +4058,7 @@
       </c>
       <c r="K69" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L69" s="4" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="K70" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L70" s="4" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="K71" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L71" s="4" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L72" s="3" t="inlineStr"/>
@@ -4262,7 +4262,7 @@
       </c>
       <c r="K73" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L73" s="6" t="inlineStr"/>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L74" s="3" t="inlineStr"/>
@@ -4358,7 +4358,7 @@
       </c>
       <c r="K75" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L75" s="6" t="inlineStr"/>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="K76" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L76" s="3" t="inlineStr"/>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="K77" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L77" s="6" t="inlineStr"/>
@@ -4502,7 +4502,7 @@
       </c>
       <c r="K78" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L78" s="3" t="inlineStr"/>
@@ -4550,7 +4550,7 @@
       </c>
       <c r="K79" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L79" s="6" t="inlineStr"/>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="K80" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L80" s="3" t="inlineStr"/>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="K81" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L81" s="6" t="inlineStr"/>
@@ -4694,7 +4694,7 @@
       </c>
       <c r="K82" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L82" s="3" t="inlineStr"/>
@@ -4742,7 +4742,7 @@
       </c>
       <c r="K83" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L83" s="6" t="inlineStr"/>
@@ -4790,7 +4790,7 @@
       </c>
       <c r="K84" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L84" s="3" t="inlineStr"/>
@@ -4838,7 +4838,7 @@
       </c>
       <c r="K85" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L85" s="6" t="inlineStr"/>
@@ -4886,7 +4886,7 @@
       </c>
       <c r="K86" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L86" s="3" t="inlineStr"/>
@@ -4934,7 +4934,7 @@
       </c>
       <c r="K87" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L87" s="6" t="inlineStr"/>
@@ -4982,7 +4982,7 @@
       </c>
       <c r="K88" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L88" s="3" t="inlineStr"/>
@@ -5030,7 +5030,7 @@
       </c>
       <c r="K89" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L89" s="6" t="inlineStr"/>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="K90" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L90" s="3" t="inlineStr"/>
@@ -5126,7 +5126,7 @@
       </c>
       <c r="K91" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L91" s="6" t="inlineStr"/>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="K92" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L92" s="3" t="inlineStr"/>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="K93" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L93" s="6" t="inlineStr"/>
@@ -5270,7 +5270,7 @@
       </c>
       <c r="K94" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L94" s="3" t="inlineStr"/>
@@ -5318,7 +5318,7 @@
       </c>
       <c r="K95" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L95" s="6" t="inlineStr"/>
@@ -5366,7 +5366,7 @@
       </c>
       <c r="K96" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L96" s="3" t="inlineStr"/>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="K97" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L97" s="6" t="inlineStr"/>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="K98" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L98" s="3" t="inlineStr"/>
@@ -5510,7 +5510,7 @@
       </c>
       <c r="K99" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L99" s="6" t="inlineStr"/>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="K100" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L100" s="3" t="inlineStr"/>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="K101" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L101" s="6" t="inlineStr"/>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="K102" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L102" s="3" t="inlineStr"/>
@@ -5702,7 +5702,7 @@
       </c>
       <c r="K103" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L103" s="6" t="inlineStr"/>
@@ -5750,7 +5750,7 @@
       </c>
       <c r="K104" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L104" s="3" t="inlineStr"/>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="K105" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L105" s="6" t="inlineStr"/>
@@ -5846,7 +5846,7 @@
       </c>
       <c r="K106" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L106" s="3" t="inlineStr"/>
@@ -5894,7 +5894,7 @@
       </c>
       <c r="K107" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L107" s="6" t="inlineStr"/>
@@ -5942,7 +5942,7 @@
       </c>
       <c r="K108" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L108" s="3" t="inlineStr"/>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="K109" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L109" s="6" t="inlineStr"/>
@@ -6038,7 +6038,7 @@
       </c>
       <c r="K110" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L110" s="3" t="inlineStr"/>
@@ -6086,7 +6086,7 @@
       </c>
       <c r="K111" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L111" s="6" t="inlineStr"/>
@@ -6134,7 +6134,7 @@
       </c>
       <c r="K112" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L112" s="3" t="inlineStr"/>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="K113" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L113" s="6" t="inlineStr"/>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="K114" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L114" s="3" t="inlineStr"/>
@@ -6278,7 +6278,7 @@
       </c>
       <c r="K115" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L115" s="6" t="inlineStr"/>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="K116" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L116" s="3" t="inlineStr"/>
@@ -6374,7 +6374,7 @@
       </c>
       <c r="K117" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L117" s="6" t="inlineStr"/>
@@ -6422,7 +6422,7 @@
       </c>
       <c r="K118" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L118" s="3" t="inlineStr"/>
@@ -6470,7 +6470,7 @@
       </c>
       <c r="K119" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L119" s="6" t="inlineStr"/>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="K120" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L120" s="3" t="inlineStr"/>
@@ -6566,7 +6566,7 @@
       </c>
       <c r="K121" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L121" s="6" t="inlineStr"/>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="K122" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L122" s="3" t="inlineStr"/>
@@ -6662,7 +6662,7 @@
       </c>
       <c r="K123" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L123" s="6" t="inlineStr"/>
@@ -6710,7 +6710,7 @@
       </c>
       <c r="K124" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L124" s="3" t="inlineStr"/>
@@ -6758,7 +6758,7 @@
       </c>
       <c r="K125" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L125" s="6" t="inlineStr"/>
@@ -6806,7 +6806,7 @@
       </c>
       <c r="K126" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L126" s="3" t="inlineStr"/>
@@ -6854,7 +6854,7 @@
       </c>
       <c r="K127" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L127" s="6" t="inlineStr"/>
@@ -6902,7 +6902,7 @@
       </c>
       <c r="K128" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L128" s="3" t="inlineStr"/>
@@ -6950,7 +6950,7 @@
       </c>
       <c r="K129" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L129" s="6" t="inlineStr"/>
@@ -6998,7 +6998,7 @@
       </c>
       <c r="K130" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L130" s="3" t="inlineStr"/>
@@ -7046,7 +7046,7 @@
       </c>
       <c r="K131" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L131" s="6" t="inlineStr"/>
@@ -7094,7 +7094,7 @@
       </c>
       <c r="K132" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L132" s="3" t="inlineStr"/>
@@ -7142,7 +7142,7 @@
       </c>
       <c r="K133" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L133" s="6" t="inlineStr"/>
@@ -7190,7 +7190,7 @@
       </c>
       <c r="K134" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L134" s="3" t="inlineStr"/>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="K135" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L135" s="6" t="inlineStr"/>
@@ -7286,7 +7286,7 @@
       </c>
       <c r="K136" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L136" s="3" t="inlineStr"/>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="K137" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L137" s="6" t="inlineStr"/>
@@ -7382,7 +7382,7 @@
       </c>
       <c r="K138" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L138" s="3" t="inlineStr"/>
@@ -7430,7 +7430,7 @@
       </c>
       <c r="K139" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L139" s="6" t="inlineStr"/>
@@ -7478,7 +7478,7 @@
       </c>
       <c r="K140" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L140" s="3" t="inlineStr"/>
@@ -7526,7 +7526,7 @@
       </c>
       <c r="K141" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L141" s="6" t="inlineStr"/>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="K142" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L142" s="3" t="inlineStr"/>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="K143" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L143" s="6" t="inlineStr"/>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="K144" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L144" s="3" t="inlineStr"/>
@@ -7718,7 +7718,7 @@
       </c>
       <c r="K145" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L145" s="6" t="inlineStr"/>
@@ -7766,7 +7766,7 @@
       </c>
       <c r="K146" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L146" s="3" t="inlineStr"/>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="K147" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L147" s="6" t="inlineStr"/>
@@ -7862,7 +7862,7 @@
       </c>
       <c r="K148" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L148" s="3" t="inlineStr"/>
@@ -7910,7 +7910,7 @@
       </c>
       <c r="K149" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L149" s="6" t="inlineStr"/>
@@ -7958,7 +7958,7 @@
       </c>
       <c r="K150" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L150" s="3" t="inlineStr"/>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="K151" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L151" s="6" t="inlineStr"/>
@@ -8054,7 +8054,7 @@
       </c>
       <c r="K152" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L152" s="3" t="inlineStr"/>
@@ -8102,7 +8102,7 @@
       </c>
       <c r="K153" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L153" s="6" t="inlineStr"/>
@@ -8150,7 +8150,7 @@
       </c>
       <c r="K154" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L154" s="3" t="inlineStr"/>
@@ -8198,7 +8198,7 @@
       </c>
       <c r="K155" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L155" s="6" t="inlineStr"/>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="K156" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L156" s="3" t="inlineStr"/>
@@ -8294,7 +8294,7 @@
       </c>
       <c r="K157" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L157" s="6" t="inlineStr"/>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="K158" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L158" s="3" t="inlineStr"/>
@@ -8390,7 +8390,7 @@
       </c>
       <c r="K159" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L159" s="6" t="inlineStr"/>
@@ -8438,7 +8438,7 @@
       </c>
       <c r="K160" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L160" s="3" t="inlineStr"/>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="K161" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L161" s="6" t="inlineStr"/>
@@ -8534,7 +8534,7 @@
       </c>
       <c r="K162" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L162" s="3" t="inlineStr"/>
@@ -8582,7 +8582,7 @@
       </c>
       <c r="K163" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L163" s="6" t="inlineStr"/>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="K164" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L164" s="3" t="inlineStr"/>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="K165" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L165" s="6" t="inlineStr"/>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="K166" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L166" s="3" t="inlineStr"/>
@@ -8774,7 +8774,7 @@
       </c>
       <c r="K167" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L167" s="6" t="inlineStr"/>
@@ -8822,7 +8822,7 @@
       </c>
       <c r="K168" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L168" s="3" t="inlineStr"/>
@@ -8870,7 +8870,7 @@
       </c>
       <c r="K169" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L169" s="6" t="inlineStr"/>
@@ -8918,7 +8918,7 @@
       </c>
       <c r="K170" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L170" s="3" t="inlineStr"/>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="K171" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L171" s="6" t="inlineStr"/>
@@ -9014,7 +9014,7 @@
       </c>
       <c r="K172" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L172" s="3" t="inlineStr"/>
@@ -9062,7 +9062,7 @@
       </c>
       <c r="K173" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L173" s="6" t="inlineStr"/>
@@ -9110,7 +9110,7 @@
       </c>
       <c r="K174" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L174" s="3" t="inlineStr"/>
@@ -9158,7 +9158,7 @@
       </c>
       <c r="K175" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L175" s="6" t="inlineStr"/>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="K176" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L176" s="3" t="inlineStr"/>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="K177" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L177" s="6" t="inlineStr"/>
@@ -9302,7 +9302,7 @@
       </c>
       <c r="K178" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L178" s="3" t="inlineStr"/>
@@ -9350,7 +9350,7 @@
       </c>
       <c r="K179" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L179" s="6" t="inlineStr"/>
@@ -9398,7 +9398,7 @@
       </c>
       <c r="K180" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L180" s="3" t="inlineStr"/>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="K181" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L181" s="6" t="inlineStr"/>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="K182" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L182" s="3" t="inlineStr"/>
@@ -9542,7 +9542,7 @@
       </c>
       <c r="K183" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L183" s="6" t="inlineStr"/>
@@ -9590,7 +9590,7 @@
       </c>
       <c r="K184" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L184" s="3" t="inlineStr"/>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="K185" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L185" s="6" t="inlineStr"/>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="K186" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L186" s="3" t="inlineStr"/>
@@ -9734,7 +9734,7 @@
       </c>
       <c r="K187" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L187" s="6" t="inlineStr"/>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="K188" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L188" s="3" t="inlineStr"/>
@@ -9830,7 +9830,7 @@
       </c>
       <c r="K189" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L189" s="6" t="inlineStr"/>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="K190" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L190" s="3" t="inlineStr"/>
@@ -9926,7 +9926,7 @@
       </c>
       <c r="K191" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L191" s="6" t="inlineStr"/>
@@ -9974,7 +9974,7 @@
       </c>
       <c r="K192" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L192" s="3" t="inlineStr"/>
@@ -10022,7 +10022,7 @@
       </c>
       <c r="K193" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L193" s="6" t="inlineStr"/>
@@ -10070,7 +10070,7 @@
       </c>
       <c r="K194" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L194" s="3" t="inlineStr"/>
@@ -10118,7 +10118,7 @@
       </c>
       <c r="K195" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L195" s="6" t="inlineStr"/>
@@ -10166,7 +10166,7 @@
       </c>
       <c r="K196" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L196" s="3" t="inlineStr"/>
@@ -10214,7 +10214,7 @@
       </c>
       <c r="K197" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L197" s="6" t="inlineStr"/>
@@ -10262,7 +10262,7 @@
       </c>
       <c r="K198" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L198" s="3" t="inlineStr"/>
@@ -10310,7 +10310,7 @@
       </c>
       <c r="K199" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L199" s="6" t="inlineStr"/>
@@ -10358,7 +10358,7 @@
       </c>
       <c r="K200" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L200" s="3" t="inlineStr"/>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="K201" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L201" s="6" t="inlineStr"/>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="K202" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L202" s="3" t="inlineStr"/>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="K203" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L203" s="6" t="inlineStr"/>
@@ -10550,7 +10550,7 @@
       </c>
       <c r="K204" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L204" s="3" t="inlineStr"/>
@@ -10598,7 +10598,7 @@
       </c>
       <c r="K205" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L205" s="6" t="inlineStr"/>
@@ -10646,7 +10646,7 @@
       </c>
       <c r="K206" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L206" s="3" t="inlineStr"/>
@@ -10694,7 +10694,7 @@
       </c>
       <c r="K207" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L207" s="6" t="inlineStr"/>
@@ -10742,7 +10742,7 @@
       </c>
       <c r="K208" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L208" s="3" t="inlineStr"/>
@@ -10790,7 +10790,7 @@
       </c>
       <c r="K209" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L209" s="6" t="inlineStr"/>
@@ -10838,7 +10838,7 @@
       </c>
       <c r="K210" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L210" s="3" t="inlineStr"/>
@@ -10886,7 +10886,7 @@
       </c>
       <c r="K211" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L211" s="6" t="inlineStr"/>
@@ -10934,7 +10934,7 @@
       </c>
       <c r="K212" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L212" s="3" t="inlineStr"/>
@@ -10982,7 +10982,7 @@
       </c>
       <c r="K213" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L213" s="6" t="inlineStr"/>
@@ -11030,7 +11030,7 @@
       </c>
       <c r="K214" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L214" s="3" t="inlineStr"/>
@@ -11078,7 +11078,7 @@
       </c>
       <c r="K215" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L215" s="6" t="inlineStr"/>
@@ -11126,7 +11126,7 @@
       </c>
       <c r="K216" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L216" s="3" t="inlineStr"/>
@@ -11174,7 +11174,7 @@
       </c>
       <c r="K217" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L217" s="6" t="inlineStr"/>
@@ -11222,7 +11222,7 @@
       </c>
       <c r="K218" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L218" s="3" t="inlineStr"/>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="K219" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L219" s="6" t="inlineStr"/>
@@ -11318,7 +11318,7 @@
       </c>
       <c r="K220" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L220" s="3" t="inlineStr"/>
@@ -11366,7 +11366,7 @@
       </c>
       <c r="K221" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L221" s="6" t="inlineStr"/>
@@ -11414,7 +11414,7 @@
       </c>
       <c r="K222" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L222" s="3" t="inlineStr"/>
@@ -11462,7 +11462,7 @@
       </c>
       <c r="K223" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L223" s="6" t="inlineStr"/>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="K224" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L224" s="3" t="inlineStr"/>
@@ -11558,7 +11558,7 @@
       </c>
       <c r="K225" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L225" s="6" t="inlineStr"/>
@@ -11606,7 +11606,7 @@
       </c>
       <c r="K226" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L226" s="3" t="inlineStr"/>
@@ -11654,7 +11654,7 @@
       </c>
       <c r="K227" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L227" s="6" t="inlineStr"/>
@@ -11702,7 +11702,7 @@
       </c>
       <c r="K228" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L228" s="3" t="inlineStr"/>
@@ -11750,7 +11750,7 @@
       </c>
       <c r="K229" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L229" s="6" t="inlineStr"/>
@@ -11798,7 +11798,7 @@
       </c>
       <c r="K230" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L230" s="3" t="inlineStr"/>
@@ -11846,7 +11846,7 @@
       </c>
       <c r="K231" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L231" s="6" t="inlineStr"/>
@@ -11894,7 +11894,7 @@
       </c>
       <c r="K232" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L232" s="3" t="inlineStr"/>
@@ -11942,7 +11942,7 @@
       </c>
       <c r="K233" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L233" s="6" t="inlineStr"/>
@@ -11990,7 +11990,7 @@
       </c>
       <c r="K234" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L234" s="3" t="inlineStr"/>
@@ -12038,7 +12038,7 @@
       </c>
       <c r="K235" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L235" s="6" t="inlineStr"/>
@@ -12086,7 +12086,7 @@
       </c>
       <c r="K236" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L236" s="3" t="inlineStr"/>
@@ -12134,7 +12134,7 @@
       </c>
       <c r="K237" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L237" s="6" t="inlineStr"/>
@@ -12182,7 +12182,7 @@
       </c>
       <c r="K238" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L238" s="3" t="inlineStr"/>
@@ -12230,7 +12230,7 @@
       </c>
       <c r="K239" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L239" s="6" t="inlineStr"/>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="K240" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L240" s="3" t="inlineStr"/>
@@ -12326,7 +12326,7 @@
       </c>
       <c r="K241" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L241" s="6" t="inlineStr"/>
@@ -12374,7 +12374,7 @@
       </c>
       <c r="K242" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L242" s="3" t="inlineStr"/>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="K243" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L243" s="6" t="inlineStr"/>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="K244" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L244" s="3" t="inlineStr"/>
@@ -12518,7 +12518,7 @@
       </c>
       <c r="K245" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L245" s="6" t="inlineStr"/>
@@ -12566,7 +12566,7 @@
       </c>
       <c r="K246" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L246" s="3" t="inlineStr"/>
@@ -12614,7 +12614,7 @@
       </c>
       <c r="K247" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L247" s="6" t="inlineStr"/>
@@ -12662,7 +12662,7 @@
       </c>
       <c r="K248" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L248" s="3" t="inlineStr"/>
@@ -12710,7 +12710,7 @@
       </c>
       <c r="K249" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L249" s="6" t="inlineStr"/>
@@ -12758,7 +12758,7 @@
       </c>
       <c r="K250" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L250" s="3" t="inlineStr"/>
@@ -12806,7 +12806,7 @@
       </c>
       <c r="K251" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L251" s="6" t="inlineStr"/>
@@ -12854,7 +12854,7 @@
       </c>
       <c r="K252" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L252" s="3" t="inlineStr"/>
@@ -12902,7 +12902,7 @@
       </c>
       <c r="K253" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L253" s="6" t="inlineStr"/>
@@ -12950,7 +12950,7 @@
       </c>
       <c r="K254" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L254" s="3" t="inlineStr"/>
@@ -12998,7 +12998,7 @@
       </c>
       <c r="K255" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L255" s="6" t="inlineStr"/>
@@ -13046,7 +13046,7 @@
       </c>
       <c r="K256" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L256" s="3" t="inlineStr"/>
@@ -13094,7 +13094,7 @@
       </c>
       <c r="K257" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L257" s="6" t="inlineStr"/>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="K258" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L258" s="3" t="inlineStr"/>
@@ -13190,7 +13190,7 @@
       </c>
       <c r="K259" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L259" s="6" t="inlineStr"/>
@@ -13238,7 +13238,7 @@
       </c>
       <c r="K260" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L260" s="3" t="inlineStr"/>
@@ -13286,7 +13286,7 @@
       </c>
       <c r="K261" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L261" s="6" t="inlineStr"/>
@@ -13334,7 +13334,7 @@
       </c>
       <c r="K262" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L262" s="3" t="inlineStr"/>
@@ -13382,7 +13382,7 @@
       </c>
       <c r="K263" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L263" s="6" t="inlineStr"/>
@@ -13430,7 +13430,7 @@
       </c>
       <c r="K264" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L264" s="3" t="inlineStr"/>
@@ -13478,7 +13478,7 @@
       </c>
       <c r="K265" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L265" s="6" t="inlineStr"/>
@@ -13526,7 +13526,7 @@
       </c>
       <c r="K266" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L266" s="3" t="inlineStr"/>
@@ -13574,7 +13574,7 @@
       </c>
       <c r="K267" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L267" s="6" t="inlineStr"/>
@@ -13622,7 +13622,7 @@
       </c>
       <c r="K268" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L268" s="3" t="inlineStr"/>
@@ -13670,7 +13670,7 @@
       </c>
       <c r="K269" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L269" s="6" t="inlineStr"/>
@@ -13718,7 +13718,7 @@
       </c>
       <c r="K270" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L270" s="3" t="inlineStr"/>
@@ -13766,7 +13766,7 @@
       </c>
       <c r="K271" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L271" s="6" t="inlineStr"/>
@@ -13814,7 +13814,7 @@
       </c>
       <c r="K272" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L272" s="3" t="inlineStr"/>
@@ -13862,7 +13862,7 @@
       </c>
       <c r="K273" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L273" s="6" t="inlineStr"/>
@@ -13910,7 +13910,7 @@
       </c>
       <c r="K274" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L274" s="3" t="inlineStr"/>
@@ -13958,7 +13958,7 @@
       </c>
       <c r="K275" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L275" s="6" t="inlineStr"/>
@@ -14006,7 +14006,7 @@
       </c>
       <c r="K276" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L276" s="3" t="inlineStr"/>
@@ -14054,7 +14054,7 @@
       </c>
       <c r="K277" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L277" s="6" t="inlineStr"/>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="K278" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L278" s="3" t="inlineStr"/>
@@ -14150,7 +14150,7 @@
       </c>
       <c r="K279" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L279" s="6" t="inlineStr"/>
@@ -14198,7 +14198,7 @@
       </c>
       <c r="K280" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L280" s="3" t="inlineStr"/>
@@ -14246,7 +14246,7 @@
       </c>
       <c r="K281" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L281" s="6" t="inlineStr"/>
@@ -14294,7 +14294,7 @@
       </c>
       <c r="K282" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L282" s="3" t="inlineStr"/>
@@ -14342,7 +14342,7 @@
       </c>
       <c r="K283" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L283" s="6" t="inlineStr"/>
@@ -14390,7 +14390,7 @@
       </c>
       <c r="K284" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L284" s="3" t="inlineStr"/>
@@ -14438,7 +14438,7 @@
       </c>
       <c r="K285" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L285" s="6" t="inlineStr"/>
@@ -14486,7 +14486,7 @@
       </c>
       <c r="K286" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L286" s="3" t="inlineStr"/>
@@ -14534,7 +14534,7 @@
       </c>
       <c r="K287" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L287" s="6" t="inlineStr"/>
@@ -14582,7 +14582,7 @@
       </c>
       <c r="K288" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L288" s="3" t="inlineStr"/>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="K289" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L289" s="6" t="inlineStr"/>
@@ -14678,7 +14678,7 @@
       </c>
       <c r="K290" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L290" s="3" t="inlineStr"/>
@@ -14726,7 +14726,7 @@
       </c>
       <c r="K291" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L291" s="6" t="inlineStr"/>
@@ -14774,7 +14774,7 @@
       </c>
       <c r="K292" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L292" s="3" t="inlineStr"/>
@@ -14822,7 +14822,7 @@
       </c>
       <c r="K293" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L293" s="6" t="inlineStr"/>
@@ -14870,7 +14870,7 @@
       </c>
       <c r="K294" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L294" s="3" t="inlineStr"/>
@@ -14918,7 +14918,7 @@
       </c>
       <c r="K295" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L295" s="6" t="inlineStr"/>
@@ -14966,7 +14966,7 @@
       </c>
       <c r="K296" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L296" s="3" t="inlineStr"/>
@@ -15014,7 +15014,7 @@
       </c>
       <c r="K297" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L297" s="6" t="inlineStr"/>
@@ -15062,7 +15062,7 @@
       </c>
       <c r="K298" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L298" s="3" t="inlineStr"/>
@@ -15110,7 +15110,7 @@
       </c>
       <c r="K299" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L299" s="6" t="inlineStr"/>
@@ -15158,7 +15158,7 @@
       </c>
       <c r="K300" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L300" s="3" t="inlineStr"/>
@@ -15206,7 +15206,7 @@
       </c>
       <c r="K301" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L301" s="6" t="inlineStr"/>
@@ -15254,7 +15254,7 @@
       </c>
       <c r="K302" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L302" s="3" t="inlineStr"/>
@@ -15302,7 +15302,7 @@
       </c>
       <c r="K303" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L303" s="6" t="inlineStr"/>
@@ -15350,7 +15350,7 @@
       </c>
       <c r="K304" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L304" s="3" t="inlineStr"/>
@@ -15398,7 +15398,7 @@
       </c>
       <c r="K305" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L305" s="6" t="inlineStr"/>
@@ -15446,7 +15446,7 @@
       </c>
       <c r="K306" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L306" s="3" t="inlineStr"/>
@@ -15494,7 +15494,7 @@
       </c>
       <c r="K307" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L307" s="6" t="inlineStr"/>
@@ -15542,7 +15542,7 @@
       </c>
       <c r="K308" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L308" s="3" t="inlineStr"/>
@@ -15590,7 +15590,7 @@
       </c>
       <c r="K309" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L309" s="6" t="inlineStr"/>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="K310" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L310" s="3" t="inlineStr"/>
@@ -15686,7 +15686,7 @@
       </c>
       <c r="K311" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L311" s="6" t="inlineStr"/>
@@ -15734,7 +15734,7 @@
       </c>
       <c r="K312" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L312" s="3" t="inlineStr"/>
@@ -15782,7 +15782,7 @@
       </c>
       <c r="K313" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L313" s="6" t="inlineStr"/>
@@ -15830,7 +15830,7 @@
       </c>
       <c r="K314" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L314" s="3" t="inlineStr"/>
@@ -15878,7 +15878,7 @@
       </c>
       <c r="K315" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L315" s="6" t="inlineStr"/>
@@ -15926,7 +15926,7 @@
       </c>
       <c r="K316" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L316" s="3" t="inlineStr"/>
@@ -15974,7 +15974,7 @@
       </c>
       <c r="K317" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L317" s="6" t="inlineStr"/>
@@ -16022,7 +16022,7 @@
       </c>
       <c r="K318" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L318" s="3" t="inlineStr"/>
@@ -16070,7 +16070,7 @@
       </c>
       <c r="K319" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L319" s="6" t="inlineStr"/>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="K320" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L320" s="3" t="inlineStr"/>
@@ -16166,7 +16166,7 @@
       </c>
       <c r="K321" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L321" s="6" t="inlineStr"/>
@@ -16214,7 +16214,7 @@
       </c>
       <c r="K322" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L322" s="3" t="inlineStr"/>
@@ -16262,7 +16262,7 @@
       </c>
       <c r="K323" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L323" s="6" t="inlineStr"/>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="K324" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L324" s="3" t="inlineStr"/>
@@ -16358,7 +16358,7 @@
       </c>
       <c r="K325" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L325" s="6" t="inlineStr"/>
@@ -16406,7 +16406,7 @@
       </c>
       <c r="K326" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L326" s="3" t="inlineStr"/>
@@ -16454,7 +16454,7 @@
       </c>
       <c r="K327" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L327" s="6" t="inlineStr"/>
@@ -16502,7 +16502,7 @@
       </c>
       <c r="K328" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L328" s="3" t="inlineStr"/>
@@ -16550,7 +16550,7 @@
       </c>
       <c r="K329" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L329" s="6" t="inlineStr"/>
@@ -16598,7 +16598,7 @@
       </c>
       <c r="K330" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L330" s="3" t="inlineStr"/>
@@ -16646,7 +16646,7 @@
       </c>
       <c r="K331" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L331" s="6" t="inlineStr"/>
@@ -16694,7 +16694,7 @@
       </c>
       <c r="K332" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L332" s="3" t="inlineStr"/>
@@ -16742,7 +16742,7 @@
       </c>
       <c r="K333" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L333" s="6" t="inlineStr"/>
@@ -16790,7 +16790,7 @@
       </c>
       <c r="K334" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L334" s="3" t="inlineStr"/>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="K335" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L335" s="6" t="inlineStr"/>
@@ -16886,7 +16886,7 @@
       </c>
       <c r="K336" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L336" s="3" t="inlineStr"/>
@@ -16934,7 +16934,7 @@
       </c>
       <c r="K337" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L337" s="6" t="inlineStr"/>
@@ -16982,7 +16982,7 @@
       </c>
       <c r="K338" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L338" s="3" t="inlineStr"/>
@@ -17030,7 +17030,7 @@
       </c>
       <c r="K339" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L339" s="6" t="inlineStr"/>
@@ -17078,7 +17078,7 @@
       </c>
       <c r="K340" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L340" s="3" t="inlineStr"/>
@@ -17126,7 +17126,7 @@
       </c>
       <c r="K341" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L341" s="6" t="inlineStr"/>
@@ -17174,7 +17174,7 @@
       </c>
       <c r="K342" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L342" s="3" t="inlineStr"/>
@@ -17222,7 +17222,7 @@
       </c>
       <c r="K343" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L343" s="6" t="inlineStr"/>
@@ -17270,7 +17270,7 @@
       </c>
       <c r="K344" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L344" s="3" t="inlineStr"/>
@@ -17318,7 +17318,7 @@
       </c>
       <c r="K345" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L345" s="6" t="inlineStr"/>
@@ -17366,7 +17366,7 @@
       </c>
       <c r="K346" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L346" s="3" t="inlineStr"/>
@@ -17414,7 +17414,7 @@
       </c>
       <c r="K347" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L347" s="6" t="inlineStr"/>
@@ -17462,7 +17462,7 @@
       </c>
       <c r="K348" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L348" s="3" t="inlineStr"/>
@@ -17510,7 +17510,7 @@
       </c>
       <c r="K349" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L349" s="6" t="inlineStr"/>
@@ -17558,7 +17558,7 @@
       </c>
       <c r="K350" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L350" s="3" t="inlineStr"/>
@@ -17606,7 +17606,7 @@
       </c>
       <c r="K351" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L351" s="6" t="inlineStr"/>
@@ -17654,7 +17654,7 @@
       </c>
       <c r="K352" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L352" s="3" t="inlineStr"/>
@@ -17702,7 +17702,7 @@
       </c>
       <c r="K353" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L353" s="6" t="inlineStr"/>
@@ -17750,7 +17750,7 @@
       </c>
       <c r="K354" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L354" s="3" t="inlineStr"/>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="K355" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L355" s="6" t="inlineStr"/>
@@ -17846,7 +17846,7 @@
       </c>
       <c r="K356" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L356" s="3" t="inlineStr"/>
@@ -17894,7 +17894,7 @@
       </c>
       <c r="K357" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L357" s="6" t="inlineStr"/>
@@ -17942,7 +17942,7 @@
       </c>
       <c r="K358" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L358" s="3" t="inlineStr"/>
@@ -17990,7 +17990,7 @@
       </c>
       <c r="K359" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L359" s="6" t="inlineStr"/>
@@ -18038,7 +18038,7 @@
       </c>
       <c r="K360" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L360" s="3" t="inlineStr"/>
@@ -18086,7 +18086,7 @@
       </c>
       <c r="K361" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L361" s="6" t="inlineStr"/>
@@ -18134,7 +18134,7 @@
       </c>
       <c r="K362" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L362" s="3" t="inlineStr"/>
@@ -18182,7 +18182,7 @@
       </c>
       <c r="K363" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L363" s="6" t="inlineStr"/>
@@ -18230,7 +18230,7 @@
       </c>
       <c r="K364" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L364" s="3" t="inlineStr"/>
@@ -18278,7 +18278,7 @@
       </c>
       <c r="K365" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L365" s="6" t="inlineStr"/>
@@ -18326,7 +18326,7 @@
       </c>
       <c r="K366" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L366" s="3" t="inlineStr"/>
@@ -18374,7 +18374,7 @@
       </c>
       <c r="K367" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L367" s="6" t="inlineStr"/>
@@ -18422,7 +18422,7 @@
       </c>
       <c r="K368" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L368" s="3" t="inlineStr"/>
@@ -18470,7 +18470,7 @@
       </c>
       <c r="K369" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L369" s="6" t="inlineStr"/>
@@ -18518,7 +18518,7 @@
       </c>
       <c r="K370" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L370" s="3" t="inlineStr"/>
@@ -18566,7 +18566,7 @@
       </c>
       <c r="K371" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L371" s="6" t="inlineStr"/>
@@ -18614,7 +18614,7 @@
       </c>
       <c r="K372" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L372" s="3" t="inlineStr"/>
@@ -18662,7 +18662,7 @@
       </c>
       <c r="K373" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L373" s="6" t="inlineStr"/>
@@ -18710,7 +18710,7 @@
       </c>
       <c r="K374" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L374" s="3" t="inlineStr"/>
@@ -18758,7 +18758,7 @@
       </c>
       <c r="K375" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L375" s="6" t="inlineStr"/>
@@ -18806,7 +18806,7 @@
       </c>
       <c r="K376" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L376" s="3" t="inlineStr"/>
@@ -18854,7 +18854,7 @@
       </c>
       <c r="K377" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L377" s="6" t="inlineStr"/>
@@ -18902,7 +18902,7 @@
       </c>
       <c r="K378" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L378" s="3" t="inlineStr"/>
@@ -18950,7 +18950,7 @@
       </c>
       <c r="K379" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L379" s="6" t="inlineStr"/>
@@ -18998,7 +18998,7 @@
       </c>
       <c r="K380" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L380" s="3" t="inlineStr"/>
@@ -19046,7 +19046,7 @@
       </c>
       <c r="K381" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L381" s="6" t="inlineStr"/>
@@ -19094,7 +19094,7 @@
       </c>
       <c r="K382" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L382" s="3" t="inlineStr"/>
@@ -19142,7 +19142,7 @@
       </c>
       <c r="K383" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L383" s="6" t="inlineStr"/>
@@ -19190,7 +19190,7 @@
       </c>
       <c r="K384" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L384" s="3" t="inlineStr"/>
@@ -19238,7 +19238,7 @@
       </c>
       <c r="K385" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L385" s="6" t="inlineStr"/>
@@ -19286,7 +19286,7 @@
       </c>
       <c r="K386" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L386" s="3" t="inlineStr"/>
@@ -19334,7 +19334,7 @@
       </c>
       <c r="K387" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L387" s="6" t="inlineStr"/>
@@ -19382,7 +19382,7 @@
       </c>
       <c r="K388" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L388" s="3" t="inlineStr"/>
@@ -19430,7 +19430,7 @@
       </c>
       <c r="K389" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L389" s="6" t="inlineStr"/>
@@ -19478,7 +19478,7 @@
       </c>
       <c r="K390" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L390" s="3" t="inlineStr"/>
@@ -19526,7 +19526,7 @@
       </c>
       <c r="K391" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L391" s="6" t="inlineStr"/>
@@ -19574,7 +19574,7 @@
       </c>
       <c r="K392" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L392" s="3" t="inlineStr"/>
@@ -19622,7 +19622,7 @@
       </c>
       <c r="K393" s="6" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L393" s="6" t="inlineStr"/>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="K394" s="3" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="L394" s="3" t="inlineStr"/>
@@ -19718,7 +19718,7 @@
       </c>
       <c r="K395" s="6" t="inlineStr">
